--- a/terrestrial/Level4_20-Aug-26.xlsx
+++ b/terrestrial/Level4_20-Aug-26.xlsx
@@ -11069,7 +11069,7 @@
       </c>
       <c r="C213" s="9" t="inlineStr">
         <is>
-          <t>Falkland Is.</t>
+          <t>Falkland Islands (Malvinas)</t>
         </is>
       </c>
       <c r="D213" s="9" t="inlineStr">

--- a/terrestrial/Level4_20-Aug-26.xlsx
+++ b/terrestrial/Level4_20-Aug-26.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1005"/>
+  <dimension ref="A1:K1005"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -462,6 +462,7 @@
     <col width="10.54296875" customWidth="1" min="8" max="8"/>
     <col width="14.453125" customWidth="1" min="9" max="9"/>
     <col width="41.7265625" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -515,6 +516,11 @@
           <t>Revision notes</t>
         </is>
       </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -547,6 +553,7 @@
       <c r="H2" s="4" t="n"/>
       <c r="I2" s="4" t="n"/>
       <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
@@ -579,6 +586,7 @@
       <c r="H3" s="4" t="n"/>
       <c r="I3" s="4" t="n"/>
       <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n"/>
@@ -611,6 +619,7 @@
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="4" t="n"/>
       <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n"/>
@@ -643,6 +652,7 @@
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="n"/>
       <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n"/>
@@ -675,6 +685,7 @@
       <c r="H6" s="4" t="n"/>
       <c r="I6" s="4" t="n"/>
       <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n"/>
@@ -707,6 +718,7 @@
       <c r="H7" s="4" t="n"/>
       <c r="I7" s="4" t="n"/>
       <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n"/>
@@ -746,6 +758,7 @@
 -AGE-DF It is not digitized on map 16 (pg 135)</t>
         </is>
       </c>
+      <c r="K8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n"/>
@@ -778,6 +791,7 @@
       <c r="H9" s="4" t="n"/>
       <c r="I9" s="4" t="n"/>
       <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n"/>
@@ -810,6 +824,7 @@
       <c r="H10" s="4" t="n"/>
       <c r="I10" s="4" t="n"/>
       <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n"/>
@@ -842,6 +857,7 @@
       <c r="H11" s="4" t="n"/>
       <c r="I11" s="4" t="n"/>
       <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n"/>
@@ -874,6 +890,7 @@
       <c r="H12" s="4" t="n"/>
       <c r="I12" s="4" t="n"/>
       <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n"/>
@@ -910,6 +927,7 @@
           <t>Typographical error, instead of AGE-SF there was AGS-SF. Only in the database. It is correct in the book/PDF</t>
         </is>
       </c>
+      <c r="K13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n"/>
@@ -942,6 +960,7 @@
       <c r="H14" s="4" t="n"/>
       <c r="I14" s="4" t="n"/>
       <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n"/>
@@ -974,6 +993,7 @@
       <c r="H15" s="4" t="n"/>
       <c r="I15" s="4" t="n"/>
       <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n"/>
@@ -1006,6 +1026,7 @@
       <c r="H16" s="4" t="n"/>
       <c r="I16" s="4" t="n"/>
       <c r="J16" s="3" t="n"/>
+      <c r="K16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n"/>
@@ -1038,6 +1059,7 @@
       <c r="H17" s="4" t="n"/>
       <c r="I17" s="4" t="n"/>
       <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n"/>
@@ -1070,6 +1092,7 @@
       <c r="H18" s="4" t="n"/>
       <c r="I18" s="4" t="n"/>
       <c r="J18" s="3" t="n"/>
+      <c r="K18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n"/>
@@ -1102,6 +1125,7 @@
       <c r="H19" s="4" t="n"/>
       <c r="I19" s="4" t="n"/>
       <c r="J19" s="3" t="n"/>
+      <c r="K19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n"/>
@@ -1134,6 +1158,7 @@
       <c r="H20" s="4" t="n"/>
       <c r="I20" s="4" t="n"/>
       <c r="J20" s="3" t="n"/>
+      <c r="K20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n"/>
@@ -1166,6 +1191,7 @@
       <c r="H21" s="4" t="n"/>
       <c r="I21" s="4" t="n"/>
       <c r="J21" s="3" t="n"/>
+      <c r="K21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n"/>
@@ -1198,6 +1224,7 @@
       <c r="H22" s="4" t="n"/>
       <c r="I22" s="4" t="n"/>
       <c r="J22" s="3" t="n"/>
+      <c r="K22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n"/>
@@ -1230,6 +1257,7 @@
       <c r="H23" s="4" t="n"/>
       <c r="I23" s="4" t="n"/>
       <c r="J23" s="3" t="n"/>
+      <c r="K23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n"/>
@@ -1262,6 +1290,7 @@
       <c r="H24" s="4" t="n"/>
       <c r="I24" s="4" t="n"/>
       <c r="J24" s="3" t="n"/>
+      <c r="K24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n"/>
@@ -1294,6 +1323,7 @@
       <c r="H25" s="4" t="n"/>
       <c r="I25" s="4" t="n"/>
       <c r="J25" s="3" t="n"/>
+      <c r="K25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n"/>
@@ -1326,6 +1356,7 @@
       <c r="H26" s="4" t="n"/>
       <c r="I26" s="4" t="n"/>
       <c r="J26" s="3" t="n"/>
+      <c r="K26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n"/>
@@ -1358,6 +1389,7 @@
       <c r="H27" s="4" t="n"/>
       <c r="I27" s="4" t="n"/>
       <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n"/>
@@ -1390,6 +1422,7 @@
       <c r="H28" s="4" t="n"/>
       <c r="I28" s="4" t="n"/>
       <c r="J28" s="3" t="n"/>
+      <c r="K28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n"/>
@@ -1422,6 +1455,7 @@
       <c r="H29" s="4" t="n"/>
       <c r="I29" s="4" t="n"/>
       <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n"/>
@@ -1454,6 +1488,7 @@
       <c r="H30" s="4" t="n"/>
       <c r="I30" s="4" t="n"/>
       <c r="J30" s="3" t="n"/>
+      <c r="K30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n"/>
@@ -1486,6 +1521,7 @@
       <c r="H31" s="4" t="n"/>
       <c r="I31" s="4" t="n"/>
       <c r="J31" s="3" t="n"/>
+      <c r="K31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n"/>
@@ -1518,6 +1554,7 @@
       <c r="H32" s="4" t="n"/>
       <c r="I32" s="4" t="n"/>
       <c r="J32" s="3" t="n"/>
+      <c r="K32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n"/>
@@ -1550,6 +1587,7 @@
           <t>Removed the L4 ISOcode (US). The Aleutian Is. belong to two distints countries.</t>
         </is>
       </c>
+      <c r="K33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n"/>
@@ -1582,6 +1620,7 @@
       <c r="H34" s="4" t="n"/>
       <c r="I34" s="4" t="n"/>
       <c r="J34" s="3" t="n"/>
+      <c r="K34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n"/>
@@ -1614,6 +1653,7 @@
       <c r="H35" s="4" t="n"/>
       <c r="I35" s="4" t="n"/>
       <c r="J35" s="3" t="n"/>
+      <c r="K35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n"/>
@@ -1646,6 +1686,7 @@
       <c r="H36" s="4" t="n"/>
       <c r="I36" s="4" t="n"/>
       <c r="J36" s="3" t="n"/>
+      <c r="K36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n"/>
@@ -1678,6 +1719,7 @@
       <c r="H37" s="4" t="n"/>
       <c r="I37" s="4" t="n"/>
       <c r="J37" s="3" t="n"/>
+      <c r="K37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n"/>
@@ -1710,6 +1752,7 @@
       <c r="H38" s="4" t="n"/>
       <c r="I38" s="4" t="n"/>
       <c r="J38" s="3" t="n"/>
+      <c r="K38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n"/>
@@ -1742,6 +1785,7 @@
       <c r="H39" s="4" t="n"/>
       <c r="I39" s="4" t="n"/>
       <c r="J39" s="3" t="n"/>
+      <c r="K39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n"/>
@@ -1774,6 +1818,7 @@
       <c r="H40" s="4" t="n"/>
       <c r="I40" s="4" t="n"/>
       <c r="J40" s="3" t="n"/>
+      <c r="K40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n"/>
@@ -1806,6 +1851,7 @@
       <c r="H41" s="4" t="n"/>
       <c r="I41" s="4" t="n"/>
       <c r="J41" s="3" t="n"/>
+      <c r="K41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n"/>
@@ -1838,6 +1884,7 @@
       <c r="H42" s="4" t="n"/>
       <c r="I42" s="4" t="n"/>
       <c r="J42" s="3" t="n"/>
+      <c r="K42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n"/>
@@ -1870,6 +1917,7 @@
       <c r="H43" s="4" t="n"/>
       <c r="I43" s="4" t="n"/>
       <c r="J43" s="3" t="n"/>
+      <c r="K43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n"/>
@@ -1902,6 +1950,7 @@
       <c r="H44" s="4" t="n"/>
       <c r="I44" s="4" t="n"/>
       <c r="J44" s="3" t="n"/>
+      <c r="K44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n"/>
@@ -1934,6 +1983,7 @@
       <c r="H45" s="4" t="n"/>
       <c r="I45" s="4" t="n"/>
       <c r="J45" s="3" t="n"/>
+      <c r="K45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n"/>
@@ -1966,6 +2016,7 @@
       <c r="H46" s="4" t="n"/>
       <c r="I46" s="4" t="n"/>
       <c r="J46" s="3" t="n"/>
+      <c r="K46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n"/>
@@ -1998,6 +2049,7 @@
       <c r="H47" s="4" t="n"/>
       <c r="I47" s="4" t="n"/>
       <c r="J47" s="3" t="n"/>
+      <c r="K47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n"/>
@@ -2030,6 +2082,7 @@
       <c r="H48" s="4" t="n"/>
       <c r="I48" s="4" t="n"/>
       <c r="J48" s="3" t="n"/>
+      <c r="K48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n"/>
@@ -2062,6 +2115,7 @@
       <c r="H49" s="4" t="n"/>
       <c r="I49" s="4" t="n"/>
       <c r="J49" s="3" t="n"/>
+      <c r="K49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n"/>
@@ -2094,6 +2148,7 @@
       <c r="H50" s="4" t="n"/>
       <c r="I50" s="4" t="n"/>
       <c r="J50" s="3" t="n"/>
+      <c r="K50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n"/>
@@ -2126,6 +2181,7 @@
       <c r="H51" s="4" t="n"/>
       <c r="I51" s="4" t="n"/>
       <c r="J51" s="3" t="n"/>
+      <c r="K51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n"/>
@@ -2158,6 +2214,7 @@
       <c r="H52" s="4" t="n"/>
       <c r="I52" s="4" t="n"/>
       <c r="J52" s="3" t="n"/>
+      <c r="K52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n"/>
@@ -2190,6 +2247,7 @@
       <c r="H53" s="4" t="n"/>
       <c r="I53" s="4" t="n"/>
       <c r="J53" s="3" t="n"/>
+      <c r="K53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n"/>
@@ -2222,6 +2280,7 @@
       <c r="H54" s="4" t="n"/>
       <c r="I54" s="4" t="n"/>
       <c r="J54" s="3" t="n"/>
+      <c r="K54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n"/>
@@ -2254,6 +2313,7 @@
       <c r="H55" s="4" t="n"/>
       <c r="I55" s="4" t="n"/>
       <c r="J55" s="3" t="n"/>
+      <c r="K55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n"/>
@@ -2286,6 +2346,7 @@
       <c r="H56" s="4" t="n"/>
       <c r="I56" s="4" t="n"/>
       <c r="J56" s="3" t="n"/>
+      <c r="K56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n"/>
@@ -2318,6 +2379,7 @@
       <c r="H57" s="4" t="n"/>
       <c r="I57" s="4" t="n"/>
       <c r="J57" s="3" t="n"/>
+      <c r="K57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n"/>
@@ -2350,6 +2412,7 @@
       <c r="H58" s="4" t="n"/>
       <c r="I58" s="4" t="n"/>
       <c r="J58" s="3" t="n"/>
+      <c r="K58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n"/>
@@ -2382,6 +2445,7 @@
       <c r="H59" s="4" t="n"/>
       <c r="I59" s="4" t="n"/>
       <c r="J59" s="3" t="n"/>
+      <c r="K59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n"/>
@@ -2414,6 +2478,7 @@
       <c r="H60" s="4" t="n"/>
       <c r="I60" s="4" t="n"/>
       <c r="J60" s="3" t="n"/>
+      <c r="K60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n"/>
@@ -2446,6 +2511,7 @@
       <c r="H61" s="4" t="n"/>
       <c r="I61" s="4" t="n"/>
       <c r="J61" s="3" t="n"/>
+      <c r="K61" s="3" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n"/>
@@ -2478,6 +2544,7 @@
       <c r="H62" s="4" t="n"/>
       <c r="I62" s="4" t="n"/>
       <c r="J62" s="3" t="n"/>
+      <c r="K62" s="3" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n"/>
@@ -2510,6 +2577,7 @@
       <c r="H63" s="4" t="n"/>
       <c r="I63" s="4" t="n"/>
       <c r="J63" s="3" t="n"/>
+      <c r="K63" s="3" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n"/>
@@ -2542,6 +2610,7 @@
       <c r="H64" s="4" t="n"/>
       <c r="I64" s="4" t="n"/>
       <c r="J64" s="3" t="n"/>
+      <c r="K64" s="3" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n"/>
@@ -2574,6 +2643,7 @@
       <c r="H65" s="4" t="n"/>
       <c r="I65" s="4" t="n"/>
       <c r="J65" s="3" t="n"/>
+      <c r="K65" s="3" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n"/>
@@ -2606,6 +2676,7 @@
       <c r="H66" s="4" t="n"/>
       <c r="I66" s="4" t="n"/>
       <c r="J66" s="3" t="n"/>
+      <c r="K66" s="3" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n"/>
@@ -2638,6 +2709,7 @@
       <c r="H67" s="4" t="n"/>
       <c r="I67" s="4" t="n"/>
       <c r="J67" s="3" t="n"/>
+      <c r="K67" s="3" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n"/>
@@ -2670,6 +2742,7 @@
       <c r="H68" s="4" t="n"/>
       <c r="I68" s="4" t="n"/>
       <c r="J68" s="3" t="n"/>
+      <c r="K68" s="3" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n"/>
@@ -2702,6 +2775,7 @@
       <c r="H69" s="4" t="n"/>
       <c r="I69" s="4" t="n"/>
       <c r="J69" s="3" t="n"/>
+      <c r="K69" s="3" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n"/>
@@ -2734,6 +2808,7 @@
       <c r="H70" s="4" t="n"/>
       <c r="I70" s="4" t="n"/>
       <c r="J70" s="3" t="n"/>
+      <c r="K70" s="3" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n"/>
@@ -2766,6 +2841,7 @@
       <c r="H71" s="4" t="n"/>
       <c r="I71" s="4" t="n"/>
       <c r="J71" s="3" t="n"/>
+      <c r="K71" s="3" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n"/>
@@ -2798,6 +2874,7 @@
       <c r="H72" s="4" t="n"/>
       <c r="I72" s="4" t="n"/>
       <c r="J72" s="3" t="n"/>
+      <c r="K72" s="3" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n"/>
@@ -2830,6 +2907,7 @@
       <c r="H73" s="4" t="n"/>
       <c r="I73" s="4" t="n"/>
       <c r="J73" s="3" t="n"/>
+      <c r="K73" s="3" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n"/>
@@ -2862,6 +2940,7 @@
       <c r="H74" s="4" t="n"/>
       <c r="I74" s="4" t="n"/>
       <c r="J74" s="3" t="n"/>
+      <c r="K74" s="3" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n"/>
@@ -2894,6 +2973,7 @@
       <c r="H75" s="4" t="n"/>
       <c r="I75" s="4" t="n"/>
       <c r="J75" s="3" t="n"/>
+      <c r="K75" s="3" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="n"/>
@@ -2926,6 +3006,7 @@
       <c r="H76" s="4" t="n"/>
       <c r="I76" s="4" t="n"/>
       <c r="J76" s="3" t="n"/>
+      <c r="K76" s="3" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n"/>
@@ -2958,6 +3039,7 @@
       <c r="H77" s="4" t="n"/>
       <c r="I77" s="4" t="n"/>
       <c r="J77" s="3" t="n"/>
+      <c r="K77" s="3" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n"/>
@@ -2990,6 +3072,7 @@
       <c r="H78" s="4" t="n"/>
       <c r="I78" s="4" t="n"/>
       <c r="J78" s="3" t="n"/>
+      <c r="K78" s="3" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n"/>
@@ -3022,6 +3105,7 @@
       <c r="H79" s="4" t="n"/>
       <c r="I79" s="4" t="n"/>
       <c r="J79" s="3" t="n"/>
+      <c r="K79" s="3" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n"/>
@@ -3054,6 +3138,7 @@
       <c r="H80" s="4" t="n"/>
       <c r="I80" s="4" t="n"/>
       <c r="J80" s="3" t="n"/>
+      <c r="K80" s="3" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n"/>
@@ -3086,6 +3171,7 @@
       <c r="H81" s="4" t="n"/>
       <c r="I81" s="4" t="n"/>
       <c r="J81" s="3" t="n"/>
+      <c r="K81" s="3" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n"/>
@@ -3118,6 +3204,7 @@
       <c r="H82" s="4" t="n"/>
       <c r="I82" s="4" t="n"/>
       <c r="J82" s="3" t="n"/>
+      <c r="K82" s="3" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n"/>
@@ -3150,6 +3237,7 @@
       <c r="H83" s="4" t="n"/>
       <c r="I83" s="4" t="n"/>
       <c r="J83" s="3" t="n"/>
+      <c r="K83" s="3" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n"/>
@@ -3182,6 +3270,7 @@
       <c r="H84" s="4" t="n"/>
       <c r="I84" s="4" t="n"/>
       <c r="J84" s="3" t="n"/>
+      <c r="K84" s="3" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n"/>
@@ -3214,6 +3303,7 @@
       <c r="H85" s="4" t="n"/>
       <c r="I85" s="4" t="n"/>
       <c r="J85" s="3" t="n"/>
+      <c r="K85" s="3" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n"/>
@@ -3246,6 +3336,7 @@
       <c r="H86" s="4" t="n"/>
       <c r="I86" s="4" t="n"/>
       <c r="J86" s="3" t="n"/>
+      <c r="K86" s="3" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n"/>
@@ -3278,6 +3369,7 @@
       <c r="H87" s="4" t="n"/>
       <c r="I87" s="4" t="n"/>
       <c r="J87" s="3" t="n"/>
+      <c r="K87" s="3" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n"/>
@@ -3310,6 +3402,7 @@
       <c r="H88" s="4" t="n"/>
       <c r="I88" s="4" t="n"/>
       <c r="J88" s="3" t="n"/>
+      <c r="K88" s="3" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n"/>
@@ -3342,6 +3435,7 @@
       <c r="H89" s="4" t="n"/>
       <c r="I89" s="4" t="n"/>
       <c r="J89" s="3" t="n"/>
+      <c r="K89" s="3" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n"/>
@@ -3374,6 +3468,7 @@
       <c r="H90" s="4" t="n"/>
       <c r="I90" s="4" t="n"/>
       <c r="J90" s="3" t="n"/>
+      <c r="K90" s="3" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n"/>
@@ -3406,6 +3501,7 @@
       <c r="H91" s="4" t="n"/>
       <c r="I91" s="4" t="n"/>
       <c r="J91" s="3" t="n"/>
+      <c r="K91" s="3" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n"/>
@@ -3438,6 +3534,7 @@
       <c r="H92" s="4" t="n"/>
       <c r="I92" s="4" t="n"/>
       <c r="J92" s="3" t="n"/>
+      <c r="K92" s="3" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n"/>
@@ -3470,6 +3567,7 @@
       <c r="H93" s="4" t="n"/>
       <c r="I93" s="4" t="n"/>
       <c r="J93" s="3" t="n"/>
+      <c r="K93" s="3" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n"/>
@@ -3502,6 +3600,7 @@
       <c r="H94" s="4" t="n"/>
       <c r="I94" s="4" t="n"/>
       <c r="J94" s="3" t="n"/>
+      <c r="K94" s="3" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n"/>
@@ -3534,6 +3633,7 @@
       <c r="H95" s="4" t="n"/>
       <c r="I95" s="4" t="n"/>
       <c r="J95" s="3" t="n"/>
+      <c r="K95" s="3" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n"/>
@@ -3566,6 +3666,7 @@
       <c r="H96" s="4" t="n"/>
       <c r="I96" s="4" t="n"/>
       <c r="J96" s="3" t="n"/>
+      <c r="K96" s="3" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n"/>
@@ -3598,6 +3699,7 @@
       <c r="H97" s="4" t="n"/>
       <c r="I97" s="4" t="n"/>
       <c r="J97" s="3" t="n"/>
+      <c r="K97" s="3" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n"/>
@@ -3630,6 +3732,7 @@
       <c r="H98" s="4" t="n"/>
       <c r="I98" s="4" t="n"/>
       <c r="J98" s="3" t="n"/>
+      <c r="K98" s="3" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n"/>
@@ -3662,6 +3765,7 @@
       <c r="H99" s="4" t="n"/>
       <c r="I99" s="4" t="n"/>
       <c r="J99" s="3" t="n"/>
+      <c r="K99" s="3" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="4" t="n"/>
@@ -3694,6 +3798,7 @@
       <c r="H100" s="4" t="n"/>
       <c r="I100" s="4" t="n"/>
       <c r="J100" s="3" t="n"/>
+      <c r="K100" s="3" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n"/>
@@ -3726,6 +3831,7 @@
       <c r="H101" s="4" t="n"/>
       <c r="I101" s="4" t="n"/>
       <c r="J101" s="3" t="n"/>
+      <c r="K101" s="3" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n"/>
@@ -3758,6 +3864,7 @@
       <c r="H102" s="4" t="n"/>
       <c r="I102" s="4" t="n"/>
       <c r="J102" s="3" t="n"/>
+      <c r="K102" s="3" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n"/>
@@ -3790,6 +3897,7 @@
       <c r="H103" s="4" t="n"/>
       <c r="I103" s="4" t="n"/>
       <c r="J103" s="3" t="n"/>
+      <c r="K103" s="3" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="4" t="n"/>
@@ -3822,6 +3930,7 @@
       <c r="H104" s="4" t="n"/>
       <c r="I104" s="4" t="n"/>
       <c r="J104" s="3" t="n"/>
+      <c r="K104" s="3" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n"/>
@@ -3854,6 +3963,7 @@
       <c r="H105" s="4" t="n"/>
       <c r="I105" s="4" t="n"/>
       <c r="J105" s="3" t="n"/>
+      <c r="K105" s="3" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="4" t="n"/>
@@ -3886,6 +3996,7 @@
       <c r="H106" s="4" t="n"/>
       <c r="I106" s="4" t="n"/>
       <c r="J106" s="3" t="n"/>
+      <c r="K106" s="3" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="n"/>
@@ -3918,6 +4029,7 @@
       <c r="H107" s="4" t="n"/>
       <c r="I107" s="4" t="n"/>
       <c r="J107" s="3" t="n"/>
+      <c r="K107" s="3" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="n"/>
@@ -3950,6 +4062,7 @@
       <c r="H108" s="4" t="n"/>
       <c r="I108" s="4" t="n"/>
       <c r="J108" s="3" t="n"/>
+      <c r="K108" s="3" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n"/>
@@ -3982,6 +4095,7 @@
       <c r="H109" s="4" t="n"/>
       <c r="I109" s="4" t="n"/>
       <c r="J109" s="3" t="n"/>
+      <c r="K109" s="3" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="4" t="n"/>
@@ -4014,6 +4128,7 @@
       <c r="H110" s="4" t="n"/>
       <c r="I110" s="4" t="n"/>
       <c r="J110" s="3" t="n"/>
+      <c r="K110" s="3" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="n"/>
@@ -4046,6 +4161,7 @@
       <c r="H111" s="4" t="n"/>
       <c r="I111" s="4" t="n"/>
       <c r="J111" s="3" t="n"/>
+      <c r="K111" s="3" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="4" t="n"/>
@@ -4078,6 +4194,7 @@
       <c r="H112" s="4" t="n"/>
       <c r="I112" s="4" t="n"/>
       <c r="J112" s="3" t="n"/>
+      <c r="K112" s="3" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="n"/>
@@ -4110,6 +4227,7 @@
       <c r="H113" s="4" t="n"/>
       <c r="I113" s="4" t="n"/>
       <c r="J113" s="3" t="n"/>
+      <c r="K113" s="3" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="4" t="n"/>
@@ -4142,6 +4260,7 @@
       <c r="H114" s="4" t="n"/>
       <c r="I114" s="4" t="n"/>
       <c r="J114" s="3" t="n"/>
+      <c r="K114" s="3" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="n"/>
@@ -4174,6 +4293,7 @@
       <c r="H115" s="4" t="n"/>
       <c r="I115" s="4" t="n"/>
       <c r="J115" s="3" t="n"/>
+      <c r="K115" s="3" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="4" t="n"/>
@@ -4206,6 +4326,7 @@
       <c r="H116" s="4" t="n"/>
       <c r="I116" s="4" t="n"/>
       <c r="J116" s="3" t="n"/>
+      <c r="K116" s="3" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="n"/>
@@ -4242,6 +4363,7 @@
         </is>
       </c>
       <c r="J117" s="3" t="n"/>
+      <c r="K117" s="3" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="4" t="n"/>
@@ -4274,6 +4396,7 @@
       <c r="H118" s="4" t="n"/>
       <c r="I118" s="4" t="n"/>
       <c r="J118" s="3" t="n"/>
+      <c r="K118" s="3" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="n"/>
@@ -4306,6 +4429,7 @@
       <c r="H119" s="4" t="n"/>
       <c r="I119" s="4" t="n"/>
       <c r="J119" s="3" t="n"/>
+      <c r="K119" s="3" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="4" t="n"/>
@@ -4338,6 +4462,7 @@
       <c r="H120" s="4" t="n"/>
       <c r="I120" s="4" t="n"/>
       <c r="J120" s="3" t="n"/>
+      <c r="K120" s="3" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="n"/>
@@ -4370,6 +4495,7 @@
       <c r="H121" s="4" t="n"/>
       <c r="I121" s="4" t="n"/>
       <c r="J121" s="3" t="n"/>
+      <c r="K121" s="3" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="4" t="n"/>
@@ -4402,6 +4528,7 @@
       <c r="H122" s="4" t="n"/>
       <c r="I122" s="4" t="n"/>
       <c r="J122" s="3" t="n"/>
+      <c r="K122" s="3" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="4" t="n"/>
@@ -4447,6 +4574,7 @@
 https://en.wikipedia.org/wiki/Jilin</t>
         </is>
       </c>
+      <c r="K123" s="3" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="4" t="n"/>
@@ -4479,6 +4607,7 @@
       <c r="H124" s="4" t="n"/>
       <c r="I124" s="4" t="n"/>
       <c r="J124" s="3" t="n"/>
+      <c r="K124" s="3" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="n"/>
@@ -4523,6 +4652,7 @@
           <t>Incorrect digitalization between Inner Mongolia and Heilongjiang Map 6/7, pg 115/116</t>
         </is>
       </c>
+      <c r="K125" s="3" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="n"/>
@@ -4568,6 +4698,7 @@
 https://en.wikipedia.org/wiki/Jilin</t>
         </is>
       </c>
+      <c r="K126" s="3" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="n"/>
@@ -4612,6 +4743,7 @@
           <t>Incorrect digitalization between Inner Mongolia and Liaoning. https://en.wikipedia.org/wiki/Liaoning</t>
         </is>
       </c>
+      <c r="K127" s="3" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="4" t="n"/>
@@ -4644,6 +4776,7 @@
       <c r="H128" s="4" t="n"/>
       <c r="I128" s="4" t="n"/>
       <c r="J128" s="3" t="n"/>
+      <c r="K128" s="3" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="4" t="n"/>
@@ -4676,6 +4809,7 @@
       <c r="H129" s="4" t="n"/>
       <c r="I129" s="4" t="n"/>
       <c r="J129" s="3" t="n"/>
+      <c r="K129" s="3" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="4" t="n"/>
@@ -4721,6 +4855,7 @@
 https://en.wikipedia.org/wiki/Henan</t>
         </is>
       </c>
+      <c r="K130" s="3" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="4" t="n"/>
@@ -4753,6 +4888,7 @@
       <c r="H131" s="4" t="n"/>
       <c r="I131" s="4" t="n"/>
       <c r="J131" s="3" t="n"/>
+      <c r="K131" s="3" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="4" t="n"/>
@@ -4785,6 +4921,7 @@
       <c r="H132" s="4" t="n"/>
       <c r="I132" s="4" t="n"/>
       <c r="J132" s="3" t="n"/>
+      <c r="K132" s="3" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="n"/>
@@ -4817,6 +4954,7 @@
       <c r="H133" s="4" t="n"/>
       <c r="I133" s="4" t="n"/>
       <c r="J133" s="3" t="n"/>
+      <c r="K133" s="3" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="4" t="n"/>
@@ -4849,6 +4987,7 @@
       <c r="H134" s="4" t="n"/>
       <c r="I134" s="4" t="n"/>
       <c r="J134" s="3" t="n"/>
+      <c r="K134" s="3" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="n"/>
@@ -4881,6 +5020,7 @@
       <c r="H135" s="4" t="n"/>
       <c r="I135" s="4" t="n"/>
       <c r="J135" s="3" t="n"/>
+      <c r="K135" s="3" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="4" t="n"/>
@@ -4913,6 +5053,7 @@
       <c r="H136" s="4" t="n"/>
       <c r="I136" s="4" t="n"/>
       <c r="J136" s="3" t="n"/>
+      <c r="K136" s="3" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="n"/>
@@ -4945,6 +5086,7 @@
       <c r="H137" s="4" t="n"/>
       <c r="I137" s="4" t="n"/>
       <c r="J137" s="3" t="n"/>
+      <c r="K137" s="3" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="4" t="n"/>
@@ -4977,6 +5119,7 @@
       <c r="H138" s="4" t="n"/>
       <c r="I138" s="4" t="n"/>
       <c r="J138" s="3" t="n"/>
+      <c r="K138" s="3" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="n"/>
@@ -5009,6 +5152,7 @@
       <c r="H139" s="4" t="n"/>
       <c r="I139" s="4" t="n"/>
       <c r="J139" s="3" t="n"/>
+      <c r="K139" s="3" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="4" t="n"/>
@@ -5054,6 +5198,7 @@
 https://en.wikipedia.org/wiki/Henan</t>
         </is>
       </c>
+      <c r="K140" s="3" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="n"/>
@@ -5086,6 +5231,7 @@
       <c r="H141" s="4" t="n"/>
       <c r="I141" s="4" t="n"/>
       <c r="J141" s="3" t="n"/>
+      <c r="K141" s="3" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="4" t="n"/>
@@ -5118,6 +5264,7 @@
       <c r="H142" s="4" t="n"/>
       <c r="I142" s="4" t="n"/>
       <c r="J142" s="3" t="n"/>
+      <c r="K142" s="3" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="4" t="n"/>
@@ -5150,6 +5297,7 @@
       <c r="H143" s="4" t="n"/>
       <c r="I143" s="4" t="n"/>
       <c r="J143" s="3" t="n"/>
+      <c r="K143" s="3" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="4" t="n"/>
@@ -5182,6 +5330,7 @@
       <c r="H144" s="4" t="n"/>
       <c r="I144" s="4" t="n"/>
       <c r="J144" s="3" t="n"/>
+      <c r="K144" s="3" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="n"/>
@@ -5214,6 +5363,7 @@
       <c r="H145" s="4" t="n"/>
       <c r="I145" s="4" t="n"/>
       <c r="J145" s="3" t="n"/>
+      <c r="K145" s="3" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="4" t="n"/>
@@ -5246,6 +5396,7 @@
       <c r="H146" s="4" t="n"/>
       <c r="I146" s="4" t="n"/>
       <c r="J146" s="3" t="n"/>
+      <c r="K146" s="3" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="4" t="n"/>
@@ -5278,6 +5429,7 @@
       <c r="H147" s="4" t="n"/>
       <c r="I147" s="4" t="n"/>
       <c r="J147" s="3" t="n"/>
+      <c r="K147" s="3" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="4" t="n"/>
@@ -5310,6 +5462,7 @@
       <c r="H148" s="4" t="n"/>
       <c r="I148" s="4" t="n"/>
       <c r="J148" s="3" t="n"/>
+      <c r="K148" s="3" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="4" t="n"/>
@@ -5342,6 +5495,7 @@
       <c r="H149" s="4" t="n"/>
       <c r="I149" s="4" t="n"/>
       <c r="J149" s="3" t="n"/>
+      <c r="K149" s="3" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="4" t="n"/>
@@ -5374,6 +5528,7 @@
       <c r="H150" s="4" t="n"/>
       <c r="I150" s="4" t="n"/>
       <c r="J150" s="3" t="n"/>
+      <c r="K150" s="3" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="n"/>
@@ -5406,6 +5561,7 @@
       <c r="H151" s="4" t="n"/>
       <c r="I151" s="4" t="n"/>
       <c r="J151" s="3" t="n"/>
+      <c r="K151" s="3" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="4" t="n"/>
@@ -5438,6 +5594,7 @@
       <c r="H152" s="4" t="n"/>
       <c r="I152" s="4" t="n"/>
       <c r="J152" s="3" t="n"/>
+      <c r="K152" s="3" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="n"/>
@@ -5478,6 +5635,7 @@
         </is>
       </c>
       <c r="J153" s="3" t="n"/>
+      <c r="K153" s="3" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="4" t="n"/>
@@ -5510,6 +5668,7 @@
       <c r="H154" s="4" t="n"/>
       <c r="I154" s="4" t="n"/>
       <c r="J154" s="3" t="n"/>
+      <c r="K154" s="3" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="n"/>
@@ -5542,6 +5701,7 @@
       <c r="H155" s="4" t="n"/>
       <c r="I155" s="4" t="n"/>
       <c r="J155" s="3" t="n"/>
+      <c r="K155" s="3" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="n"/>
@@ -5574,6 +5734,7 @@
       <c r="H156" s="4" t="n"/>
       <c r="I156" s="4" t="n"/>
       <c r="J156" s="3" t="n"/>
+      <c r="K156" s="3" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="n"/>
@@ -5614,6 +5775,7 @@
         </is>
       </c>
       <c r="J157" s="3" t="n"/>
+      <c r="K157" s="3" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="4" t="n"/>
@@ -5646,6 +5808,7 @@
       <c r="H158" s="4" t="n"/>
       <c r="I158" s="4" t="n"/>
       <c r="J158" s="3" t="n"/>
+      <c r="K158" s="3" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="4" t="n"/>
@@ -5678,6 +5841,7 @@
       <c r="H159" s="4" t="n"/>
       <c r="I159" s="4" t="n"/>
       <c r="J159" s="3" t="n"/>
+      <c r="K159" s="3" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="4" t="n"/>
@@ -5710,6 +5874,7 @@
       <c r="H160" s="4" t="n"/>
       <c r="I160" s="4" t="n"/>
       <c r="J160" s="3" t="n"/>
+      <c r="K160" s="3" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="n"/>
@@ -5742,6 +5907,7 @@
       <c r="H161" s="4" t="n"/>
       <c r="I161" s="4" t="n"/>
       <c r="J161" s="3" t="n"/>
+      <c r="K161" s="3" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="4" t="n"/>
@@ -5774,6 +5940,7 @@
       <c r="H162" s="4" t="n"/>
       <c r="I162" s="4" t="n"/>
       <c r="J162" s="3" t="n"/>
+      <c r="K162" s="3" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="4" t="n"/>
@@ -5806,6 +5973,7 @@
       <c r="H163" s="4" t="n"/>
       <c r="I163" s="4" t="n"/>
       <c r="J163" s="3" t="n"/>
+      <c r="K163" s="3" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="4" t="n"/>
@@ -5850,6 +6018,7 @@
           <t>Added level 4 Arica and Parinacota Region to Chile (is region 15 in the very north)</t>
         </is>
       </c>
+      <c r="K164" s="3" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="4" t="n"/>
@@ -5882,6 +6051,7 @@
       <c r="H165" s="4" t="n"/>
       <c r="I165" s="4" t="n"/>
       <c r="J165" s="3" t="n"/>
+      <c r="K165" s="3" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="4" t="n"/>
@@ -5914,6 +6084,7 @@
       <c r="H166" s="4" t="n"/>
       <c r="I166" s="4" t="n"/>
       <c r="J166" s="3" t="n"/>
+      <c r="K166" s="3" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="4" t="n"/>
@@ -5946,6 +6117,7 @@
       <c r="H167" s="4" t="n"/>
       <c r="I167" s="4" t="n"/>
       <c r="J167" s="3" t="n"/>
+      <c r="K167" s="3" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="4" t="n"/>
@@ -5978,6 +6150,7 @@
       <c r="H168" s="4" t="n"/>
       <c r="I168" s="4" t="n"/>
       <c r="J168" s="3" t="n"/>
+      <c r="K168" s="3" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="n"/>
@@ -6010,6 +6183,7 @@
       <c r="H169" s="4" t="n"/>
       <c r="I169" s="4" t="n"/>
       <c r="J169" s="3" t="n"/>
+      <c r="K169" s="3" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="4" t="n"/>
@@ -6042,6 +6216,7 @@
       <c r="H170" s="4" t="n"/>
       <c r="I170" s="4" t="n"/>
       <c r="J170" s="3" t="n"/>
+      <c r="K170" s="3" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="4" t="n"/>
@@ -6074,6 +6249,7 @@
       <c r="H171" s="4" t="n"/>
       <c r="I171" s="4" t="n"/>
       <c r="J171" s="3" t="n"/>
+      <c r="K171" s="3" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="4" t="n"/>
@@ -6106,6 +6282,7 @@
       <c r="H172" s="4" t="n"/>
       <c r="I172" s="4" t="n"/>
       <c r="J172" s="3" t="n"/>
+      <c r="K172" s="3" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="4" t="n"/>
@@ -6138,6 +6315,7 @@
       <c r="H173" s="4" t="n"/>
       <c r="I173" s="4" t="n"/>
       <c r="J173" s="3" t="n"/>
+      <c r="K173" s="3" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="4" t="n"/>
@@ -6170,6 +6348,7 @@
       <c r="H174" s="4" t="n"/>
       <c r="I174" s="4" t="n"/>
       <c r="J174" s="3" t="n"/>
+      <c r="K174" s="3" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="4" t="n"/>
@@ -6202,6 +6381,7 @@
       <c r="H175" s="4" t="n"/>
       <c r="I175" s="4" t="n"/>
       <c r="J175" s="3" t="n"/>
+      <c r="K175" s="3" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="4" t="n"/>
@@ -6234,6 +6414,7 @@
       <c r="H176" s="4" t="n"/>
       <c r="I176" s="4" t="n"/>
       <c r="J176" s="3" t="n"/>
+      <c r="K176" s="3" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="4" t="n"/>
@@ -6266,6 +6447,7 @@
       <c r="H177" s="4" t="n"/>
       <c r="I177" s="4" t="n"/>
       <c r="J177" s="3" t="n"/>
+      <c r="K177" s="3" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="4" t="n"/>
@@ -6298,6 +6480,7 @@
       <c r="H178" s="4" t="n"/>
       <c r="I178" s="4" t="n"/>
       <c r="J178" s="3" t="n"/>
+      <c r="K178" s="3" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="4" t="n"/>
@@ -6330,6 +6513,7 @@
       <c r="H179" s="4" t="n"/>
       <c r="I179" s="4" t="n"/>
       <c r="J179" s="3" t="n"/>
+      <c r="K179" s="3" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="4" t="n"/>
@@ -6362,6 +6546,7 @@
       <c r="H180" s="4" t="n"/>
       <c r="I180" s="4" t="n"/>
       <c r="J180" s="3" t="n"/>
+      <c r="K180" s="3" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="4" t="n"/>
@@ -6394,6 +6579,7 @@
       <c r="H181" s="4" t="n"/>
       <c r="I181" s="4" t="n"/>
       <c r="J181" s="3" t="n"/>
+      <c r="K181" s="3" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="4" t="n"/>
@@ -6426,6 +6612,7 @@
       <c r="H182" s="4" t="n"/>
       <c r="I182" s="4" t="n"/>
       <c r="J182" s="3" t="n"/>
+      <c r="K182" s="3" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="4" t="n"/>
@@ -6458,6 +6645,7 @@
       <c r="H183" s="4" t="n"/>
       <c r="I183" s="4" t="n"/>
       <c r="J183" s="3" t="n"/>
+      <c r="K183" s="3" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="4" t="n"/>
@@ -6490,6 +6678,7 @@
       <c r="H184" s="4" t="n"/>
       <c r="I184" s="4" t="n"/>
       <c r="J184" s="3" t="n"/>
+      <c r="K184" s="3" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="4" t="n"/>
@@ -6522,6 +6711,7 @@
       <c r="H185" s="4" t="n"/>
       <c r="I185" s="4" t="n"/>
       <c r="J185" s="3" t="n"/>
+      <c r="K185" s="3" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="4" t="n"/>
@@ -6554,6 +6744,7 @@
       <c r="H186" s="4" t="n"/>
       <c r="I186" s="4" t="n"/>
       <c r="J186" s="3" t="n"/>
+      <c r="K186" s="3" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="4" t="n"/>
@@ -6586,6 +6777,7 @@
       <c r="H187" s="4" t="n"/>
       <c r="I187" s="4" t="n"/>
       <c r="J187" s="3" t="n"/>
+      <c r="K187" s="3" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="4" t="n"/>
@@ -6626,6 +6818,7 @@
           <t>Named Chita in previous edition</t>
         </is>
       </c>
+      <c r="K188" s="3" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="4" t="n"/>
@@ -6658,6 +6851,7 @@
       <c r="H189" s="4" t="n"/>
       <c r="I189" s="4" t="n"/>
       <c r="J189" s="3" t="n"/>
+      <c r="K189" s="3" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="4" t="n"/>
@@ -6690,6 +6884,7 @@
       <c r="H190" s="4" t="n"/>
       <c r="I190" s="4" t="n"/>
       <c r="J190" s="3" t="n"/>
+      <c r="K190" s="3" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="4" t="n"/>
@@ -6722,6 +6917,7 @@
       <c r="H191" s="4" t="n"/>
       <c r="I191" s="4" t="n"/>
       <c r="J191" s="3" t="n"/>
+      <c r="K191" s="3" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="4" t="n"/>
@@ -6754,6 +6950,7 @@
       <c r="H192" s="4" t="n"/>
       <c r="I192" s="4" t="n"/>
       <c r="J192" s="3" t="n"/>
+      <c r="K192" s="3" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="4" t="n"/>
@@ -6786,6 +6983,7 @@
       <c r="H193" s="4" t="n"/>
       <c r="I193" s="4" t="n"/>
       <c r="J193" s="3" t="n"/>
+      <c r="K193" s="3" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="4" t="n"/>
@@ -6818,6 +7016,7 @@
       <c r="H194" s="4" t="n"/>
       <c r="I194" s="4" t="n"/>
       <c r="J194" s="3" t="n"/>
+      <c r="K194" s="3" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="4" t="n"/>
@@ -6850,6 +7049,7 @@
       <c r="H195" s="4" t="n"/>
       <c r="I195" s="4" t="n"/>
       <c r="J195" s="3" t="n"/>
+      <c r="K195" s="3" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="4" t="n"/>
@@ -6882,6 +7082,7 @@
       <c r="H196" s="4" t="n"/>
       <c r="I196" s="4" t="n"/>
       <c r="J196" s="3" t="n"/>
+      <c r="K196" s="3" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="4" t="n"/>
@@ -6914,6 +7115,7 @@
       <c r="H197" s="4" t="n"/>
       <c r="I197" s="4" t="n"/>
       <c r="J197" s="3" t="n"/>
+      <c r="K197" s="3" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="4" t="n"/>
@@ -6946,6 +7148,7 @@
       <c r="H198" s="4" t="n"/>
       <c r="I198" s="4" t="n"/>
       <c r="J198" s="3" t="n"/>
+      <c r="K198" s="3" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="4" t="n"/>
@@ -6982,6 +7185,7 @@
       <c r="H199" s="4" t="n"/>
       <c r="I199" s="4" t="n"/>
       <c r="J199" s="3" t="n"/>
+      <c r="K199" s="3" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="4" t="n"/>
@@ -7014,6 +7218,7 @@
       <c r="H200" s="4" t="n"/>
       <c r="I200" s="4" t="n"/>
       <c r="J200" s="3" t="n"/>
+      <c r="K200" s="3" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="4" t="n"/>
@@ -7046,6 +7251,7 @@
       <c r="H201" s="4" t="n"/>
       <c r="I201" s="4" t="n"/>
       <c r="J201" s="3" t="n"/>
+      <c r="K201" s="3" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="4" t="n"/>
@@ -7078,6 +7284,7 @@
       <c r="H202" s="4" t="n"/>
       <c r="I202" s="4" t="n"/>
       <c r="J202" s="3" t="n"/>
+      <c r="K202" s="3" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="4" t="n"/>
@@ -7110,6 +7317,7 @@
       <c r="H203" s="4" t="n"/>
       <c r="I203" s="4" t="n"/>
       <c r="J203" s="3" t="n"/>
+      <c r="K203" s="3" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="4" t="n"/>
@@ -7142,6 +7350,7 @@
       <c r="H204" s="4" t="n"/>
       <c r="I204" s="4" t="n"/>
       <c r="J204" s="3" t="n"/>
+      <c r="K204" s="3" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="4" t="n"/>
@@ -7174,6 +7383,7 @@
       <c r="H205" s="4" t="n"/>
       <c r="I205" s="4" t="n"/>
       <c r="J205" s="3" t="n"/>
+      <c r="K205" s="3" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="4" t="n"/>
@@ -7206,6 +7416,7 @@
       <c r="H206" s="4" t="n"/>
       <c r="I206" s="4" t="n"/>
       <c r="J206" s="3" t="n"/>
+      <c r="K206" s="3" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="4" t="n"/>
@@ -7238,6 +7449,7 @@
       <c r="H207" s="4" t="n"/>
       <c r="I207" s="4" t="n"/>
       <c r="J207" s="3" t="n"/>
+      <c r="K207" s="3" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="4" t="n"/>
@@ -7270,6 +7482,7 @@
       <c r="H208" s="4" t="n"/>
       <c r="I208" s="4" t="n"/>
       <c r="J208" s="3" t="n"/>
+      <c r="K208" s="3" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="4" t="n"/>
@@ -7302,6 +7515,7 @@
       <c r="H209" s="4" t="n"/>
       <c r="I209" s="4" t="n"/>
       <c r="J209" s="3" t="n"/>
+      <c r="K209" s="3" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="4" t="n"/>
@@ -7334,6 +7548,7 @@
       <c r="H210" s="4" t="n"/>
       <c r="I210" s="4" t="n"/>
       <c r="J210" s="3" t="n"/>
+      <c r="K210" s="3" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="4" t="n"/>
@@ -7375,6 +7590,7 @@
 https://en.wikipedia.org/wiki/Eswatini</t>
         </is>
       </c>
+      <c r="K211" s="3" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="4" t="n"/>
@@ -7407,6 +7623,7 @@
       <c r="H212" s="4" t="n"/>
       <c r="I212" s="4" t="n"/>
       <c r="J212" s="3" t="n"/>
+      <c r="K212" s="3" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="4" t="n"/>
@@ -7439,6 +7656,7 @@
       <c r="H213" s="4" t="n"/>
       <c r="I213" s="4" t="n"/>
       <c r="J213" s="3" t="n"/>
+      <c r="K213" s="3" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="4" t="n"/>
@@ -7471,6 +7689,7 @@
       <c r="H214" s="4" t="n"/>
       <c r="I214" s="4" t="n"/>
       <c r="J214" s="3" t="n"/>
+      <c r="K214" s="3" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="4" t="n"/>
@@ -7503,6 +7722,7 @@
       <c r="H215" s="4" t="n"/>
       <c r="I215" s="4" t="n"/>
       <c r="J215" s="3" t="n"/>
+      <c r="K215" s="3" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="4" t="n"/>
@@ -7535,6 +7755,7 @@
       <c r="H216" s="4" t="n"/>
       <c r="I216" s="4" t="n"/>
       <c r="J216" s="3" t="n"/>
+      <c r="K216" s="3" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="4" t="n"/>
@@ -7567,6 +7788,7 @@
       <c r="H217" s="4" t="n"/>
       <c r="I217" s="4" t="n"/>
       <c r="J217" s="3" t="n"/>
+      <c r="K217" s="3" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="4" t="n"/>
@@ -7599,6 +7821,7 @@
       <c r="H218" s="4" t="n"/>
       <c r="I218" s="4" t="n"/>
       <c r="J218" s="3" t="n"/>
+      <c r="K218" s="3" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="4" t="n"/>
@@ -7631,6 +7854,7 @@
       <c r="H219" s="4" t="n"/>
       <c r="I219" s="4" t="n"/>
       <c r="J219" s="3" t="n"/>
+      <c r="K219" s="3" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="4" t="n"/>
@@ -7663,6 +7887,7 @@
       <c r="H220" s="4" t="n"/>
       <c r="I220" s="4" t="n"/>
       <c r="J220" s="3" t="n"/>
+      <c r="K220" s="3" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="4" t="n"/>
@@ -7695,6 +7920,7 @@
       <c r="H221" s="4" t="n"/>
       <c r="I221" s="4" t="n"/>
       <c r="J221" s="3" t="n"/>
+      <c r="K221" s="3" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="4" t="n"/>
@@ -7727,6 +7953,7 @@
       <c r="H222" s="4" t="n"/>
       <c r="I222" s="4" t="n"/>
       <c r="J222" s="3" t="n"/>
+      <c r="K222" s="3" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="4" t="n"/>
@@ -7759,6 +7986,7 @@
       <c r="H223" s="4" t="n"/>
       <c r="I223" s="4" t="n"/>
       <c r="J223" s="3" t="n"/>
+      <c r="K223" s="3" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="4" t="n"/>
@@ -7791,6 +8019,7 @@
       <c r="H224" s="4" t="n"/>
       <c r="I224" s="4" t="n"/>
       <c r="J224" s="3" t="n"/>
+      <c r="K224" s="3" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="4" t="n"/>
@@ -7823,6 +8052,7 @@
       <c r="H225" s="4" t="n"/>
       <c r="I225" s="4" t="n"/>
       <c r="J225" s="3" t="n"/>
+      <c r="K225" s="3" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="4" t="n"/>
@@ -7855,6 +8085,7 @@
       <c r="H226" s="4" t="n"/>
       <c r="I226" s="4" t="n"/>
       <c r="J226" s="3" t="n"/>
+      <c r="K226" s="3" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="4" t="n"/>
@@ -7887,6 +8118,7 @@
       <c r="H227" s="4" t="n"/>
       <c r="I227" s="4" t="n"/>
       <c r="J227" s="3" t="n"/>
+      <c r="K227" s="3" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="4" t="n"/>
@@ -7919,6 +8151,7 @@
       <c r="H228" s="4" t="n"/>
       <c r="I228" s="4" t="n"/>
       <c r="J228" s="3" t="n"/>
+      <c r="K228" s="3" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="4" t="n"/>
@@ -7951,6 +8184,7 @@
       <c r="H229" s="4" t="n"/>
       <c r="I229" s="4" t="n"/>
       <c r="J229" s="3" t="n"/>
+      <c r="K229" s="3" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="4" t="n"/>
@@ -7983,6 +8217,7 @@
       <c r="H230" s="4" t="n"/>
       <c r="I230" s="4" t="n"/>
       <c r="J230" s="3" t="n"/>
+      <c r="K230" s="3" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="4" t="n"/>
@@ -8015,6 +8250,7 @@
       <c r="H231" s="4" t="n"/>
       <c r="I231" s="4" t="n"/>
       <c r="J231" s="3" t="n"/>
+      <c r="K231" s="3" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="4" t="n"/>
@@ -8047,6 +8283,7 @@
       <c r="H232" s="4" t="n"/>
       <c r="I232" s="4" t="n"/>
       <c r="J232" s="3" t="n"/>
+      <c r="K232" s="3" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="4" t="n"/>
@@ -8079,6 +8316,7 @@
       <c r="H233" s="4" t="n"/>
       <c r="I233" s="4" t="n"/>
       <c r="J233" s="3" t="n"/>
+      <c r="K233" s="3" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="4" t="n"/>
@@ -8111,6 +8349,7 @@
       <c r="H234" s="4" t="n"/>
       <c r="I234" s="4" t="n"/>
       <c r="J234" s="3" t="n"/>
+      <c r="K234" s="3" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="4" t="n"/>
@@ -8143,6 +8382,7 @@
       <c r="H235" s="4" t="n"/>
       <c r="I235" s="4" t="n"/>
       <c r="J235" s="3" t="n"/>
+      <c r="K235" s="3" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="4" t="n"/>
@@ -8175,6 +8415,7 @@
       <c r="H236" s="4" t="n"/>
       <c r="I236" s="4" t="n"/>
       <c r="J236" s="3" t="n"/>
+      <c r="K236" s="3" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="4" t="n"/>
@@ -8207,6 +8448,7 @@
       <c r="H237" s="4" t="n"/>
       <c r="I237" s="4" t="n"/>
       <c r="J237" s="3" t="n"/>
+      <c r="K237" s="3" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="4" t="n"/>
@@ -8239,6 +8481,7 @@
       <c r="H238" s="4" t="n"/>
       <c r="I238" s="4" t="n"/>
       <c r="J238" s="3" t="n"/>
+      <c r="K238" s="3" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="4" t="n"/>
@@ -8271,6 +8514,7 @@
       <c r="H239" s="4" t="n"/>
       <c r="I239" s="4" t="n"/>
       <c r="J239" s="3" t="n"/>
+      <c r="K239" s="3" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="4" t="n"/>
@@ -8303,6 +8547,7 @@
       <c r="H240" s="4" t="n"/>
       <c r="I240" s="4" t="n"/>
       <c r="J240" s="3" t="n"/>
+      <c r="K240" s="3" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="4" t="n"/>
@@ -8335,6 +8580,7 @@
       <c r="H241" s="4" t="n"/>
       <c r="I241" s="4" t="n"/>
       <c r="J241" s="3" t="n"/>
+      <c r="K241" s="3" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="4" t="n"/>
@@ -8367,6 +8613,7 @@
       <c r="H242" s="4" t="n"/>
       <c r="I242" s="4" t="n"/>
       <c r="J242" s="3" t="n"/>
+      <c r="K242" s="3" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="4" t="n"/>
@@ -8399,6 +8646,7 @@
       <c r="H243" s="4" t="n"/>
       <c r="I243" s="4" t="n"/>
       <c r="J243" s="3" t="n"/>
+      <c r="K243" s="3" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="4" t="n"/>
@@ -8439,6 +8687,7 @@
           <t>Since no significative developments have occurred in this dispute since the publication of the WGSRPD ed. 2, we opt for maintaining codes and name as they were</t>
         </is>
       </c>
+      <c r="K244" s="3" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="4" t="n"/>
@@ -8471,6 +8720,7 @@
       <c r="H245" s="4" t="n"/>
       <c r="I245" s="4" t="n"/>
       <c r="J245" s="3" t="n"/>
+      <c r="K245" s="3" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="4" t="n"/>
@@ -8503,6 +8753,7 @@
       <c r="H246" s="4" t="n"/>
       <c r="I246" s="4" t="n"/>
       <c r="J246" s="3" t="n"/>
+      <c r="K246" s="3" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="4" t="n"/>
@@ -8535,6 +8786,7 @@
       <c r="H247" s="4" t="n"/>
       <c r="I247" s="4" t="n"/>
       <c r="J247" s="3" t="n"/>
+      <c r="K247" s="3" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="4" t="n"/>
@@ -8567,6 +8819,7 @@
       <c r="H248" s="4" t="n"/>
       <c r="I248" s="4" t="n"/>
       <c r="J248" s="3" t="n"/>
+      <c r="K248" s="3" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="4" t="n"/>
@@ -8599,6 +8852,7 @@
       <c r="H249" s="4" t="n"/>
       <c r="I249" s="4" t="n"/>
       <c r="J249" s="3" t="n"/>
+      <c r="K249" s="3" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="4" t="n"/>
@@ -8631,6 +8885,7 @@
       <c r="H250" s="4" t="n"/>
       <c r="I250" s="4" t="n"/>
       <c r="J250" s="3" t="n"/>
+      <c r="K250" s="3" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="4" t="n"/>
@@ -8663,6 +8918,7 @@
       <c r="H251" s="4" t="n"/>
       <c r="I251" s="4" t="n"/>
       <c r="J251" s="3" t="n"/>
+      <c r="K251" s="3" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="4" t="n"/>
@@ -8695,6 +8951,7 @@
       <c r="H252" s="4" t="n"/>
       <c r="I252" s="4" t="n"/>
       <c r="J252" s="3" t="n"/>
+      <c r="K252" s="3" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="4" t="n"/>
@@ -8727,6 +8984,7 @@
       <c r="H253" s="4" t="n"/>
       <c r="I253" s="4" t="n"/>
       <c r="J253" s="3" t="n"/>
+      <c r="K253" s="3" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="4" t="n"/>
@@ -8759,6 +9017,7 @@
       <c r="H254" s="4" t="n"/>
       <c r="I254" s="4" t="n"/>
       <c r="J254" s="3" t="n"/>
+      <c r="K254" s="3" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="4" t="n"/>
@@ -8799,6 +9058,7 @@
         </is>
       </c>
       <c r="J255" s="3" t="n"/>
+      <c r="K255" s="3" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="4" t="n"/>
@@ -8831,6 +9091,7 @@
       <c r="H256" s="4" t="n"/>
       <c r="I256" s="4" t="n"/>
       <c r="J256" s="3" t="n"/>
+      <c r="K256" s="3" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="4" t="n"/>
@@ -8863,6 +9124,7 @@
       <c r="H257" s="4" t="n"/>
       <c r="I257" s="4" t="n"/>
       <c r="J257" s="3" t="n"/>
+      <c r="K257" s="3" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="4" t="n"/>
@@ -8895,6 +9157,7 @@
       <c r="H258" s="4" t="n"/>
       <c r="I258" s="4" t="n"/>
       <c r="J258" s="3" t="n"/>
+      <c r="K258" s="3" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="4" t="n"/>
@@ -8927,6 +9190,7 @@
       <c r="H259" s="4" t="n"/>
       <c r="I259" s="4" t="n"/>
       <c r="J259" s="3" t="n"/>
+      <c r="K259" s="3" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="4" t="n"/>
@@ -8959,6 +9223,7 @@
       <c r="H260" s="4" t="n"/>
       <c r="I260" s="4" t="n"/>
       <c r="J260" s="3" t="n"/>
+      <c r="K260" s="3" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="4" t="n"/>
@@ -8991,6 +9256,7 @@
       <c r="H261" s="4" t="n"/>
       <c r="I261" s="4" t="n"/>
       <c r="J261" s="3" t="n"/>
+      <c r="K261" s="3" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="4" t="n"/>
@@ -9023,6 +9289,7 @@
       <c r="H262" s="4" t="n"/>
       <c r="I262" s="4" t="n"/>
       <c r="J262" s="3" t="n"/>
+      <c r="K262" s="3" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="4" t="n"/>
@@ -9055,6 +9322,7 @@
       <c r="H263" s="4" t="n"/>
       <c r="I263" s="4" t="n"/>
       <c r="J263" s="3" t="n"/>
+      <c r="K263" s="3" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="4" t="n"/>
@@ -9087,6 +9355,7 @@
       <c r="H264" s="4" t="n"/>
       <c r="I264" s="4" t="n"/>
       <c r="J264" s="3" t="n"/>
+      <c r="K264" s="3" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="4" t="n"/>
@@ -9119,6 +9388,7 @@
       <c r="H265" s="4" t="n"/>
       <c r="I265" s="4" t="n"/>
       <c r="J265" s="3" t="n"/>
+      <c r="K265" s="3" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="4" t="n"/>
@@ -9151,6 +9421,7 @@
       <c r="H266" s="4" t="n"/>
       <c r="I266" s="4" t="n"/>
       <c r="J266" s="3" t="n"/>
+      <c r="K266" s="3" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="4" t="n"/>
@@ -9183,6 +9454,7 @@
       <c r="H267" s="4" t="n"/>
       <c r="I267" s="4" t="n"/>
       <c r="J267" s="3" t="n"/>
+      <c r="K267" s="3" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="4" t="n"/>
@@ -9215,6 +9487,7 @@
       <c r="H268" s="4" t="n"/>
       <c r="I268" s="4" t="n"/>
       <c r="J268" s="3" t="n"/>
+      <c r="K268" s="3" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="4" t="n"/>
@@ -9247,6 +9520,7 @@
       <c r="H269" s="4" t="n"/>
       <c r="I269" s="4" t="n"/>
       <c r="J269" s="3" t="n"/>
+      <c r="K269" s="3" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="4" t="n"/>
@@ -9279,6 +9553,7 @@
       <c r="H270" s="4" t="n"/>
       <c r="I270" s="4" t="n"/>
       <c r="J270" s="3" t="n"/>
+      <c r="K270" s="3" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="4" t="n"/>
@@ -9311,6 +9586,7 @@
       <c r="H271" s="4" t="n"/>
       <c r="I271" s="4" t="n"/>
       <c r="J271" s="3" t="n"/>
+      <c r="K271" s="3" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="4" t="n"/>
@@ -9343,6 +9619,7 @@
       <c r="H272" s="4" t="n"/>
       <c r="I272" s="4" t="n"/>
       <c r="J272" s="3" t="n"/>
+      <c r="K272" s="3" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="4" t="n"/>
@@ -9375,6 +9652,7 @@
       <c r="H273" s="4" t="n"/>
       <c r="I273" s="4" t="n"/>
       <c r="J273" s="3" t="n"/>
+      <c r="K273" s="3" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="4" t="n"/>
@@ -9407,6 +9685,7 @@
       <c r="H274" s="4" t="n"/>
       <c r="I274" s="4" t="n"/>
       <c r="J274" s="3" t="n"/>
+      <c r="K274" s="3" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="4" t="n"/>
@@ -9439,6 +9718,7 @@
       <c r="H275" s="4" t="n"/>
       <c r="I275" s="4" t="n"/>
       <c r="J275" s="3" t="n"/>
+      <c r="K275" s="3" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="4" t="n"/>
@@ -9471,6 +9751,7 @@
       <c r="H276" s="4" t="n"/>
       <c r="I276" s="4" t="n"/>
       <c r="J276" s="3" t="n"/>
+      <c r="K276" s="3" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="4" t="n"/>
@@ -9503,6 +9784,7 @@
       <c r="H277" s="4" t="n"/>
       <c r="I277" s="4" t="n"/>
       <c r="J277" s="3" t="n"/>
+      <c r="K277" s="3" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="4" t="n"/>
@@ -9535,6 +9817,7 @@
       <c r="H278" s="4" t="n"/>
       <c r="I278" s="4" t="n"/>
       <c r="J278" s="3" t="n"/>
+      <c r="K278" s="3" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="4" t="n"/>
@@ -9567,6 +9850,7 @@
       <c r="H279" s="4" t="n"/>
       <c r="I279" s="4" t="n"/>
       <c r="J279" s="3" t="n"/>
+      <c r="K279" s="3" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="4" t="n"/>
@@ -9599,6 +9883,7 @@
       <c r="H280" s="4" t="n"/>
       <c r="I280" s="4" t="n"/>
       <c r="J280" s="3" t="n"/>
+      <c r="K280" s="3" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="4" t="n"/>
@@ -9631,6 +9916,7 @@
       <c r="H281" s="4" t="n"/>
       <c r="I281" s="4" t="n"/>
       <c r="J281" s="3" t="n"/>
+      <c r="K281" s="3" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="4" t="n"/>
@@ -9663,6 +9949,7 @@
       <c r="H282" s="4" t="n"/>
       <c r="I282" s="4" t="n"/>
       <c r="J282" s="3" t="n"/>
+      <c r="K282" s="3" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="4" t="n"/>
@@ -9695,6 +9982,7 @@
       <c r="H283" s="4" t="n"/>
       <c r="I283" s="4" t="n"/>
       <c r="J283" s="3" t="n"/>
+      <c r="K283" s="3" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="4" t="n"/>
@@ -9727,6 +10015,7 @@
       <c r="H284" s="4" t="n"/>
       <c r="I284" s="4" t="n"/>
       <c r="J284" s="3" t="n"/>
+      <c r="K284" s="3" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="4" t="n"/>
@@ -9759,6 +10048,7 @@
       <c r="H285" s="4" t="n"/>
       <c r="I285" s="4" t="n"/>
       <c r="J285" s="3" t="n"/>
+      <c r="K285" s="3" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="4" t="n"/>
@@ -9791,6 +10081,7 @@
       <c r="H286" s="4" t="n"/>
       <c r="I286" s="4" t="n"/>
       <c r="J286" s="3" t="n"/>
+      <c r="K286" s="3" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="4" t="n"/>
@@ -9823,6 +10114,7 @@
       <c r="H287" s="4" t="n"/>
       <c r="I287" s="4" t="n"/>
       <c r="J287" s="3" t="n"/>
+      <c r="K287" s="3" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="4" t="n"/>
@@ -9855,6 +10147,7 @@
       <c r="H288" s="4" t="n"/>
       <c r="I288" s="4" t="n"/>
       <c r="J288" s="3" t="n"/>
+      <c r="K288" s="3" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="4" t="n"/>
@@ -9887,6 +10180,7 @@
       <c r="H289" s="4" t="n"/>
       <c r="I289" s="4" t="n"/>
       <c r="J289" s="3" t="n"/>
+      <c r="K289" s="3" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="4" t="n"/>
@@ -9919,6 +10213,7 @@
       <c r="H290" s="4" t="n"/>
       <c r="I290" s="4" t="n"/>
       <c r="J290" s="3" t="n"/>
+      <c r="K290" s="3" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="4" t="n"/>
@@ -9951,6 +10246,7 @@
       <c r="H291" s="4" t="n"/>
       <c r="I291" s="4" t="n"/>
       <c r="J291" s="3" t="n"/>
+      <c r="K291" s="3" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="4" t="n"/>
@@ -9983,6 +10279,7 @@
       <c r="H292" s="4" t="n"/>
       <c r="I292" s="4" t="n"/>
       <c r="J292" s="3" t="n"/>
+      <c r="K292" s="3" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="4" t="n"/>
@@ -10015,6 +10312,7 @@
       <c r="H293" s="4" t="n"/>
       <c r="I293" s="4" t="n"/>
       <c r="J293" s="3" t="n"/>
+      <c r="K293" s="3" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="4" t="n"/>
@@ -10047,6 +10345,7 @@
       <c r="H294" s="4" t="n"/>
       <c r="I294" s="4" t="n"/>
       <c r="J294" s="3" t="n"/>
+      <c r="K294" s="3" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="4" t="n"/>
@@ -10079,6 +10378,7 @@
       <c r="H295" s="4" t="n"/>
       <c r="I295" s="4" t="n"/>
       <c r="J295" s="3" t="n"/>
+      <c r="K295" s="3" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="4" t="n"/>
@@ -10111,6 +10411,7 @@
       <c r="H296" s="4" t="n"/>
       <c r="I296" s="4" t="n"/>
       <c r="J296" s="3" t="n"/>
+      <c r="K296" s="3" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="4" t="n"/>
@@ -10143,6 +10444,7 @@
       <c r="H297" s="4" t="n"/>
       <c r="I297" s="4" t="n"/>
       <c r="J297" s="3" t="n"/>
+      <c r="K297" s="3" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="4" t="n"/>
@@ -10175,6 +10477,7 @@
       <c r="H298" s="4" t="n"/>
       <c r="I298" s="4" t="n"/>
       <c r="J298" s="3" t="n"/>
+      <c r="K298" s="3" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="4" t="n"/>
@@ -10207,6 +10510,7 @@
       <c r="H299" s="4" t="n"/>
       <c r="I299" s="4" t="n"/>
       <c r="J299" s="3" t="n"/>
+      <c r="K299" s="3" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="4" t="n"/>
@@ -10239,6 +10543,7 @@
       <c r="H300" s="4" t="n"/>
       <c r="I300" s="4" t="n"/>
       <c r="J300" s="3" t="n"/>
+      <c r="K300" s="3" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="4" t="n"/>
@@ -10271,6 +10576,7 @@
       <c r="H301" s="4" t="n"/>
       <c r="I301" s="4" t="n"/>
       <c r="J301" s="3" t="n"/>
+      <c r="K301" s="3" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="4" t="n"/>
@@ -10303,6 +10609,7 @@
       <c r="H302" s="4" t="n"/>
       <c r="I302" s="4" t="n"/>
       <c r="J302" s="3" t="n"/>
+      <c r="K302" s="3" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="4" t="n"/>
@@ -10335,6 +10642,7 @@
       <c r="H303" s="4" t="n"/>
       <c r="I303" s="4" t="n"/>
       <c r="J303" s="3" t="n"/>
+      <c r="K303" s="3" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="4" t="n"/>
@@ -10367,6 +10675,7 @@
       <c r="H304" s="4" t="n"/>
       <c r="I304" s="4" t="n"/>
       <c r="J304" s="3" t="n"/>
+      <c r="K304" s="3" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="4" t="n"/>
@@ -10399,6 +10708,7 @@
       <c r="H305" s="4" t="n"/>
       <c r="I305" s="4" t="n"/>
       <c r="J305" s="3" t="n"/>
+      <c r="K305" s="3" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="4" t="n"/>
@@ -10431,6 +10741,7 @@
       <c r="H306" s="4" t="n"/>
       <c r="I306" s="4" t="n"/>
       <c r="J306" s="3" t="n"/>
+      <c r="K306" s="3" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="4" t="n"/>
@@ -10463,6 +10774,7 @@
       <c r="H307" s="4" t="n"/>
       <c r="I307" s="4" t="n"/>
       <c r="J307" s="3" t="n"/>
+      <c r="K307" s="3" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="4" t="n"/>
@@ -10495,6 +10807,7 @@
       <c r="H308" s="4" t="n"/>
       <c r="I308" s="4" t="n"/>
       <c r="J308" s="3" t="n"/>
+      <c r="K308" s="3" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="4" t="n"/>
@@ -10527,6 +10840,7 @@
       <c r="H309" s="4" t="n"/>
       <c r="I309" s="4" t="n"/>
       <c r="J309" s="3" t="n"/>
+      <c r="K309" s="3" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="4" t="n"/>
@@ -10559,6 +10873,7 @@
       <c r="H310" s="4" t="n"/>
       <c r="I310" s="4" t="n"/>
       <c r="J310" s="3" t="n"/>
+      <c r="K310" s="3" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="4" t="n"/>
@@ -10595,6 +10910,7 @@
           <t>We conclude that no changes are needed in this regard</t>
         </is>
       </c>
+      <c r="K311" s="3" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="4" t="n"/>
@@ -10627,6 +10943,7 @@
       <c r="H312" s="4" t="n"/>
       <c r="I312" s="4" t="n"/>
       <c r="J312" s="3" t="n"/>
+      <c r="K312" s="3" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="4" t="n"/>
@@ -10659,6 +10976,7 @@
       <c r="H313" s="4" t="n"/>
       <c r="I313" s="4" t="n"/>
       <c r="J313" s="3" t="n"/>
+      <c r="K313" s="3" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="4" t="n"/>
@@ -10691,6 +11009,7 @@
       <c r="H314" s="4" t="n"/>
       <c r="I314" s="4" t="n"/>
       <c r="J314" s="3" t="n"/>
+      <c r="K314" s="3" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="4" t="n"/>
@@ -10723,6 +11042,7 @@
       <c r="H315" s="4" t="n"/>
       <c r="I315" s="4" t="n"/>
       <c r="J315" s="3" t="n"/>
+      <c r="K315" s="3" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="4" t="n"/>
@@ -10755,6 +11075,7 @@
       <c r="H316" s="4" t="n"/>
       <c r="I316" s="4" t="n"/>
       <c r="J316" s="3" t="n"/>
+      <c r="K316" s="3" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="4" t="n"/>
@@ -10787,6 +11108,7 @@
       <c r="H317" s="4" t="n"/>
       <c r="I317" s="4" t="n"/>
       <c r="J317" s="3" t="n"/>
+      <c r="K317" s="3" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="4" t="n"/>
@@ -10819,6 +11141,7 @@
       <c r="H318" s="4" t="n"/>
       <c r="I318" s="4" t="n"/>
       <c r="J318" s="3" t="n"/>
+      <c r="K318" s="3" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="4" t="n"/>
@@ -10851,6 +11174,7 @@
       <c r="H319" s="4" t="n"/>
       <c r="I319" s="4" t="n"/>
       <c r="J319" s="3" t="n"/>
+      <c r="K319" s="3" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="4" t="n"/>
@@ -10883,6 +11207,7 @@
       <c r="H320" s="4" t="n"/>
       <c r="I320" s="4" t="n"/>
       <c r="J320" s="3" t="n"/>
+      <c r="K320" s="3" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="4" t="n"/>
@@ -10915,6 +11240,7 @@
       <c r="H321" s="4" t="n"/>
       <c r="I321" s="4" t="n"/>
       <c r="J321" s="3" t="n"/>
+      <c r="K321" s="3" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="4" t="n"/>
@@ -10947,6 +11273,7 @@
       <c r="H322" s="4" t="n"/>
       <c r="I322" s="4" t="n"/>
       <c r="J322" s="3" t="n"/>
+      <c r="K322" s="3" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="4" t="n"/>
@@ -10979,6 +11306,7 @@
       <c r="H323" s="4" t="n"/>
       <c r="I323" s="4" t="n"/>
       <c r="J323" s="3" t="n"/>
+      <c r="K323" s="3" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="4" t="n"/>
@@ -11011,6 +11339,7 @@
       <c r="H324" s="4" t="n"/>
       <c r="I324" s="4" t="n"/>
       <c r="J324" s="3" t="n"/>
+      <c r="K324" s="3" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="4" t="n"/>
@@ -11043,6 +11372,7 @@
       <c r="H325" s="4" t="n"/>
       <c r="I325" s="4" t="n"/>
       <c r="J325" s="3" t="n"/>
+      <c r="K325" s="3" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="4" t="n"/>
@@ -11075,6 +11405,7 @@
       <c r="H326" s="4" t="n"/>
       <c r="I326" s="4" t="n"/>
       <c r="J326" s="3" t="n"/>
+      <c r="K326" s="3" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="4" t="n"/>
@@ -11107,6 +11438,7 @@
       <c r="H327" s="4" t="n"/>
       <c r="I327" s="4" t="n"/>
       <c r="J327" s="3" t="n"/>
+      <c r="K327" s="3" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="4" t="n"/>
@@ -11139,6 +11471,7 @@
       <c r="H328" s="4" t="n"/>
       <c r="I328" s="4" t="n"/>
       <c r="J328" s="3" t="n"/>
+      <c r="K328" s="3" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="4" t="n"/>
@@ -11171,6 +11504,7 @@
           <t>No ISO code as BQ Also includes Bonaire, not part of this unit</t>
         </is>
       </c>
+      <c r="K329" s="3" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="4" t="n"/>
@@ -11203,6 +11537,7 @@
       <c r="H330" s="4" t="n"/>
       <c r="I330" s="4" t="n"/>
       <c r="J330" s="3" t="n"/>
+      <c r="K330" s="3" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="4" t="n"/>
@@ -11236,6 +11571,7 @@
 https://en.wikipedia.org/wiki/Saint_Martin_(island)</t>
         </is>
       </c>
+      <c r="K331" s="3" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="4" t="n"/>
@@ -11268,6 +11604,7 @@
       <c r="H332" s="4" t="n"/>
       <c r="I332" s="4" t="n"/>
       <c r="J332" s="3" t="n"/>
+      <c r="K332" s="3" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="4" t="n"/>
@@ -11300,6 +11637,7 @@
       <c r="H333" s="4" t="n"/>
       <c r="I333" s="4" t="n"/>
       <c r="J333" s="3" t="n"/>
+      <c r="K333" s="3" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="4" t="n"/>
@@ -11332,6 +11670,7 @@
       <c r="H334" s="4" t="n"/>
       <c r="I334" s="4" t="n"/>
       <c r="J334" s="3" t="n"/>
+      <c r="K334" s="3" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="4" t="n"/>
@@ -11364,6 +11703,7 @@
       <c r="H335" s="4" t="n"/>
       <c r="I335" s="4" t="n"/>
       <c r="J335" s="3" t="n"/>
+      <c r="K335" s="3" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="4" t="n"/>
@@ -11396,6 +11736,7 @@
       <c r="H336" s="4" t="n"/>
       <c r="I336" s="4" t="n"/>
       <c r="J336" s="3" t="n"/>
+      <c r="K336" s="3" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="4" t="n"/>
@@ -11428,6 +11769,7 @@
       <c r="H337" s="4" t="n"/>
       <c r="I337" s="4" t="n"/>
       <c r="J337" s="3" t="n"/>
+      <c r="K337" s="3" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="4" t="inlineStr">
@@ -11476,6 +11818,7 @@
           <t>ISO Code for LSI-ET changes to TL</t>
         </is>
       </c>
+      <c r="K338" s="3" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="4" t="n"/>
@@ -11520,6 +11863,7 @@
           <t>Limits of LSI-LS, changes to exclude the Indonesian part of Timor from this unit.</t>
         </is>
       </c>
+      <c r="K339" s="3" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="4" t="n"/>
@@ -11552,6 +11896,7 @@
       <c r="H340" s="4" t="n"/>
       <c r="I340" s="4" t="n"/>
       <c r="J340" s="3" t="n"/>
+      <c r="K340" s="3" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="4" t="n"/>
@@ -11584,6 +11929,7 @@
       <c r="H341" s="4" t="n"/>
       <c r="I341" s="4" t="n"/>
       <c r="J341" s="3" t="n"/>
+      <c r="K341" s="3" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="4" t="n"/>
@@ -11616,6 +11962,7 @@
       <c r="H342" s="4" t="n"/>
       <c r="I342" s="4" t="n"/>
       <c r="J342" s="3" t="n"/>
+      <c r="K342" s="3" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="4" t="n"/>
@@ -11648,6 +11995,7 @@
       <c r="H343" s="4" t="n"/>
       <c r="I343" s="4" t="n"/>
       <c r="J343" s="3" t="n"/>
+      <c r="K343" s="3" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="4" t="n"/>
@@ -11680,6 +12028,7 @@
       <c r="H344" s="4" t="n"/>
       <c r="I344" s="4" t="n"/>
       <c r="J344" s="3" t="n"/>
+      <c r="K344" s="3" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="4" t="n"/>
@@ -11712,6 +12061,7 @@
       <c r="H345" s="4" t="n"/>
       <c r="I345" s="4" t="n"/>
       <c r="J345" s="3" t="n"/>
+      <c r="K345" s="3" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="4" t="n"/>
@@ -11745,6 +12095,7 @@
 https://en.wikipedia.org/wiki/Mozambique_Channel</t>
         </is>
       </c>
+      <c r="K346" s="3" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="4" t="n"/>
@@ -11777,6 +12128,7 @@
       <c r="H347" s="4" t="n"/>
       <c r="I347" s="4" t="n"/>
       <c r="J347" s="3" t="n"/>
+      <c r="K347" s="3" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="4" t="n"/>
@@ -11809,6 +12161,7 @@
       <c r="H348" s="4" t="n"/>
       <c r="I348" s="4" t="n"/>
       <c r="J348" s="3" t="n"/>
+      <c r="K348" s="3" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="4" t="n"/>
@@ -11841,6 +12194,7 @@
       <c r="H349" s="4" t="n"/>
       <c r="I349" s="4" t="n"/>
       <c r="J349" s="3" t="n"/>
+      <c r="K349" s="3" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="4" t="n"/>
@@ -11873,6 +12227,7 @@
       <c r="H350" s="4" t="n"/>
       <c r="I350" s="4" t="n"/>
       <c r="J350" s="3" t="n"/>
+      <c r="K350" s="3" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="4" t="n"/>
@@ -11905,6 +12260,7 @@
       <c r="H351" s="4" t="n"/>
       <c r="I351" s="4" t="n"/>
       <c r="J351" s="3" t="n"/>
+      <c r="K351" s="3" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="4" t="n"/>
@@ -11937,6 +12293,7 @@
       <c r="H352" s="4" t="n"/>
       <c r="I352" s="4" t="n"/>
       <c r="J352" s="3" t="n"/>
+      <c r="K352" s="3" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="4" t="n"/>
@@ -11969,6 +12326,7 @@
       <c r="H353" s="4" t="n"/>
       <c r="I353" s="4" t="n"/>
       <c r="J353" s="3" t="n"/>
+      <c r="K353" s="3" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="4" t="n"/>
@@ -12001,6 +12359,7 @@
       <c r="H354" s="4" t="n"/>
       <c r="I354" s="4" t="n"/>
       <c r="J354" s="3" t="n"/>
+      <c r="K354" s="3" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="4" t="n"/>
@@ -12033,6 +12392,7 @@
       <c r="H355" s="4" t="n"/>
       <c r="I355" s="4" t="n"/>
       <c r="J355" s="3" t="n"/>
+      <c r="K355" s="3" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="4" t="n"/>
@@ -12065,6 +12425,7 @@
       <c r="H356" s="4" t="n"/>
       <c r="I356" s="4" t="n"/>
       <c r="J356" s="3" t="n"/>
+      <c r="K356" s="3" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="4" t="n"/>
@@ -12097,6 +12458,7 @@
       <c r="H357" s="4" t="n"/>
       <c r="I357" s="4" t="n"/>
       <c r="J357" s="3" t="n"/>
+      <c r="K357" s="3" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="4" t="n"/>
@@ -12129,6 +12491,7 @@
       <c r="H358" s="4" t="n"/>
       <c r="I358" s="4" t="n"/>
       <c r="J358" s="3" t="n"/>
+      <c r="K358" s="3" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="4" t="n"/>
@@ -12161,6 +12524,7 @@
       <c r="H359" s="4" t="n"/>
       <c r="I359" s="4" t="n"/>
       <c r="J359" s="3" t="n"/>
+      <c r="K359" s="3" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="4" t="n"/>
@@ -12193,6 +12557,7 @@
       <c r="H360" s="4" t="n"/>
       <c r="I360" s="4" t="n"/>
       <c r="J360" s="3" t="n"/>
+      <c r="K360" s="3" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="4" t="n"/>
@@ -12225,6 +12590,7 @@
       <c r="H361" s="4" t="n"/>
       <c r="I361" s="4" t="n"/>
       <c r="J361" s="3" t="n"/>
+      <c r="K361" s="3" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="4" t="n"/>
@@ -12257,6 +12623,7 @@
       <c r="H362" s="4" t="n"/>
       <c r="I362" s="4" t="n"/>
       <c r="J362" s="3" t="n"/>
+      <c r="K362" s="3" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="4" t="n"/>
@@ -12289,6 +12656,7 @@
       <c r="H363" s="4" t="n"/>
       <c r="I363" s="4" t="n"/>
       <c r="J363" s="3" t="n"/>
+      <c r="K363" s="3" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="4" t="n"/>
@@ -12321,6 +12689,7 @@
       <c r="H364" s="4" t="n"/>
       <c r="I364" s="4" t="n"/>
       <c r="J364" s="3" t="n"/>
+      <c r="K364" s="3" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="4" t="n"/>
@@ -12353,6 +12722,7 @@
       <c r="H365" s="4" t="n"/>
       <c r="I365" s="4" t="n"/>
       <c r="J365" s="3" t="n"/>
+      <c r="K365" s="3" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="4" t="n"/>
@@ -12385,6 +12755,7 @@
       <c r="H366" s="4" t="n"/>
       <c r="I366" s="4" t="n"/>
       <c r="J366" s="3" t="n"/>
+      <c r="K366" s="3" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="4" t="n"/>
@@ -12417,6 +12788,7 @@
       <c r="H367" s="4" t="n"/>
       <c r="I367" s="4" t="n"/>
       <c r="J367" s="3" t="n"/>
+      <c r="K367" s="3" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="4" t="n"/>
@@ -12449,6 +12821,7 @@
       <c r="H368" s="4" t="n"/>
       <c r="I368" s="4" t="n"/>
       <c r="J368" s="3" t="n"/>
+      <c r="K368" s="3" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="4" t="n"/>
@@ -12481,6 +12854,7 @@
       <c r="H369" s="4" t="n"/>
       <c r="I369" s="4" t="n"/>
       <c r="J369" s="3" t="n"/>
+      <c r="K369" s="3" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="4" t="n"/>
@@ -12513,6 +12887,7 @@
       <c r="H370" s="4" t="n"/>
       <c r="I370" s="4" t="n"/>
       <c r="J370" s="3" t="n"/>
+      <c r="K370" s="3" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="4" t="n"/>
@@ -12545,6 +12920,7 @@
       <c r="H371" s="4" t="n"/>
       <c r="I371" s="4" t="n"/>
       <c r="J371" s="3" t="n"/>
+      <c r="K371" s="3" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="4" t="n"/>
@@ -12577,6 +12953,7 @@
       <c r="H372" s="4" t="n"/>
       <c r="I372" s="4" t="n"/>
       <c r="J372" s="3" t="n"/>
+      <c r="K372" s="3" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="4" t="n"/>
@@ -12609,6 +12986,7 @@
       <c r="H373" s="4" t="n"/>
       <c r="I373" s="4" t="n"/>
       <c r="J373" s="3" t="n"/>
+      <c r="K373" s="3" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="4" t="n"/>
@@ -12641,6 +13019,7 @@
       <c r="H374" s="4" t="n"/>
       <c r="I374" s="4" t="n"/>
       <c r="J374" s="3" t="n"/>
+      <c r="K374" s="3" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="4" t="n"/>
@@ -12673,6 +13052,7 @@
       <c r="H375" s="4" t="n"/>
       <c r="I375" s="4" t="n"/>
       <c r="J375" s="3" t="n"/>
+      <c r="K375" s="3" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="4" t="n"/>
@@ -12705,6 +13085,7 @@
       <c r="H376" s="4" t="n"/>
       <c r="I376" s="4" t="n"/>
       <c r="J376" s="3" t="n"/>
+      <c r="K376" s="3" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="4" t="n"/>
@@ -12737,6 +13118,7 @@
       <c r="H377" s="4" t="n"/>
       <c r="I377" s="4" t="n"/>
       <c r="J377" s="3" t="n"/>
+      <c r="K377" s="3" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="4" t="n"/>
@@ -12769,6 +13151,7 @@
       <c r="H378" s="4" t="n"/>
       <c r="I378" s="4" t="n"/>
       <c r="J378" s="3" t="n"/>
+      <c r="K378" s="3" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="4" t="n"/>
@@ -12801,6 +13184,7 @@
       <c r="H379" s="4" t="n"/>
       <c r="I379" s="4" t="n"/>
       <c r="J379" s="3" t="n"/>
+      <c r="K379" s="3" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="4" t="n"/>
@@ -12833,6 +13217,7 @@
       <c r="H380" s="4" t="n"/>
       <c r="I380" s="4" t="n"/>
       <c r="J380" s="3" t="n"/>
+      <c r="K380" s="3" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="4" t="n"/>
@@ -12865,6 +13250,7 @@
       <c r="H381" s="4" t="n"/>
       <c r="I381" s="4" t="n"/>
       <c r="J381" s="3" t="n"/>
+      <c r="K381" s="3" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="4" t="n"/>
@@ -12897,6 +13283,7 @@
       <c r="H382" s="4" t="n"/>
       <c r="I382" s="4" t="n"/>
       <c r="J382" s="3" t="n"/>
+      <c r="K382" s="3" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="4" t="n"/>
@@ -12929,6 +13316,7 @@
       <c r="H383" s="4" t="n"/>
       <c r="I383" s="4" t="n"/>
       <c r="J383" s="3" t="n"/>
+      <c r="K383" s="3" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="4" t="n"/>
@@ -12961,6 +13349,7 @@
       <c r="H384" s="4" t="n"/>
       <c r="I384" s="4" t="n"/>
       <c r="J384" s="3" t="n"/>
+      <c r="K384" s="3" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="4" t="n"/>
@@ -12993,6 +13382,7 @@
       <c r="H385" s="4" t="n"/>
       <c r="I385" s="4" t="n"/>
       <c r="J385" s="3" t="n"/>
+      <c r="K385" s="3" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="4" t="n"/>
@@ -13025,6 +13415,7 @@
       <c r="H386" s="4" t="n"/>
       <c r="I386" s="4" t="n"/>
       <c r="J386" s="3" t="n"/>
+      <c r="K386" s="3" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="4" t="n"/>
@@ -13057,6 +13448,7 @@
       <c r="H387" s="4" t="n"/>
       <c r="I387" s="4" t="n"/>
       <c r="J387" s="3" t="n"/>
+      <c r="K387" s="3" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="4" t="n"/>
@@ -13089,6 +13481,7 @@
       <c r="H388" s="4" t="n"/>
       <c r="I388" s="4" t="n"/>
       <c r="J388" s="3" t="n"/>
+      <c r="K388" s="3" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="4" t="n"/>
@@ -13121,6 +13514,7 @@
       <c r="H389" s="4" t="n"/>
       <c r="I389" s="4" t="n"/>
       <c r="J389" s="3" t="n"/>
+      <c r="K389" s="3" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="4" t="n"/>
@@ -13153,6 +13547,7 @@
       <c r="H390" s="4" t="n"/>
       <c r="I390" s="4" t="n"/>
       <c r="J390" s="3" t="n"/>
+      <c r="K390" s="3" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="4" t="n"/>
@@ -13185,6 +13580,7 @@
       <c r="H391" s="4" t="n"/>
       <c r="I391" s="4" t="n"/>
       <c r="J391" s="3" t="n"/>
+      <c r="K391" s="3" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="4" t="n"/>
@@ -13217,6 +13613,7 @@
       <c r="H392" s="4" t="n"/>
       <c r="I392" s="4" t="n"/>
       <c r="J392" s="3" t="n"/>
+      <c r="K392" s="3" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="4" t="n"/>
@@ -13249,6 +13646,7 @@
       <c r="H393" s="4" t="n"/>
       <c r="I393" s="4" t="n"/>
       <c r="J393" s="3" t="n"/>
+      <c r="K393" s="3" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="4" t="n"/>
@@ -13281,6 +13679,7 @@
       <c r="H394" s="4" t="n"/>
       <c r="I394" s="4" t="n"/>
       <c r="J394" s="3" t="n"/>
+      <c r="K394" s="3" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="4" t="n"/>
@@ -13313,6 +13712,7 @@
       <c r="H395" s="4" t="n"/>
       <c r="I395" s="4" t="n"/>
       <c r="J395" s="3" t="n"/>
+      <c r="K395" s="3" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="4" t="n"/>
@@ -13345,6 +13745,7 @@
       <c r="H396" s="4" t="n"/>
       <c r="I396" s="4" t="n"/>
       <c r="J396" s="3" t="n"/>
+      <c r="K396" s="3" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="4" t="n"/>
@@ -13377,6 +13778,7 @@
       <c r="H397" s="4" t="n"/>
       <c r="I397" s="4" t="n"/>
       <c r="J397" s="3" t="n"/>
+      <c r="K397" s="3" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="4" t="n"/>
@@ -13409,6 +13811,7 @@
       <c r="H398" s="4" t="n"/>
       <c r="I398" s="4" t="n"/>
       <c r="J398" s="3" t="n"/>
+      <c r="K398" s="3" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="4" t="n"/>
@@ -13441,6 +13844,7 @@
       <c r="H399" s="4" t="n"/>
       <c r="I399" s="4" t="n"/>
       <c r="J399" s="3" t="n"/>
+      <c r="K399" s="3" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="4" t="n"/>
@@ -13473,6 +13877,7 @@
       <c r="H400" s="4" t="n"/>
       <c r="I400" s="4" t="n"/>
       <c r="J400" s="3" t="n"/>
+      <c r="K400" s="3" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="4" t="n"/>
@@ -13505,6 +13910,7 @@
       <c r="H401" s="4" t="n"/>
       <c r="I401" s="4" t="n"/>
       <c r="J401" s="3" t="n"/>
+      <c r="K401" s="3" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="4" t="n"/>
@@ -13537,6 +13943,7 @@
       <c r="H402" s="4" t="n"/>
       <c r="I402" s="4" t="n"/>
       <c r="J402" s="3" t="n"/>
+      <c r="K402" s="3" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="4" t="n"/>
@@ -13569,6 +13976,7 @@
       <c r="H403" s="4" t="n"/>
       <c r="I403" s="4" t="n"/>
       <c r="J403" s="3" t="n"/>
+      <c r="K403" s="3" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="4" t="n"/>
@@ -13601,6 +14009,7 @@
       <c r="H404" s="4" t="n"/>
       <c r="I404" s="4" t="n"/>
       <c r="J404" s="3" t="n"/>
+      <c r="K404" s="3" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="4" t="n"/>
@@ -13633,6 +14042,7 @@
       <c r="H405" s="4" t="n"/>
       <c r="I405" s="4" t="n"/>
       <c r="J405" s="3" t="n"/>
+      <c r="K405" s="3" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="4" t="n"/>
@@ -13665,6 +14075,7 @@
       <c r="H406" s="4" t="n"/>
       <c r="I406" s="4" t="n"/>
       <c r="J406" s="3" t="n"/>
+      <c r="K406" s="3" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="4" t="n"/>
@@ -13697,6 +14108,7 @@
       <c r="H407" s="4" t="n"/>
       <c r="I407" s="4" t="n"/>
       <c r="J407" s="3" t="n"/>
+      <c r="K407" s="3" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="4" t="n"/>
@@ -13729,6 +14141,7 @@
       <c r="H408" s="4" t="n"/>
       <c r="I408" s="4" t="n"/>
       <c r="J408" s="3" t="n"/>
+      <c r="K408" s="3" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="4" t="n"/>
@@ -13761,6 +14174,7 @@
       <c r="H409" s="4" t="n"/>
       <c r="I409" s="4" t="n"/>
       <c r="J409" s="3" t="n"/>
+      <c r="K409" s="3" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="4" t="n"/>
@@ -13793,6 +14207,7 @@
       <c r="H410" s="4" t="n"/>
       <c r="I410" s="4" t="n"/>
       <c r="J410" s="3" t="n"/>
+      <c r="K410" s="3" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="4" t="n"/>
@@ -13825,6 +14240,7 @@
       <c r="H411" s="4" t="n"/>
       <c r="I411" s="4" t="n"/>
       <c r="J411" s="3" t="n"/>
+      <c r="K411" s="3" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="4" t="n"/>
@@ -13857,6 +14273,7 @@
       <c r="H412" s="4" t="n"/>
       <c r="I412" s="4" t="n"/>
       <c r="J412" s="3" t="n"/>
+      <c r="K412" s="3" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="4" t="n"/>
@@ -13889,6 +14306,7 @@
       <c r="H413" s="4" t="n"/>
       <c r="I413" s="4" t="n"/>
       <c r="J413" s="3" t="n"/>
+      <c r="K413" s="3" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="4" t="n"/>
@@ -13921,6 +14339,7 @@
       <c r="H414" s="4" t="n"/>
       <c r="I414" s="4" t="n"/>
       <c r="J414" s="3" t="n"/>
+      <c r="K414" s="3" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="4" t="n"/>
@@ -13953,6 +14372,7 @@
       <c r="H415" s="4" t="n"/>
       <c r="I415" s="4" t="n"/>
       <c r="J415" s="3" t="n"/>
+      <c r="K415" s="3" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="4" t="n"/>
@@ -13985,6 +14405,7 @@
       <c r="H416" s="4" t="n"/>
       <c r="I416" s="4" t="n"/>
       <c r="J416" s="3" t="n"/>
+      <c r="K416" s="3" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="4" t="n"/>
@@ -14017,6 +14438,7 @@
       <c r="H417" s="4" t="n"/>
       <c r="I417" s="4" t="n"/>
       <c r="J417" s="3" t="n"/>
+      <c r="K417" s="3" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="4" t="n"/>
@@ -14049,6 +14471,7 @@
       <c r="H418" s="4" t="n"/>
       <c r="I418" s="4" t="n"/>
       <c r="J418" s="3" t="n"/>
+      <c r="K418" s="3" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="4" t="n"/>
@@ -14081,6 +14504,7 @@
       <c r="H419" s="4" t="n"/>
       <c r="I419" s="4" t="n"/>
       <c r="J419" s="3" t="n"/>
+      <c r="K419" s="3" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="4" t="n"/>
@@ -14113,6 +14537,7 @@
       <c r="H420" s="4" t="n"/>
       <c r="I420" s="4" t="n"/>
       <c r="J420" s="3" t="n"/>
+      <c r="K420" s="3" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="4" t="n"/>
@@ -14145,6 +14570,7 @@
       <c r="H421" s="4" t="n"/>
       <c r="I421" s="4" t="n"/>
       <c r="J421" s="3" t="n"/>
+      <c r="K421" s="3" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="4" t="n"/>
@@ -14177,6 +14603,7 @@
       <c r="H422" s="4" t="n"/>
       <c r="I422" s="4" t="n"/>
       <c r="J422" s="3" t="n"/>
+      <c r="K422" s="3" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="4" t="n"/>
@@ -14209,6 +14636,7 @@
       <c r="H423" s="4" t="n"/>
       <c r="I423" s="4" t="n"/>
       <c r="J423" s="3" t="n"/>
+      <c r="K423" s="3" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="4" t="n"/>
@@ -14241,6 +14669,7 @@
       <c r="H424" s="4" t="n"/>
       <c r="I424" s="4" t="n"/>
       <c r="J424" s="3" t="n"/>
+      <c r="K424" s="3" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="4" t="n"/>
@@ -14273,6 +14702,7 @@
       <c r="H425" s="4" t="n"/>
       <c r="I425" s="4" t="n"/>
       <c r="J425" s="3" t="n"/>
+      <c r="K425" s="3" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="4" t="n"/>
@@ -14305,6 +14735,7 @@
       <c r="H426" s="4" t="n"/>
       <c r="I426" s="4" t="n"/>
       <c r="J426" s="3" t="n"/>
+      <c r="K426" s="3" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="4" t="n"/>
@@ -14337,6 +14768,7 @@
       <c r="H427" s="4" t="n"/>
       <c r="I427" s="4" t="n"/>
       <c r="J427" s="3" t="n"/>
+      <c r="K427" s="3" t="n"/>
     </row>
     <row r="428">
       <c r="A428" s="4" t="n"/>
@@ -14369,6 +14801,7 @@
       <c r="H428" s="4" t="n"/>
       <c r="I428" s="4" t="n"/>
       <c r="J428" s="3" t="n"/>
+      <c r="K428" s="3" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="4" t="n"/>
@@ -14401,6 +14834,7 @@
       <c r="H429" s="4" t="n"/>
       <c r="I429" s="4" t="n"/>
       <c r="J429" s="3" t="n"/>
+      <c r="K429" s="3" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="4" t="n"/>
@@ -14433,6 +14867,7 @@
       <c r="H430" s="4" t="n"/>
       <c r="I430" s="4" t="n"/>
       <c r="J430" s="3" t="n"/>
+      <c r="K430" s="3" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="4" t="n"/>
@@ -14465,6 +14900,7 @@
       <c r="H431" s="4" t="n"/>
       <c r="I431" s="4" t="n"/>
       <c r="J431" s="3" t="n"/>
+      <c r="K431" s="3" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="4" t="n"/>
@@ -14497,6 +14933,7 @@
       <c r="H432" s="4" t="n"/>
       <c r="I432" s="4" t="n"/>
       <c r="J432" s="3" t="n"/>
+      <c r="K432" s="3" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="4" t="n"/>
@@ -14535,6 +14972,7 @@
 https://en.wikipedia.org/wiki/Caribbean_Netherlands</t>
         </is>
       </c>
+      <c r="K433" s="3" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="4" t="n"/>
@@ -14573,6 +15011,7 @@
 https://www.bbc.com/news/world-latin-america-11511355</t>
         </is>
       </c>
+      <c r="K434" s="3" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="4" t="n"/>
@@ -14605,6 +15044,7 @@
       <c r="H435" s="4" t="n"/>
       <c r="I435" s="4" t="n"/>
       <c r="J435" s="3" t="n"/>
+      <c r="K435" s="3" t="n"/>
     </row>
     <row r="436">
       <c r="A436" s="4" t="n"/>
@@ -14637,6 +15077,7 @@
       <c r="H436" s="4" t="n"/>
       <c r="I436" s="4" t="n"/>
       <c r="J436" s="3" t="n"/>
+      <c r="K436" s="3" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="4" t="n"/>
@@ -14677,6 +15118,7 @@
         </is>
       </c>
       <c r="J437" s="3" t="n"/>
+      <c r="K437" s="3" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="4" t="inlineStr">
@@ -14725,6 +15167,7 @@
           <t>TVL-NP as a Level 4 unit, is it correct to change the L4 code (Table 4 in WGSRPD 2) to TVL-LI and the L4 country to Limpopo ?.</t>
         </is>
       </c>
+      <c r="K438" s="3" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="4" t="n"/>
@@ -14761,6 +15204,7 @@
       <c r="H439" s="4" t="n"/>
       <c r="I439" s="4" t="n"/>
       <c r="J439" s="3" t="n"/>
+      <c r="K439" s="3" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="4" t="n"/>
@@ -14797,6 +15241,7 @@
       <c r="H440" s="4" t="n"/>
       <c r="I440" s="4" t="n"/>
       <c r="J440" s="3" t="n"/>
+      <c r="K440" s="3" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="4" t="n"/>
@@ -14829,6 +15274,7 @@
       <c r="H441" s="4" t="n"/>
       <c r="I441" s="4" t="n"/>
       <c r="J441" s="3" t="n"/>
+      <c r="K441" s="3" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="4" t="n"/>
@@ -14861,6 +15307,7 @@
       <c r="H442" s="4" t="n"/>
       <c r="I442" s="4" t="n"/>
       <c r="J442" s="3" t="n"/>
+      <c r="K442" s="3" t="n"/>
     </row>
     <row r="443">
       <c r="A443" s="4" t="n"/>
@@ -14893,6 +15340,7 @@
       <c r="H443" s="4" t="n"/>
       <c r="I443" s="4" t="n"/>
       <c r="J443" s="3" t="n"/>
+      <c r="K443" s="3" t="n"/>
     </row>
     <row r="444">
       <c r="A444" s="4" t="n"/>
@@ -14925,6 +15373,7 @@
       <c r="H444" s="4" t="n"/>
       <c r="I444" s="4" t="n"/>
       <c r="J444" s="3" t="n"/>
+      <c r="K444" s="3" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="4" t="n"/>
@@ -14957,6 +15406,7 @@
       <c r="H445" s="4" t="n"/>
       <c r="I445" s="4" t="n"/>
       <c r="J445" s="3" t="n"/>
+      <c r="K445" s="3" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="4" t="n"/>
@@ -14989,6 +15439,7 @@
       <c r="H446" s="4" t="n"/>
       <c r="I446" s="4" t="n"/>
       <c r="J446" s="3" t="n"/>
+      <c r="K446" s="3" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="4" t="n"/>
@@ -15021,6 +15472,7 @@
       <c r="H447" s="4" t="n"/>
       <c r="I447" s="4" t="n"/>
       <c r="J447" s="3" t="n"/>
+      <c r="K447" s="3" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="4" t="inlineStr">
@@ -15069,6 +15521,7 @@
           <t>New name for former Yugoslavia: Balkans or West Balkans?New name for former Yugoslavia: Balkans or West Balkans? (LEVEL 3)</t>
         </is>
       </c>
+      <c r="K448" s="3" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="4" t="inlineStr">
@@ -15117,6 +15570,7 @@
           <t>New name for former Yugoslavia: Balkans or West Balkans?New name for former Yugoslavia: Balkans or West Balkans? (LEVEL 3)</t>
         </is>
       </c>
+      <c r="K449" s="3" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="4" t="inlineStr">
@@ -15165,6 +15619,7 @@
           <t>New name for former Yugoslavia: Balkans or West Balkans?New name for former Yugoslavia: Balkans or West Balkans? (LEVEL 3)</t>
         </is>
       </c>
+      <c r="K450" s="3" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="4" t="inlineStr">
@@ -15213,6 +15668,7 @@
           <t>New name for former Yugoslavia: Balkans or West Balkans?New name for former Yugoslavia: Balkans or West Balkans? (LEVEL 3)</t>
         </is>
       </c>
+      <c r="K451" s="3" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="4" t="inlineStr">
@@ -15261,6 +15717,7 @@
           <t>New name for former Yugoslavia: Balkans or West Balkans?New name for former Yugoslavia: Balkans or West Balkans? (LEVEL 3)</t>
         </is>
       </c>
+      <c r="K452" s="3" t="n"/>
     </row>
     <row r="453">
       <c r="A453" s="4" t="inlineStr">
@@ -15309,6 +15766,7 @@
           <t>New name for former Yugoslavia: Balkans or West Balkans?New name for former Yugoslavia: Balkans or West Balkans? (LEVEL 3)</t>
         </is>
       </c>
+      <c r="K453" s="3" t="n"/>
     </row>
     <row r="454">
       <c r="A454" s="4" t="inlineStr">
@@ -15357,6 +15815,7 @@
           <t>New name for former Yugoslavia: Balkans or West Balkans?New name for former Yugoslavia: Balkans or West Balkans? (LEVEL 3)</t>
         </is>
       </c>
+      <c r="K454" s="3" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="4" t="n"/>
@@ -15389,6 +15848,7 @@
       <c r="H455" s="4" t="n"/>
       <c r="I455" s="4" t="n"/>
       <c r="J455" s="3" t="n"/>
+      <c r="K455" s="3" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="4" t="n"/>
@@ -15421,6 +15881,7 @@
       <c r="H456" s="4" t="n"/>
       <c r="I456" s="4" t="n"/>
       <c r="J456" s="3" t="n"/>
+      <c r="K456" s="3" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="4" t="n"/>
@@ -15453,6 +15914,7 @@
       <c r="H457" s="4" t="n"/>
       <c r="I457" s="4" t="n"/>
       <c r="J457" s="3" t="n"/>
+      <c r="K457" s="3" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="4" t="n"/>
@@ -15485,6 +15947,7 @@
       <c r="H458" s="4" t="n"/>
       <c r="I458" s="4" t="n"/>
       <c r="J458" s="3" t="n"/>
+      <c r="K458" s="3" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="4" t="n"/>
@@ -15517,6 +15980,7 @@
       <c r="H459" s="4" t="n"/>
       <c r="I459" s="4" t="n"/>
       <c r="J459" s="3" t="n"/>
+      <c r="K459" s="3" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="4" t="n"/>
@@ -15549,6 +16013,7 @@
       <c r="H460" s="4" t="n"/>
       <c r="I460" s="4" t="n"/>
       <c r="J460" s="3" t="n"/>
+      <c r="K460" s="3" t="n"/>
     </row>
     <row r="461">
       <c r="A461" s="4" t="n"/>
@@ -15581,6 +16046,7 @@
       <c r="H461" s="4" t="n"/>
       <c r="I461" s="4" t="n"/>
       <c r="J461" s="3" t="n"/>
+      <c r="K461" s="3" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="4" t="n"/>
@@ -15613,6 +16079,7 @@
       <c r="H462" s="4" t="n"/>
       <c r="I462" s="4" t="n"/>
       <c r="J462" s="3" t="n"/>
+      <c r="K462" s="3" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="4" t="n"/>
@@ -15645,6 +16112,7 @@
       <c r="H463" s="4" t="n"/>
       <c r="I463" s="4" t="n"/>
       <c r="J463" s="3" t="n"/>
+      <c r="K463" s="3" t="n"/>
     </row>
     <row r="464">
       <c r="A464" s="4" t="n"/>
@@ -15677,6 +16145,7 @@
       <c r="H464" s="4" t="n"/>
       <c r="I464" s="4" t="n"/>
       <c r="J464" s="3" t="n"/>
+      <c r="K464" s="3" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="4" t="n"/>
@@ -15709,6 +16178,7 @@
       <c r="H465" s="4" t="n"/>
       <c r="I465" s="4" t="n"/>
       <c r="J465" s="3" t="n"/>
+      <c r="K465" s="3" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="4" t="n"/>
@@ -15741,6 +16211,7 @@
       <c r="H466" s="4" t="n"/>
       <c r="I466" s="4" t="n"/>
       <c r="J466" s="3" t="n"/>
+      <c r="K466" s="3" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="4" t="n"/>
@@ -15773,6 +16244,7 @@
       <c r="H467" s="4" t="n"/>
       <c r="I467" s="4" t="n"/>
       <c r="J467" s="3" t="n"/>
+      <c r="K467" s="3" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="4" t="n"/>
@@ -15805,6 +16277,7 @@
       <c r="H468" s="4" t="n"/>
       <c r="I468" s="4" t="n"/>
       <c r="J468" s="3" t="n"/>
+      <c r="K468" s="3" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="4" t="n"/>
@@ -15837,6 +16310,7 @@
       <c r="H469" s="4" t="n"/>
       <c r="I469" s="4" t="n"/>
       <c r="J469" s="3" t="n"/>
+      <c r="K469" s="3" t="n"/>
     </row>
     <row r="470">
       <c r="A470" s="4" t="n"/>
@@ -15869,6 +16343,7 @@
       <c r="H470" s="4" t="n"/>
       <c r="I470" s="4" t="n"/>
       <c r="J470" s="3" t="n"/>
+      <c r="K470" s="3" t="n"/>
     </row>
     <row r="471">
       <c r="A471" s="4" t="n"/>
@@ -15901,6 +16376,7 @@
       <c r="H471" s="4" t="n"/>
       <c r="I471" s="4" t="n"/>
       <c r="J471" s="3" t="n"/>
+      <c r="K471" s="3" t="n"/>
     </row>
     <row r="472">
       <c r="A472" s="4" t="n"/>
@@ -15933,6 +16409,7 @@
       <c r="H472" s="4" t="n"/>
       <c r="I472" s="4" t="n"/>
       <c r="J472" s="3" t="n"/>
+      <c r="K472" s="3" t="n"/>
     </row>
     <row r="473">
       <c r="A473" s="4" t="n"/>
@@ -15973,6 +16450,7 @@
           <t>New unit, split from PAL-IS per GSTerr9.</t>
         </is>
       </c>
+      <c r="K473" s="3" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="4" t="n"/>
@@ -16013,6 +16491,7 @@
           <t>Redefined per GSTerr9: previously included Gaza Strip and West Bank (WGSRPD ed. 2 limits); now split into PAL-GZ and PAL-WB.</t>
         </is>
       </c>
+      <c r="K474" s="3" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="4" t="n"/>
@@ -16045,6 +16524,7 @@
       <c r="H475" s="4" t="n"/>
       <c r="I475" s="4" t="n"/>
       <c r="J475" s="3" t="n"/>
+      <c r="K475" s="3" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="4" t="n"/>
@@ -16085,6 +16565,7 @@
           <t>New unit, split from PAL-IS per GSTerr9.</t>
         </is>
       </c>
+      <c r="K476" s="3" t="n"/>
     </row>
     <row r="477">
       <c r="A477" s="4" t="n"/>
@@ -16117,6 +16598,7 @@
       <c r="H477" s="4" t="n"/>
       <c r="I477" s="4" t="n"/>
       <c r="J477" s="3" t="n"/>
+      <c r="K477" s="3" t="n"/>
     </row>
     <row r="478">
       <c r="A478" s="4" t="n"/>
@@ -16149,6 +16631,7 @@
       <c r="H478" s="4" t="n"/>
       <c r="I478" s="4" t="n"/>
       <c r="J478" s="3" t="n"/>
+      <c r="K478" s="3" t="n"/>
     </row>
     <row r="479">
       <c r="A479" s="4" t="n"/>
@@ -16181,6 +16664,7 @@
       <c r="H479" s="4" t="n"/>
       <c r="I479" s="4" t="n"/>
       <c r="J479" s="3" t="n"/>
+      <c r="K479" s="3" t="n"/>
     </row>
     <row r="480">
       <c r="A480" s="4" t="n"/>
@@ -16213,6 +16697,7 @@
       <c r="H480" s="4" t="n"/>
       <c r="I480" s="4" t="n"/>
       <c r="J480" s="3" t="n"/>
+      <c r="K480" s="3" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="4" t="n"/>
@@ -16245,6 +16730,7 @@
       <c r="H481" s="4" t="n"/>
       <c r="I481" s="4" t="n"/>
       <c r="J481" s="3" t="n"/>
+      <c r="K481" s="3" t="n"/>
     </row>
     <row r="482">
       <c r="A482" s="4" t="n"/>
@@ -16277,6 +16763,7 @@
       <c r="H482" s="4" t="n"/>
       <c r="I482" s="4" t="n"/>
       <c r="J482" s="3" t="n"/>
+      <c r="K482" s="3" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="4" t="n"/>
@@ -16309,6 +16796,7 @@
       <c r="H483" s="4" t="n"/>
       <c r="I483" s="4" t="n"/>
       <c r="J483" s="3" t="n"/>
+      <c r="K483" s="3" t="n"/>
     </row>
     <row r="484">
       <c r="A484" s="4" t="n"/>
@@ -16341,6 +16829,7 @@
       <c r="H484" s="4" t="n"/>
       <c r="I484" s="4" t="n"/>
       <c r="J484" s="3" t="n"/>
+      <c r="K484" s="3" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="4" t="n"/>
@@ -16373,6 +16862,7 @@
       <c r="H485" s="4" t="n"/>
       <c r="I485" s="4" t="n"/>
       <c r="J485" s="3" t="n"/>
+      <c r="K485" s="3" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="4" t="n"/>
@@ -16405,6 +16895,7 @@
       <c r="H486" s="4" t="n"/>
       <c r="I486" s="4" t="n"/>
       <c r="J486" s="3" t="n"/>
+      <c r="K486" s="3" t="n"/>
     </row>
     <row r="487">
       <c r="A487" s="4" t="n"/>
@@ -16437,6 +16928,7 @@
       <c r="H487" s="4" t="n"/>
       <c r="I487" s="4" t="n"/>
       <c r="J487" s="3" t="n"/>
+      <c r="K487" s="3" t="n"/>
     </row>
     <row r="488">
       <c r="A488" s="4" t="n"/>
@@ -16469,6 +16961,7 @@
       <c r="H488" s="4" t="n"/>
       <c r="I488" s="4" t="n"/>
       <c r="J488" s="3" t="n"/>
+      <c r="K488" s="3" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="4" t="n"/>
@@ -16501,6 +16994,7 @@
       <c r="H489" s="4" t="n"/>
       <c r="I489" s="4" t="n"/>
       <c r="J489" s="3" t="n"/>
+      <c r="K489" s="3" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="4" t="n"/>
@@ -16533,6 +17027,7 @@
       <c r="H490" s="4" t="n"/>
       <c r="I490" s="4" t="n"/>
       <c r="J490" s="3" t="n"/>
+      <c r="K490" s="3" t="n"/>
     </row>
     <row r="491">
       <c r="A491" s="4" t="n"/>
@@ -16565,6 +17060,7 @@
       <c r="H491" s="4" t="n"/>
       <c r="I491" s="4" t="n"/>
       <c r="J491" s="3" t="n"/>
+      <c r="K491" s="3" t="n"/>
     </row>
     <row r="492">
       <c r="A492" s="4" t="n"/>
@@ -16601,6 +17097,7 @@
       <c r="H492" s="4" t="n"/>
       <c r="I492" s="4" t="n"/>
       <c r="J492" s="3" t="n"/>
+      <c r="K492" s="3" t="n"/>
     </row>
     <row r="493">
       <c r="A493" s="4" t="n"/>
@@ -16637,6 +17134,7 @@
       <c r="H493" s="4" t="n"/>
       <c r="I493" s="4" t="n"/>
       <c r="J493" s="3" t="n"/>
+      <c r="K493" s="3" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="4" t="n"/>
@@ -16669,6 +17167,7 @@
       <c r="H494" s="4" t="n"/>
       <c r="I494" s="4" t="n"/>
       <c r="J494" s="3" t="n"/>
+      <c r="K494" s="3" t="n"/>
     </row>
     <row r="495">
       <c r="A495" s="4" t="n"/>
@@ -16701,6 +17200,7 @@
       <c r="H495" s="4" t="n"/>
       <c r="I495" s="4" t="n"/>
       <c r="J495" s="3" t="n"/>
+      <c r="K495" s="3" t="n"/>
     </row>
     <row r="496">
       <c r="A496" s="4" t="n"/>
@@ -16733,6 +17233,7 @@
       <c r="H496" s="4" t="n"/>
       <c r="I496" s="4" t="n"/>
       <c r="J496" s="3" t="n"/>
+      <c r="K496" s="3" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="4" t="n"/>
@@ -16765,6 +17266,7 @@
       <c r="H497" s="4" t="n"/>
       <c r="I497" s="4" t="n"/>
       <c r="J497" s="3" t="n"/>
+      <c r="K497" s="3" t="n"/>
     </row>
     <row r="498">
       <c r="A498" s="4" t="n"/>
@@ -16797,6 +17299,7 @@
       <c r="H498" s="4" t="n"/>
       <c r="I498" s="4" t="n"/>
       <c r="J498" s="3" t="n"/>
+      <c r="K498" s="3" t="n"/>
     </row>
     <row r="499">
       <c r="A499" s="4" t="n"/>
@@ -16829,6 +17332,7 @@
       <c r="H499" s="4" t="n"/>
       <c r="I499" s="4" t="n"/>
       <c r="J499" s="3" t="n"/>
+      <c r="K499" s="3" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="4" t="n"/>
@@ -16861,6 +17365,7 @@
       <c r="H500" s="4" t="n"/>
       <c r="I500" s="4" t="n"/>
       <c r="J500" s="3" t="n"/>
+      <c r="K500" s="3" t="n"/>
     </row>
     <row r="501">
       <c r="A501" s="4" t="n"/>
@@ -16893,6 +17398,7 @@
       <c r="H501" s="4" t="n"/>
       <c r="I501" s="4" t="n"/>
       <c r="J501" s="3" t="n"/>
+      <c r="K501" s="3" t="n"/>
     </row>
     <row r="502">
       <c r="A502" s="4" t="n"/>
@@ -16925,6 +17431,7 @@
       <c r="H502" s="4" t="n"/>
       <c r="I502" s="4" t="n"/>
       <c r="J502" s="3" t="n"/>
+      <c r="K502" s="3" t="n"/>
     </row>
     <row r="503">
       <c r="A503" s="4" t="n"/>
@@ -16957,6 +17464,7 @@
       <c r="H503" s="4" t="n"/>
       <c r="I503" s="4" t="n"/>
       <c r="J503" s="3" t="n"/>
+      <c r="K503" s="3" t="n"/>
     </row>
     <row r="504">
       <c r="A504" s="4" t="n"/>
@@ -16989,6 +17497,7 @@
       <c r="H504" s="4" t="n"/>
       <c r="I504" s="4" t="n"/>
       <c r="J504" s="3" t="n"/>
+      <c r="K504" s="3" t="n"/>
     </row>
     <row r="505">
       <c r="A505" s="4" t="n"/>
@@ -17025,6 +17534,7 @@
         </is>
       </c>
       <c r="J505" s="3" t="n"/>
+      <c r="K505" s="3" t="n"/>
     </row>
     <row r="506">
       <c r="A506" s="4" t="n"/>
@@ -17057,6 +17567,7 @@
       <c r="H506" s="4" t="n"/>
       <c r="I506" s="4" t="n"/>
       <c r="J506" s="3" t="n"/>
+      <c r="K506" s="3" t="n"/>
     </row>
     <row r="507">
       <c r="A507" s="4" t="n"/>
@@ -17089,6 +17600,7 @@
       <c r="H507" s="4" t="n"/>
       <c r="I507" s="4" t="n"/>
       <c r="J507" s="3" t="n"/>
+      <c r="K507" s="3" t="n"/>
     </row>
     <row r="508">
       <c r="A508" s="4" t="n"/>
@@ -17121,6 +17633,7 @@
       <c r="H508" s="4" t="n"/>
       <c r="I508" s="4" t="n"/>
       <c r="J508" s="3" t="n"/>
+      <c r="K508" s="3" t="n"/>
     </row>
     <row r="509">
       <c r="A509" s="4" t="n"/>
@@ -17153,6 +17666,7 @@
       <c r="H509" s="4" t="n"/>
       <c r="I509" s="4" t="n"/>
       <c r="J509" s="3" t="n"/>
+      <c r="K509" s="3" t="n"/>
     </row>
     <row r="510">
       <c r="A510" s="4" t="n"/>
@@ -17185,6 +17699,7 @@
       <c r="H510" s="4" t="n"/>
       <c r="I510" s="4" t="n"/>
       <c r="J510" s="3" t="n"/>
+      <c r="K510" s="3" t="n"/>
     </row>
     <row r="511">
       <c r="A511" s="4" t="n"/>
@@ -17221,6 +17736,7 @@
           <t>The annotation must be included in the footer: "The PI* code  is adopted here unofficially for Paracel Is. though the ISO does not give them any code as their political status is disputed"</t>
         </is>
       </c>
+      <c r="K511" s="3" t="n"/>
     </row>
     <row r="512">
       <c r="A512" s="4" t="n"/>
@@ -17257,6 +17773,7 @@
           <t>Typographical error in L4 ISOcode, SI is replaced by PI *</t>
         </is>
       </c>
+      <c r="K512" s="3" t="n"/>
     </row>
     <row r="513">
       <c r="A513" s="4" t="n"/>
@@ -17289,6 +17806,7 @@
       <c r="H513" s="4" t="n"/>
       <c r="I513" s="4" t="n"/>
       <c r="J513" s="3" t="n"/>
+      <c r="K513" s="3" t="n"/>
     </row>
     <row r="514">
       <c r="A514" s="4" t="n"/>
@@ -17321,6 +17839,7 @@
       <c r="H514" s="4" t="n"/>
       <c r="I514" s="4" t="n"/>
       <c r="J514" s="3" t="n"/>
+      <c r="K514" s="3" t="n"/>
     </row>
     <row r="515">
       <c r="A515" s="4" t="n"/>
@@ -17353,6 +17872,7 @@
       <c r="H515" s="4" t="n"/>
       <c r="I515" s="4" t="n"/>
       <c r="J515" s="3" t="n"/>
+      <c r="K515" s="3" t="n"/>
     </row>
     <row r="516">
       <c r="A516" s="4" t="n"/>
@@ -17385,6 +17905,7 @@
       <c r="H516" s="4" t="n"/>
       <c r="I516" s="4" t="n"/>
       <c r="J516" s="3" t="n"/>
+      <c r="K516" s="3" t="n"/>
     </row>
     <row r="517">
       <c r="A517" s="4" t="n"/>
@@ -17417,6 +17938,7 @@
       <c r="H517" s="4" t="n"/>
       <c r="I517" s="4" t="n"/>
       <c r="J517" s="3" t="n"/>
+      <c r="K517" s="3" t="n"/>
     </row>
     <row r="518">
       <c r="A518" s="4" t="n"/>
@@ -17449,6 +17971,7 @@
       <c r="H518" s="4" t="n"/>
       <c r="I518" s="4" t="n"/>
       <c r="J518" s="3" t="n"/>
+      <c r="K518" s="3" t="n"/>
     </row>
     <row r="519">
       <c r="A519" s="4" t="n"/>
@@ -17481,6 +18004,7 @@
       <c r="H519" s="4" t="n"/>
       <c r="I519" s="4" t="n"/>
       <c r="J519" s="3" t="n"/>
+      <c r="K519" s="3" t="n"/>
     </row>
     <row r="520">
       <c r="A520" s="4" t="n"/>
@@ -17513,6 +18037,7 @@
       <c r="H520" s="4" t="n"/>
       <c r="I520" s="4" t="n"/>
       <c r="J520" s="3" t="n"/>
+      <c r="K520" s="3" t="n"/>
     </row>
     <row r="521">
       <c r="A521" s="4" t="n"/>
@@ -17545,6 +18070,7 @@
       <c r="H521" s="4" t="n"/>
       <c r="I521" s="4" t="n"/>
       <c r="J521" s="3" t="n"/>
+      <c r="K521" s="3" t="n"/>
     </row>
     <row r="522">
       <c r="A522" s="4" t="n"/>
@@ -17577,6 +18103,7 @@
       <c r="H522" s="4" t="n"/>
       <c r="I522" s="4" t="n"/>
       <c r="J522" s="3" t="n"/>
+      <c r="K522" s="3" t="n"/>
     </row>
     <row r="523">
       <c r="A523" s="4" t="n"/>
@@ -17609,6 +18136,7 @@
       <c r="H523" s="4" t="n"/>
       <c r="I523" s="4" t="n"/>
       <c r="J523" s="3" t="n"/>
+      <c r="K523" s="3" t="n"/>
     </row>
     <row r="524">
       <c r="A524" s="4" t="n"/>
@@ -17641,6 +18169,7 @@
       <c r="H524" s="4" t="n"/>
       <c r="I524" s="4" t="n"/>
       <c r="J524" s="3" t="n"/>
+      <c r="K524" s="3" t="n"/>
     </row>
     <row r="525">
       <c r="A525" s="4" t="n"/>
@@ -17673,6 +18202,7 @@
       <c r="H525" s="4" t="n"/>
       <c r="I525" s="4" t="n"/>
       <c r="J525" s="3" t="n"/>
+      <c r="K525" s="3" t="n"/>
     </row>
     <row r="526">
       <c r="A526" s="4" t="n"/>
@@ -17705,6 +18235,7 @@
       <c r="H526" s="4" t="n"/>
       <c r="I526" s="4" t="n"/>
       <c r="J526" s="3" t="n"/>
+      <c r="K526" s="3" t="n"/>
     </row>
     <row r="527">
       <c r="A527" s="4" t="n"/>
@@ -17737,6 +18268,7 @@
       <c r="H527" s="4" t="n"/>
       <c r="I527" s="4" t="n"/>
       <c r="J527" s="3" t="n"/>
+      <c r="K527" s="3" t="n"/>
     </row>
     <row r="528">
       <c r="A528" s="4" t="n"/>
@@ -17769,6 +18301,7 @@
       <c r="H528" s="4" t="n"/>
       <c r="I528" s="4" t="n"/>
       <c r="J528" s="3" t="n"/>
+      <c r="K528" s="3" t="n"/>
     </row>
     <row r="529">
       <c r="A529" s="4" t="n"/>
@@ -17801,6 +18334,7 @@
       <c r="H529" s="4" t="n"/>
       <c r="I529" s="4" t="n"/>
       <c r="J529" s="3" t="n"/>
+      <c r="K529" s="3" t="n"/>
     </row>
     <row r="530">
       <c r="A530" s="4" t="n"/>
@@ -17833,6 +18367,7 @@
       <c r="H530" s="4" t="n"/>
       <c r="I530" s="4" t="n"/>
       <c r="J530" s="3" t="n"/>
+      <c r="K530" s="3" t="n"/>
     </row>
     <row r="531">
       <c r="A531" s="4" t="n"/>
@@ -17865,6 +18400,7 @@
       <c r="H531" s="4" t="n"/>
       <c r="I531" s="4" t="n"/>
       <c r="J531" s="3" t="n"/>
+      <c r="K531" s="3" t="n"/>
     </row>
     <row r="532">
       <c r="A532" s="4" t="n"/>
@@ -17901,6 +18437,7 @@
         </is>
       </c>
       <c r="J532" s="3" t="n"/>
+      <c r="K532" s="3" t="n"/>
     </row>
     <row r="533">
       <c r="A533" s="4" t="n"/>
@@ -17933,6 +18470,7 @@
       <c r="H533" s="4" t="n"/>
       <c r="I533" s="4" t="n"/>
       <c r="J533" s="3" t="n"/>
+      <c r="K533" s="3" t="n"/>
     </row>
     <row r="534">
       <c r="A534" s="4" t="inlineStr">
@@ -17981,6 +18519,7 @@
           <t>Country area reduced by the creation of a South Sudan, new Level 4 Unit created, old Level 4 unid (SUD-OO) deprecated</t>
         </is>
       </c>
+      <c r="K534" s="3" t="n"/>
     </row>
     <row r="535">
       <c r="A535" s="4" t="inlineStr">
@@ -18029,6 +18568,7 @@
           <t>New country, new Level 4 Unit</t>
         </is>
       </c>
+      <c r="K535" s="3" t="n"/>
     </row>
     <row r="536">
       <c r="A536" s="4" t="n"/>
@@ -18061,6 +18601,7 @@
       <c r="H536" s="4" t="n"/>
       <c r="I536" s="4" t="n"/>
       <c r="J536" s="3" t="n"/>
+      <c r="K536" s="3" t="n"/>
     </row>
     <row r="537">
       <c r="A537" s="4" t="n"/>
@@ -18093,6 +18634,7 @@
       <c r="H537" s="4" t="n"/>
       <c r="I537" s="4" t="n"/>
       <c r="J537" s="3" t="n"/>
+      <c r="K537" s="3" t="n"/>
     </row>
     <row r="538">
       <c r="A538" s="4" t="n"/>
@@ -18125,6 +18667,7 @@
       <c r="H538" s="4" t="n"/>
       <c r="I538" s="4" t="n"/>
       <c r="J538" s="3" t="n"/>
+      <c r="K538" s="3" t="n"/>
     </row>
     <row r="539">
       <c r="A539" s="4" t="n"/>
@@ -18157,6 +18700,7 @@
       <c r="H539" s="4" t="n"/>
       <c r="I539" s="4" t="n"/>
       <c r="J539" s="3" t="n"/>
+      <c r="K539" s="3" t="n"/>
     </row>
     <row r="540">
       <c r="A540" s="4" t="n"/>
@@ -18189,6 +18733,7 @@
       <c r="H540" s="4" t="n"/>
       <c r="I540" s="4" t="n"/>
       <c r="J540" s="3" t="n"/>
+      <c r="K540" s="3" t="n"/>
     </row>
     <row r="541">
       <c r="A541" s="4" t="n"/>
@@ -18221,6 +18766,7 @@
       <c r="H541" s="4" t="n"/>
       <c r="I541" s="4" t="n"/>
       <c r="J541" s="3" t="n"/>
+      <c r="K541" s="3" t="n"/>
     </row>
     <row r="542">
       <c r="A542" s="4" t="n"/>
@@ -18253,6 +18799,7 @@
       <c r="H542" s="4" t="n"/>
       <c r="I542" s="4" t="n"/>
       <c r="J542" s="3" t="n"/>
+      <c r="K542" s="3" t="n"/>
     </row>
     <row r="543">
       <c r="A543" s="4" t="n"/>
@@ -18293,6 +18840,7 @@
           <t>https://en.wikipedia.org/wiki/Eswatini</t>
         </is>
       </c>
+      <c r="K543" s="3" t="n"/>
     </row>
     <row r="544">
       <c r="A544" s="4" t="n"/>
@@ -18325,6 +18873,7 @@
       <c r="H544" s="4" t="n"/>
       <c r="I544" s="4" t="n"/>
       <c r="J544" s="3" t="n"/>
+      <c r="K544" s="3" t="n"/>
     </row>
     <row r="545">
       <c r="A545" s="4" t="n"/>
@@ -18357,6 +18906,7 @@
       <c r="H545" s="4" t="n"/>
       <c r="I545" s="4" t="n"/>
       <c r="J545" s="3" t="n"/>
+      <c r="K545" s="3" t="n"/>
     </row>
     <row r="546">
       <c r="A546" s="4" t="n"/>
@@ -18389,6 +18939,7 @@
       <c r="H546" s="4" t="n"/>
       <c r="I546" s="4" t="n"/>
       <c r="J546" s="3" t="n"/>
+      <c r="K546" s="3" t="n"/>
     </row>
     <row r="547">
       <c r="A547" s="4" t="n"/>
@@ -18425,6 +18976,7 @@
         </is>
       </c>
       <c r="J547" s="3" t="n"/>
+      <c r="K547" s="3" t="n"/>
     </row>
     <row r="548">
       <c r="A548" s="4" t="n"/>
@@ -18457,6 +19009,7 @@
       <c r="H548" s="4" t="n"/>
       <c r="I548" s="4" t="n"/>
       <c r="J548" s="3" t="n"/>
+      <c r="K548" s="3" t="n"/>
     </row>
     <row r="549">
       <c r="A549" s="4" t="n"/>
@@ -18501,6 +19054,7 @@
           <t>The cartographic limits of the absajia region are discontinuous in google maps and the country to which it corresponds is not labeled. Does this region correspond to Georgia?</t>
         </is>
       </c>
+      <c r="K549" s="3" t="n"/>
     </row>
     <row r="550">
       <c r="A550" s="4" t="n"/>
@@ -18533,6 +19087,7 @@
       <c r="H550" s="4" t="n"/>
       <c r="I550" s="4" t="n"/>
       <c r="J550" s="3" t="n"/>
+      <c r="K550" s="3" t="n"/>
     </row>
     <row r="551">
       <c r="A551" s="4" t="n"/>
@@ -18565,6 +19120,7 @@
       <c r="H551" s="4" t="n"/>
       <c r="I551" s="4" t="n"/>
       <c r="J551" s="3" t="n"/>
+      <c r="K551" s="3" t="n"/>
     </row>
     <row r="552">
       <c r="A552" s="4" t="n"/>
@@ -18597,6 +19153,7 @@
       <c r="H552" s="4" t="n"/>
       <c r="I552" s="4" t="n"/>
       <c r="J552" s="3" t="n"/>
+      <c r="K552" s="3" t="n"/>
     </row>
     <row r="553">
       <c r="A553" s="4" t="n"/>
@@ -18633,6 +19190,7 @@
         </is>
       </c>
       <c r="J553" s="3" t="n"/>
+      <c r="K553" s="3" t="n"/>
     </row>
     <row r="554">
       <c r="A554" s="4" t="n"/>
@@ -18665,6 +19223,7 @@
       <c r="H554" s="4" t="n"/>
       <c r="I554" s="4" t="n"/>
       <c r="J554" s="3" t="n"/>
+      <c r="K554" s="3" t="n"/>
     </row>
     <row r="555">
       <c r="A555" s="4" t="n"/>
@@ -18707,6 +19266,7 @@
 Nagorno-Karabakh, is a region disputed between Armenia and Azerbaijan for decades. The Republic of Artsakh controls the de facto self-governed Nagorno-Karabakh even though it is legally part of Azerbaijan.</t>
         </is>
       </c>
+      <c r="K555" s="3" t="n"/>
     </row>
     <row r="556">
       <c r="A556" s="4" t="n"/>
@@ -18739,6 +19299,7 @@
       <c r="H556" s="4" t="n"/>
       <c r="I556" s="4" t="n"/>
       <c r="J556" s="3" t="n"/>
+      <c r="K556" s="3" t="n"/>
     </row>
     <row r="557">
       <c r="A557" s="4" t="n"/>
@@ -18771,6 +19332,7 @@
       <c r="H557" s="4" t="n"/>
       <c r="I557" s="4" t="n"/>
       <c r="J557" s="3" t="n"/>
+      <c r="K557" s="3" t="n"/>
     </row>
     <row r="558">
       <c r="A558" s="4" t="n"/>
@@ -18803,6 +19365,7 @@
       <c r="H558" s="4" t="n"/>
       <c r="I558" s="4" t="n"/>
       <c r="J558" s="3" t="n"/>
+      <c r="K558" s="3" t="n"/>
     </row>
     <row r="559">
       <c r="A559" s="4" t="n"/>
@@ -18835,6 +19398,7 @@
       <c r="H559" s="4" t="n"/>
       <c r="I559" s="4" t="n"/>
       <c r="J559" s="3" t="n"/>
+      <c r="K559" s="3" t="n"/>
     </row>
     <row r="560">
       <c r="A560" s="4" t="n"/>
@@ -18867,6 +19431,7 @@
       <c r="H560" s="4" t="n"/>
       <c r="I560" s="4" t="n"/>
       <c r="J560" s="3" t="n"/>
+      <c r="K560" s="3" t="n"/>
     </row>
     <row r="561">
       <c r="A561" s="4" t="n"/>
@@ -18899,6 +19464,7 @@
       <c r="H561" s="4" t="n"/>
       <c r="I561" s="4" t="n"/>
       <c r="J561" s="3" t="n"/>
+      <c r="K561" s="3" t="n"/>
     </row>
     <row r="562">
       <c r="A562" s="4" t="n"/>
@@ -18931,6 +19497,7 @@
       <c r="H562" s="4" t="n"/>
       <c r="I562" s="4" t="n"/>
       <c r="J562" s="3" t="n"/>
+      <c r="K562" s="3" t="n"/>
     </row>
     <row r="563">
       <c r="A563" s="4" t="n"/>
@@ -18963,6 +19530,7 @@
       <c r="H563" s="4" t="n"/>
       <c r="I563" s="4" t="n"/>
       <c r="J563" s="3" t="n"/>
+      <c r="K563" s="3" t="n"/>
     </row>
     <row r="564">
       <c r="A564" s="4" t="n"/>
@@ -18995,6 +19563,7 @@
       <c r="H564" s="4" t="n"/>
       <c r="I564" s="4" t="n"/>
       <c r="J564" s="3" t="n"/>
+      <c r="K564" s="3" t="n"/>
     </row>
     <row r="565">
       <c r="A565" s="4" t="n"/>
@@ -19027,6 +19596,7 @@
       <c r="H565" s="4" t="n"/>
       <c r="I565" s="4" t="n"/>
       <c r="J565" s="3" t="n"/>
+      <c r="K565" s="3" t="n"/>
     </row>
     <row r="566">
       <c r="A566" s="4" t="n"/>
@@ -19059,6 +19629,7 @@
       <c r="H566" s="4" t="n"/>
       <c r="I566" s="4" t="n"/>
       <c r="J566" s="3" t="n"/>
+      <c r="K566" s="3" t="n"/>
     </row>
     <row r="567">
       <c r="A567" s="4" t="n"/>
@@ -19091,6 +19662,7 @@
       <c r="H567" s="4" t="n"/>
       <c r="I567" s="4" t="n"/>
       <c r="J567" s="3" t="n"/>
+      <c r="K567" s="3" t="n"/>
     </row>
     <row r="568">
       <c r="A568" s="4" t="n"/>
@@ -19123,6 +19695,7 @@
       <c r="H568" s="4" t="n"/>
       <c r="I568" s="4" t="n"/>
       <c r="J568" s="3" t="n"/>
+      <c r="K568" s="3" t="n"/>
     </row>
     <row r="569">
       <c r="A569" s="4" t="n"/>
@@ -19159,6 +19732,7 @@
       <c r="H569" s="4" t="n"/>
       <c r="I569" s="4" t="n"/>
       <c r="J569" s="3" t="n"/>
+      <c r="K569" s="3" t="n"/>
     </row>
     <row r="570">
       <c r="A570" s="4" t="n"/>
@@ -19191,6 +19765,7 @@
       <c r="H570" s="4" t="n"/>
       <c r="I570" s="4" t="n"/>
       <c r="J570" s="3" t="n"/>
+      <c r="K570" s="3" t="n"/>
     </row>
     <row r="571">
       <c r="A571" s="4" t="n"/>
@@ -19227,6 +19802,7 @@
       <c r="H571" s="4" t="n"/>
       <c r="I571" s="4" t="n"/>
       <c r="J571" s="3" t="n"/>
+      <c r="K571" s="3" t="n"/>
     </row>
     <row r="572">
       <c r="A572" s="4" t="n"/>
@@ -19259,6 +19835,7 @@
       <c r="H572" s="4" t="n"/>
       <c r="I572" s="4" t="n"/>
       <c r="J572" s="3" t="n"/>
+      <c r="K572" s="3" t="n"/>
     </row>
     <row r="573">
       <c r="A573" s="4" t="n"/>
@@ -19291,6 +19868,7 @@
       <c r="H573" s="4" t="n"/>
       <c r="I573" s="4" t="n"/>
       <c r="J573" s="3" t="n"/>
+      <c r="K573" s="3" t="n"/>
     </row>
     <row r="574">
       <c r="A574" s="4" t="n"/>
@@ -19323,6 +19901,7 @@
       <c r="H574" s="4" t="n"/>
       <c r="I574" s="4" t="n"/>
       <c r="J574" s="3" t="n"/>
+      <c r="K574" s="3" t="n"/>
     </row>
     <row r="575">
       <c r="A575" s="4" t="n"/>
@@ -19355,6 +19934,7 @@
       <c r="H575" s="4" t="n"/>
       <c r="I575" s="4" t="n"/>
       <c r="J575" s="3" t="n"/>
+      <c r="K575" s="3" t="n"/>
     </row>
     <row r="576">
       <c r="A576" s="4" t="n"/>
@@ -19387,6 +19967,7 @@
       <c r="H576" s="4" t="n"/>
       <c r="I576" s="4" t="n"/>
       <c r="J576" s="3" t="n"/>
+      <c r="K576" s="3" t="n"/>
     </row>
     <row r="577">
       <c r="A577" s="4" t="n"/>
@@ -19419,6 +20000,7 @@
       <c r="H577" s="4" t="n"/>
       <c r="I577" s="4" t="n"/>
       <c r="J577" s="3" t="n"/>
+      <c r="K577" s="3" t="n"/>
     </row>
     <row r="578">
       <c r="A578" s="4" t="n"/>
@@ -19451,6 +20033,7 @@
       <c r="H578" s="4" t="n"/>
       <c r="I578" s="4" t="n"/>
       <c r="J578" s="3" t="n"/>
+      <c r="K578" s="3" t="n"/>
     </row>
     <row r="579">
       <c r="A579" s="4" t="n"/>
@@ -19483,6 +20066,7 @@
       <c r="H579" s="4" t="n"/>
       <c r="I579" s="4" t="n"/>
       <c r="J579" s="3" t="n"/>
+      <c r="K579" s="3" t="n"/>
     </row>
     <row r="580">
       <c r="A580" s="4" t="n"/>
@@ -19515,6 +20099,7 @@
       <c r="H580" s="4" t="n"/>
       <c r="I580" s="4" t="n"/>
       <c r="J580" s="3" t="n"/>
+      <c r="K580" s="3" t="n"/>
     </row>
     <row r="581">
       <c r="A581" s="4" t="n"/>
@@ -19547,6 +20132,7 @@
       <c r="H581" s="4" t="n"/>
       <c r="I581" s="4" t="n"/>
       <c r="J581" s="3" t="n"/>
+      <c r="K581" s="3" t="n"/>
     </row>
     <row r="582">
       <c r="A582" s="4" t="n"/>
@@ -19579,6 +20165,7 @@
       <c r="H582" s="4" t="n"/>
       <c r="I582" s="4" t="n"/>
       <c r="J582" s="3" t="n"/>
+      <c r="K582" s="3" t="n"/>
     </row>
     <row r="583">
       <c r="A583" s="4" t="n"/>
@@ -19611,6 +20198,7 @@
       <c r="H583" s="4" t="n"/>
       <c r="I583" s="4" t="n"/>
       <c r="J583" s="3" t="n"/>
+      <c r="K583" s="3" t="n"/>
     </row>
     <row r="584">
       <c r="A584" s="4" t="n"/>
@@ -19643,6 +20231,7 @@
       <c r="H584" s="4" t="n"/>
       <c r="I584" s="4" t="n"/>
       <c r="J584" s="3" t="n"/>
+      <c r="K584" s="3" t="n"/>
     </row>
     <row r="585">
       <c r="A585" s="4" t="n"/>
@@ -19675,6 +20264,7 @@
       <c r="H585" s="4" t="n"/>
       <c r="I585" s="4" t="n"/>
       <c r="J585" s="3" t="n"/>
+      <c r="K585" s="3" t="n"/>
     </row>
     <row r="586">
       <c r="A586" s="4" t="n"/>
@@ -19707,6 +20297,7 @@
       <c r="H586" s="4" t="n"/>
       <c r="I586" s="4" t="n"/>
       <c r="J586" s="3" t="n"/>
+      <c r="K586" s="3" t="n"/>
     </row>
     <row r="587">
       <c r="A587" s="4" t="n"/>
@@ -19739,6 +20330,7 @@
       <c r="H587" s="4" t="n"/>
       <c r="I587" s="4" t="n"/>
       <c r="J587" s="3" t="n"/>
+      <c r="K587" s="3" t="n"/>
     </row>
     <row r="588">
       <c r="A588" s="4" t="n"/>
@@ -19771,6 +20363,7 @@
       <c r="H588" s="4" t="n"/>
       <c r="I588" s="4" t="n"/>
       <c r="J588" s="3" t="n"/>
+      <c r="K588" s="3" t="n"/>
     </row>
     <row r="589">
       <c r="A589" s="4" t="n"/>
@@ -19803,6 +20396,7 @@
       <c r="H589" s="4" t="n"/>
       <c r="I589" s="4" t="n"/>
       <c r="J589" s="3" t="n"/>
+      <c r="K589" s="3" t="n"/>
     </row>
     <row r="590">
       <c r="A590" s="4" t="n"/>
@@ -19835,6 +20429,7 @@
       <c r="H590" s="4" t="n"/>
       <c r="I590" s="4" t="n"/>
       <c r="J590" s="3" t="n"/>
+      <c r="K590" s="3" t="n"/>
     </row>
     <row r="591">
       <c r="A591" s="4" t="n"/>
@@ -19867,6 +20462,7 @@
       <c r="H591" s="4" t="n"/>
       <c r="I591" s="4" t="n"/>
       <c r="J591" s="3" t="n"/>
+      <c r="K591" s="3" t="n"/>
     </row>
     <row r="592">
       <c r="A592" s="4" t="n"/>
@@ -19899,6 +20495,7 @@
       <c r="H592" s="4" t="n"/>
       <c r="I592" s="4" t="n"/>
       <c r="J592" s="3" t="n"/>
+      <c r="K592" s="3" t="n"/>
     </row>
     <row r="593">
       <c r="A593" s="4" t="n"/>
@@ -19931,6 +20528,7 @@
       <c r="H593" s="4" t="n"/>
       <c r="I593" s="4" t="n"/>
       <c r="J593" s="3" t="n"/>
+      <c r="K593" s="3" t="n"/>
     </row>
     <row r="594">
       <c r="A594" s="4" t="n"/>
@@ -19963,6 +20561,7 @@
       <c r="H594" s="4" t="n"/>
       <c r="I594" s="4" t="n"/>
       <c r="J594" s="3" t="n"/>
+      <c r="K594" s="3" t="n"/>
     </row>
     <row r="595">
       <c r="A595" s="4" t="n"/>
@@ -19995,6 +20594,7 @@
       <c r="H595" s="4" t="n"/>
       <c r="I595" s="4" t="n"/>
       <c r="J595" s="3" t="n"/>
+      <c r="K595" s="3" t="n"/>
     </row>
     <row r="596">
       <c r="A596" s="4" t="n"/>
@@ -20027,6 +20627,7 @@
       <c r="H596" s="4" t="n"/>
       <c r="I596" s="4" t="n"/>
       <c r="J596" s="3" t="n"/>
+      <c r="K596" s="3" t="n"/>
     </row>
     <row r="597">
       <c r="A597" s="4" t="n"/>
@@ -20059,6 +20660,7 @@
       <c r="H597" s="4" t="n"/>
       <c r="I597" s="4" t="n"/>
       <c r="J597" s="3" t="n"/>
+      <c r="K597" s="3" t="n"/>
     </row>
     <row r="598">
       <c r="A598" s="4" t="n"/>
@@ -20091,6 +20693,7 @@
       <c r="H598" s="4" t="n"/>
       <c r="I598" s="4" t="n"/>
       <c r="J598" s="3" t="n"/>
+      <c r="K598" s="3" t="n"/>
     </row>
     <row r="599">
       <c r="A599" s="4" t="n"/>
@@ -20123,6 +20726,7 @@
       <c r="H599" s="4" t="n"/>
       <c r="I599" s="4" t="n"/>
       <c r="J599" s="3" t="n"/>
+      <c r="K599" s="3" t="n"/>
     </row>
     <row r="600">
       <c r="A600" s="4" t="n"/>
@@ -20163,6 +20767,7 @@
           <t>https://en.wikipedia.org/wiki/Saint_Vincent_and_the_Grenadines</t>
         </is>
       </c>
+      <c r="K600" s="3" t="n"/>
     </row>
     <row r="601">
       <c r="A601" s="4" t="n"/>
@@ -20195,6 +20800,7 @@
       <c r="H601" s="4" t="n"/>
       <c r="I601" s="4" t="n"/>
       <c r="J601" s="3" t="n"/>
+      <c r="K601" s="3" t="n"/>
     </row>
     <row r="602">
       <c r="A602" s="4" t="n"/>
@@ -20241,6 +20847,7 @@
 Name for unit "WIN-SV" Changed to "St. Vincent and the Grenadines" in the working documents. The use of "St." for "·Saint" is maintained flowing the rule stated on page 9 of the 2nd Ed. of the standard</t>
         </is>
       </c>
+      <c r="K602" s="3" t="n"/>
     </row>
     <row r="603">
       <c r="A603" s="4" t="n"/>
@@ -20273,6 +20880,7 @@
       <c r="H603" s="4" t="n"/>
       <c r="I603" s="4" t="n"/>
       <c r="J603" s="3" t="n"/>
+      <c r="K603" s="3" t="n"/>
     </row>
     <row r="604">
       <c r="A604" s="4" t="n"/>
@@ -20305,6 +20913,7 @@
       <c r="H604" s="4" t="n"/>
       <c r="I604" s="4" t="n"/>
       <c r="J604" s="3" t="n"/>
+      <c r="K604" s="3" t="n"/>
     </row>
     <row r="605">
       <c r="A605" s="4" t="n"/>
@@ -20337,6 +20946,7 @@
       <c r="H605" s="4" t="n"/>
       <c r="I605" s="4" t="n"/>
       <c r="J605" s="3" t="n"/>
+      <c r="K605" s="3" t="n"/>
     </row>
     <row r="606">
       <c r="A606" s="4" t="n"/>
@@ -20369,6 +20979,7 @@
       <c r="H606" s="4" t="n"/>
       <c r="I606" s="4" t="n"/>
       <c r="J606" s="3" t="n"/>
+      <c r="K606" s="3" t="n"/>
     </row>
     <row r="607">
       <c r="A607" s="4" t="n"/>
@@ -20401,6 +21012,7 @@
       <c r="H607" s="4" t="n"/>
       <c r="I607" s="4" t="n"/>
       <c r="J607" s="3" t="n"/>
+      <c r="K607" s="3" t="n"/>
     </row>
     <row r="608">
       <c r="A608" s="4" t="n"/>
@@ -20433,6 +21045,7 @@
       <c r="H608" s="4" t="n"/>
       <c r="I608" s="4" t="n"/>
       <c r="J608" s="3" t="n"/>
+      <c r="K608" s="3" t="n"/>
     </row>
     <row r="609">
       <c r="A609" s="4" t="n"/>
@@ -20465,6 +21078,7 @@
       <c r="H609" s="4" t="n"/>
       <c r="I609" s="4" t="n"/>
       <c r="J609" s="3" t="n"/>
+      <c r="K609" s="3" t="n"/>
     </row>
     <row r="610">
       <c r="A610" s="4" t="n"/>
@@ -20501,6 +21115,7 @@
         </is>
       </c>
       <c r="J610" s="3" t="n"/>
+      <c r="K610" s="3" t="n"/>
     </row>
     <row r="611">
       <c r="A611" s="4" t="n"/>
@@ -20537,6 +21152,7 @@
         </is>
       </c>
       <c r="J611" s="3" t="n"/>
+      <c r="K611" s="3" t="n"/>
     </row>
     <row r="612">
       <c r="A612" s="4" t="n"/>
@@ -20569,6 +21185,7 @@
       <c r="H612" s="4" t="n"/>
       <c r="I612" s="4" t="n"/>
       <c r="J612" s="3" t="n"/>
+      <c r="K612" s="3" t="n"/>
     </row>
     <row r="613">
       <c r="A613" s="4" t="n"/>
@@ -20609,6 +21226,7 @@
         </is>
       </c>
       <c r="J613" s="3" t="n"/>
+      <c r="K613" s="3" t="n"/>
     </row>
     <row r="614">
       <c r="A614" s="4" t="n"/>
@@ -20641,6 +21259,7 @@
       <c r="H614" s="4" t="n"/>
       <c r="I614" s="4" t="n"/>
       <c r="J614" s="3" t="n"/>
+      <c r="K614" s="3" t="n"/>
     </row>
     <row r="615">
       <c r="A615" s="4" t="n"/>
@@ -20673,6 +21292,7 @@
       <c r="H615" s="4" t="n"/>
       <c r="I615" s="4" t="n"/>
       <c r="J615" s="3" t="n"/>
+      <c r="K615" s="3" t="n"/>
     </row>
     <row r="616">
       <c r="A616" s="4" t="n"/>
@@ -20713,6 +21333,7 @@
         </is>
       </c>
       <c r="J616" s="3" t="n"/>
+      <c r="K616" s="3" t="n"/>
     </row>
     <row r="617">
       <c r="A617" s="4" t="n"/>
@@ -20753,6 +21374,7 @@
         </is>
       </c>
       <c r="J617" s="3" t="n"/>
+      <c r="K617" s="3" t="n"/>
     </row>
     <row r="618">
       <c r="A618" s="4" t="n"/>
@@ -20797,6 +21419,7 @@
           <t>I agree. That implies the creation of a new level 4 unit and the modification of the limits of unit TARAPACÁ 85 CLN-TA [CL]</t>
         </is>
       </c>
+      <c r="K618" s="3" t="n"/>
     </row>
     <row r="619">
       <c r="A619" s="4" t="inlineStr">
@@ -20841,6 +21464,7 @@
         </is>
       </c>
       <c r="J619" s="3" t="n"/>
+      <c r="K619" s="3" t="n"/>
     </row>
     <row r="620">
       <c r="A620" s="4" t="n"/>
@@ -20853,6 +21477,7 @@
       <c r="H620" s="4" t="n"/>
       <c r="I620" s="4" t="n"/>
       <c r="J620" s="3" t="n"/>
+      <c r="K620" s="3" t="n"/>
     </row>
     <row r="621">
       <c r="A621" s="4" t="n"/>
@@ -20865,6 +21490,7 @@
       <c r="H621" s="4" t="n"/>
       <c r="I621" s="4" t="n"/>
       <c r="J621" s="3" t="n"/>
+      <c r="K621" s="3" t="n"/>
     </row>
     <row r="622">
       <c r="A622" s="4" t="n"/>
@@ -20877,6 +21503,7 @@
       <c r="H622" s="4" t="n"/>
       <c r="I622" s="4" t="n"/>
       <c r="J622" s="3" t="n"/>
+      <c r="K622" s="3" t="n"/>
     </row>
     <row r="623">
       <c r="A623" s="4" t="n"/>
@@ -20889,6 +21516,7 @@
       <c r="H623" s="4" t="n"/>
       <c r="I623" s="4" t="n"/>
       <c r="J623" s="3" t="n"/>
+      <c r="K623" s="3" t="n"/>
     </row>
     <row r="624">
       <c r="A624" s="4" t="n"/>
@@ -20901,6 +21529,7 @@
       <c r="H624" s="4" t="n"/>
       <c r="I624" s="4" t="n"/>
       <c r="J624" s="3" t="n"/>
+      <c r="K624" s="3" t="n"/>
     </row>
     <row r="625">
       <c r="A625" s="4" t="n"/>
@@ -20913,6 +21542,7 @@
       <c r="H625" s="4" t="n"/>
       <c r="I625" s="4" t="n"/>
       <c r="J625" s="3" t="n"/>
+      <c r="K625" s="3" t="n"/>
     </row>
     <row r="626">
       <c r="A626" s="4" t="n"/>
@@ -20925,6 +21555,7 @@
       <c r="H626" s="4" t="n"/>
       <c r="I626" s="4" t="n"/>
       <c r="J626" s="3" t="n"/>
+      <c r="K626" s="3" t="n"/>
     </row>
     <row r="627">
       <c r="A627" s="4" t="n"/>
@@ -20937,6 +21568,7 @@
       <c r="H627" s="4" t="n"/>
       <c r="I627" s="4" t="n"/>
       <c r="J627" s="3" t="n"/>
+      <c r="K627" s="3" t="n"/>
     </row>
     <row r="628">
       <c r="A628" s="4" t="n"/>
@@ -20949,6 +21581,7 @@
       <c r="H628" s="4" t="n"/>
       <c r="I628" s="4" t="n"/>
       <c r="J628" s="3" t="n"/>
+      <c r="K628" s="3" t="n"/>
     </row>
     <row r="629">
       <c r="A629" s="4" t="n"/>
@@ -20961,6 +21594,7 @@
       <c r="H629" s="4" t="n"/>
       <c r="I629" s="4" t="n"/>
       <c r="J629" s="3" t="n"/>
+      <c r="K629" s="3" t="n"/>
     </row>
     <row r="630">
       <c r="A630" s="4" t="n"/>
@@ -20973,6 +21607,7 @@
       <c r="H630" s="4" t="n"/>
       <c r="I630" s="4" t="n"/>
       <c r="J630" s="3" t="n"/>
+      <c r="K630" s="3" t="n"/>
     </row>
     <row r="631">
       <c r="A631" s="4" t="n"/>
@@ -20985,6 +21620,7 @@
       <c r="H631" s="4" t="n"/>
       <c r="I631" s="4" t="n"/>
       <c r="J631" s="3" t="n"/>
+      <c r="K631" s="3" t="n"/>
     </row>
     <row r="632">
       <c r="A632" s="4" t="n"/>
@@ -20997,6 +21633,7 @@
       <c r="H632" s="4" t="n"/>
       <c r="I632" s="4" t="n"/>
       <c r="J632" s="3" t="n"/>
+      <c r="K632" s="3" t="n"/>
     </row>
     <row r="633">
       <c r="A633" s="4" t="n"/>
@@ -21009,6 +21646,7 @@
       <c r="H633" s="4" t="n"/>
       <c r="I633" s="4" t="n"/>
       <c r="J633" s="3" t="n"/>
+      <c r="K633" s="3" t="n"/>
     </row>
     <row r="634">
       <c r="A634" s="4" t="n"/>
@@ -21021,6 +21659,7 @@
       <c r="H634" s="4" t="n"/>
       <c r="I634" s="4" t="n"/>
       <c r="J634" s="3" t="n"/>
+      <c r="K634" s="3" t="n"/>
     </row>
     <row r="635">
       <c r="A635" s="4" t="n"/>
@@ -21033,6 +21672,7 @@
       <c r="H635" s="4" t="n"/>
       <c r="I635" s="4" t="n"/>
       <c r="J635" s="3" t="n"/>
+      <c r="K635" s="3" t="n"/>
     </row>
     <row r="636">
       <c r="A636" s="4" t="n"/>
@@ -21045,6 +21685,7 @@
       <c r="H636" s="4" t="n"/>
       <c r="I636" s="4" t="n"/>
       <c r="J636" s="3" t="n"/>
+      <c r="K636" s="3" t="n"/>
     </row>
     <row r="637">
       <c r="A637" s="4" t="n"/>
@@ -21057,6 +21698,7 @@
       <c r="H637" s="4" t="n"/>
       <c r="I637" s="4" t="n"/>
       <c r="J637" s="3" t="n"/>
+      <c r="K637" s="3" t="n"/>
     </row>
     <row r="638">
       <c r="A638" s="4" t="n"/>
@@ -21069,6 +21711,7 @@
       <c r="H638" s="4" t="n"/>
       <c r="I638" s="4" t="n"/>
       <c r="J638" s="3" t="n"/>
+      <c r="K638" s="3" t="n"/>
     </row>
     <row r="639">
       <c r="A639" s="4" t="n"/>
@@ -21081,6 +21724,7 @@
       <c r="H639" s="4" t="n"/>
       <c r="I639" s="4" t="n"/>
       <c r="J639" s="3" t="n"/>
+      <c r="K639" s="3" t="n"/>
     </row>
     <row r="640">
       <c r="A640" s="4" t="n"/>
@@ -21093,6 +21737,7 @@
       <c r="H640" s="4" t="n"/>
       <c r="I640" s="4" t="n"/>
       <c r="J640" s="3" t="n"/>
+      <c r="K640" s="3" t="n"/>
     </row>
     <row r="641">
       <c r="A641" s="4" t="n"/>
@@ -21105,6 +21750,7 @@
       <c r="H641" s="4" t="n"/>
       <c r="I641" s="4" t="n"/>
       <c r="J641" s="3" t="n"/>
+      <c r="K641" s="3" t="n"/>
     </row>
     <row r="642">
       <c r="A642" s="4" t="n"/>
@@ -21117,6 +21763,7 @@
       <c r="H642" s="4" t="n"/>
       <c r="I642" s="4" t="n"/>
       <c r="J642" s="3" t="n"/>
+      <c r="K642" s="3" t="n"/>
     </row>
     <row r="643">
       <c r="A643" s="4" t="n"/>
@@ -21129,6 +21776,7 @@
       <c r="H643" s="4" t="n"/>
       <c r="I643" s="4" t="n"/>
       <c r="J643" s="3" t="n"/>
+      <c r="K643" s="3" t="n"/>
     </row>
     <row r="644">
       <c r="A644" s="4" t="n"/>
@@ -21141,6 +21789,7 @@
       <c r="H644" s="4" t="n"/>
       <c r="I644" s="4" t="n"/>
       <c r="J644" s="3" t="n"/>
+      <c r="K644" s="3" t="n"/>
     </row>
     <row r="645">
       <c r="A645" s="4" t="n"/>
@@ -21153,6 +21802,7 @@
       <c r="H645" s="4" t="n"/>
       <c r="I645" s="4" t="n"/>
       <c r="J645" s="3" t="n"/>
+      <c r="K645" s="3" t="n"/>
     </row>
     <row r="646">
       <c r="A646" s="4" t="n"/>
@@ -21165,6 +21815,7 @@
       <c r="H646" s="4" t="n"/>
       <c r="I646" s="4" t="n"/>
       <c r="J646" s="3" t="n"/>
+      <c r="K646" s="3" t="n"/>
     </row>
     <row r="647">
       <c r="A647" s="4" t="n"/>
@@ -21177,6 +21828,7 @@
       <c r="H647" s="4" t="n"/>
       <c r="I647" s="4" t="n"/>
       <c r="J647" s="3" t="n"/>
+      <c r="K647" s="3" t="n"/>
     </row>
     <row r="648">
       <c r="A648" s="4" t="n"/>
@@ -21189,6 +21841,7 @@
       <c r="H648" s="4" t="n"/>
       <c r="I648" s="4" t="n"/>
       <c r="J648" s="3" t="n"/>
+      <c r="K648" s="3" t="n"/>
     </row>
     <row r="649">
       <c r="A649" s="4" t="n"/>
@@ -21201,6 +21854,7 @@
       <c r="H649" s="4" t="n"/>
       <c r="I649" s="4" t="n"/>
       <c r="J649" s="3" t="n"/>
+      <c r="K649" s="3" t="n"/>
     </row>
     <row r="650">
       <c r="A650" s="4" t="n"/>
@@ -21213,6 +21867,7 @@
       <c r="H650" s="4" t="n"/>
       <c r="I650" s="4" t="n"/>
       <c r="J650" s="3" t="n"/>
+      <c r="K650" s="3" t="n"/>
     </row>
     <row r="651">
       <c r="A651" s="4" t="n"/>
@@ -21225,6 +21880,7 @@
       <c r="H651" s="4" t="n"/>
       <c r="I651" s="4" t="n"/>
       <c r="J651" s="3" t="n"/>
+      <c r="K651" s="3" t="n"/>
     </row>
     <row r="652">
       <c r="A652" s="4" t="n"/>
@@ -21237,6 +21893,7 @@
       <c r="H652" s="4" t="n"/>
       <c r="I652" s="4" t="n"/>
       <c r="J652" s="3" t="n"/>
+      <c r="K652" s="3" t="n"/>
     </row>
     <row r="653">
       <c r="A653" s="4" t="n"/>
@@ -21249,6 +21906,7 @@
       <c r="H653" s="4" t="n"/>
       <c r="I653" s="4" t="n"/>
       <c r="J653" s="3" t="n"/>
+      <c r="K653" s="3" t="n"/>
     </row>
     <row r="654">
       <c r="A654" s="4" t="n"/>
@@ -21261,6 +21919,7 @@
       <c r="H654" s="4" t="n"/>
       <c r="I654" s="4" t="n"/>
       <c r="J654" s="3" t="n"/>
+      <c r="K654" s="3" t="n"/>
     </row>
     <row r="655">
       <c r="A655" s="4" t="n"/>
@@ -21273,6 +21932,7 @@
       <c r="H655" s="4" t="n"/>
       <c r="I655" s="4" t="n"/>
       <c r="J655" s="3" t="n"/>
+      <c r="K655" s="3" t="n"/>
     </row>
     <row r="656">
       <c r="A656" s="4" t="n"/>
@@ -21285,6 +21945,7 @@
       <c r="H656" s="4" t="n"/>
       <c r="I656" s="4" t="n"/>
       <c r="J656" s="3" t="n"/>
+      <c r="K656" s="3" t="n"/>
     </row>
     <row r="657">
       <c r="A657" s="4" t="n"/>
@@ -21297,6 +21958,7 @@
       <c r="H657" s="4" t="n"/>
       <c r="I657" s="4" t="n"/>
       <c r="J657" s="3" t="n"/>
+      <c r="K657" s="3" t="n"/>
     </row>
     <row r="658">
       <c r="A658" s="4" t="n"/>
@@ -21309,6 +21971,7 @@
       <c r="H658" s="4" t="n"/>
       <c r="I658" s="4" t="n"/>
       <c r="J658" s="3" t="n"/>
+      <c r="K658" s="3" t="n"/>
     </row>
     <row r="659">
       <c r="A659" s="4" t="n"/>
@@ -21321,6 +21984,7 @@
       <c r="H659" s="4" t="n"/>
       <c r="I659" s="4" t="n"/>
       <c r="J659" s="3" t="n"/>
+      <c r="K659" s="3" t="n"/>
     </row>
     <row r="660">
       <c r="A660" s="4" t="n"/>
@@ -21333,6 +21997,7 @@
       <c r="H660" s="4" t="n"/>
       <c r="I660" s="4" t="n"/>
       <c r="J660" s="3" t="n"/>
+      <c r="K660" s="3" t="n"/>
     </row>
     <row r="661">
       <c r="A661" s="4" t="n"/>
@@ -21345,6 +22010,7 @@
       <c r="H661" s="4" t="n"/>
       <c r="I661" s="4" t="n"/>
       <c r="J661" s="3" t="n"/>
+      <c r="K661" s="3" t="n"/>
     </row>
     <row r="662">
       <c r="A662" s="4" t="n"/>
@@ -21357,6 +22023,7 @@
       <c r="H662" s="4" t="n"/>
       <c r="I662" s="4" t="n"/>
       <c r="J662" s="3" t="n"/>
+      <c r="K662" s="3" t="n"/>
     </row>
     <row r="663">
       <c r="A663" s="4" t="n"/>
@@ -21369,6 +22036,7 @@
       <c r="H663" s="4" t="n"/>
       <c r="I663" s="4" t="n"/>
       <c r="J663" s="3" t="n"/>
+      <c r="K663" s="3" t="n"/>
     </row>
     <row r="664">
       <c r="A664" s="4" t="n"/>
@@ -21381,6 +22049,7 @@
       <c r="H664" s="4" t="n"/>
       <c r="I664" s="4" t="n"/>
       <c r="J664" s="3" t="n"/>
+      <c r="K664" s="3" t="n"/>
     </row>
     <row r="665">
       <c r="A665" s="4" t="n"/>
@@ -21393,6 +22062,7 @@
       <c r="H665" s="4" t="n"/>
       <c r="I665" s="4" t="n"/>
       <c r="J665" s="3" t="n"/>
+      <c r="K665" s="3" t="n"/>
     </row>
     <row r="666">
       <c r="A666" s="4" t="n"/>
@@ -21405,6 +22075,7 @@
       <c r="H666" s="4" t="n"/>
       <c r="I666" s="4" t="n"/>
       <c r="J666" s="3" t="n"/>
+      <c r="K666" s="3" t="n"/>
     </row>
     <row r="667">
       <c r="A667" s="4" t="n"/>
@@ -21417,6 +22088,7 @@
       <c r="H667" s="4" t="n"/>
       <c r="I667" s="4" t="n"/>
       <c r="J667" s="3" t="n"/>
+      <c r="K667" s="3" t="n"/>
     </row>
     <row r="668">
       <c r="A668" s="4" t="n"/>
@@ -21429,6 +22101,7 @@
       <c r="H668" s="4" t="n"/>
       <c r="I668" s="4" t="n"/>
       <c r="J668" s="3" t="n"/>
+      <c r="K668" s="3" t="n"/>
     </row>
     <row r="669">
       <c r="A669" s="4" t="n"/>
@@ -21441,6 +22114,7 @@
       <c r="H669" s="4" t="n"/>
       <c r="I669" s="4" t="n"/>
       <c r="J669" s="3" t="n"/>
+      <c r="K669" s="3" t="n"/>
     </row>
     <row r="670">
       <c r="A670" s="4" t="n"/>
@@ -21453,6 +22127,7 @@
       <c r="H670" s="4" t="n"/>
       <c r="I670" s="4" t="n"/>
       <c r="J670" s="3" t="n"/>
+      <c r="K670" s="3" t="n"/>
     </row>
     <row r="671">
       <c r="A671" s="4" t="n"/>
@@ -21465,6 +22140,7 @@
       <c r="H671" s="4" t="n"/>
       <c r="I671" s="4" t="n"/>
       <c r="J671" s="3" t="n"/>
+      <c r="K671" s="3" t="n"/>
     </row>
     <row r="672">
       <c r="A672" s="4" t="n"/>
@@ -21477,6 +22153,7 @@
       <c r="H672" s="4" t="n"/>
       <c r="I672" s="4" t="n"/>
       <c r="J672" s="3" t="n"/>
+      <c r="K672" s="3" t="n"/>
     </row>
     <row r="673">
       <c r="A673" s="4" t="n"/>
@@ -21489,6 +22166,7 @@
       <c r="H673" s="4" t="n"/>
       <c r="I673" s="4" t="n"/>
       <c r="J673" s="3" t="n"/>
+      <c r="K673" s="3" t="n"/>
     </row>
     <row r="674">
       <c r="A674" s="4" t="n"/>
@@ -21501,6 +22179,7 @@
       <c r="H674" s="4" t="n"/>
       <c r="I674" s="4" t="n"/>
       <c r="J674" s="3" t="n"/>
+      <c r="K674" s="3" t="n"/>
     </row>
     <row r="675">
       <c r="A675" s="4" t="n"/>
@@ -21513,6 +22192,7 @@
       <c r="H675" s="4" t="n"/>
       <c r="I675" s="4" t="n"/>
       <c r="J675" s="3" t="n"/>
+      <c r="K675" s="3" t="n"/>
     </row>
     <row r="676">
       <c r="A676" s="4" t="n"/>
@@ -21525,6 +22205,7 @@
       <c r="H676" s="4" t="n"/>
       <c r="I676" s="4" t="n"/>
       <c r="J676" s="3" t="n"/>
+      <c r="K676" s="3" t="n"/>
     </row>
     <row r="677">
       <c r="A677" s="4" t="n"/>
@@ -21537,6 +22218,7 @@
       <c r="H677" s="4" t="n"/>
       <c r="I677" s="4" t="n"/>
       <c r="J677" s="3" t="n"/>
+      <c r="K677" s="3" t="n"/>
     </row>
     <row r="678">
       <c r="A678" s="4" t="n"/>
@@ -21549,6 +22231,7 @@
       <c r="H678" s="4" t="n"/>
       <c r="I678" s="4" t="n"/>
       <c r="J678" s="3" t="n"/>
+      <c r="K678" s="3" t="n"/>
     </row>
     <row r="679">
       <c r="A679" s="4" t="n"/>
@@ -21561,6 +22244,7 @@
       <c r="H679" s="4" t="n"/>
       <c r="I679" s="4" t="n"/>
       <c r="J679" s="3" t="n"/>
+      <c r="K679" s="3" t="n"/>
     </row>
     <row r="680">
       <c r="A680" s="4" t="n"/>
@@ -21573,6 +22257,7 @@
       <c r="H680" s="4" t="n"/>
       <c r="I680" s="4" t="n"/>
       <c r="J680" s="3" t="n"/>
+      <c r="K680" s="3" t="n"/>
     </row>
     <row r="681">
       <c r="A681" s="4" t="n"/>
@@ -21585,6 +22270,7 @@
       <c r="H681" s="4" t="n"/>
       <c r="I681" s="4" t="n"/>
       <c r="J681" s="3" t="n"/>
+      <c r="K681" s="3" t="n"/>
     </row>
     <row r="682">
       <c r="A682" s="4" t="n"/>
@@ -21597,6 +22283,7 @@
       <c r="H682" s="4" t="n"/>
       <c r="I682" s="4" t="n"/>
       <c r="J682" s="3" t="n"/>
+      <c r="K682" s="3" t="n"/>
     </row>
     <row r="683">
       <c r="A683" s="4" t="n"/>
@@ -21609,6 +22296,7 @@
       <c r="H683" s="4" t="n"/>
       <c r="I683" s="4" t="n"/>
       <c r="J683" s="3" t="n"/>
+      <c r="K683" s="3" t="n"/>
     </row>
     <row r="684">
       <c r="A684" s="4" t="n"/>
@@ -21621,6 +22309,7 @@
       <c r="H684" s="4" t="n"/>
       <c r="I684" s="4" t="n"/>
       <c r="J684" s="3" t="n"/>
+      <c r="K684" s="3" t="n"/>
     </row>
     <row r="685">
       <c r="A685" s="4" t="n"/>
@@ -21633,6 +22322,7 @@
       <c r="H685" s="4" t="n"/>
       <c r="I685" s="4" t="n"/>
       <c r="J685" s="3" t="n"/>
+      <c r="K685" s="3" t="n"/>
     </row>
     <row r="686">
       <c r="A686" s="4" t="n"/>
@@ -21645,6 +22335,7 @@
       <c r="H686" s="4" t="n"/>
       <c r="I686" s="4" t="n"/>
       <c r="J686" s="3" t="n"/>
+      <c r="K686" s="3" t="n"/>
     </row>
     <row r="687">
       <c r="A687" s="4" t="n"/>
@@ -21657,6 +22348,7 @@
       <c r="H687" s="4" t="n"/>
       <c r="I687" s="4" t="n"/>
       <c r="J687" s="3" t="n"/>
+      <c r="K687" s="3" t="n"/>
     </row>
     <row r="688">
       <c r="A688" s="4" t="n"/>
@@ -21669,6 +22361,7 @@
       <c r="H688" s="4" t="n"/>
       <c r="I688" s="4" t="n"/>
       <c r="J688" s="3" t="n"/>
+      <c r="K688" s="3" t="n"/>
     </row>
     <row r="689">
       <c r="A689" s="4" t="n"/>
@@ -21681,6 +22374,7 @@
       <c r="H689" s="4" t="n"/>
       <c r="I689" s="4" t="n"/>
       <c r="J689" s="3" t="n"/>
+      <c r="K689" s="3" t="n"/>
     </row>
     <row r="690">
       <c r="A690" s="4" t="n"/>
@@ -21693,6 +22387,7 @@
       <c r="H690" s="4" t="n"/>
       <c r="I690" s="4" t="n"/>
       <c r="J690" s="3" t="n"/>
+      <c r="K690" s="3" t="n"/>
     </row>
     <row r="691">
       <c r="A691" s="4" t="n"/>
@@ -21705,6 +22400,7 @@
       <c r="H691" s="4" t="n"/>
       <c r="I691" s="4" t="n"/>
       <c r="J691" s="3" t="n"/>
+      <c r="K691" s="3" t="n"/>
     </row>
     <row r="692">
       <c r="A692" s="4" t="n"/>
@@ -21717,6 +22413,7 @@
       <c r="H692" s="4" t="n"/>
       <c r="I692" s="4" t="n"/>
       <c r="J692" s="3" t="n"/>
+      <c r="K692" s="3" t="n"/>
     </row>
     <row r="693">
       <c r="A693" s="4" t="n"/>
@@ -21729,6 +22426,7 @@
       <c r="H693" s="4" t="n"/>
       <c r="I693" s="4" t="n"/>
       <c r="J693" s="3" t="n"/>
+      <c r="K693" s="3" t="n"/>
     </row>
     <row r="694">
       <c r="A694" s="4" t="n"/>
@@ -21741,6 +22439,7 @@
       <c r="H694" s="4" t="n"/>
       <c r="I694" s="4" t="n"/>
       <c r="J694" s="3" t="n"/>
+      <c r="K694" s="3" t="n"/>
     </row>
     <row r="695">
       <c r="A695" s="4" t="n"/>
@@ -21753,6 +22452,7 @@
       <c r="H695" s="4" t="n"/>
       <c r="I695" s="4" t="n"/>
       <c r="J695" s="3" t="n"/>
+      <c r="K695" s="3" t="n"/>
     </row>
     <row r="696">
       <c r="A696" s="4" t="n"/>
@@ -21765,6 +22465,7 @@
       <c r="H696" s="4" t="n"/>
       <c r="I696" s="4" t="n"/>
       <c r="J696" s="3" t="n"/>
+      <c r="K696" s="3" t="n"/>
     </row>
     <row r="697">
       <c r="A697" s="4" t="n"/>
@@ -21777,6 +22478,7 @@
       <c r="H697" s="4" t="n"/>
       <c r="I697" s="4" t="n"/>
       <c r="J697" s="3" t="n"/>
+      <c r="K697" s="3" t="n"/>
     </row>
     <row r="698">
       <c r="A698" s="4" t="n"/>
@@ -21789,6 +22491,7 @@
       <c r="H698" s="4" t="n"/>
       <c r="I698" s="4" t="n"/>
       <c r="J698" s="3" t="n"/>
+      <c r="K698" s="3" t="n"/>
     </row>
     <row r="699">
       <c r="A699" s="4" t="n"/>
@@ -21801,6 +22504,7 @@
       <c r="H699" s="4" t="n"/>
       <c r="I699" s="4" t="n"/>
       <c r="J699" s="3" t="n"/>
+      <c r="K699" s="3" t="n"/>
     </row>
     <row r="700">
       <c r="A700" s="4" t="n"/>
@@ -21813,6 +22517,7 @@
       <c r="H700" s="4" t="n"/>
       <c r="I700" s="4" t="n"/>
       <c r="J700" s="3" t="n"/>
+      <c r="K700" s="3" t="n"/>
     </row>
     <row r="701">
       <c r="A701" s="4" t="n"/>
@@ -21825,6 +22530,7 @@
       <c r="H701" s="4" t="n"/>
       <c r="I701" s="4" t="n"/>
       <c r="J701" s="3" t="n"/>
+      <c r="K701" s="3" t="n"/>
     </row>
     <row r="702">
       <c r="A702" s="4" t="n"/>
@@ -21837,6 +22543,7 @@
       <c r="H702" s="4" t="n"/>
       <c r="I702" s="4" t="n"/>
       <c r="J702" s="3" t="n"/>
+      <c r="K702" s="3" t="n"/>
     </row>
     <row r="703">
       <c r="A703" s="4" t="n"/>
@@ -21849,6 +22556,7 @@
       <c r="H703" s="4" t="n"/>
       <c r="I703" s="4" t="n"/>
       <c r="J703" s="3" t="n"/>
+      <c r="K703" s="3" t="n"/>
     </row>
     <row r="704">
       <c r="A704" s="4" t="n"/>
@@ -21861,6 +22569,7 @@
       <c r="H704" s="4" t="n"/>
       <c r="I704" s="4" t="n"/>
       <c r="J704" s="3" t="n"/>
+      <c r="K704" s="3" t="n"/>
     </row>
     <row r="705">
       <c r="A705" s="4" t="n"/>
@@ -21873,6 +22582,7 @@
       <c r="H705" s="4" t="n"/>
       <c r="I705" s="4" t="n"/>
       <c r="J705" s="3" t="n"/>
+      <c r="K705" s="3" t="n"/>
     </row>
     <row r="706">
       <c r="A706" s="4" t="n"/>
@@ -21885,6 +22595,7 @@
       <c r="H706" s="4" t="n"/>
       <c r="I706" s="4" t="n"/>
       <c r="J706" s="3" t="n"/>
+      <c r="K706" s="3" t="n"/>
     </row>
     <row r="707">
       <c r="A707" s="4" t="n"/>
@@ -21897,6 +22608,7 @@
       <c r="H707" s="4" t="n"/>
       <c r="I707" s="4" t="n"/>
       <c r="J707" s="3" t="n"/>
+      <c r="K707" s="3" t="n"/>
     </row>
     <row r="708">
       <c r="A708" s="4" t="n"/>
@@ -21909,6 +22621,7 @@
       <c r="H708" s="4" t="n"/>
       <c r="I708" s="4" t="n"/>
       <c r="J708" s="3" t="n"/>
+      <c r="K708" s="3" t="n"/>
     </row>
     <row r="709">
       <c r="A709" s="4" t="n"/>
@@ -21921,6 +22634,7 @@
       <c r="H709" s="4" t="n"/>
       <c r="I709" s="4" t="n"/>
       <c r="J709" s="3" t="n"/>
+      <c r="K709" s="3" t="n"/>
     </row>
     <row r="710">
       <c r="A710" s="4" t="n"/>
@@ -21933,6 +22647,7 @@
       <c r="H710" s="4" t="n"/>
       <c r="I710" s="4" t="n"/>
       <c r="J710" s="3" t="n"/>
+      <c r="K710" s="3" t="n"/>
     </row>
     <row r="711">
       <c r="A711" s="4" t="n"/>
@@ -21945,6 +22660,7 @@
       <c r="H711" s="4" t="n"/>
       <c r="I711" s="4" t="n"/>
       <c r="J711" s="3" t="n"/>
+      <c r="K711" s="3" t="n"/>
     </row>
     <row r="712">
       <c r="A712" s="4" t="n"/>
@@ -21957,6 +22673,7 @@
       <c r="H712" s="4" t="n"/>
       <c r="I712" s="4" t="n"/>
       <c r="J712" s="3" t="n"/>
+      <c r="K712" s="3" t="n"/>
     </row>
     <row r="713">
       <c r="A713" s="4" t="n"/>
@@ -21969,6 +22686,7 @@
       <c r="H713" s="4" t="n"/>
       <c r="I713" s="4" t="n"/>
       <c r="J713" s="3" t="n"/>
+      <c r="K713" s="3" t="n"/>
     </row>
     <row r="714">
       <c r="A714" s="4" t="n"/>
@@ -21981,6 +22699,7 @@
       <c r="H714" s="4" t="n"/>
       <c r="I714" s="4" t="n"/>
       <c r="J714" s="3" t="n"/>
+      <c r="K714" s="3" t="n"/>
     </row>
     <row r="715">
       <c r="A715" s="4" t="n"/>
@@ -21993,6 +22712,7 @@
       <c r="H715" s="4" t="n"/>
       <c r="I715" s="4" t="n"/>
       <c r="J715" s="3" t="n"/>
+      <c r="K715" s="3" t="n"/>
     </row>
     <row r="716">
       <c r="A716" s="4" t="n"/>
@@ -22005,6 +22725,7 @@
       <c r="H716" s="4" t="n"/>
       <c r="I716" s="4" t="n"/>
       <c r="J716" s="3" t="n"/>
+      <c r="K716" s="3" t="n"/>
     </row>
     <row r="717">
       <c r="A717" s="4" t="n"/>
@@ -22017,6 +22738,7 @@
       <c r="H717" s="4" t="n"/>
       <c r="I717" s="4" t="n"/>
       <c r="J717" s="3" t="n"/>
+      <c r="K717" s="3" t="n"/>
     </row>
     <row r="718">
       <c r="A718" s="4" t="n"/>
@@ -22029,6 +22751,7 @@
       <c r="H718" s="4" t="n"/>
       <c r="I718" s="4" t="n"/>
       <c r="J718" s="3" t="n"/>
+      <c r="K718" s="3" t="n"/>
     </row>
     <row r="719">
       <c r="A719" s="4" t="n"/>
@@ -22041,6 +22764,7 @@
       <c r="H719" s="4" t="n"/>
       <c r="I719" s="4" t="n"/>
       <c r="J719" s="3" t="n"/>
+      <c r="K719" s="3" t="n"/>
     </row>
     <row r="720">
       <c r="A720" s="4" t="n"/>
@@ -22053,6 +22777,7 @@
       <c r="H720" s="4" t="n"/>
       <c r="I720" s="4" t="n"/>
       <c r="J720" s="3" t="n"/>
+      <c r="K720" s="3" t="n"/>
     </row>
     <row r="721">
       <c r="A721" s="4" t="n"/>
@@ -22065,6 +22790,7 @@
       <c r="H721" s="4" t="n"/>
       <c r="I721" s="4" t="n"/>
       <c r="J721" s="3" t="n"/>
+      <c r="K721" s="3" t="n"/>
     </row>
     <row r="722">
       <c r="A722" s="4" t="n"/>
@@ -22077,6 +22803,7 @@
       <c r="H722" s="4" t="n"/>
       <c r="I722" s="4" t="n"/>
       <c r="J722" s="3" t="n"/>
+      <c r="K722" s="3" t="n"/>
     </row>
     <row r="723">
       <c r="A723" s="4" t="n"/>
@@ -22089,6 +22816,7 @@
       <c r="H723" s="4" t="n"/>
       <c r="I723" s="4" t="n"/>
       <c r="J723" s="3" t="n"/>
+      <c r="K723" s="3" t="n"/>
     </row>
     <row r="724">
       <c r="A724" s="4" t="n"/>
@@ -22101,6 +22829,7 @@
       <c r="H724" s="4" t="n"/>
       <c r="I724" s="4" t="n"/>
       <c r="J724" s="3" t="n"/>
+      <c r="K724" s="3" t="n"/>
     </row>
     <row r="725">
       <c r="A725" s="4" t="n"/>
@@ -22113,6 +22842,7 @@
       <c r="H725" s="4" t="n"/>
       <c r="I725" s="4" t="n"/>
       <c r="J725" s="3" t="n"/>
+      <c r="K725" s="3" t="n"/>
     </row>
     <row r="726">
       <c r="A726" s="4" t="n"/>
@@ -22125,6 +22855,7 @@
       <c r="H726" s="4" t="n"/>
       <c r="I726" s="4" t="n"/>
       <c r="J726" s="3" t="n"/>
+      <c r="K726" s="3" t="n"/>
     </row>
     <row r="727">
       <c r="A727" s="4" t="n"/>
@@ -22137,6 +22868,7 @@
       <c r="H727" s="4" t="n"/>
       <c r="I727" s="4" t="n"/>
       <c r="J727" s="3" t="n"/>
+      <c r="K727" s="3" t="n"/>
     </row>
     <row r="728">
       <c r="A728" s="4" t="n"/>
@@ -22149,6 +22881,7 @@
       <c r="H728" s="4" t="n"/>
       <c r="I728" s="4" t="n"/>
       <c r="J728" s="3" t="n"/>
+      <c r="K728" s="3" t="n"/>
     </row>
     <row r="729">
       <c r="A729" s="4" t="n"/>
@@ -22161,6 +22894,7 @@
       <c r="H729" s="4" t="n"/>
       <c r="I729" s="4" t="n"/>
       <c r="J729" s="3" t="n"/>
+      <c r="K729" s="3" t="n"/>
     </row>
     <row r="730">
       <c r="A730" s="4" t="n"/>
@@ -22173,6 +22907,7 @@
       <c r="H730" s="4" t="n"/>
       <c r="I730" s="4" t="n"/>
       <c r="J730" s="3" t="n"/>
+      <c r="K730" s="3" t="n"/>
     </row>
     <row r="731">
       <c r="A731" s="4" t="n"/>
@@ -22185,6 +22920,7 @@
       <c r="H731" s="4" t="n"/>
       <c r="I731" s="4" t="n"/>
       <c r="J731" s="3" t="n"/>
+      <c r="K731" s="3" t="n"/>
     </row>
     <row r="732">
       <c r="A732" s="4" t="n"/>
@@ -22197,6 +22933,7 @@
       <c r="H732" s="4" t="n"/>
       <c r="I732" s="4" t="n"/>
       <c r="J732" s="3" t="n"/>
+      <c r="K732" s="3" t="n"/>
     </row>
     <row r="733">
       <c r="A733" s="4" t="n"/>
@@ -22209,6 +22946,7 @@
       <c r="H733" s="4" t="n"/>
       <c r="I733" s="4" t="n"/>
       <c r="J733" s="3" t="n"/>
+      <c r="K733" s="3" t="n"/>
     </row>
     <row r="734">
       <c r="A734" s="4" t="n"/>
@@ -22221,6 +22959,7 @@
       <c r="H734" s="4" t="n"/>
       <c r="I734" s="4" t="n"/>
       <c r="J734" s="3" t="n"/>
+      <c r="K734" s="3" t="n"/>
     </row>
     <row r="735">
       <c r="A735" s="4" t="n"/>
@@ -22233,6 +22972,7 @@
       <c r="H735" s="4" t="n"/>
       <c r="I735" s="4" t="n"/>
       <c r="J735" s="3" t="n"/>
+      <c r="K735" s="3" t="n"/>
     </row>
     <row r="736">
       <c r="A736" s="4" t="n"/>
@@ -22245,6 +22985,7 @@
       <c r="H736" s="4" t="n"/>
       <c r="I736" s="4" t="n"/>
       <c r="J736" s="3" t="n"/>
+      <c r="K736" s="3" t="n"/>
     </row>
     <row r="737">
       <c r="A737" s="4" t="n"/>
@@ -22257,6 +22998,7 @@
       <c r="H737" s="4" t="n"/>
       <c r="I737" s="4" t="n"/>
       <c r="J737" s="3" t="n"/>
+      <c r="K737" s="3" t="n"/>
     </row>
     <row r="738">
       <c r="A738" s="4" t="n"/>
@@ -22269,6 +23011,7 @@
       <c r="H738" s="4" t="n"/>
       <c r="I738" s="4" t="n"/>
       <c r="J738" s="3" t="n"/>
+      <c r="K738" s="3" t="n"/>
     </row>
     <row r="739">
       <c r="A739" s="4" t="n"/>
@@ -22281,6 +23024,7 @@
       <c r="H739" s="4" t="n"/>
       <c r="I739" s="4" t="n"/>
       <c r="J739" s="3" t="n"/>
+      <c r="K739" s="3" t="n"/>
     </row>
     <row r="740">
       <c r="A740" s="4" t="n"/>
@@ -22293,6 +23037,7 @@
       <c r="H740" s="4" t="n"/>
       <c r="I740" s="4" t="n"/>
       <c r="J740" s="3" t="n"/>
+      <c r="K740" s="3" t="n"/>
     </row>
     <row r="741">
       <c r="A741" s="4" t="n"/>
@@ -22305,6 +23050,7 @@
       <c r="H741" s="4" t="n"/>
       <c r="I741" s="4" t="n"/>
       <c r="J741" s="3" t="n"/>
+      <c r="K741" s="3" t="n"/>
     </row>
     <row r="742">
       <c r="A742" s="4" t="n"/>
@@ -22317,6 +23063,7 @@
       <c r="H742" s="4" t="n"/>
       <c r="I742" s="4" t="n"/>
       <c r="J742" s="3" t="n"/>
+      <c r="K742" s="3" t="n"/>
     </row>
     <row r="743">
       <c r="A743" s="4" t="n"/>
@@ -22329,6 +23076,7 @@
       <c r="H743" s="4" t="n"/>
       <c r="I743" s="4" t="n"/>
       <c r="J743" s="3" t="n"/>
+      <c r="K743" s="3" t="n"/>
     </row>
     <row r="744">
       <c r="A744" s="4" t="n"/>
@@ -22341,6 +23089,7 @@
       <c r="H744" s="4" t="n"/>
       <c r="I744" s="4" t="n"/>
       <c r="J744" s="3" t="n"/>
+      <c r="K744" s="3" t="n"/>
     </row>
     <row r="745">
       <c r="A745" s="4" t="n"/>
@@ -22353,6 +23102,7 @@
       <c r="H745" s="4" t="n"/>
       <c r="I745" s="4" t="n"/>
       <c r="J745" s="3" t="n"/>
+      <c r="K745" s="3" t="n"/>
     </row>
     <row r="746">
       <c r="A746" s="4" t="n"/>
@@ -22365,6 +23115,7 @@
       <c r="H746" s="4" t="n"/>
       <c r="I746" s="4" t="n"/>
       <c r="J746" s="3" t="n"/>
+      <c r="K746" s="3" t="n"/>
     </row>
     <row r="747">
       <c r="A747" s="4" t="n"/>
@@ -22377,6 +23128,7 @@
       <c r="H747" s="4" t="n"/>
       <c r="I747" s="4" t="n"/>
       <c r="J747" s="3" t="n"/>
+      <c r="K747" s="3" t="n"/>
     </row>
     <row r="748">
       <c r="A748" s="4" t="n"/>
@@ -22389,6 +23141,7 @@
       <c r="H748" s="4" t="n"/>
       <c r="I748" s="4" t="n"/>
       <c r="J748" s="3" t="n"/>
+      <c r="K748" s="3" t="n"/>
     </row>
     <row r="749">
       <c r="A749" s="4" t="n"/>
@@ -22401,6 +23154,7 @@
       <c r="H749" s="4" t="n"/>
       <c r="I749" s="4" t="n"/>
       <c r="J749" s="3" t="n"/>
+      <c r="K749" s="3" t="n"/>
     </row>
     <row r="750">
       <c r="A750" s="4" t="n"/>
@@ -22413,6 +23167,7 @@
       <c r="H750" s="4" t="n"/>
       <c r="I750" s="4" t="n"/>
       <c r="J750" s="3" t="n"/>
+      <c r="K750" s="3" t="n"/>
     </row>
     <row r="751">
       <c r="A751" s="4" t="n"/>
@@ -22425,6 +23180,7 @@
       <c r="H751" s="4" t="n"/>
       <c r="I751" s="4" t="n"/>
       <c r="J751" s="3" t="n"/>
+      <c r="K751" s="3" t="n"/>
     </row>
     <row r="752">
       <c r="A752" s="4" t="n"/>
@@ -22437,6 +23193,7 @@
       <c r="H752" s="4" t="n"/>
       <c r="I752" s="4" t="n"/>
       <c r="J752" s="3" t="n"/>
+      <c r="K752" s="3" t="n"/>
     </row>
     <row r="753">
       <c r="A753" s="4" t="n"/>
@@ -22449,6 +23206,7 @@
       <c r="H753" s="4" t="n"/>
       <c r="I753" s="4" t="n"/>
       <c r="J753" s="3" t="n"/>
+      <c r="K753" s="3" t="n"/>
     </row>
     <row r="754">
       <c r="A754" s="4" t="n"/>
@@ -22461,6 +23219,7 @@
       <c r="H754" s="4" t="n"/>
       <c r="I754" s="4" t="n"/>
       <c r="J754" s="3" t="n"/>
+      <c r="K754" s="3" t="n"/>
     </row>
     <row r="755">
       <c r="A755" s="4" t="n"/>
@@ -22473,6 +23232,7 @@
       <c r="H755" s="4" t="n"/>
       <c r="I755" s="4" t="n"/>
       <c r="J755" s="3" t="n"/>
+      <c r="K755" s="3" t="n"/>
     </row>
     <row r="756">
       <c r="A756" s="4" t="n"/>
@@ -22485,6 +23245,7 @@
       <c r="H756" s="4" t="n"/>
       <c r="I756" s="4" t="n"/>
       <c r="J756" s="3" t="n"/>
+      <c r="K756" s="3" t="n"/>
     </row>
     <row r="757">
       <c r="A757" s="4" t="n"/>
@@ -22497,6 +23258,7 @@
       <c r="H757" s="4" t="n"/>
       <c r="I757" s="4" t="n"/>
       <c r="J757" s="3" t="n"/>
+      <c r="K757" s="3" t="n"/>
     </row>
     <row r="758">
       <c r="A758" s="4" t="n"/>
@@ -22509,6 +23271,7 @@
       <c r="H758" s="4" t="n"/>
       <c r="I758" s="4" t="n"/>
       <c r="J758" s="3" t="n"/>
+      <c r="K758" s="3" t="n"/>
     </row>
     <row r="759">
       <c r="A759" s="4" t="n"/>
@@ -22521,6 +23284,7 @@
       <c r="H759" s="4" t="n"/>
       <c r="I759" s="4" t="n"/>
       <c r="J759" s="3" t="n"/>
+      <c r="K759" s="3" t="n"/>
     </row>
     <row r="760">
       <c r="A760" s="4" t="n"/>
@@ -22533,6 +23297,7 @@
       <c r="H760" s="4" t="n"/>
       <c r="I760" s="4" t="n"/>
       <c r="J760" s="3" t="n"/>
+      <c r="K760" s="3" t="n"/>
     </row>
     <row r="761">
       <c r="A761" s="4" t="n"/>
@@ -22545,6 +23310,7 @@
       <c r="H761" s="4" t="n"/>
       <c r="I761" s="4" t="n"/>
       <c r="J761" s="3" t="n"/>
+      <c r="K761" s="3" t="n"/>
     </row>
     <row r="762">
       <c r="A762" s="4" t="n"/>
@@ -22557,6 +23323,7 @@
       <c r="H762" s="4" t="n"/>
       <c r="I762" s="4" t="n"/>
       <c r="J762" s="3" t="n"/>
+      <c r="K762" s="3" t="n"/>
     </row>
     <row r="763">
       <c r="A763" s="4" t="n"/>
@@ -22569,6 +23336,7 @@
       <c r="H763" s="4" t="n"/>
       <c r="I763" s="4" t="n"/>
       <c r="J763" s="3" t="n"/>
+      <c r="K763" s="3" t="n"/>
     </row>
     <row r="764">
       <c r="A764" s="4" t="n"/>
@@ -22581,6 +23349,7 @@
       <c r="H764" s="4" t="n"/>
       <c r="I764" s="4" t="n"/>
       <c r="J764" s="3" t="n"/>
+      <c r="K764" s="3" t="n"/>
     </row>
     <row r="765">
       <c r="A765" s="4" t="n"/>
@@ -22593,6 +23362,7 @@
       <c r="H765" s="4" t="n"/>
       <c r="I765" s="4" t="n"/>
       <c r="J765" s="3" t="n"/>
+      <c r="K765" s="3" t="n"/>
     </row>
     <row r="766">
       <c r="A766" s="4" t="n"/>
@@ -22605,6 +23375,7 @@
       <c r="H766" s="4" t="n"/>
       <c r="I766" s="4" t="n"/>
       <c r="J766" s="3" t="n"/>
+      <c r="K766" s="3" t="n"/>
     </row>
     <row r="767">
       <c r="A767" s="4" t="n"/>
@@ -22617,6 +23388,7 @@
       <c r="H767" s="4" t="n"/>
       <c r="I767" s="4" t="n"/>
       <c r="J767" s="3" t="n"/>
+      <c r="K767" s="3" t="n"/>
     </row>
     <row r="768">
       <c r="A768" s="4" t="n"/>
@@ -22629,6 +23401,7 @@
       <c r="H768" s="4" t="n"/>
       <c r="I768" s="4" t="n"/>
       <c r="J768" s="3" t="n"/>
+      <c r="K768" s="3" t="n"/>
     </row>
     <row r="769">
       <c r="A769" s="4" t="n"/>
@@ -22641,6 +23414,7 @@
       <c r="H769" s="4" t="n"/>
       <c r="I769" s="4" t="n"/>
       <c r="J769" s="3" t="n"/>
+      <c r="K769" s="3" t="n"/>
     </row>
     <row r="770">
       <c r="A770" s="4" t="n"/>
@@ -22653,6 +23427,7 @@
       <c r="H770" s="4" t="n"/>
       <c r="I770" s="4" t="n"/>
       <c r="J770" s="3" t="n"/>
+      <c r="K770" s="3" t="n"/>
     </row>
     <row r="771">
       <c r="A771" s="4" t="n"/>
@@ -22665,6 +23440,7 @@
       <c r="H771" s="4" t="n"/>
       <c r="I771" s="4" t="n"/>
       <c r="J771" s="3" t="n"/>
+      <c r="K771" s="3" t="n"/>
     </row>
     <row r="772">
       <c r="A772" s="4" t="n"/>
@@ -22677,6 +23453,7 @@
       <c r="H772" s="4" t="n"/>
       <c r="I772" s="4" t="n"/>
       <c r="J772" s="3" t="n"/>
+      <c r="K772" s="3" t="n"/>
     </row>
     <row r="773">
       <c r="A773" s="4" t="n"/>
@@ -22689,6 +23466,7 @@
       <c r="H773" s="4" t="n"/>
       <c r="I773" s="4" t="n"/>
       <c r="J773" s="3" t="n"/>
+      <c r="K773" s="3" t="n"/>
     </row>
     <row r="774">
       <c r="A774" s="4" t="n"/>
@@ -22701,6 +23479,7 @@
       <c r="H774" s="4" t="n"/>
       <c r="I774" s="4" t="n"/>
       <c r="J774" s="3" t="n"/>
+      <c r="K774" s="3" t="n"/>
     </row>
     <row r="775">
       <c r="A775" s="4" t="n"/>
@@ -22713,6 +23492,7 @@
       <c r="H775" s="4" t="n"/>
       <c r="I775" s="4" t="n"/>
       <c r="J775" s="3" t="n"/>
+      <c r="K775" s="3" t="n"/>
     </row>
     <row r="776">
       <c r="A776" s="4" t="n"/>
@@ -22725,6 +23505,7 @@
       <c r="H776" s="4" t="n"/>
       <c r="I776" s="4" t="n"/>
       <c r="J776" s="3" t="n"/>
+      <c r="K776" s="3" t="n"/>
     </row>
     <row r="777">
       <c r="A777" s="4" t="n"/>
@@ -22737,6 +23518,7 @@
       <c r="H777" s="4" t="n"/>
       <c r="I777" s="4" t="n"/>
       <c r="J777" s="3" t="n"/>
+      <c r="K777" s="3" t="n"/>
     </row>
     <row r="778">
       <c r="A778" s="4" t="n"/>
@@ -22749,6 +23531,7 @@
       <c r="H778" s="4" t="n"/>
       <c r="I778" s="4" t="n"/>
       <c r="J778" s="3" t="n"/>
+      <c r="K778" s="3" t="n"/>
     </row>
     <row r="779">
       <c r="A779" s="4" t="n"/>
@@ -22761,6 +23544,7 @@
       <c r="H779" s="4" t="n"/>
       <c r="I779" s="4" t="n"/>
       <c r="J779" s="3" t="n"/>
+      <c r="K779" s="3" t="n"/>
     </row>
     <row r="780">
       <c r="A780" s="4" t="n"/>
@@ -22773,6 +23557,7 @@
       <c r="H780" s="4" t="n"/>
       <c r="I780" s="4" t="n"/>
       <c r="J780" s="3" t="n"/>
+      <c r="K780" s="3" t="n"/>
     </row>
     <row r="781">
       <c r="A781" s="4" t="n"/>
@@ -22785,6 +23570,7 @@
       <c r="H781" s="4" t="n"/>
       <c r="I781" s="4" t="n"/>
       <c r="J781" s="3" t="n"/>
+      <c r="K781" s="3" t="n"/>
     </row>
     <row r="782">
       <c r="A782" s="4" t="n"/>
@@ -22797,6 +23583,7 @@
       <c r="H782" s="4" t="n"/>
       <c r="I782" s="4" t="n"/>
       <c r="J782" s="3" t="n"/>
+      <c r="K782" s="3" t="n"/>
     </row>
     <row r="783">
       <c r="A783" s="4" t="n"/>
@@ -22809,6 +23596,7 @@
       <c r="H783" s="4" t="n"/>
       <c r="I783" s="4" t="n"/>
       <c r="J783" s="3" t="n"/>
+      <c r="K783" s="3" t="n"/>
     </row>
     <row r="784">
       <c r="A784" s="4" t="n"/>
@@ -22821,6 +23609,7 @@
       <c r="H784" s="4" t="n"/>
       <c r="I784" s="4" t="n"/>
       <c r="J784" s="3" t="n"/>
+      <c r="K784" s="3" t="n"/>
     </row>
     <row r="785">
       <c r="A785" s="4" t="n"/>
@@ -22833,6 +23622,7 @@
       <c r="H785" s="4" t="n"/>
       <c r="I785" s="4" t="n"/>
       <c r="J785" s="3" t="n"/>
+      <c r="K785" s="3" t="n"/>
     </row>
     <row r="786">
       <c r="A786" s="4" t="n"/>
@@ -22845,6 +23635,7 @@
       <c r="H786" s="4" t="n"/>
       <c r="I786" s="4" t="n"/>
       <c r="J786" s="3" t="n"/>
+      <c r="K786" s="3" t="n"/>
     </row>
     <row r="787">
       <c r="A787" s="4" t="n"/>
@@ -22857,6 +23648,7 @@
       <c r="H787" s="4" t="n"/>
       <c r="I787" s="4" t="n"/>
       <c r="J787" s="3" t="n"/>
+      <c r="K787" s="3" t="n"/>
     </row>
     <row r="788">
       <c r="A788" s="4" t="n"/>
@@ -22869,6 +23661,7 @@
       <c r="H788" s="4" t="n"/>
       <c r="I788" s="4" t="n"/>
       <c r="J788" s="3" t="n"/>
+      <c r="K788" s="3" t="n"/>
     </row>
     <row r="789">
       <c r="A789" s="4" t="n"/>
@@ -22881,6 +23674,7 @@
       <c r="H789" s="4" t="n"/>
       <c r="I789" s="4" t="n"/>
       <c r="J789" s="3" t="n"/>
+      <c r="K789" s="3" t="n"/>
     </row>
     <row r="790">
       <c r="A790" s="4" t="n"/>
@@ -22893,6 +23687,7 @@
       <c r="H790" s="4" t="n"/>
       <c r="I790" s="4" t="n"/>
       <c r="J790" s="3" t="n"/>
+      <c r="K790" s="3" t="n"/>
     </row>
     <row r="791">
       <c r="A791" s="4" t="n"/>
@@ -22905,6 +23700,7 @@
       <c r="H791" s="4" t="n"/>
       <c r="I791" s="4" t="n"/>
       <c r="J791" s="3" t="n"/>
+      <c r="K791" s="3" t="n"/>
     </row>
     <row r="792">
       <c r="A792" s="4" t="n"/>
@@ -22917,6 +23713,7 @@
       <c r="H792" s="4" t="n"/>
       <c r="I792" s="4" t="n"/>
       <c r="J792" s="3" t="n"/>
+      <c r="K792" s="3" t="n"/>
     </row>
     <row r="793">
       <c r="A793" s="4" t="n"/>
@@ -22929,6 +23726,7 @@
       <c r="H793" s="4" t="n"/>
       <c r="I793" s="4" t="n"/>
       <c r="J793" s="3" t="n"/>
+      <c r="K793" s="3" t="n"/>
     </row>
     <row r="794">
       <c r="A794" s="4" t="n"/>
@@ -22941,6 +23739,7 @@
       <c r="H794" s="4" t="n"/>
       <c r="I794" s="4" t="n"/>
       <c r="J794" s="3" t="n"/>
+      <c r="K794" s="3" t="n"/>
     </row>
     <row r="795">
       <c r="A795" s="4" t="n"/>
@@ -22953,6 +23752,7 @@
       <c r="H795" s="4" t="n"/>
       <c r="I795" s="4" t="n"/>
       <c r="J795" s="3" t="n"/>
+      <c r="K795" s="3" t="n"/>
     </row>
     <row r="796">
       <c r="A796" s="4" t="n"/>
@@ -22965,6 +23765,7 @@
       <c r="H796" s="4" t="n"/>
       <c r="I796" s="4" t="n"/>
       <c r="J796" s="3" t="n"/>
+      <c r="K796" s="3" t="n"/>
     </row>
     <row r="797">
       <c r="A797" s="4" t="n"/>
@@ -22977,6 +23778,7 @@
       <c r="H797" s="4" t="n"/>
       <c r="I797" s="4" t="n"/>
       <c r="J797" s="3" t="n"/>
+      <c r="K797" s="3" t="n"/>
     </row>
     <row r="798">
       <c r="A798" s="4" t="n"/>
@@ -22989,6 +23791,7 @@
       <c r="H798" s="4" t="n"/>
       <c r="I798" s="4" t="n"/>
       <c r="J798" s="3" t="n"/>
+      <c r="K798" s="3" t="n"/>
     </row>
     <row r="799">
       <c r="A799" s="4" t="n"/>
@@ -23001,6 +23804,7 @@
       <c r="H799" s="4" t="n"/>
       <c r="I799" s="4" t="n"/>
       <c r="J799" s="3" t="n"/>
+      <c r="K799" s="3" t="n"/>
     </row>
     <row r="800">
       <c r="A800" s="4" t="n"/>
@@ -23013,6 +23817,7 @@
       <c r="H800" s="4" t="n"/>
       <c r="I800" s="4" t="n"/>
       <c r="J800" s="3" t="n"/>
+      <c r="K800" s="3" t="n"/>
     </row>
     <row r="801">
       <c r="A801" s="4" t="n"/>
@@ -23025,6 +23830,7 @@
       <c r="H801" s="4" t="n"/>
       <c r="I801" s="4" t="n"/>
       <c r="J801" s="3" t="n"/>
+      <c r="K801" s="3" t="n"/>
     </row>
     <row r="802">
       <c r="A802" s="4" t="n"/>
@@ -23037,6 +23843,7 @@
       <c r="H802" s="4" t="n"/>
       <c r="I802" s="4" t="n"/>
       <c r="J802" s="3" t="n"/>
+      <c r="K802" s="3" t="n"/>
     </row>
     <row r="803">
       <c r="A803" s="4" t="n"/>
@@ -23049,6 +23856,7 @@
       <c r="H803" s="4" t="n"/>
       <c r="I803" s="4" t="n"/>
       <c r="J803" s="3" t="n"/>
+      <c r="K803" s="3" t="n"/>
     </row>
     <row r="804">
       <c r="A804" s="4" t="n"/>
@@ -23061,6 +23869,7 @@
       <c r="H804" s="4" t="n"/>
       <c r="I804" s="4" t="n"/>
       <c r="J804" s="3" t="n"/>
+      <c r="K804" s="3" t="n"/>
     </row>
     <row r="805">
       <c r="A805" s="4" t="n"/>
@@ -23073,6 +23882,7 @@
       <c r="H805" s="4" t="n"/>
       <c r="I805" s="4" t="n"/>
       <c r="J805" s="3" t="n"/>
+      <c r="K805" s="3" t="n"/>
     </row>
     <row r="806">
       <c r="A806" s="4" t="n"/>
@@ -23085,6 +23895,7 @@
       <c r="H806" s="4" t="n"/>
       <c r="I806" s="4" t="n"/>
       <c r="J806" s="3" t="n"/>
+      <c r="K806" s="3" t="n"/>
     </row>
     <row r="807">
       <c r="A807" s="4" t="n"/>
@@ -23097,6 +23908,7 @@
       <c r="H807" s="4" t="n"/>
       <c r="I807" s="4" t="n"/>
       <c r="J807" s="3" t="n"/>
+      <c r="K807" s="3" t="n"/>
     </row>
     <row r="808">
       <c r="A808" s="4" t="n"/>
@@ -23109,6 +23921,7 @@
       <c r="H808" s="4" t="n"/>
       <c r="I808" s="4" t="n"/>
       <c r="J808" s="3" t="n"/>
+      <c r="K808" s="3" t="n"/>
     </row>
     <row r="809">
       <c r="A809" s="4" t="n"/>
@@ -23121,6 +23934,7 @@
       <c r="H809" s="4" t="n"/>
       <c r="I809" s="4" t="n"/>
       <c r="J809" s="3" t="n"/>
+      <c r="K809" s="3" t="n"/>
     </row>
     <row r="810">
       <c r="A810" s="4" t="n"/>
@@ -23133,6 +23947,7 @@
       <c r="H810" s="4" t="n"/>
       <c r="I810" s="4" t="n"/>
       <c r="J810" s="3" t="n"/>
+      <c r="K810" s="3" t="n"/>
     </row>
     <row r="811">
       <c r="A811" s="4" t="n"/>
@@ -23145,6 +23960,7 @@
       <c r="H811" s="4" t="n"/>
       <c r="I811" s="4" t="n"/>
       <c r="J811" s="3" t="n"/>
+      <c r="K811" s="3" t="n"/>
     </row>
     <row r="812">
       <c r="A812" s="4" t="n"/>
@@ -23157,6 +23973,7 @@
       <c r="H812" s="4" t="n"/>
       <c r="I812" s="4" t="n"/>
       <c r="J812" s="3" t="n"/>
+      <c r="K812" s="3" t="n"/>
     </row>
     <row r="813">
       <c r="A813" s="4" t="n"/>
@@ -23169,6 +23986,7 @@
       <c r="H813" s="4" t="n"/>
       <c r="I813" s="4" t="n"/>
       <c r="J813" s="3" t="n"/>
+      <c r="K813" s="3" t="n"/>
     </row>
     <row r="814">
       <c r="A814" s="4" t="n"/>
@@ -23181,6 +23999,7 @@
       <c r="H814" s="4" t="n"/>
       <c r="I814" s="4" t="n"/>
       <c r="J814" s="3" t="n"/>
+      <c r="K814" s="3" t="n"/>
     </row>
     <row r="815">
       <c r="A815" s="4" t="n"/>
@@ -23193,6 +24012,7 @@
       <c r="H815" s="4" t="n"/>
       <c r="I815" s="4" t="n"/>
       <c r="J815" s="3" t="n"/>
+      <c r="K815" s="3" t="n"/>
     </row>
     <row r="816">
       <c r="A816" s="4" t="n"/>
@@ -23205,6 +24025,7 @@
       <c r="H816" s="4" t="n"/>
       <c r="I816" s="4" t="n"/>
       <c r="J816" s="3" t="n"/>
+      <c r="K816" s="3" t="n"/>
     </row>
     <row r="817">
       <c r="A817" s="4" t="n"/>
@@ -23217,6 +24038,7 @@
       <c r="H817" s="4" t="n"/>
       <c r="I817" s="4" t="n"/>
       <c r="J817" s="3" t="n"/>
+      <c r="K817" s="3" t="n"/>
     </row>
     <row r="818">
       <c r="A818" s="4" t="n"/>
@@ -23229,6 +24051,7 @@
       <c r="H818" s="4" t="n"/>
       <c r="I818" s="4" t="n"/>
       <c r="J818" s="3" t="n"/>
+      <c r="K818" s="3" t="n"/>
     </row>
     <row r="819">
       <c r="A819" s="4" t="n"/>
@@ -23241,6 +24064,7 @@
       <c r="H819" s="4" t="n"/>
       <c r="I819" s="4" t="n"/>
       <c r="J819" s="3" t="n"/>
+      <c r="K819" s="3" t="n"/>
     </row>
     <row r="820">
       <c r="A820" s="4" t="n"/>
@@ -23253,6 +24077,7 @@
       <c r="H820" s="4" t="n"/>
       <c r="I820" s="4" t="n"/>
       <c r="J820" s="3" t="n"/>
+      <c r="K820" s="3" t="n"/>
     </row>
     <row r="821">
       <c r="A821" s="4" t="n"/>
@@ -23265,6 +24090,7 @@
       <c r="H821" s="4" t="n"/>
       <c r="I821" s="4" t="n"/>
       <c r="J821" s="3" t="n"/>
+      <c r="K821" s="3" t="n"/>
     </row>
     <row r="822">
       <c r="A822" s="4" t="n"/>
@@ -23277,6 +24103,7 @@
       <c r="H822" s="4" t="n"/>
       <c r="I822" s="4" t="n"/>
       <c r="J822" s="3" t="n"/>
+      <c r="K822" s="3" t="n"/>
     </row>
     <row r="823">
       <c r="A823" s="4" t="n"/>
@@ -23289,6 +24116,7 @@
       <c r="H823" s="4" t="n"/>
       <c r="I823" s="4" t="n"/>
       <c r="J823" s="3" t="n"/>
+      <c r="K823" s="3" t="n"/>
     </row>
     <row r="824">
       <c r="A824" s="4" t="n"/>
@@ -23301,6 +24129,7 @@
       <c r="H824" s="4" t="n"/>
       <c r="I824" s="4" t="n"/>
       <c r="J824" s="3" t="n"/>
+      <c r="K824" s="3" t="n"/>
     </row>
     <row r="825">
       <c r="A825" s="4" t="n"/>
@@ -23313,6 +24142,7 @@
       <c r="H825" s="4" t="n"/>
       <c r="I825" s="4" t="n"/>
       <c r="J825" s="3" t="n"/>
+      <c r="K825" s="3" t="n"/>
     </row>
     <row r="826">
       <c r="A826" s="4" t="n"/>
@@ -23325,6 +24155,7 @@
       <c r="H826" s="4" t="n"/>
       <c r="I826" s="4" t="n"/>
       <c r="J826" s="3" t="n"/>
+      <c r="K826" s="3" t="n"/>
     </row>
     <row r="827">
       <c r="A827" s="4" t="n"/>
@@ -23337,6 +24168,7 @@
       <c r="H827" s="4" t="n"/>
       <c r="I827" s="4" t="n"/>
       <c r="J827" s="3" t="n"/>
+      <c r="K827" s="3" t="n"/>
     </row>
     <row r="828">
       <c r="A828" s="4" t="n"/>
@@ -23349,6 +24181,7 @@
       <c r="H828" s="4" t="n"/>
       <c r="I828" s="4" t="n"/>
       <c r="J828" s="3" t="n"/>
+      <c r="K828" s="3" t="n"/>
     </row>
     <row r="829">
       <c r="A829" s="4" t="n"/>
@@ -23361,6 +24194,7 @@
       <c r="H829" s="4" t="n"/>
       <c r="I829" s="4" t="n"/>
       <c r="J829" s="3" t="n"/>
+      <c r="K829" s="3" t="n"/>
     </row>
     <row r="830">
       <c r="A830" s="4" t="n"/>
@@ -23373,6 +24207,7 @@
       <c r="H830" s="4" t="n"/>
       <c r="I830" s="4" t="n"/>
       <c r="J830" s="3" t="n"/>
+      <c r="K830" s="3" t="n"/>
     </row>
     <row r="831">
       <c r="A831" s="4" t="n"/>
@@ -23385,6 +24220,7 @@
       <c r="H831" s="4" t="n"/>
       <c r="I831" s="4" t="n"/>
       <c r="J831" s="3" t="n"/>
+      <c r="K831" s="3" t="n"/>
     </row>
     <row r="832">
       <c r="A832" s="4" t="n"/>
@@ -23397,6 +24233,7 @@
       <c r="H832" s="4" t="n"/>
       <c r="I832" s="4" t="n"/>
       <c r="J832" s="3" t="n"/>
+      <c r="K832" s="3" t="n"/>
     </row>
     <row r="833">
       <c r="A833" s="4" t="n"/>
@@ -23409,6 +24246,7 @@
       <c r="H833" s="4" t="n"/>
       <c r="I833" s="4" t="n"/>
       <c r="J833" s="3" t="n"/>
+      <c r="K833" s="3" t="n"/>
     </row>
     <row r="834">
       <c r="A834" s="4" t="n"/>
@@ -23421,6 +24259,7 @@
       <c r="H834" s="4" t="n"/>
       <c r="I834" s="4" t="n"/>
       <c r="J834" s="3" t="n"/>
+      <c r="K834" s="3" t="n"/>
     </row>
     <row r="835">
       <c r="A835" s="4" t="n"/>
@@ -23433,6 +24272,7 @@
       <c r="H835" s="4" t="n"/>
       <c r="I835" s="4" t="n"/>
       <c r="J835" s="3" t="n"/>
+      <c r="K835" s="3" t="n"/>
     </row>
     <row r="836">
       <c r="A836" s="4" t="n"/>
@@ -23445,6 +24285,7 @@
       <c r="H836" s="4" t="n"/>
       <c r="I836" s="4" t="n"/>
       <c r="J836" s="3" t="n"/>
+      <c r="K836" s="3" t="n"/>
     </row>
     <row r="837">
       <c r="A837" s="4" t="n"/>
@@ -23457,6 +24298,7 @@
       <c r="H837" s="4" t="n"/>
       <c r="I837" s="4" t="n"/>
       <c r="J837" s="3" t="n"/>
+      <c r="K837" s="3" t="n"/>
     </row>
     <row r="838">
       <c r="A838" s="4" t="n"/>
@@ -23469,6 +24311,7 @@
       <c r="H838" s="4" t="n"/>
       <c r="I838" s="4" t="n"/>
       <c r="J838" s="3" t="n"/>
+      <c r="K838" s="3" t="n"/>
     </row>
     <row r="839">
       <c r="A839" s="4" t="n"/>
@@ -23481,6 +24324,7 @@
       <c r="H839" s="4" t="n"/>
       <c r="I839" s="4" t="n"/>
       <c r="J839" s="3" t="n"/>
+      <c r="K839" s="3" t="n"/>
     </row>
     <row r="840">
       <c r="A840" s="4" t="n"/>
@@ -23493,6 +24337,7 @@
       <c r="H840" s="4" t="n"/>
       <c r="I840" s="4" t="n"/>
       <c r="J840" s="3" t="n"/>
+      <c r="K840" s="3" t="n"/>
     </row>
     <row r="841">
       <c r="A841" s="4" t="n"/>
@@ -23505,6 +24350,7 @@
       <c r="H841" s="4" t="n"/>
       <c r="I841" s="4" t="n"/>
       <c r="J841" s="3" t="n"/>
+      <c r="K841" s="3" t="n"/>
     </row>
     <row r="842">
       <c r="A842" s="4" t="n"/>
@@ -23517,6 +24363,7 @@
       <c r="H842" s="4" t="n"/>
       <c r="I842" s="4" t="n"/>
       <c r="J842" s="3" t="n"/>
+      <c r="K842" s="3" t="n"/>
     </row>
     <row r="843">
       <c r="A843" s="4" t="n"/>
@@ -23529,6 +24376,7 @@
       <c r="H843" s="4" t="n"/>
       <c r="I843" s="4" t="n"/>
       <c r="J843" s="3" t="n"/>
+      <c r="K843" s="3" t="n"/>
     </row>
     <row r="844">
       <c r="A844" s="4" t="n"/>
@@ -23541,6 +24389,7 @@
       <c r="H844" s="4" t="n"/>
       <c r="I844" s="4" t="n"/>
       <c r="J844" s="3" t="n"/>
+      <c r="K844" s="3" t="n"/>
     </row>
     <row r="845">
       <c r="A845" s="4" t="n"/>
@@ -23553,6 +24402,7 @@
       <c r="H845" s="4" t="n"/>
       <c r="I845" s="4" t="n"/>
       <c r="J845" s="3" t="n"/>
+      <c r="K845" s="3" t="n"/>
     </row>
     <row r="846">
       <c r="A846" s="4" t="n"/>
@@ -23565,6 +24415,7 @@
       <c r="H846" s="4" t="n"/>
       <c r="I846" s="4" t="n"/>
       <c r="J846" s="3" t="n"/>
+      <c r="K846" s="3" t="n"/>
     </row>
     <row r="847">
       <c r="A847" s="4" t="n"/>
@@ -23577,6 +24428,7 @@
       <c r="H847" s="4" t="n"/>
       <c r="I847" s="4" t="n"/>
       <c r="J847" s="3" t="n"/>
+      <c r="K847" s="3" t="n"/>
     </row>
     <row r="848">
       <c r="A848" s="4" t="n"/>
@@ -23589,6 +24441,7 @@
       <c r="H848" s="4" t="n"/>
       <c r="I848" s="4" t="n"/>
       <c r="J848" s="3" t="n"/>
+      <c r="K848" s="3" t="n"/>
     </row>
     <row r="849">
       <c r="A849" s="4" t="n"/>
@@ -23601,6 +24454,7 @@
       <c r="H849" s="4" t="n"/>
       <c r="I849" s="4" t="n"/>
       <c r="J849" s="3" t="n"/>
+      <c r="K849" s="3" t="n"/>
     </row>
     <row r="850">
       <c r="A850" s="4" t="n"/>
@@ -23613,6 +24467,7 @@
       <c r="H850" s="4" t="n"/>
       <c r="I850" s="4" t="n"/>
       <c r="J850" s="3" t="n"/>
+      <c r="K850" s="3" t="n"/>
     </row>
     <row r="851">
       <c r="A851" s="4" t="n"/>
@@ -23625,6 +24480,7 @@
       <c r="H851" s="4" t="n"/>
       <c r="I851" s="4" t="n"/>
       <c r="J851" s="3" t="n"/>
+      <c r="K851" s="3" t="n"/>
     </row>
     <row r="852">
       <c r="A852" s="4" t="n"/>
@@ -23637,6 +24493,7 @@
       <c r="H852" s="4" t="n"/>
       <c r="I852" s="4" t="n"/>
       <c r="J852" s="3" t="n"/>
+      <c r="K852" s="3" t="n"/>
     </row>
     <row r="853">
       <c r="A853" s="4" t="n"/>
@@ -23649,6 +24506,7 @@
       <c r="H853" s="4" t="n"/>
       <c r="I853" s="4" t="n"/>
       <c r="J853" s="3" t="n"/>
+      <c r="K853" s="3" t="n"/>
     </row>
     <row r="854">
       <c r="A854" s="4" t="n"/>
@@ -23661,6 +24519,7 @@
       <c r="H854" s="4" t="n"/>
       <c r="I854" s="4" t="n"/>
       <c r="J854" s="3" t="n"/>
+      <c r="K854" s="3" t="n"/>
     </row>
     <row r="855">
       <c r="A855" s="4" t="n"/>
@@ -23673,6 +24532,7 @@
       <c r="H855" s="4" t="n"/>
       <c r="I855" s="4" t="n"/>
       <c r="J855" s="3" t="n"/>
+      <c r="K855" s="3" t="n"/>
     </row>
     <row r="856">
       <c r="A856" s="4" t="n"/>
@@ -23685,6 +24545,7 @@
       <c r="H856" s="4" t="n"/>
       <c r="I856" s="4" t="n"/>
       <c r="J856" s="3" t="n"/>
+      <c r="K856" s="3" t="n"/>
     </row>
     <row r="857">
       <c r="A857" s="4" t="n"/>
@@ -23697,6 +24558,7 @@
       <c r="H857" s="4" t="n"/>
       <c r="I857" s="4" t="n"/>
       <c r="J857" s="3" t="n"/>
+      <c r="K857" s="3" t="n"/>
     </row>
     <row r="858">
       <c r="A858" s="4" t="n"/>
@@ -23709,6 +24571,7 @@
       <c r="H858" s="4" t="n"/>
       <c r="I858" s="4" t="n"/>
       <c r="J858" s="3" t="n"/>
+      <c r="K858" s="3" t="n"/>
     </row>
     <row r="859">
       <c r="A859" s="4" t="n"/>
@@ -23721,6 +24584,7 @@
       <c r="H859" s="4" t="n"/>
       <c r="I859" s="4" t="n"/>
       <c r="J859" s="3" t="n"/>
+      <c r="K859" s="3" t="n"/>
     </row>
     <row r="860">
       <c r="A860" s="4" t="n"/>
@@ -23733,6 +24597,7 @@
       <c r="H860" s="4" t="n"/>
       <c r="I860" s="4" t="n"/>
       <c r="J860" s="3" t="n"/>
+      <c r="K860" s="3" t="n"/>
     </row>
     <row r="861">
       <c r="A861" s="4" t="n"/>
@@ -23745,6 +24610,7 @@
       <c r="H861" s="4" t="n"/>
       <c r="I861" s="4" t="n"/>
       <c r="J861" s="3" t="n"/>
+      <c r="K861" s="3" t="n"/>
     </row>
     <row r="862">
       <c r="A862" s="4" t="n"/>
@@ -23757,6 +24623,7 @@
       <c r="H862" s="4" t="n"/>
       <c r="I862" s="4" t="n"/>
       <c r="J862" s="3" t="n"/>
+      <c r="K862" s="3" t="n"/>
     </row>
     <row r="863">
       <c r="A863" s="4" t="n"/>
@@ -23769,6 +24636,7 @@
       <c r="H863" s="4" t="n"/>
       <c r="I863" s="4" t="n"/>
       <c r="J863" s="3" t="n"/>
+      <c r="K863" s="3" t="n"/>
     </row>
     <row r="864">
       <c r="A864" s="4" t="n"/>
@@ -23781,6 +24649,7 @@
       <c r="H864" s="4" t="n"/>
       <c r="I864" s="4" t="n"/>
       <c r="J864" s="3" t="n"/>
+      <c r="K864" s="3" t="n"/>
     </row>
     <row r="865">
       <c r="A865" s="4" t="n"/>
@@ -23793,6 +24662,7 @@
       <c r="H865" s="4" t="n"/>
       <c r="I865" s="4" t="n"/>
       <c r="J865" s="3" t="n"/>
+      <c r="K865" s="3" t="n"/>
     </row>
     <row r="866">
       <c r="A866" s="4" t="n"/>
@@ -23805,6 +24675,7 @@
       <c r="H866" s="4" t="n"/>
       <c r="I866" s="4" t="n"/>
       <c r="J866" s="3" t="n"/>
+      <c r="K866" s="3" t="n"/>
     </row>
     <row r="867">
       <c r="A867" s="4" t="n"/>
@@ -23817,6 +24688,7 @@
       <c r="H867" s="4" t="n"/>
       <c r="I867" s="4" t="n"/>
       <c r="J867" s="3" t="n"/>
+      <c r="K867" s="3" t="n"/>
     </row>
     <row r="868">
       <c r="A868" s="4" t="n"/>
@@ -23829,6 +24701,7 @@
       <c r="H868" s="4" t="n"/>
       <c r="I868" s="4" t="n"/>
       <c r="J868" s="3" t="n"/>
+      <c r="K868" s="3" t="n"/>
     </row>
     <row r="869">
       <c r="A869" s="4" t="n"/>
@@ -23841,6 +24714,7 @@
       <c r="H869" s="4" t="n"/>
       <c r="I869" s="4" t="n"/>
       <c r="J869" s="3" t="n"/>
+      <c r="K869" s="3" t="n"/>
     </row>
     <row r="870">
       <c r="A870" s="4" t="n"/>
@@ -23853,6 +24727,7 @@
       <c r="H870" s="4" t="n"/>
       <c r="I870" s="4" t="n"/>
       <c r="J870" s="3" t="n"/>
+      <c r="K870" s="3" t="n"/>
     </row>
     <row r="871">
       <c r="A871" s="4" t="n"/>
@@ -23865,6 +24740,7 @@
       <c r="H871" s="4" t="n"/>
       <c r="I871" s="4" t="n"/>
       <c r="J871" s="3" t="n"/>
+      <c r="K871" s="3" t="n"/>
     </row>
     <row r="872">
       <c r="A872" s="4" t="n"/>
@@ -23877,6 +24753,7 @@
       <c r="H872" s="4" t="n"/>
       <c r="I872" s="4" t="n"/>
       <c r="J872" s="3" t="n"/>
+      <c r="K872" s="3" t="n"/>
     </row>
     <row r="873">
       <c r="A873" s="4" t="n"/>
@@ -23889,6 +24766,7 @@
       <c r="H873" s="4" t="n"/>
       <c r="I873" s="4" t="n"/>
       <c r="J873" s="3" t="n"/>
+      <c r="K873" s="3" t="n"/>
     </row>
     <row r="874">
       <c r="A874" s="4" t="n"/>
@@ -23901,6 +24779,7 @@
       <c r="H874" s="4" t="n"/>
       <c r="I874" s="4" t="n"/>
       <c r="J874" s="3" t="n"/>
+      <c r="K874" s="3" t="n"/>
     </row>
     <row r="875">
       <c r="A875" s="4" t="n"/>
@@ -23913,6 +24792,7 @@
       <c r="H875" s="4" t="n"/>
       <c r="I875" s="4" t="n"/>
       <c r="J875" s="3" t="n"/>
+      <c r="K875" s="3" t="n"/>
     </row>
     <row r="876">
       <c r="A876" s="4" t="n"/>
@@ -23925,6 +24805,7 @@
       <c r="H876" s="4" t="n"/>
       <c r="I876" s="4" t="n"/>
       <c r="J876" s="3" t="n"/>
+      <c r="K876" s="3" t="n"/>
     </row>
     <row r="877">
       <c r="A877" s="4" t="n"/>
@@ -23937,6 +24818,7 @@
       <c r="H877" s="4" t="n"/>
       <c r="I877" s="4" t="n"/>
       <c r="J877" s="3" t="n"/>
+      <c r="K877" s="3" t="n"/>
     </row>
     <row r="878">
       <c r="A878" s="4" t="n"/>
@@ -23949,6 +24831,7 @@
       <c r="H878" s="4" t="n"/>
       <c r="I878" s="4" t="n"/>
       <c r="J878" s="3" t="n"/>
+      <c r="K878" s="3" t="n"/>
     </row>
     <row r="879">
       <c r="A879" s="4" t="n"/>
@@ -23961,6 +24844,7 @@
       <c r="H879" s="4" t="n"/>
       <c r="I879" s="4" t="n"/>
       <c r="J879" s="3" t="n"/>
+      <c r="K879" s="3" t="n"/>
     </row>
     <row r="880">
       <c r="A880" s="4" t="n"/>
@@ -23973,6 +24857,7 @@
       <c r="H880" s="4" t="n"/>
       <c r="I880" s="4" t="n"/>
       <c r="J880" s="3" t="n"/>
+      <c r="K880" s="3" t="n"/>
     </row>
     <row r="881">
       <c r="A881" s="4" t="n"/>
@@ -23985,6 +24870,7 @@
       <c r="H881" s="4" t="n"/>
       <c r="I881" s="4" t="n"/>
       <c r="J881" s="3" t="n"/>
+      <c r="K881" s="3" t="n"/>
     </row>
     <row r="882">
       <c r="A882" s="4" t="n"/>
@@ -23997,6 +24883,7 @@
       <c r="H882" s="4" t="n"/>
       <c r="I882" s="4" t="n"/>
       <c r="J882" s="3" t="n"/>
+      <c r="K882" s="3" t="n"/>
     </row>
     <row r="883">
       <c r="A883" s="4" t="n"/>
@@ -24009,6 +24896,7 @@
       <c r="H883" s="4" t="n"/>
       <c r="I883" s="4" t="n"/>
       <c r="J883" s="3" t="n"/>
+      <c r="K883" s="3" t="n"/>
     </row>
     <row r="884">
       <c r="A884" s="4" t="n"/>
@@ -24021,6 +24909,7 @@
       <c r="H884" s="4" t="n"/>
       <c r="I884" s="4" t="n"/>
       <c r="J884" s="3" t="n"/>
+      <c r="K884" s="3" t="n"/>
     </row>
     <row r="885">
       <c r="A885" s="4" t="n"/>
@@ -24033,6 +24922,7 @@
       <c r="H885" s="4" t="n"/>
       <c r="I885" s="4" t="n"/>
       <c r="J885" s="3" t="n"/>
+      <c r="K885" s="3" t="n"/>
     </row>
     <row r="886">
       <c r="A886" s="4" t="n"/>
@@ -24045,6 +24935,7 @@
       <c r="H886" s="4" t="n"/>
       <c r="I886" s="4" t="n"/>
       <c r="J886" s="3" t="n"/>
+      <c r="K886" s="3" t="n"/>
     </row>
     <row r="887">
       <c r="A887" s="4" t="n"/>
@@ -24057,6 +24948,7 @@
       <c r="H887" s="4" t="n"/>
       <c r="I887" s="4" t="n"/>
       <c r="J887" s="3" t="n"/>
+      <c r="K887" s="3" t="n"/>
     </row>
     <row r="888">
       <c r="A888" s="4" t="n"/>
@@ -24069,6 +24961,7 @@
       <c r="H888" s="4" t="n"/>
       <c r="I888" s="4" t="n"/>
       <c r="J888" s="3" t="n"/>
+      <c r="K888" s="3" t="n"/>
     </row>
     <row r="889">
       <c r="A889" s="4" t="n"/>
@@ -24081,6 +24974,7 @@
       <c r="H889" s="4" t="n"/>
       <c r="I889" s="4" t="n"/>
       <c r="J889" s="3" t="n"/>
+      <c r="K889" s="3" t="n"/>
     </row>
     <row r="890">
       <c r="A890" s="4" t="n"/>
@@ -24093,6 +24987,7 @@
       <c r="H890" s="4" t="n"/>
       <c r="I890" s="4" t="n"/>
       <c r="J890" s="3" t="n"/>
+      <c r="K890" s="3" t="n"/>
     </row>
     <row r="891">
       <c r="A891" s="4" t="n"/>
@@ -24105,6 +25000,7 @@
       <c r="H891" s="4" t="n"/>
       <c r="I891" s="4" t="n"/>
       <c r="J891" s="3" t="n"/>
+      <c r="K891" s="3" t="n"/>
     </row>
     <row r="892">
       <c r="A892" s="4" t="n"/>
@@ -24117,6 +25013,7 @@
       <c r="H892" s="4" t="n"/>
       <c r="I892" s="4" t="n"/>
       <c r="J892" s="3" t="n"/>
+      <c r="K892" s="3" t="n"/>
     </row>
     <row r="893">
       <c r="A893" s="4" t="n"/>
@@ -24129,6 +25026,7 @@
       <c r="H893" s="4" t="n"/>
       <c r="I893" s="4" t="n"/>
       <c r="J893" s="3" t="n"/>
+      <c r="K893" s="3" t="n"/>
     </row>
     <row r="894">
       <c r="A894" s="4" t="n"/>
@@ -24141,6 +25039,7 @@
       <c r="H894" s="4" t="n"/>
       <c r="I894" s="4" t="n"/>
       <c r="J894" s="3" t="n"/>
+      <c r="K894" s="3" t="n"/>
     </row>
     <row r="895">
       <c r="A895" s="4" t="n"/>
@@ -24153,6 +25052,7 @@
       <c r="H895" s="4" t="n"/>
       <c r="I895" s="4" t="n"/>
       <c r="J895" s="3" t="n"/>
+      <c r="K895" s="3" t="n"/>
     </row>
     <row r="896">
       <c r="A896" s="4" t="n"/>
@@ -24165,6 +25065,7 @@
       <c r="H896" s="4" t="n"/>
       <c r="I896" s="4" t="n"/>
       <c r="J896" s="3" t="n"/>
+      <c r="K896" s="3" t="n"/>
     </row>
     <row r="897">
       <c r="A897" s="4" t="n"/>
@@ -24177,6 +25078,7 @@
       <c r="H897" s="4" t="n"/>
       <c r="I897" s="4" t="n"/>
       <c r="J897" s="3" t="n"/>
+      <c r="K897" s="3" t="n"/>
     </row>
     <row r="898">
       <c r="A898" s="4" t="n"/>
@@ -24189,6 +25091,7 @@
       <c r="H898" s="4" t="n"/>
       <c r="I898" s="4" t="n"/>
       <c r="J898" s="3" t="n"/>
+      <c r="K898" s="3" t="n"/>
     </row>
     <row r="899">
       <c r="A899" s="4" t="n"/>
@@ -24201,6 +25104,7 @@
       <c r="H899" s="4" t="n"/>
       <c r="I899" s="4" t="n"/>
       <c r="J899" s="3" t="n"/>
+      <c r="K899" s="3" t="n"/>
     </row>
     <row r="900">
       <c r="A900" s="4" t="n"/>
@@ -24213,6 +25117,7 @@
       <c r="H900" s="4" t="n"/>
       <c r="I900" s="4" t="n"/>
       <c r="J900" s="3" t="n"/>
+      <c r="K900" s="3" t="n"/>
     </row>
     <row r="901">
       <c r="A901" s="4" t="n"/>
@@ -24225,6 +25130,7 @@
       <c r="H901" s="4" t="n"/>
       <c r="I901" s="4" t="n"/>
       <c r="J901" s="3" t="n"/>
+      <c r="K901" s="3" t="n"/>
     </row>
     <row r="902">
       <c r="A902" s="4" t="n"/>
@@ -24237,6 +25143,7 @@
       <c r="H902" s="4" t="n"/>
       <c r="I902" s="4" t="n"/>
       <c r="J902" s="3" t="n"/>
+      <c r="K902" s="3" t="n"/>
     </row>
     <row r="903">
       <c r="A903" s="4" t="n"/>
@@ -24249,6 +25156,7 @@
       <c r="H903" s="4" t="n"/>
       <c r="I903" s="4" t="n"/>
       <c r="J903" s="3" t="n"/>
+      <c r="K903" s="3" t="n"/>
     </row>
     <row r="904">
       <c r="A904" s="4" t="n"/>
@@ -24261,6 +25169,7 @@
       <c r="H904" s="4" t="n"/>
       <c r="I904" s="4" t="n"/>
       <c r="J904" s="3" t="n"/>
+      <c r="K904" s="3" t="n"/>
     </row>
     <row r="905">
       <c r="A905" s="4" t="n"/>
@@ -24273,6 +25182,7 @@
       <c r="H905" s="4" t="n"/>
       <c r="I905" s="4" t="n"/>
       <c r="J905" s="3" t="n"/>
+      <c r="K905" s="3" t="n"/>
     </row>
     <row r="906">
       <c r="A906" s="4" t="n"/>
@@ -24285,6 +25195,7 @@
       <c r="H906" s="4" t="n"/>
       <c r="I906" s="4" t="n"/>
       <c r="J906" s="3" t="n"/>
+      <c r="K906" s="3" t="n"/>
     </row>
     <row r="907">
       <c r="A907" s="4" t="n"/>
@@ -24297,6 +25208,7 @@
       <c r="H907" s="4" t="n"/>
       <c r="I907" s="4" t="n"/>
       <c r="J907" s="3" t="n"/>
+      <c r="K907" s="3" t="n"/>
     </row>
     <row r="908">
       <c r="A908" s="4" t="n"/>
@@ -24309,6 +25221,7 @@
       <c r="H908" s="4" t="n"/>
       <c r="I908" s="4" t="n"/>
       <c r="J908" s="3" t="n"/>
+      <c r="K908" s="3" t="n"/>
     </row>
     <row r="909">
       <c r="A909" s="4" t="n"/>
@@ -24321,6 +25234,7 @@
       <c r="H909" s="4" t="n"/>
       <c r="I909" s="4" t="n"/>
       <c r="J909" s="3" t="n"/>
+      <c r="K909" s="3" t="n"/>
     </row>
     <row r="910">
       <c r="A910" s="4" t="n"/>
@@ -24333,6 +25247,7 @@
       <c r="H910" s="4" t="n"/>
       <c r="I910" s="4" t="n"/>
       <c r="J910" s="3" t="n"/>
+      <c r="K910" s="3" t="n"/>
     </row>
     <row r="911">
       <c r="A911" s="4" t="n"/>
@@ -24345,6 +25260,7 @@
       <c r="H911" s="4" t="n"/>
       <c r="I911" s="4" t="n"/>
       <c r="J911" s="3" t="n"/>
+      <c r="K911" s="3" t="n"/>
     </row>
     <row r="912">
       <c r="A912" s="4" t="n"/>
@@ -24357,6 +25273,7 @@
       <c r="H912" s="4" t="n"/>
       <c r="I912" s="4" t="n"/>
       <c r="J912" s="3" t="n"/>
+      <c r="K912" s="3" t="n"/>
     </row>
     <row r="913">
       <c r="A913" s="4" t="n"/>
@@ -24369,6 +25286,7 @@
       <c r="H913" s="4" t="n"/>
       <c r="I913" s="4" t="n"/>
       <c r="J913" s="3" t="n"/>
+      <c r="K913" s="3" t="n"/>
     </row>
     <row r="914">
       <c r="A914" s="4" t="n"/>
@@ -24381,6 +25299,7 @@
       <c r="H914" s="4" t="n"/>
       <c r="I914" s="4" t="n"/>
       <c r="J914" s="3" t="n"/>
+      <c r="K914" s="3" t="n"/>
     </row>
     <row r="915">
       <c r="A915" s="4" t="n"/>
@@ -24393,6 +25312,7 @@
       <c r="H915" s="4" t="n"/>
       <c r="I915" s="4" t="n"/>
       <c r="J915" s="3" t="n"/>
+      <c r="K915" s="3" t="n"/>
     </row>
     <row r="916">
       <c r="A916" s="4" t="n"/>
@@ -24405,6 +25325,7 @@
       <c r="H916" s="4" t="n"/>
       <c r="I916" s="4" t="n"/>
       <c r="J916" s="3" t="n"/>
+      <c r="K916" s="3" t="n"/>
     </row>
     <row r="917">
       <c r="A917" s="4" t="n"/>
@@ -24417,6 +25338,7 @@
       <c r="H917" s="4" t="n"/>
       <c r="I917" s="4" t="n"/>
       <c r="J917" s="3" t="n"/>
+      <c r="K917" s="3" t="n"/>
     </row>
     <row r="918">
       <c r="A918" s="4" t="n"/>
@@ -24429,6 +25351,7 @@
       <c r="H918" s="4" t="n"/>
       <c r="I918" s="4" t="n"/>
       <c r="J918" s="3" t="n"/>
+      <c r="K918" s="3" t="n"/>
     </row>
     <row r="919">
       <c r="A919" s="4" t="n"/>
@@ -24441,6 +25364,7 @@
       <c r="H919" s="4" t="n"/>
       <c r="I919" s="4" t="n"/>
       <c r="J919" s="3" t="n"/>
+      <c r="K919" s="3" t="n"/>
     </row>
     <row r="920">
       <c r="A920" s="4" t="n"/>
@@ -24453,6 +25377,7 @@
       <c r="H920" s="4" t="n"/>
       <c r="I920" s="4" t="n"/>
       <c r="J920" s="3" t="n"/>
+      <c r="K920" s="3" t="n"/>
     </row>
     <row r="921">
       <c r="A921" s="4" t="n"/>
@@ -24465,6 +25390,7 @@
       <c r="H921" s="4" t="n"/>
       <c r="I921" s="4" t="n"/>
       <c r="J921" s="3" t="n"/>
+      <c r="K921" s="3" t="n"/>
     </row>
     <row r="922">
       <c r="A922" s="4" t="n"/>
@@ -24477,6 +25403,7 @@
       <c r="H922" s="4" t="n"/>
       <c r="I922" s="4" t="n"/>
       <c r="J922" s="3" t="n"/>
+      <c r="K922" s="3" t="n"/>
     </row>
     <row r="923">
       <c r="A923" s="4" t="n"/>
@@ -24489,6 +25416,7 @@
       <c r="H923" s="4" t="n"/>
       <c r="I923" s="4" t="n"/>
       <c r="J923" s="3" t="n"/>
+      <c r="K923" s="3" t="n"/>
     </row>
     <row r="924">
       <c r="A924" s="4" t="n"/>
@@ -24501,6 +25429,7 @@
       <c r="H924" s="4" t="n"/>
       <c r="I924" s="4" t="n"/>
       <c r="J924" s="3" t="n"/>
+      <c r="K924" s="3" t="n"/>
     </row>
     <row r="925">
       <c r="A925" s="4" t="n"/>
@@ -24513,6 +25442,7 @@
       <c r="H925" s="4" t="n"/>
       <c r="I925" s="4" t="n"/>
       <c r="J925" s="3" t="n"/>
+      <c r="K925" s="3" t="n"/>
     </row>
     <row r="926">
       <c r="A926" s="4" t="n"/>
@@ -24525,6 +25455,7 @@
       <c r="H926" s="4" t="n"/>
       <c r="I926" s="4" t="n"/>
       <c r="J926" s="3" t="n"/>
+      <c r="K926" s="3" t="n"/>
     </row>
     <row r="927">
       <c r="A927" s="4" t="n"/>
@@ -24537,6 +25468,7 @@
       <c r="H927" s="4" t="n"/>
       <c r="I927" s="4" t="n"/>
       <c r="J927" s="3" t="n"/>
+      <c r="K927" s="3" t="n"/>
     </row>
     <row r="928">
       <c r="A928" s="4" t="n"/>
@@ -24549,6 +25481,7 @@
       <c r="H928" s="4" t="n"/>
       <c r="I928" s="4" t="n"/>
       <c r="J928" s="3" t="n"/>
+      <c r="K928" s="3" t="n"/>
     </row>
     <row r="929">
       <c r="A929" s="4" t="n"/>
@@ -24561,6 +25494,7 @@
       <c r="H929" s="4" t="n"/>
       <c r="I929" s="4" t="n"/>
       <c r="J929" s="3" t="n"/>
+      <c r="K929" s="3" t="n"/>
     </row>
     <row r="930">
       <c r="A930" s="4" t="n"/>
@@ -24573,6 +25507,7 @@
       <c r="H930" s="4" t="n"/>
       <c r="I930" s="4" t="n"/>
       <c r="J930" s="3" t="n"/>
+      <c r="K930" s="3" t="n"/>
     </row>
     <row r="931">
       <c r="A931" s="4" t="n"/>
@@ -24585,6 +25520,7 @@
       <c r="H931" s="4" t="n"/>
       <c r="I931" s="4" t="n"/>
       <c r="J931" s="3" t="n"/>
+      <c r="K931" s="3" t="n"/>
     </row>
     <row r="932">
       <c r="A932" s="4" t="n"/>
@@ -24597,6 +25533,7 @@
       <c r="H932" s="4" t="n"/>
       <c r="I932" s="4" t="n"/>
       <c r="J932" s="3" t="n"/>
+      <c r="K932" s="3" t="n"/>
     </row>
     <row r="933">
       <c r="A933" s="4" t="n"/>
@@ -24609,6 +25546,7 @@
       <c r="H933" s="4" t="n"/>
       <c r="I933" s="4" t="n"/>
       <c r="J933" s="3" t="n"/>
+      <c r="K933" s="3" t="n"/>
     </row>
     <row r="934">
       <c r="A934" s="4" t="n"/>
@@ -24621,6 +25559,7 @@
       <c r="H934" s="4" t="n"/>
       <c r="I934" s="4" t="n"/>
       <c r="J934" s="3" t="n"/>
+      <c r="K934" s="3" t="n"/>
     </row>
     <row r="935">
       <c r="A935" s="4" t="n"/>
@@ -24633,6 +25572,7 @@
       <c r="H935" s="4" t="n"/>
       <c r="I935" s="4" t="n"/>
       <c r="J935" s="3" t="n"/>
+      <c r="K935" s="3" t="n"/>
     </row>
     <row r="936">
       <c r="A936" s="4" t="n"/>
@@ -24645,6 +25585,7 @@
       <c r="H936" s="4" t="n"/>
       <c r="I936" s="4" t="n"/>
       <c r="J936" s="3" t="n"/>
+      <c r="K936" s="3" t="n"/>
     </row>
     <row r="937">
       <c r="A937" s="4" t="n"/>
@@ -24657,6 +25598,7 @@
       <c r="H937" s="4" t="n"/>
       <c r="I937" s="4" t="n"/>
       <c r="J937" s="3" t="n"/>
+      <c r="K937" s="3" t="n"/>
     </row>
     <row r="938">
       <c r="A938" s="4" t="n"/>
@@ -24669,6 +25611,7 @@
       <c r="H938" s="4" t="n"/>
       <c r="I938" s="4" t="n"/>
       <c r="J938" s="3" t="n"/>
+      <c r="K938" s="3" t="n"/>
     </row>
     <row r="939">
       <c r="A939" s="4" t="n"/>
@@ -24681,6 +25624,7 @@
       <c r="H939" s="4" t="n"/>
       <c r="I939" s="4" t="n"/>
       <c r="J939" s="3" t="n"/>
+      <c r="K939" s="3" t="n"/>
     </row>
     <row r="940">
       <c r="A940" s="4" t="n"/>
@@ -24693,6 +25637,7 @@
       <c r="H940" s="4" t="n"/>
       <c r="I940" s="4" t="n"/>
       <c r="J940" s="3" t="n"/>
+      <c r="K940" s="3" t="n"/>
     </row>
     <row r="941">
       <c r="A941" s="4" t="n"/>
@@ -24705,6 +25650,7 @@
       <c r="H941" s="4" t="n"/>
       <c r="I941" s="4" t="n"/>
       <c r="J941" s="3" t="n"/>
+      <c r="K941" s="3" t="n"/>
     </row>
     <row r="942">
       <c r="A942" s="4" t="n"/>
@@ -24717,6 +25663,7 @@
       <c r="H942" s="4" t="n"/>
       <c r="I942" s="4" t="n"/>
       <c r="J942" s="3" t="n"/>
+      <c r="K942" s="3" t="n"/>
     </row>
     <row r="943">
       <c r="A943" s="4" t="n"/>
@@ -24729,6 +25676,7 @@
       <c r="H943" s="4" t="n"/>
       <c r="I943" s="4" t="n"/>
       <c r="J943" s="3" t="n"/>
+      <c r="K943" s="3" t="n"/>
     </row>
     <row r="944">
       <c r="A944" s="4" t="n"/>
@@ -24741,6 +25689,7 @@
       <c r="H944" s="4" t="n"/>
       <c r="I944" s="4" t="n"/>
       <c r="J944" s="3" t="n"/>
+      <c r="K944" s="3" t="n"/>
     </row>
     <row r="945">
       <c r="A945" s="4" t="n"/>
@@ -24753,6 +25702,7 @@
       <c r="H945" s="4" t="n"/>
       <c r="I945" s="4" t="n"/>
       <c r="J945" s="3" t="n"/>
+      <c r="K945" s="3" t="n"/>
     </row>
     <row r="946">
       <c r="A946" s="4" t="n"/>
@@ -24765,6 +25715,7 @@
       <c r="H946" s="4" t="n"/>
       <c r="I946" s="4" t="n"/>
       <c r="J946" s="3" t="n"/>
+      <c r="K946" s="3" t="n"/>
     </row>
     <row r="947">
       <c r="A947" s="4" t="n"/>
@@ -24777,6 +25728,7 @@
       <c r="H947" s="4" t="n"/>
       <c r="I947" s="4" t="n"/>
       <c r="J947" s="3" t="n"/>
+      <c r="K947" s="3" t="n"/>
     </row>
     <row r="948">
       <c r="A948" s="4" t="n"/>
@@ -24789,6 +25741,7 @@
       <c r="H948" s="4" t="n"/>
       <c r="I948" s="4" t="n"/>
       <c r="J948" s="3" t="n"/>
+      <c r="K948" s="3" t="n"/>
     </row>
     <row r="949">
       <c r="A949" s="4" t="n"/>
@@ -24801,6 +25754,7 @@
       <c r="H949" s="4" t="n"/>
       <c r="I949" s="4" t="n"/>
       <c r="J949" s="3" t="n"/>
+      <c r="K949" s="3" t="n"/>
     </row>
     <row r="950">
       <c r="A950" s="4" t="n"/>
@@ -24813,6 +25767,7 @@
       <c r="H950" s="4" t="n"/>
       <c r="I950" s="4" t="n"/>
       <c r="J950" s="3" t="n"/>
+      <c r="K950" s="3" t="n"/>
     </row>
     <row r="951">
       <c r="A951" s="4" t="n"/>
@@ -24825,6 +25780,7 @@
       <c r="H951" s="4" t="n"/>
       <c r="I951" s="4" t="n"/>
       <c r="J951" s="3" t="n"/>
+      <c r="K951" s="3" t="n"/>
     </row>
     <row r="952">
       <c r="A952" s="4" t="n"/>
@@ -24837,6 +25793,7 @@
       <c r="H952" s="4" t="n"/>
       <c r="I952" s="4" t="n"/>
       <c r="J952" s="3" t="n"/>
+      <c r="K952" s="3" t="n"/>
     </row>
     <row r="953">
       <c r="A953" s="4" t="n"/>
@@ -24849,6 +25806,7 @@
       <c r="H953" s="4" t="n"/>
       <c r="I953" s="4" t="n"/>
       <c r="J953" s="3" t="n"/>
+      <c r="K953" s="3" t="n"/>
     </row>
     <row r="954">
       <c r="A954" s="4" t="n"/>
@@ -24861,6 +25819,7 @@
       <c r="H954" s="4" t="n"/>
       <c r="I954" s="4" t="n"/>
       <c r="J954" s="3" t="n"/>
+      <c r="K954" s="3" t="n"/>
     </row>
     <row r="955">
       <c r="A955" s="4" t="n"/>
@@ -24873,6 +25832,7 @@
       <c r="H955" s="4" t="n"/>
       <c r="I955" s="4" t="n"/>
       <c r="J955" s="3" t="n"/>
+      <c r="K955" s="3" t="n"/>
     </row>
     <row r="956">
       <c r="A956" s="4" t="n"/>
@@ -24885,6 +25845,7 @@
       <c r="H956" s="4" t="n"/>
       <c r="I956" s="4" t="n"/>
       <c r="J956" s="3" t="n"/>
+      <c r="K956" s="3" t="n"/>
     </row>
     <row r="957">
       <c r="A957" s="4" t="n"/>
@@ -24897,6 +25858,7 @@
       <c r="H957" s="4" t="n"/>
       <c r="I957" s="4" t="n"/>
       <c r="J957" s="3" t="n"/>
+      <c r="K957" s="3" t="n"/>
     </row>
     <row r="958">
       <c r="A958" s="4" t="n"/>
@@ -24909,6 +25871,7 @@
       <c r="H958" s="4" t="n"/>
       <c r="I958" s="4" t="n"/>
       <c r="J958" s="3" t="n"/>
+      <c r="K958" s="3" t="n"/>
     </row>
     <row r="959">
       <c r="A959" s="4" t="n"/>
@@ -24921,6 +25884,7 @@
       <c r="H959" s="4" t="n"/>
       <c r="I959" s="4" t="n"/>
       <c r="J959" s="3" t="n"/>
+      <c r="K959" s="3" t="n"/>
     </row>
     <row r="960">
       <c r="A960" s="4" t="n"/>
@@ -24933,6 +25897,7 @@
       <c r="H960" s="4" t="n"/>
       <c r="I960" s="4" t="n"/>
       <c r="J960" s="3" t="n"/>
+      <c r="K960" s="3" t="n"/>
     </row>
     <row r="961">
       <c r="A961" s="4" t="n"/>
@@ -24945,6 +25910,7 @@
       <c r="H961" s="4" t="n"/>
       <c r="I961" s="4" t="n"/>
       <c r="J961" s="3" t="n"/>
+      <c r="K961" s="3" t="n"/>
     </row>
     <row r="962">
       <c r="A962" s="4" t="n"/>
@@ -24957,6 +25923,7 @@
       <c r="H962" s="4" t="n"/>
       <c r="I962" s="4" t="n"/>
       <c r="J962" s="3" t="n"/>
+      <c r="K962" s="3" t="n"/>
     </row>
     <row r="963">
       <c r="A963" s="4" t="n"/>
@@ -24969,6 +25936,7 @@
       <c r="H963" s="4" t="n"/>
       <c r="I963" s="4" t="n"/>
       <c r="J963" s="3" t="n"/>
+      <c r="K963" s="3" t="n"/>
     </row>
     <row r="964">
       <c r="A964" s="4" t="n"/>
@@ -24981,6 +25949,7 @@
       <c r="H964" s="4" t="n"/>
       <c r="I964" s="4" t="n"/>
       <c r="J964" s="3" t="n"/>
+      <c r="K964" s="3" t="n"/>
     </row>
     <row r="965">
       <c r="A965" s="4" t="n"/>
@@ -24993,6 +25962,7 @@
       <c r="H965" s="4" t="n"/>
       <c r="I965" s="4" t="n"/>
       <c r="J965" s="3" t="n"/>
+      <c r="K965" s="3" t="n"/>
     </row>
     <row r="966">
       <c r="A966" s="4" t="n"/>
@@ -25005,6 +25975,7 @@
       <c r="H966" s="4" t="n"/>
       <c r="I966" s="4" t="n"/>
       <c r="J966" s="3" t="n"/>
+      <c r="K966" s="3" t="n"/>
     </row>
     <row r="967">
       <c r="A967" s="4" t="n"/>
@@ -25017,6 +25988,7 @@
       <c r="H967" s="4" t="n"/>
       <c r="I967" s="4" t="n"/>
       <c r="J967" s="3" t="n"/>
+      <c r="K967" s="3" t="n"/>
     </row>
     <row r="968">
       <c r="A968" s="4" t="n"/>
@@ -25029,6 +26001,7 @@
       <c r="H968" s="4" t="n"/>
       <c r="I968" s="4" t="n"/>
       <c r="J968" s="3" t="n"/>
+      <c r="K968" s="3" t="n"/>
     </row>
     <row r="969">
       <c r="A969" s="4" t="n"/>
@@ -25041,6 +26014,7 @@
       <c r="H969" s="4" t="n"/>
       <c r="I969" s="4" t="n"/>
       <c r="J969" s="3" t="n"/>
+      <c r="K969" s="3" t="n"/>
     </row>
     <row r="970">
       <c r="A970" s="4" t="n"/>
@@ -25053,6 +26027,7 @@
       <c r="H970" s="4" t="n"/>
       <c r="I970" s="4" t="n"/>
       <c r="J970" s="3" t="n"/>
+      <c r="K970" s="3" t="n"/>
     </row>
     <row r="971">
       <c r="A971" s="4" t="n"/>
@@ -25065,6 +26040,7 @@
       <c r="H971" s="4" t="n"/>
       <c r="I971" s="4" t="n"/>
       <c r="J971" s="3" t="n"/>
+      <c r="K971" s="3" t="n"/>
     </row>
     <row r="972">
       <c r="A972" s="4" t="n"/>
@@ -25077,6 +26053,7 @@
       <c r="H972" s="4" t="n"/>
       <c r="I972" s="4" t="n"/>
       <c r="J972" s="3" t="n"/>
+      <c r="K972" s="3" t="n"/>
     </row>
     <row r="973">
       <c r="A973" s="4" t="n"/>
@@ -25089,6 +26066,7 @@
       <c r="H973" s="4" t="n"/>
       <c r="I973" s="4" t="n"/>
       <c r="J973" s="3" t="n"/>
+      <c r="K973" s="3" t="n"/>
     </row>
     <row r="974">
       <c r="A974" s="4" t="n"/>
@@ -25101,6 +26079,7 @@
       <c r="H974" s="4" t="n"/>
       <c r="I974" s="4" t="n"/>
       <c r="J974" s="3" t="n"/>
+      <c r="K974" s="3" t="n"/>
     </row>
     <row r="975">
       <c r="A975" s="4" t="n"/>
@@ -25113,6 +26092,7 @@
       <c r="H975" s="4" t="n"/>
       <c r="I975" s="4" t="n"/>
       <c r="J975" s="3" t="n"/>
+      <c r="K975" s="3" t="n"/>
     </row>
     <row r="976">
       <c r="A976" s="4" t="n"/>
@@ -25125,6 +26105,7 @@
       <c r="H976" s="4" t="n"/>
       <c r="I976" s="4" t="n"/>
       <c r="J976" s="3" t="n"/>
+      <c r="K976" s="3" t="n"/>
     </row>
     <row r="977">
       <c r="A977" s="4" t="n"/>
@@ -25137,6 +26118,7 @@
       <c r="H977" s="4" t="n"/>
       <c r="I977" s="4" t="n"/>
       <c r="J977" s="3" t="n"/>
+      <c r="K977" s="3" t="n"/>
     </row>
     <row r="978">
       <c r="A978" s="4" t="n"/>
@@ -25149,6 +26131,7 @@
       <c r="H978" s="4" t="n"/>
       <c r="I978" s="4" t="n"/>
       <c r="J978" s="3" t="n"/>
+      <c r="K978" s="3" t="n"/>
     </row>
     <row r="979">
       <c r="A979" s="4" t="n"/>
@@ -25161,6 +26144,7 @@
       <c r="H979" s="4" t="n"/>
       <c r="I979" s="4" t="n"/>
       <c r="J979" s="3" t="n"/>
+      <c r="K979" s="3" t="n"/>
     </row>
     <row r="980">
       <c r="A980" s="4" t="n"/>
@@ -25173,6 +26157,7 @@
       <c r="H980" s="4" t="n"/>
       <c r="I980" s="4" t="n"/>
       <c r="J980" s="3" t="n"/>
+      <c r="K980" s="3" t="n"/>
     </row>
     <row r="981">
       <c r="A981" s="4" t="n"/>
@@ -25185,6 +26170,7 @@
       <c r="H981" s="4" t="n"/>
       <c r="I981" s="4" t="n"/>
       <c r="J981" s="3" t="n"/>
+      <c r="K981" s="3" t="n"/>
     </row>
     <row r="982">
       <c r="A982" s="4" t="n"/>
@@ -25197,6 +26183,7 @@
       <c r="H982" s="4" t="n"/>
       <c r="I982" s="4" t="n"/>
       <c r="J982" s="3" t="n"/>
+      <c r="K982" s="3" t="n"/>
     </row>
     <row r="983">
       <c r="A983" s="4" t="n"/>
@@ -25209,6 +26196,7 @@
       <c r="H983" s="4" t="n"/>
       <c r="I983" s="4" t="n"/>
       <c r="J983" s="3" t="n"/>
+      <c r="K983" s="3" t="n"/>
     </row>
     <row r="984">
       <c r="A984" s="4" t="n"/>
@@ -25221,6 +26209,7 @@
       <c r="H984" s="4" t="n"/>
       <c r="I984" s="4" t="n"/>
       <c r="J984" s="3" t="n"/>
+      <c r="K984" s="3" t="n"/>
     </row>
     <row r="985">
       <c r="A985" s="4" t="n"/>
@@ -25233,6 +26222,7 @@
       <c r="H985" s="4" t="n"/>
       <c r="I985" s="4" t="n"/>
       <c r="J985" s="3" t="n"/>
+      <c r="K985" s="3" t="n"/>
     </row>
     <row r="986">
       <c r="A986" s="4" t="n"/>
@@ -25245,6 +26235,7 @@
       <c r="H986" s="4" t="n"/>
       <c r="I986" s="4" t="n"/>
       <c r="J986" s="3" t="n"/>
+      <c r="K986" s="3" t="n"/>
     </row>
     <row r="987">
       <c r="A987" s="4" t="n"/>
@@ -25257,6 +26248,7 @@
       <c r="H987" s="4" t="n"/>
       <c r="I987" s="4" t="n"/>
       <c r="J987" s="3" t="n"/>
+      <c r="K987" s="3" t="n"/>
     </row>
     <row r="988">
       <c r="A988" s="4" t="n"/>
@@ -25269,6 +26261,7 @@
       <c r="H988" s="4" t="n"/>
       <c r="I988" s="4" t="n"/>
       <c r="J988" s="3" t="n"/>
+      <c r="K988" s="3" t="n"/>
     </row>
     <row r="989">
       <c r="A989" s="4" t="n"/>
@@ -25281,6 +26274,7 @@
       <c r="H989" s="4" t="n"/>
       <c r="I989" s="4" t="n"/>
       <c r="J989" s="3" t="n"/>
+      <c r="K989" s="3" t="n"/>
     </row>
     <row r="990">
       <c r="A990" s="4" t="n"/>
@@ -25293,6 +26287,7 @@
       <c r="H990" s="4" t="n"/>
       <c r="I990" s="4" t="n"/>
       <c r="J990" s="3" t="n"/>
+      <c r="K990" s="3" t="n"/>
     </row>
     <row r="991">
       <c r="A991" s="4" t="n"/>
@@ -25305,6 +26300,7 @@
       <c r="H991" s="4" t="n"/>
       <c r="I991" s="4" t="n"/>
       <c r="J991" s="3" t="n"/>
+      <c r="K991" s="3" t="n"/>
     </row>
     <row r="992">
       <c r="A992" s="4" t="n"/>
@@ -25317,6 +26313,7 @@
       <c r="H992" s="4" t="n"/>
       <c r="I992" s="4" t="n"/>
       <c r="J992" s="3" t="n"/>
+      <c r="K992" s="3" t="n"/>
     </row>
     <row r="993">
       <c r="A993" s="4" t="n"/>
@@ -25329,6 +26326,7 @@
       <c r="H993" s="4" t="n"/>
       <c r="I993" s="4" t="n"/>
       <c r="J993" s="3" t="n"/>
+      <c r="K993" s="3" t="n"/>
     </row>
     <row r="994">
       <c r="A994" s="4" t="n"/>
@@ -25341,6 +26339,7 @@
       <c r="H994" s="4" t="n"/>
       <c r="I994" s="4" t="n"/>
       <c r="J994" s="3" t="n"/>
+      <c r="K994" s="3" t="n"/>
     </row>
     <row r="995">
       <c r="A995" s="4" t="n"/>
@@ -25353,6 +26352,7 @@
       <c r="H995" s="4" t="n"/>
       <c r="I995" s="4" t="n"/>
       <c r="J995" s="3" t="n"/>
+      <c r="K995" s="3" t="n"/>
     </row>
     <row r="996">
       <c r="A996" s="4" t="n"/>
@@ -25365,6 +26365,7 @@
       <c r="H996" s="4" t="n"/>
       <c r="I996" s="4" t="n"/>
       <c r="J996" s="3" t="n"/>
+      <c r="K996" s="3" t="n"/>
     </row>
     <row r="997">
       <c r="A997" s="4" t="n"/>
@@ -25377,6 +26378,7 @@
       <c r="H997" s="4" t="n"/>
       <c r="I997" s="4" t="n"/>
       <c r="J997" s="3" t="n"/>
+      <c r="K997" s="3" t="n"/>
     </row>
     <row r="998">
       <c r="A998" s="4" t="n"/>
@@ -25389,6 +26391,7 @@
       <c r="H998" s="4" t="n"/>
       <c r="I998" s="4" t="n"/>
       <c r="J998" s="3" t="n"/>
+      <c r="K998" s="3" t="n"/>
     </row>
     <row r="999">
       <c r="A999" s="4" t="n"/>
@@ -25401,6 +26404,7 @@
       <c r="H999" s="4" t="n"/>
       <c r="I999" s="4" t="n"/>
       <c r="J999" s="3" t="n"/>
+      <c r="K999" s="3" t="n"/>
     </row>
     <row r="1000">
       <c r="A1000" s="4" t="n"/>
@@ -25413,6 +26417,7 @@
       <c r="H1000" s="4" t="n"/>
       <c r="I1000" s="4" t="n"/>
       <c r="J1000" s="3" t="n"/>
+      <c r="K1000" s="3" t="n"/>
     </row>
     <row r="1001">
       <c r="A1001" s="4" t="n"/>
@@ -25425,6 +26430,7 @@
       <c r="H1001" s="4" t="n"/>
       <c r="I1001" s="4" t="n"/>
       <c r="J1001" s="3" t="n"/>
+      <c r="K1001" s="3" t="n"/>
     </row>
     <row r="1002">
       <c r="A1002" s="4" t="n"/>
@@ -25437,6 +26443,7 @@
       <c r="H1002" s="4" t="n"/>
       <c r="I1002" s="4" t="n"/>
       <c r="J1002" s="3" t="n"/>
+      <c r="K1002" s="3" t="n"/>
     </row>
     <row r="1003">
       <c r="A1003" s="4" t="n"/>
@@ -25449,6 +26456,7 @@
       <c r="H1003" s="4" t="n"/>
       <c r="I1003" s="4" t="n"/>
       <c r="J1003" s="3" t="n"/>
+      <c r="K1003" s="3" t="n"/>
     </row>
     <row r="1004">
       <c r="A1004" s="4" t="n"/>
@@ -25461,6 +26469,7 @@
       <c r="H1004" s="4" t="n"/>
       <c r="I1004" s="4" t="n"/>
       <c r="J1004" s="3" t="n"/>
+      <c r="K1004" s="3" t="n"/>
     </row>
     <row r="1005">
       <c r="A1005" s="4" t="n"/>
@@ -25473,6 +26482,7 @@
       <c r="H1005" s="4" t="n"/>
       <c r="I1005" s="4" t="n"/>
       <c r="J1005" s="3" t="n"/>
+      <c r="K1005" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/terrestrial/Level4_20-Aug-26.xlsx
+++ b/terrestrial/Level4_20-Aug-26.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1005"/>
+  <dimension ref="A1:K618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -473,22 +473,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>L4 code</t>
+          <t>Local_name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>L4 area</t>
+          <t>Full_name</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>L3 code</t>
+          <t>Level_3</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>L4 ISOcode</t>
+          <t>ISO_ter1</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Argentina Distrito Federal</t>
+          <t>Ciudad Autónoma de Buenos Aires</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -742,18 +742,21 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H8" s="4" t="n"/>
       <c r="I8" s="4" t="n"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>AGE-DF (Argentina Distrito Federal) is integrated into AGE-BA. It is an incoherent disvision. Both are level 4 entities. Should AGE-DR be removed? 
-The toponym used for AGE-DR is not the most appropriate. The Autonomous City of Buenos Aires could have been used. http://www.infoleg.gob.ar/?page_id=166
+          <t>Ciudad Autónoma de Buenos Aires
 -Typographical error, where AGE-DR exists, there was AGE-DF. It is corrected according to TDWG.
 -AGE-DF It is not digitized on map 16 (pg 135)</t>
         </is>
@@ -16447,7 +16450,7 @@
       </c>
       <c r="J473" s="3" t="inlineStr">
         <is>
-          <t>New unit, split from PAL-IS per GSTerr9.</t>
+          <t>New unit, split from PAL-IS per issue #10.</t>
         </is>
       </c>
       <c r="K473" s="3" t="n"/>
@@ -16488,7 +16491,7 @@
       </c>
       <c r="J474" s="3" t="inlineStr">
         <is>
-          <t>Redefined per GSTerr9: previously included Gaza Strip and West Bank (WGSRPD ed. 2 limits); now split into PAL-GZ and PAL-WB.</t>
+          <t>Redefined per issue #10: previously included Gaza Strip and West Bank (WGSRPD ed. 2 limits); now split into PAL-GZ and PAL-WB.</t>
         </is>
       </c>
       <c r="K474" s="3" t="n"/>
@@ -16562,7 +16565,7 @@
       </c>
       <c r="J476" s="3" t="inlineStr">
         <is>
-          <t>New unit, split from PAL-IS per GSTerr9.</t>
+          <t>New unit, split from PAL-IS per issue #10.</t>
         </is>
       </c>
       <c r="K476" s="3" t="n"/>
@@ -17718,22 +17721,18 @@
           <t>SCS</t>
         </is>
       </c>
-      <c r="E511" s="4" t="inlineStr">
-        <is>
-          <t>PI*</t>
-        </is>
-      </c>
+      <c r="E511" s="4" t="n"/>
       <c r="F511" s="4" t="n"/>
       <c r="G511" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H511" s="4" t="n"/>
       <c r="I511" s="4" t="n"/>
       <c r="J511" s="3" t="inlineStr">
         <is>
-          <t>The annotation must be included in the footer: "The PI* code  is adopted here unofficially for Paracel Is. though the ISO does not give them any code as their political status is disputed"</t>
+          <t>political status is disputed</t>
         </is>
       </c>
       <c r="K511" s="3" t="n"/>
@@ -19036,7 +19035,7 @@
       <c r="F549" s="4" t="n"/>
       <c r="G549" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H549" s="4" t="inlineStr">
@@ -19250,7 +19249,7 @@
       <c r="F555" s="4" t="n"/>
       <c r="G555" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H555" s="4" t="n"/>
@@ -21421,5069 +21420,6 @@
       </c>
       <c r="K618" s="3" t="n"/>
     </row>
-    <row r="619">
-      <c r="A619" s="4" t="inlineStr">
-        <is>
-          <t>SUD_OO</t>
-        </is>
-      </c>
-      <c r="B619" s="4" t="inlineStr">
-        <is>
-          <t>SUD-OO</t>
-        </is>
-      </c>
-      <c r="C619" s="4" t="inlineStr">
-        <is>
-          <t>Sudan</t>
-        </is>
-      </c>
-      <c r="D619" s="4" t="inlineStr">
-        <is>
-          <t>SUD</t>
-        </is>
-      </c>
-      <c r="E619" s="4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="F619" s="4" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G619" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H619" s="4" t="n"/>
-      <c r="I619" s="4" t="inlineStr">
-        <is>
-          <t>#11</t>
-        </is>
-      </c>
-      <c r="J619" s="3" t="n"/>
-      <c r="K619" s="3" t="n"/>
-    </row>
-    <row r="620">
-      <c r="A620" s="4" t="n"/>
-      <c r="B620" s="4" t="n"/>
-      <c r="C620" s="4" t="n"/>
-      <c r="D620" s="4" t="n"/>
-      <c r="E620" s="4" t="n"/>
-      <c r="F620" s="4" t="n"/>
-      <c r="G620" s="4" t="n"/>
-      <c r="H620" s="4" t="n"/>
-      <c r="I620" s="4" t="n"/>
-      <c r="J620" s="3" t="n"/>
-      <c r="K620" s="3" t="n"/>
-    </row>
-    <row r="621">
-      <c r="A621" s="4" t="n"/>
-      <c r="B621" s="4" t="n"/>
-      <c r="C621" s="4" t="n"/>
-      <c r="D621" s="4" t="n"/>
-      <c r="E621" s="4" t="n"/>
-      <c r="F621" s="4" t="n"/>
-      <c r="G621" s="4" t="n"/>
-      <c r="H621" s="4" t="n"/>
-      <c r="I621" s="4" t="n"/>
-      <c r="J621" s="3" t="n"/>
-      <c r="K621" s="3" t="n"/>
-    </row>
-    <row r="622">
-      <c r="A622" s="4" t="n"/>
-      <c r="B622" s="4" t="n"/>
-      <c r="C622" s="4" t="n"/>
-      <c r="D622" s="4" t="n"/>
-      <c r="E622" s="4" t="n"/>
-      <c r="F622" s="4" t="n"/>
-      <c r="G622" s="4" t="n"/>
-      <c r="H622" s="4" t="n"/>
-      <c r="I622" s="4" t="n"/>
-      <c r="J622" s="3" t="n"/>
-      <c r="K622" s="3" t="n"/>
-    </row>
-    <row r="623">
-      <c r="A623" s="4" t="n"/>
-      <c r="B623" s="4" t="n"/>
-      <c r="C623" s="4" t="n"/>
-      <c r="D623" s="4" t="n"/>
-      <c r="E623" s="4" t="n"/>
-      <c r="F623" s="4" t="n"/>
-      <c r="G623" s="4" t="n"/>
-      <c r="H623" s="4" t="n"/>
-      <c r="I623" s="4" t="n"/>
-      <c r="J623" s="3" t="n"/>
-      <c r="K623" s="3" t="n"/>
-    </row>
-    <row r="624">
-      <c r="A624" s="4" t="n"/>
-      <c r="B624" s="4" t="n"/>
-      <c r="C624" s="4" t="n"/>
-      <c r="D624" s="4" t="n"/>
-      <c r="E624" s="4" t="n"/>
-      <c r="F624" s="4" t="n"/>
-      <c r="G624" s="4" t="n"/>
-      <c r="H624" s="4" t="n"/>
-      <c r="I624" s="4" t="n"/>
-      <c r="J624" s="3" t="n"/>
-      <c r="K624" s="3" t="n"/>
-    </row>
-    <row r="625">
-      <c r="A625" s="4" t="n"/>
-      <c r="B625" s="4" t="n"/>
-      <c r="C625" s="4" t="n"/>
-      <c r="D625" s="4" t="n"/>
-      <c r="E625" s="4" t="n"/>
-      <c r="F625" s="4" t="n"/>
-      <c r="G625" s="4" t="n"/>
-      <c r="H625" s="4" t="n"/>
-      <c r="I625" s="4" t="n"/>
-      <c r="J625" s="3" t="n"/>
-      <c r="K625" s="3" t="n"/>
-    </row>
-    <row r="626">
-      <c r="A626" s="4" t="n"/>
-      <c r="B626" s="4" t="n"/>
-      <c r="C626" s="4" t="n"/>
-      <c r="D626" s="4" t="n"/>
-      <c r="E626" s="4" t="n"/>
-      <c r="F626" s="4" t="n"/>
-      <c r="G626" s="4" t="n"/>
-      <c r="H626" s="4" t="n"/>
-      <c r="I626" s="4" t="n"/>
-      <c r="J626" s="3" t="n"/>
-      <c r="K626" s="3" t="n"/>
-    </row>
-    <row r="627">
-      <c r="A627" s="4" t="n"/>
-      <c r="B627" s="4" t="n"/>
-      <c r="C627" s="4" t="n"/>
-      <c r="D627" s="4" t="n"/>
-      <c r="E627" s="4" t="n"/>
-      <c r="F627" s="4" t="n"/>
-      <c r="G627" s="4" t="n"/>
-      <c r="H627" s="4" t="n"/>
-      <c r="I627" s="4" t="n"/>
-      <c r="J627" s="3" t="n"/>
-      <c r="K627" s="3" t="n"/>
-    </row>
-    <row r="628">
-      <c r="A628" s="4" t="n"/>
-      <c r="B628" s="4" t="n"/>
-      <c r="C628" s="4" t="n"/>
-      <c r="D628" s="4" t="n"/>
-      <c r="E628" s="4" t="n"/>
-      <c r="F628" s="4" t="n"/>
-      <c r="G628" s="4" t="n"/>
-      <c r="H628" s="4" t="n"/>
-      <c r="I628" s="4" t="n"/>
-      <c r="J628" s="3" t="n"/>
-      <c r="K628" s="3" t="n"/>
-    </row>
-    <row r="629">
-      <c r="A629" s="4" t="n"/>
-      <c r="B629" s="4" t="n"/>
-      <c r="C629" s="4" t="n"/>
-      <c r="D629" s="4" t="n"/>
-      <c r="E629" s="4" t="n"/>
-      <c r="F629" s="4" t="n"/>
-      <c r="G629" s="4" t="n"/>
-      <c r="H629" s="4" t="n"/>
-      <c r="I629" s="4" t="n"/>
-      <c r="J629" s="3" t="n"/>
-      <c r="K629" s="3" t="n"/>
-    </row>
-    <row r="630">
-      <c r="A630" s="4" t="n"/>
-      <c r="B630" s="4" t="n"/>
-      <c r="C630" s="4" t="n"/>
-      <c r="D630" s="4" t="n"/>
-      <c r="E630" s="4" t="n"/>
-      <c r="F630" s="4" t="n"/>
-      <c r="G630" s="4" t="n"/>
-      <c r="H630" s="4" t="n"/>
-      <c r="I630" s="4" t="n"/>
-      <c r="J630" s="3" t="n"/>
-      <c r="K630" s="3" t="n"/>
-    </row>
-    <row r="631">
-      <c r="A631" s="4" t="n"/>
-      <c r="B631" s="4" t="n"/>
-      <c r="C631" s="4" t="n"/>
-      <c r="D631" s="4" t="n"/>
-      <c r="E631" s="4" t="n"/>
-      <c r="F631" s="4" t="n"/>
-      <c r="G631" s="4" t="n"/>
-      <c r="H631" s="4" t="n"/>
-      <c r="I631" s="4" t="n"/>
-      <c r="J631" s="3" t="n"/>
-      <c r="K631" s="3" t="n"/>
-    </row>
-    <row r="632">
-      <c r="A632" s="4" t="n"/>
-      <c r="B632" s="4" t="n"/>
-      <c r="C632" s="4" t="n"/>
-      <c r="D632" s="4" t="n"/>
-      <c r="E632" s="4" t="n"/>
-      <c r="F632" s="4" t="n"/>
-      <c r="G632" s="4" t="n"/>
-      <c r="H632" s="4" t="n"/>
-      <c r="I632" s="4" t="n"/>
-      <c r="J632" s="3" t="n"/>
-      <c r="K632" s="3" t="n"/>
-    </row>
-    <row r="633">
-      <c r="A633" s="4" t="n"/>
-      <c r="B633" s="4" t="n"/>
-      <c r="C633" s="4" t="n"/>
-      <c r="D633" s="4" t="n"/>
-      <c r="E633" s="4" t="n"/>
-      <c r="F633" s="4" t="n"/>
-      <c r="G633" s="4" t="n"/>
-      <c r="H633" s="4" t="n"/>
-      <c r="I633" s="4" t="n"/>
-      <c r="J633" s="3" t="n"/>
-      <c r="K633" s="3" t="n"/>
-    </row>
-    <row r="634">
-      <c r="A634" s="4" t="n"/>
-      <c r="B634" s="4" t="n"/>
-      <c r="C634" s="4" t="n"/>
-      <c r="D634" s="4" t="n"/>
-      <c r="E634" s="4" t="n"/>
-      <c r="F634" s="4" t="n"/>
-      <c r="G634" s="4" t="n"/>
-      <c r="H634" s="4" t="n"/>
-      <c r="I634" s="4" t="n"/>
-      <c r="J634" s="3" t="n"/>
-      <c r="K634" s="3" t="n"/>
-    </row>
-    <row r="635">
-      <c r="A635" s="4" t="n"/>
-      <c r="B635" s="4" t="n"/>
-      <c r="C635" s="4" t="n"/>
-      <c r="D635" s="4" t="n"/>
-      <c r="E635" s="4" t="n"/>
-      <c r="F635" s="4" t="n"/>
-      <c r="G635" s="4" t="n"/>
-      <c r="H635" s="4" t="n"/>
-      <c r="I635" s="4" t="n"/>
-      <c r="J635" s="3" t="n"/>
-      <c r="K635" s="3" t="n"/>
-    </row>
-    <row r="636">
-      <c r="A636" s="4" t="n"/>
-      <c r="B636" s="4" t="n"/>
-      <c r="C636" s="4" t="n"/>
-      <c r="D636" s="4" t="n"/>
-      <c r="E636" s="4" t="n"/>
-      <c r="F636" s="4" t="n"/>
-      <c r="G636" s="4" t="n"/>
-      <c r="H636" s="4" t="n"/>
-      <c r="I636" s="4" t="n"/>
-      <c r="J636" s="3" t="n"/>
-      <c r="K636" s="3" t="n"/>
-    </row>
-    <row r="637">
-      <c r="A637" s="4" t="n"/>
-      <c r="B637" s="4" t="n"/>
-      <c r="C637" s="4" t="n"/>
-      <c r="D637" s="4" t="n"/>
-      <c r="E637" s="4" t="n"/>
-      <c r="F637" s="4" t="n"/>
-      <c r="G637" s="4" t="n"/>
-      <c r="H637" s="4" t="n"/>
-      <c r="I637" s="4" t="n"/>
-      <c r="J637" s="3" t="n"/>
-      <c r="K637" s="3" t="n"/>
-    </row>
-    <row r="638">
-      <c r="A638" s="4" t="n"/>
-      <c r="B638" s="4" t="n"/>
-      <c r="C638" s="4" t="n"/>
-      <c r="D638" s="4" t="n"/>
-      <c r="E638" s="4" t="n"/>
-      <c r="F638" s="4" t="n"/>
-      <c r="G638" s="4" t="n"/>
-      <c r="H638" s="4" t="n"/>
-      <c r="I638" s="4" t="n"/>
-      <c r="J638" s="3" t="n"/>
-      <c r="K638" s="3" t="n"/>
-    </row>
-    <row r="639">
-      <c r="A639" s="4" t="n"/>
-      <c r="B639" s="4" t="n"/>
-      <c r="C639" s="4" t="n"/>
-      <c r="D639" s="4" t="n"/>
-      <c r="E639" s="4" t="n"/>
-      <c r="F639" s="4" t="n"/>
-      <c r="G639" s="4" t="n"/>
-      <c r="H639" s="4" t="n"/>
-      <c r="I639" s="4" t="n"/>
-      <c r="J639" s="3" t="n"/>
-      <c r="K639" s="3" t="n"/>
-    </row>
-    <row r="640">
-      <c r="A640" s="4" t="n"/>
-      <c r="B640" s="4" t="n"/>
-      <c r="C640" s="4" t="n"/>
-      <c r="D640" s="4" t="n"/>
-      <c r="E640" s="4" t="n"/>
-      <c r="F640" s="4" t="n"/>
-      <c r="G640" s="4" t="n"/>
-      <c r="H640" s="4" t="n"/>
-      <c r="I640" s="4" t="n"/>
-      <c r="J640" s="3" t="n"/>
-      <c r="K640" s="3" t="n"/>
-    </row>
-    <row r="641">
-      <c r="A641" s="4" t="n"/>
-      <c r="B641" s="4" t="n"/>
-      <c r="C641" s="4" t="n"/>
-      <c r="D641" s="4" t="n"/>
-      <c r="E641" s="4" t="n"/>
-      <c r="F641" s="4" t="n"/>
-      <c r="G641" s="4" t="n"/>
-      <c r="H641" s="4" t="n"/>
-      <c r="I641" s="4" t="n"/>
-      <c r="J641" s="3" t="n"/>
-      <c r="K641" s="3" t="n"/>
-    </row>
-    <row r="642">
-      <c r="A642" s="4" t="n"/>
-      <c r="B642" s="4" t="n"/>
-      <c r="C642" s="4" t="n"/>
-      <c r="D642" s="4" t="n"/>
-      <c r="E642" s="4" t="n"/>
-      <c r="F642" s="4" t="n"/>
-      <c r="G642" s="4" t="n"/>
-      <c r="H642" s="4" t="n"/>
-      <c r="I642" s="4" t="n"/>
-      <c r="J642" s="3" t="n"/>
-      <c r="K642" s="3" t="n"/>
-    </row>
-    <row r="643">
-      <c r="A643" s="4" t="n"/>
-      <c r="B643" s="4" t="n"/>
-      <c r="C643" s="4" t="n"/>
-      <c r="D643" s="4" t="n"/>
-      <c r="E643" s="4" t="n"/>
-      <c r="F643" s="4" t="n"/>
-      <c r="G643" s="4" t="n"/>
-      <c r="H643" s="4" t="n"/>
-      <c r="I643" s="4" t="n"/>
-      <c r="J643" s="3" t="n"/>
-      <c r="K643" s="3" t="n"/>
-    </row>
-    <row r="644">
-      <c r="A644" s="4" t="n"/>
-      <c r="B644" s="4" t="n"/>
-      <c r="C644" s="4" t="n"/>
-      <c r="D644" s="4" t="n"/>
-      <c r="E644" s="4" t="n"/>
-      <c r="F644" s="4" t="n"/>
-      <c r="G644" s="4" t="n"/>
-      <c r="H644" s="4" t="n"/>
-      <c r="I644" s="4" t="n"/>
-      <c r="J644" s="3" t="n"/>
-      <c r="K644" s="3" t="n"/>
-    </row>
-    <row r="645">
-      <c r="A645" s="4" t="n"/>
-      <c r="B645" s="4" t="n"/>
-      <c r="C645" s="4" t="n"/>
-      <c r="D645" s="4" t="n"/>
-      <c r="E645" s="4" t="n"/>
-      <c r="F645" s="4" t="n"/>
-      <c r="G645" s="4" t="n"/>
-      <c r="H645" s="4" t="n"/>
-      <c r="I645" s="4" t="n"/>
-      <c r="J645" s="3" t="n"/>
-      <c r="K645" s="3" t="n"/>
-    </row>
-    <row r="646">
-      <c r="A646" s="4" t="n"/>
-      <c r="B646" s="4" t="n"/>
-      <c r="C646" s="4" t="n"/>
-      <c r="D646" s="4" t="n"/>
-      <c r="E646" s="4" t="n"/>
-      <c r="F646" s="4" t="n"/>
-      <c r="G646" s="4" t="n"/>
-      <c r="H646" s="4" t="n"/>
-      <c r="I646" s="4" t="n"/>
-      <c r="J646" s="3" t="n"/>
-      <c r="K646" s="3" t="n"/>
-    </row>
-    <row r="647">
-      <c r="A647" s="4" t="n"/>
-      <c r="B647" s="4" t="n"/>
-      <c r="C647" s="4" t="n"/>
-      <c r="D647" s="4" t="n"/>
-      <c r="E647" s="4" t="n"/>
-      <c r="F647" s="4" t="n"/>
-      <c r="G647" s="4" t="n"/>
-      <c r="H647" s="4" t="n"/>
-      <c r="I647" s="4" t="n"/>
-      <c r="J647" s="3" t="n"/>
-      <c r="K647" s="3" t="n"/>
-    </row>
-    <row r="648">
-      <c r="A648" s="4" t="n"/>
-      <c r="B648" s="4" t="n"/>
-      <c r="C648" s="4" t="n"/>
-      <c r="D648" s="4" t="n"/>
-      <c r="E648" s="4" t="n"/>
-      <c r="F648" s="4" t="n"/>
-      <c r="G648" s="4" t="n"/>
-      <c r="H648" s="4" t="n"/>
-      <c r="I648" s="4" t="n"/>
-      <c r="J648" s="3" t="n"/>
-      <c r="K648" s="3" t="n"/>
-    </row>
-    <row r="649">
-      <c r="A649" s="4" t="n"/>
-      <c r="B649" s="4" t="n"/>
-      <c r="C649" s="4" t="n"/>
-      <c r="D649" s="4" t="n"/>
-      <c r="E649" s="4" t="n"/>
-      <c r="F649" s="4" t="n"/>
-      <c r="G649" s="4" t="n"/>
-      <c r="H649" s="4" t="n"/>
-      <c r="I649" s="4" t="n"/>
-      <c r="J649" s="3" t="n"/>
-      <c r="K649" s="3" t="n"/>
-    </row>
-    <row r="650">
-      <c r="A650" s="4" t="n"/>
-      <c r="B650" s="4" t="n"/>
-      <c r="C650" s="4" t="n"/>
-      <c r="D650" s="4" t="n"/>
-      <c r="E650" s="4" t="n"/>
-      <c r="F650" s="4" t="n"/>
-      <c r="G650" s="4" t="n"/>
-      <c r="H650" s="4" t="n"/>
-      <c r="I650" s="4" t="n"/>
-      <c r="J650" s="3" t="n"/>
-      <c r="K650" s="3" t="n"/>
-    </row>
-    <row r="651">
-      <c r="A651" s="4" t="n"/>
-      <c r="B651" s="4" t="n"/>
-      <c r="C651" s="4" t="n"/>
-      <c r="D651" s="4" t="n"/>
-      <c r="E651" s="4" t="n"/>
-      <c r="F651" s="4" t="n"/>
-      <c r="G651" s="4" t="n"/>
-      <c r="H651" s="4" t="n"/>
-      <c r="I651" s="4" t="n"/>
-      <c r="J651" s="3" t="n"/>
-      <c r="K651" s="3" t="n"/>
-    </row>
-    <row r="652">
-      <c r="A652" s="4" t="n"/>
-      <c r="B652" s="4" t="n"/>
-      <c r="C652" s="4" t="n"/>
-      <c r="D652" s="4" t="n"/>
-      <c r="E652" s="4" t="n"/>
-      <c r="F652" s="4" t="n"/>
-      <c r="G652" s="4" t="n"/>
-      <c r="H652" s="4" t="n"/>
-      <c r="I652" s="4" t="n"/>
-      <c r="J652" s="3" t="n"/>
-      <c r="K652" s="3" t="n"/>
-    </row>
-    <row r="653">
-      <c r="A653" s="4" t="n"/>
-      <c r="B653" s="4" t="n"/>
-      <c r="C653" s="4" t="n"/>
-      <c r="D653" s="4" t="n"/>
-      <c r="E653" s="4" t="n"/>
-      <c r="F653" s="4" t="n"/>
-      <c r="G653" s="4" t="n"/>
-      <c r="H653" s="4" t="n"/>
-      <c r="I653" s="4" t="n"/>
-      <c r="J653" s="3" t="n"/>
-      <c r="K653" s="3" t="n"/>
-    </row>
-    <row r="654">
-      <c r="A654" s="4" t="n"/>
-      <c r="B654" s="4" t="n"/>
-      <c r="C654" s="4" t="n"/>
-      <c r="D654" s="4" t="n"/>
-      <c r="E654" s="4" t="n"/>
-      <c r="F654" s="4" t="n"/>
-      <c r="G654" s="4" t="n"/>
-      <c r="H654" s="4" t="n"/>
-      <c r="I654" s="4" t="n"/>
-      <c r="J654" s="3" t="n"/>
-      <c r="K654" s="3" t="n"/>
-    </row>
-    <row r="655">
-      <c r="A655" s="4" t="n"/>
-      <c r="B655" s="4" t="n"/>
-      <c r="C655" s="4" t="n"/>
-      <c r="D655" s="4" t="n"/>
-      <c r="E655" s="4" t="n"/>
-      <c r="F655" s="4" t="n"/>
-      <c r="G655" s="4" t="n"/>
-      <c r="H655" s="4" t="n"/>
-      <c r="I655" s="4" t="n"/>
-      <c r="J655" s="3" t="n"/>
-      <c r="K655" s="3" t="n"/>
-    </row>
-    <row r="656">
-      <c r="A656" s="4" t="n"/>
-      <c r="B656" s="4" t="n"/>
-      <c r="C656" s="4" t="n"/>
-      <c r="D656" s="4" t="n"/>
-      <c r="E656" s="4" t="n"/>
-      <c r="F656" s="4" t="n"/>
-      <c r="G656" s="4" t="n"/>
-      <c r="H656" s="4" t="n"/>
-      <c r="I656" s="4" t="n"/>
-      <c r="J656" s="3" t="n"/>
-      <c r="K656" s="3" t="n"/>
-    </row>
-    <row r="657">
-      <c r="A657" s="4" t="n"/>
-      <c r="B657" s="4" t="n"/>
-      <c r="C657" s="4" t="n"/>
-      <c r="D657" s="4" t="n"/>
-      <c r="E657" s="4" t="n"/>
-      <c r="F657" s="4" t="n"/>
-      <c r="G657" s="4" t="n"/>
-      <c r="H657" s="4" t="n"/>
-      <c r="I657" s="4" t="n"/>
-      <c r="J657" s="3" t="n"/>
-      <c r="K657" s="3" t="n"/>
-    </row>
-    <row r="658">
-      <c r="A658" s="4" t="n"/>
-      <c r="B658" s="4" t="n"/>
-      <c r="C658" s="4" t="n"/>
-      <c r="D658" s="4" t="n"/>
-      <c r="E658" s="4" t="n"/>
-      <c r="F658" s="4" t="n"/>
-      <c r="G658" s="4" t="n"/>
-      <c r="H658" s="4" t="n"/>
-      <c r="I658" s="4" t="n"/>
-      <c r="J658" s="3" t="n"/>
-      <c r="K658" s="3" t="n"/>
-    </row>
-    <row r="659">
-      <c r="A659" s="4" t="n"/>
-      <c r="B659" s="4" t="n"/>
-      <c r="C659" s="4" t="n"/>
-      <c r="D659" s="4" t="n"/>
-      <c r="E659" s="4" t="n"/>
-      <c r="F659" s="4" t="n"/>
-      <c r="G659" s="4" t="n"/>
-      <c r="H659" s="4" t="n"/>
-      <c r="I659" s="4" t="n"/>
-      <c r="J659" s="3" t="n"/>
-      <c r="K659" s="3" t="n"/>
-    </row>
-    <row r="660">
-      <c r="A660" s="4" t="n"/>
-      <c r="B660" s="4" t="n"/>
-      <c r="C660" s="4" t="n"/>
-      <c r="D660" s="4" t="n"/>
-      <c r="E660" s="4" t="n"/>
-      <c r="F660" s="4" t="n"/>
-      <c r="G660" s="4" t="n"/>
-      <c r="H660" s="4" t="n"/>
-      <c r="I660" s="4" t="n"/>
-      <c r="J660" s="3" t="n"/>
-      <c r="K660" s="3" t="n"/>
-    </row>
-    <row r="661">
-      <c r="A661" s="4" t="n"/>
-      <c r="B661" s="4" t="n"/>
-      <c r="C661" s="4" t="n"/>
-      <c r="D661" s="4" t="n"/>
-      <c r="E661" s="4" t="n"/>
-      <c r="F661" s="4" t="n"/>
-      <c r="G661" s="4" t="n"/>
-      <c r="H661" s="4" t="n"/>
-      <c r="I661" s="4" t="n"/>
-      <c r="J661" s="3" t="n"/>
-      <c r="K661" s="3" t="n"/>
-    </row>
-    <row r="662">
-      <c r="A662" s="4" t="n"/>
-      <c r="B662" s="4" t="n"/>
-      <c r="C662" s="4" t="n"/>
-      <c r="D662" s="4" t="n"/>
-      <c r="E662" s="4" t="n"/>
-      <c r="F662" s="4" t="n"/>
-      <c r="G662" s="4" t="n"/>
-      <c r="H662" s="4" t="n"/>
-      <c r="I662" s="4" t="n"/>
-      <c r="J662" s="3" t="n"/>
-      <c r="K662" s="3" t="n"/>
-    </row>
-    <row r="663">
-      <c r="A663" s="4" t="n"/>
-      <c r="B663" s="4" t="n"/>
-      <c r="C663" s="4" t="n"/>
-      <c r="D663" s="4" t="n"/>
-      <c r="E663" s="4" t="n"/>
-      <c r="F663" s="4" t="n"/>
-      <c r="G663" s="4" t="n"/>
-      <c r="H663" s="4" t="n"/>
-      <c r="I663" s="4" t="n"/>
-      <c r="J663" s="3" t="n"/>
-      <c r="K663" s="3" t="n"/>
-    </row>
-    <row r="664">
-      <c r="A664" s="4" t="n"/>
-      <c r="B664" s="4" t="n"/>
-      <c r="C664" s="4" t="n"/>
-      <c r="D664" s="4" t="n"/>
-      <c r="E664" s="4" t="n"/>
-      <c r="F664" s="4" t="n"/>
-      <c r="G664" s="4" t="n"/>
-      <c r="H664" s="4" t="n"/>
-      <c r="I664" s="4" t="n"/>
-      <c r="J664" s="3" t="n"/>
-      <c r="K664" s="3" t="n"/>
-    </row>
-    <row r="665">
-      <c r="A665" s="4" t="n"/>
-      <c r="B665" s="4" t="n"/>
-      <c r="C665" s="4" t="n"/>
-      <c r="D665" s="4" t="n"/>
-      <c r="E665" s="4" t="n"/>
-      <c r="F665" s="4" t="n"/>
-      <c r="G665" s="4" t="n"/>
-      <c r="H665" s="4" t="n"/>
-      <c r="I665" s="4" t="n"/>
-      <c r="J665" s="3" t="n"/>
-      <c r="K665" s="3" t="n"/>
-    </row>
-    <row r="666">
-      <c r="A666" s="4" t="n"/>
-      <c r="B666" s="4" t="n"/>
-      <c r="C666" s="4" t="n"/>
-      <c r="D666" s="4" t="n"/>
-      <c r="E666" s="4" t="n"/>
-      <c r="F666" s="4" t="n"/>
-      <c r="G666" s="4" t="n"/>
-      <c r="H666" s="4" t="n"/>
-      <c r="I666" s="4" t="n"/>
-      <c r="J666" s="3" t="n"/>
-      <c r="K666" s="3" t="n"/>
-    </row>
-    <row r="667">
-      <c r="A667" s="4" t="n"/>
-      <c r="B667" s="4" t="n"/>
-      <c r="C667" s="4" t="n"/>
-      <c r="D667" s="4" t="n"/>
-      <c r="E667" s="4" t="n"/>
-      <c r="F667" s="4" t="n"/>
-      <c r="G667" s="4" t="n"/>
-      <c r="H667" s="4" t="n"/>
-      <c r="I667" s="4" t="n"/>
-      <c r="J667" s="3" t="n"/>
-      <c r="K667" s="3" t="n"/>
-    </row>
-    <row r="668">
-      <c r="A668" s="4" t="n"/>
-      <c r="B668" s="4" t="n"/>
-      <c r="C668" s="4" t="n"/>
-      <c r="D668" s="4" t="n"/>
-      <c r="E668" s="4" t="n"/>
-      <c r="F668" s="4" t="n"/>
-      <c r="G668" s="4" t="n"/>
-      <c r="H668" s="4" t="n"/>
-      <c r="I668" s="4" t="n"/>
-      <c r="J668" s="3" t="n"/>
-      <c r="K668" s="3" t="n"/>
-    </row>
-    <row r="669">
-      <c r="A669" s="4" t="n"/>
-      <c r="B669" s="4" t="n"/>
-      <c r="C669" s="4" t="n"/>
-      <c r="D669" s="4" t="n"/>
-      <c r="E669" s="4" t="n"/>
-      <c r="F669" s="4" t="n"/>
-      <c r="G669" s="4" t="n"/>
-      <c r="H669" s="4" t="n"/>
-      <c r="I669" s="4" t="n"/>
-      <c r="J669" s="3" t="n"/>
-      <c r="K669" s="3" t="n"/>
-    </row>
-    <row r="670">
-      <c r="A670" s="4" t="n"/>
-      <c r="B670" s="4" t="n"/>
-      <c r="C670" s="4" t="n"/>
-      <c r="D670" s="4" t="n"/>
-      <c r="E670" s="4" t="n"/>
-      <c r="F670" s="4" t="n"/>
-      <c r="G670" s="4" t="n"/>
-      <c r="H670" s="4" t="n"/>
-      <c r="I670" s="4" t="n"/>
-      <c r="J670" s="3" t="n"/>
-      <c r="K670" s="3" t="n"/>
-    </row>
-    <row r="671">
-      <c r="A671" s="4" t="n"/>
-      <c r="B671" s="4" t="n"/>
-      <c r="C671" s="4" t="n"/>
-      <c r="D671" s="4" t="n"/>
-      <c r="E671" s="4" t="n"/>
-      <c r="F671" s="4" t="n"/>
-      <c r="G671" s="4" t="n"/>
-      <c r="H671" s="4" t="n"/>
-      <c r="I671" s="4" t="n"/>
-      <c r="J671" s="3" t="n"/>
-      <c r="K671" s="3" t="n"/>
-    </row>
-    <row r="672">
-      <c r="A672" s="4" t="n"/>
-      <c r="B672" s="4" t="n"/>
-      <c r="C672" s="4" t="n"/>
-      <c r="D672" s="4" t="n"/>
-      <c r="E672" s="4" t="n"/>
-      <c r="F672" s="4" t="n"/>
-      <c r="G672" s="4" t="n"/>
-      <c r="H672" s="4" t="n"/>
-      <c r="I672" s="4" t="n"/>
-      <c r="J672" s="3" t="n"/>
-      <c r="K672" s="3" t="n"/>
-    </row>
-    <row r="673">
-      <c r="A673" s="4" t="n"/>
-      <c r="B673" s="4" t="n"/>
-      <c r="C673" s="4" t="n"/>
-      <c r="D673" s="4" t="n"/>
-      <c r="E673" s="4" t="n"/>
-      <c r="F673" s="4" t="n"/>
-      <c r="G673" s="4" t="n"/>
-      <c r="H673" s="4" t="n"/>
-      <c r="I673" s="4" t="n"/>
-      <c r="J673" s="3" t="n"/>
-      <c r="K673" s="3" t="n"/>
-    </row>
-    <row r="674">
-      <c r="A674" s="4" t="n"/>
-      <c r="B674" s="4" t="n"/>
-      <c r="C674" s="4" t="n"/>
-      <c r="D674" s="4" t="n"/>
-      <c r="E674" s="4" t="n"/>
-      <c r="F674" s="4" t="n"/>
-      <c r="G674" s="4" t="n"/>
-      <c r="H674" s="4" t="n"/>
-      <c r="I674" s="4" t="n"/>
-      <c r="J674" s="3" t="n"/>
-      <c r="K674" s="3" t="n"/>
-    </row>
-    <row r="675">
-      <c r="A675" s="4" t="n"/>
-      <c r="B675" s="4" t="n"/>
-      <c r="C675" s="4" t="n"/>
-      <c r="D675" s="4" t="n"/>
-      <c r="E675" s="4" t="n"/>
-      <c r="F675" s="4" t="n"/>
-      <c r="G675" s="4" t="n"/>
-      <c r="H675" s="4" t="n"/>
-      <c r="I675" s="4" t="n"/>
-      <c r="J675" s="3" t="n"/>
-      <c r="K675" s="3" t="n"/>
-    </row>
-    <row r="676">
-      <c r="A676" s="4" t="n"/>
-      <c r="B676" s="4" t="n"/>
-      <c r="C676" s="4" t="n"/>
-      <c r="D676" s="4" t="n"/>
-      <c r="E676" s="4" t="n"/>
-      <c r="F676" s="4" t="n"/>
-      <c r="G676" s="4" t="n"/>
-      <c r="H676" s="4" t="n"/>
-      <c r="I676" s="4" t="n"/>
-      <c r="J676" s="3" t="n"/>
-      <c r="K676" s="3" t="n"/>
-    </row>
-    <row r="677">
-      <c r="A677" s="4" t="n"/>
-      <c r="B677" s="4" t="n"/>
-      <c r="C677" s="4" t="n"/>
-      <c r="D677" s="4" t="n"/>
-      <c r="E677" s="4" t="n"/>
-      <c r="F677" s="4" t="n"/>
-      <c r="G677" s="4" t="n"/>
-      <c r="H677" s="4" t="n"/>
-      <c r="I677" s="4" t="n"/>
-      <c r="J677" s="3" t="n"/>
-      <c r="K677" s="3" t="n"/>
-    </row>
-    <row r="678">
-      <c r="A678" s="4" t="n"/>
-      <c r="B678" s="4" t="n"/>
-      <c r="C678" s="4" t="n"/>
-      <c r="D678" s="4" t="n"/>
-      <c r="E678" s="4" t="n"/>
-      <c r="F678" s="4" t="n"/>
-      <c r="G678" s="4" t="n"/>
-      <c r="H678" s="4" t="n"/>
-      <c r="I678" s="4" t="n"/>
-      <c r="J678" s="3" t="n"/>
-      <c r="K678" s="3" t="n"/>
-    </row>
-    <row r="679">
-      <c r="A679" s="4" t="n"/>
-      <c r="B679" s="4" t="n"/>
-      <c r="C679" s="4" t="n"/>
-      <c r="D679" s="4" t="n"/>
-      <c r="E679" s="4" t="n"/>
-      <c r="F679" s="4" t="n"/>
-      <c r="G679" s="4" t="n"/>
-      <c r="H679" s="4" t="n"/>
-      <c r="I679" s="4" t="n"/>
-      <c r="J679" s="3" t="n"/>
-      <c r="K679" s="3" t="n"/>
-    </row>
-    <row r="680">
-      <c r="A680" s="4" t="n"/>
-      <c r="B680" s="4" t="n"/>
-      <c r="C680" s="4" t="n"/>
-      <c r="D680" s="4" t="n"/>
-      <c r="E680" s="4" t="n"/>
-      <c r="F680" s="4" t="n"/>
-      <c r="G680" s="4" t="n"/>
-      <c r="H680" s="4" t="n"/>
-      <c r="I680" s="4" t="n"/>
-      <c r="J680" s="3" t="n"/>
-      <c r="K680" s="3" t="n"/>
-    </row>
-    <row r="681">
-      <c r="A681" s="4" t="n"/>
-      <c r="B681" s="4" t="n"/>
-      <c r="C681" s="4" t="n"/>
-      <c r="D681" s="4" t="n"/>
-      <c r="E681" s="4" t="n"/>
-      <c r="F681" s="4" t="n"/>
-      <c r="G681" s="4" t="n"/>
-      <c r="H681" s="4" t="n"/>
-      <c r="I681" s="4" t="n"/>
-      <c r="J681" s="3" t="n"/>
-      <c r="K681" s="3" t="n"/>
-    </row>
-    <row r="682">
-      <c r="A682" s="4" t="n"/>
-      <c r="B682" s="4" t="n"/>
-      <c r="C682" s="4" t="n"/>
-      <c r="D682" s="4" t="n"/>
-      <c r="E682" s="4" t="n"/>
-      <c r="F682" s="4" t="n"/>
-      <c r="G682" s="4" t="n"/>
-      <c r="H682" s="4" t="n"/>
-      <c r="I682" s="4" t="n"/>
-      <c r="J682" s="3" t="n"/>
-      <c r="K682" s="3" t="n"/>
-    </row>
-    <row r="683">
-      <c r="A683" s="4" t="n"/>
-      <c r="B683" s="4" t="n"/>
-      <c r="C683" s="4" t="n"/>
-      <c r="D683" s="4" t="n"/>
-      <c r="E683" s="4" t="n"/>
-      <c r="F683" s="4" t="n"/>
-      <c r="G683" s="4" t="n"/>
-      <c r="H683" s="4" t="n"/>
-      <c r="I683" s="4" t="n"/>
-      <c r="J683" s="3" t="n"/>
-      <c r="K683" s="3" t="n"/>
-    </row>
-    <row r="684">
-      <c r="A684" s="4" t="n"/>
-      <c r="B684" s="4" t="n"/>
-      <c r="C684" s="4" t="n"/>
-      <c r="D684" s="4" t="n"/>
-      <c r="E684" s="4" t="n"/>
-      <c r="F684" s="4" t="n"/>
-      <c r="G684" s="4" t="n"/>
-      <c r="H684" s="4" t="n"/>
-      <c r="I684" s="4" t="n"/>
-      <c r="J684" s="3" t="n"/>
-      <c r="K684" s="3" t="n"/>
-    </row>
-    <row r="685">
-      <c r="A685" s="4" t="n"/>
-      <c r="B685" s="4" t="n"/>
-      <c r="C685" s="4" t="n"/>
-      <c r="D685" s="4" t="n"/>
-      <c r="E685" s="4" t="n"/>
-      <c r="F685" s="4" t="n"/>
-      <c r="G685" s="4" t="n"/>
-      <c r="H685" s="4" t="n"/>
-      <c r="I685" s="4" t="n"/>
-      <c r="J685" s="3" t="n"/>
-      <c r="K685" s="3" t="n"/>
-    </row>
-    <row r="686">
-      <c r="A686" s="4" t="n"/>
-      <c r="B686" s="4" t="n"/>
-      <c r="C686" s="4" t="n"/>
-      <c r="D686" s="4" t="n"/>
-      <c r="E686" s="4" t="n"/>
-      <c r="F686" s="4" t="n"/>
-      <c r="G686" s="4" t="n"/>
-      <c r="H686" s="4" t="n"/>
-      <c r="I686" s="4" t="n"/>
-      <c r="J686" s="3" t="n"/>
-      <c r="K686" s="3" t="n"/>
-    </row>
-    <row r="687">
-      <c r="A687" s="4" t="n"/>
-      <c r="B687" s="4" t="n"/>
-      <c r="C687" s="4" t="n"/>
-      <c r="D687" s="4" t="n"/>
-      <c r="E687" s="4" t="n"/>
-      <c r="F687" s="4" t="n"/>
-      <c r="G687" s="4" t="n"/>
-      <c r="H687" s="4" t="n"/>
-      <c r="I687" s="4" t="n"/>
-      <c r="J687" s="3" t="n"/>
-      <c r="K687" s="3" t="n"/>
-    </row>
-    <row r="688">
-      <c r="A688" s="4" t="n"/>
-      <c r="B688" s="4" t="n"/>
-      <c r="C688" s="4" t="n"/>
-      <c r="D688" s="4" t="n"/>
-      <c r="E688" s="4" t="n"/>
-      <c r="F688" s="4" t="n"/>
-      <c r="G688" s="4" t="n"/>
-      <c r="H688" s="4" t="n"/>
-      <c r="I688" s="4" t="n"/>
-      <c r="J688" s="3" t="n"/>
-      <c r="K688" s="3" t="n"/>
-    </row>
-    <row r="689">
-      <c r="A689" s="4" t="n"/>
-      <c r="B689" s="4" t="n"/>
-      <c r="C689" s="4" t="n"/>
-      <c r="D689" s="4" t="n"/>
-      <c r="E689" s="4" t="n"/>
-      <c r="F689" s="4" t="n"/>
-      <c r="G689" s="4" t="n"/>
-      <c r="H689" s="4" t="n"/>
-      <c r="I689" s="4" t="n"/>
-      <c r="J689" s="3" t="n"/>
-      <c r="K689" s="3" t="n"/>
-    </row>
-    <row r="690">
-      <c r="A690" s="4" t="n"/>
-      <c r="B690" s="4" t="n"/>
-      <c r="C690" s="4" t="n"/>
-      <c r="D690" s="4" t="n"/>
-      <c r="E690" s="4" t="n"/>
-      <c r="F690" s="4" t="n"/>
-      <c r="G690" s="4" t="n"/>
-      <c r="H690" s="4" t="n"/>
-      <c r="I690" s="4" t="n"/>
-      <c r="J690" s="3" t="n"/>
-      <c r="K690" s="3" t="n"/>
-    </row>
-    <row r="691">
-      <c r="A691" s="4" t="n"/>
-      <c r="B691" s="4" t="n"/>
-      <c r="C691" s="4" t="n"/>
-      <c r="D691" s="4" t="n"/>
-      <c r="E691" s="4" t="n"/>
-      <c r="F691" s="4" t="n"/>
-      <c r="G691" s="4" t="n"/>
-      <c r="H691" s="4" t="n"/>
-      <c r="I691" s="4" t="n"/>
-      <c r="J691" s="3" t="n"/>
-      <c r="K691" s="3" t="n"/>
-    </row>
-    <row r="692">
-      <c r="A692" s="4" t="n"/>
-      <c r="B692" s="4" t="n"/>
-      <c r="C692" s="4" t="n"/>
-      <c r="D692" s="4" t="n"/>
-      <c r="E692" s="4" t="n"/>
-      <c r="F692" s="4" t="n"/>
-      <c r="G692" s="4" t="n"/>
-      <c r="H692" s="4" t="n"/>
-      <c r="I692" s="4" t="n"/>
-      <c r="J692" s="3" t="n"/>
-      <c r="K692" s="3" t="n"/>
-    </row>
-    <row r="693">
-      <c r="A693" s="4" t="n"/>
-      <c r="B693" s="4" t="n"/>
-      <c r="C693" s="4" t="n"/>
-      <c r="D693" s="4" t="n"/>
-      <c r="E693" s="4" t="n"/>
-      <c r="F693" s="4" t="n"/>
-      <c r="G693" s="4" t="n"/>
-      <c r="H693" s="4" t="n"/>
-      <c r="I693" s="4" t="n"/>
-      <c r="J693" s="3" t="n"/>
-      <c r="K693" s="3" t="n"/>
-    </row>
-    <row r="694">
-      <c r="A694" s="4" t="n"/>
-      <c r="B694" s="4" t="n"/>
-      <c r="C694" s="4" t="n"/>
-      <c r="D694" s="4" t="n"/>
-      <c r="E694" s="4" t="n"/>
-      <c r="F694" s="4" t="n"/>
-      <c r="G694" s="4" t="n"/>
-      <c r="H694" s="4" t="n"/>
-      <c r="I694" s="4" t="n"/>
-      <c r="J694" s="3" t="n"/>
-      <c r="K694" s="3" t="n"/>
-    </row>
-    <row r="695">
-      <c r="A695" s="4" t="n"/>
-      <c r="B695" s="4" t="n"/>
-      <c r="C695" s="4" t="n"/>
-      <c r="D695" s="4" t="n"/>
-      <c r="E695" s="4" t="n"/>
-      <c r="F695" s="4" t="n"/>
-      <c r="G695" s="4" t="n"/>
-      <c r="H695" s="4" t="n"/>
-      <c r="I695" s="4" t="n"/>
-      <c r="J695" s="3" t="n"/>
-      <c r="K695" s="3" t="n"/>
-    </row>
-    <row r="696">
-      <c r="A696" s="4" t="n"/>
-      <c r="B696" s="4" t="n"/>
-      <c r="C696" s="4" t="n"/>
-      <c r="D696" s="4" t="n"/>
-      <c r="E696" s="4" t="n"/>
-      <c r="F696" s="4" t="n"/>
-      <c r="G696" s="4" t="n"/>
-      <c r="H696" s="4" t="n"/>
-      <c r="I696" s="4" t="n"/>
-      <c r="J696" s="3" t="n"/>
-      <c r="K696" s="3" t="n"/>
-    </row>
-    <row r="697">
-      <c r="A697" s="4" t="n"/>
-      <c r="B697" s="4" t="n"/>
-      <c r="C697" s="4" t="n"/>
-      <c r="D697" s="4" t="n"/>
-      <c r="E697" s="4" t="n"/>
-      <c r="F697" s="4" t="n"/>
-      <c r="G697" s="4" t="n"/>
-      <c r="H697" s="4" t="n"/>
-      <c r="I697" s="4" t="n"/>
-      <c r="J697" s="3" t="n"/>
-      <c r="K697" s="3" t="n"/>
-    </row>
-    <row r="698">
-      <c r="A698" s="4" t="n"/>
-      <c r="B698" s="4" t="n"/>
-      <c r="C698" s="4" t="n"/>
-      <c r="D698" s="4" t="n"/>
-      <c r="E698" s="4" t="n"/>
-      <c r="F698" s="4" t="n"/>
-      <c r="G698" s="4" t="n"/>
-      <c r="H698" s="4" t="n"/>
-      <c r="I698" s="4" t="n"/>
-      <c r="J698" s="3" t="n"/>
-      <c r="K698" s="3" t="n"/>
-    </row>
-    <row r="699">
-      <c r="A699" s="4" t="n"/>
-      <c r="B699" s="4" t="n"/>
-      <c r="C699" s="4" t="n"/>
-      <c r="D699" s="4" t="n"/>
-      <c r="E699" s="4" t="n"/>
-      <c r="F699" s="4" t="n"/>
-      <c r="G699" s="4" t="n"/>
-      <c r="H699" s="4" t="n"/>
-      <c r="I699" s="4" t="n"/>
-      <c r="J699" s="3" t="n"/>
-      <c r="K699" s="3" t="n"/>
-    </row>
-    <row r="700">
-      <c r="A700" s="4" t="n"/>
-      <c r="B700" s="4" t="n"/>
-      <c r="C700" s="4" t="n"/>
-      <c r="D700" s="4" t="n"/>
-      <c r="E700" s="4" t="n"/>
-      <c r="F700" s="4" t="n"/>
-      <c r="G700" s="4" t="n"/>
-      <c r="H700" s="4" t="n"/>
-      <c r="I700" s="4" t="n"/>
-      <c r="J700" s="3" t="n"/>
-      <c r="K700" s="3" t="n"/>
-    </row>
-    <row r="701">
-      <c r="A701" s="4" t="n"/>
-      <c r="B701" s="4" t="n"/>
-      <c r="C701" s="4" t="n"/>
-      <c r="D701" s="4" t="n"/>
-      <c r="E701" s="4" t="n"/>
-      <c r="F701" s="4" t="n"/>
-      <c r="G701" s="4" t="n"/>
-      <c r="H701" s="4" t="n"/>
-      <c r="I701" s="4" t="n"/>
-      <c r="J701" s="3" t="n"/>
-      <c r="K701" s="3" t="n"/>
-    </row>
-    <row r="702">
-      <c r="A702" s="4" t="n"/>
-      <c r="B702" s="4" t="n"/>
-      <c r="C702" s="4" t="n"/>
-      <c r="D702" s="4" t="n"/>
-      <c r="E702" s="4" t="n"/>
-      <c r="F702" s="4" t="n"/>
-      <c r="G702" s="4" t="n"/>
-      <c r="H702" s="4" t="n"/>
-      <c r="I702" s="4" t="n"/>
-      <c r="J702" s="3" t="n"/>
-      <c r="K702" s="3" t="n"/>
-    </row>
-    <row r="703">
-      <c r="A703" s="4" t="n"/>
-      <c r="B703" s="4" t="n"/>
-      <c r="C703" s="4" t="n"/>
-      <c r="D703" s="4" t="n"/>
-      <c r="E703" s="4" t="n"/>
-      <c r="F703" s="4" t="n"/>
-      <c r="G703" s="4" t="n"/>
-      <c r="H703" s="4" t="n"/>
-      <c r="I703" s="4" t="n"/>
-      <c r="J703" s="3" t="n"/>
-      <c r="K703" s="3" t="n"/>
-    </row>
-    <row r="704">
-      <c r="A704" s="4" t="n"/>
-      <c r="B704" s="4" t="n"/>
-      <c r="C704" s="4" t="n"/>
-      <c r="D704" s="4" t="n"/>
-      <c r="E704" s="4" t="n"/>
-      <c r="F704" s="4" t="n"/>
-      <c r="G704" s="4" t="n"/>
-      <c r="H704" s="4" t="n"/>
-      <c r="I704" s="4" t="n"/>
-      <c r="J704" s="3" t="n"/>
-      <c r="K704" s="3" t="n"/>
-    </row>
-    <row r="705">
-      <c r="A705" s="4" t="n"/>
-      <c r="B705" s="4" t="n"/>
-      <c r="C705" s="4" t="n"/>
-      <c r="D705" s="4" t="n"/>
-      <c r="E705" s="4" t="n"/>
-      <c r="F705" s="4" t="n"/>
-      <c r="G705" s="4" t="n"/>
-      <c r="H705" s="4" t="n"/>
-      <c r="I705" s="4" t="n"/>
-      <c r="J705" s="3" t="n"/>
-      <c r="K705" s="3" t="n"/>
-    </row>
-    <row r="706">
-      <c r="A706" s="4" t="n"/>
-      <c r="B706" s="4" t="n"/>
-      <c r="C706" s="4" t="n"/>
-      <c r="D706" s="4" t="n"/>
-      <c r="E706" s="4" t="n"/>
-      <c r="F706" s="4" t="n"/>
-      <c r="G706" s="4" t="n"/>
-      <c r="H706" s="4" t="n"/>
-      <c r="I706" s="4" t="n"/>
-      <c r="J706" s="3" t="n"/>
-      <c r="K706" s="3" t="n"/>
-    </row>
-    <row r="707">
-      <c r="A707" s="4" t="n"/>
-      <c r="B707" s="4" t="n"/>
-      <c r="C707" s="4" t="n"/>
-      <c r="D707" s="4" t="n"/>
-      <c r="E707" s="4" t="n"/>
-      <c r="F707" s="4" t="n"/>
-      <c r="G707" s="4" t="n"/>
-      <c r="H707" s="4" t="n"/>
-      <c r="I707" s="4" t="n"/>
-      <c r="J707" s="3" t="n"/>
-      <c r="K707" s="3" t="n"/>
-    </row>
-    <row r="708">
-      <c r="A708" s="4" t="n"/>
-      <c r="B708" s="4" t="n"/>
-      <c r="C708" s="4" t="n"/>
-      <c r="D708" s="4" t="n"/>
-      <c r="E708" s="4" t="n"/>
-      <c r="F708" s="4" t="n"/>
-      <c r="G708" s="4" t="n"/>
-      <c r="H708" s="4" t="n"/>
-      <c r="I708" s="4" t="n"/>
-      <c r="J708" s="3" t="n"/>
-      <c r="K708" s="3" t="n"/>
-    </row>
-    <row r="709">
-      <c r="A709" s="4" t="n"/>
-      <c r="B709" s="4" t="n"/>
-      <c r="C709" s="4" t="n"/>
-      <c r="D709" s="4" t="n"/>
-      <c r="E709" s="4" t="n"/>
-      <c r="F709" s="4" t="n"/>
-      <c r="G709" s="4" t="n"/>
-      <c r="H709" s="4" t="n"/>
-      <c r="I709" s="4" t="n"/>
-      <c r="J709" s="3" t="n"/>
-      <c r="K709" s="3" t="n"/>
-    </row>
-    <row r="710">
-      <c r="A710" s="4" t="n"/>
-      <c r="B710" s="4" t="n"/>
-      <c r="C710" s="4" t="n"/>
-      <c r="D710" s="4" t="n"/>
-      <c r="E710" s="4" t="n"/>
-      <c r="F710" s="4" t="n"/>
-      <c r="G710" s="4" t="n"/>
-      <c r="H710" s="4" t="n"/>
-      <c r="I710" s="4" t="n"/>
-      <c r="J710" s="3" t="n"/>
-      <c r="K710" s="3" t="n"/>
-    </row>
-    <row r="711">
-      <c r="A711" s="4" t="n"/>
-      <c r="B711" s="4" t="n"/>
-      <c r="C711" s="4" t="n"/>
-      <c r="D711" s="4" t="n"/>
-      <c r="E711" s="4" t="n"/>
-      <c r="F711" s="4" t="n"/>
-      <c r="G711" s="4" t="n"/>
-      <c r="H711" s="4" t="n"/>
-      <c r="I711" s="4" t="n"/>
-      <c r="J711" s="3" t="n"/>
-      <c r="K711" s="3" t="n"/>
-    </row>
-    <row r="712">
-      <c r="A712" s="4" t="n"/>
-      <c r="B712" s="4" t="n"/>
-      <c r="C712" s="4" t="n"/>
-      <c r="D712" s="4" t="n"/>
-      <c r="E712" s="4" t="n"/>
-      <c r="F712" s="4" t="n"/>
-      <c r="G712" s="4" t="n"/>
-      <c r="H712" s="4" t="n"/>
-      <c r="I712" s="4" t="n"/>
-      <c r="J712" s="3" t="n"/>
-      <c r="K712" s="3" t="n"/>
-    </row>
-    <row r="713">
-      <c r="A713" s="4" t="n"/>
-      <c r="B713" s="4" t="n"/>
-      <c r="C713" s="4" t="n"/>
-      <c r="D713" s="4" t="n"/>
-      <c r="E713" s="4" t="n"/>
-      <c r="F713" s="4" t="n"/>
-      <c r="G713" s="4" t="n"/>
-      <c r="H713" s="4" t="n"/>
-      <c r="I713" s="4" t="n"/>
-      <c r="J713" s="3" t="n"/>
-      <c r="K713" s="3" t="n"/>
-    </row>
-    <row r="714">
-      <c r="A714" s="4" t="n"/>
-      <c r="B714" s="4" t="n"/>
-      <c r="C714" s="4" t="n"/>
-      <c r="D714" s="4" t="n"/>
-      <c r="E714" s="4" t="n"/>
-      <c r="F714" s="4" t="n"/>
-      <c r="G714" s="4" t="n"/>
-      <c r="H714" s="4" t="n"/>
-      <c r="I714" s="4" t="n"/>
-      <c r="J714" s="3" t="n"/>
-      <c r="K714" s="3" t="n"/>
-    </row>
-    <row r="715">
-      <c r="A715" s="4" t="n"/>
-      <c r="B715" s="4" t="n"/>
-      <c r="C715" s="4" t="n"/>
-      <c r="D715" s="4" t="n"/>
-      <c r="E715" s="4" t="n"/>
-      <c r="F715" s="4" t="n"/>
-      <c r="G715" s="4" t="n"/>
-      <c r="H715" s="4" t="n"/>
-      <c r="I715" s="4" t="n"/>
-      <c r="J715" s="3" t="n"/>
-      <c r="K715" s="3" t="n"/>
-    </row>
-    <row r="716">
-      <c r="A716" s="4" t="n"/>
-      <c r="B716" s="4" t="n"/>
-      <c r="C716" s="4" t="n"/>
-      <c r="D716" s="4" t="n"/>
-      <c r="E716" s="4" t="n"/>
-      <c r="F716" s="4" t="n"/>
-      <c r="G716" s="4" t="n"/>
-      <c r="H716" s="4" t="n"/>
-      <c r="I716" s="4" t="n"/>
-      <c r="J716" s="3" t="n"/>
-      <c r="K716" s="3" t="n"/>
-    </row>
-    <row r="717">
-      <c r="A717" s="4" t="n"/>
-      <c r="B717" s="4" t="n"/>
-      <c r="C717" s="4" t="n"/>
-      <c r="D717" s="4" t="n"/>
-      <c r="E717" s="4" t="n"/>
-      <c r="F717" s="4" t="n"/>
-      <c r="G717" s="4" t="n"/>
-      <c r="H717" s="4" t="n"/>
-      <c r="I717" s="4" t="n"/>
-      <c r="J717" s="3" t="n"/>
-      <c r="K717" s="3" t="n"/>
-    </row>
-    <row r="718">
-      <c r="A718" s="4" t="n"/>
-      <c r="B718" s="4" t="n"/>
-      <c r="C718" s="4" t="n"/>
-      <c r="D718" s="4" t="n"/>
-      <c r="E718" s="4" t="n"/>
-      <c r="F718" s="4" t="n"/>
-      <c r="G718" s="4" t="n"/>
-      <c r="H718" s="4" t="n"/>
-      <c r="I718" s="4" t="n"/>
-      <c r="J718" s="3" t="n"/>
-      <c r="K718" s="3" t="n"/>
-    </row>
-    <row r="719">
-      <c r="A719" s="4" t="n"/>
-      <c r="B719" s="4" t="n"/>
-      <c r="C719" s="4" t="n"/>
-      <c r="D719" s="4" t="n"/>
-      <c r="E719" s="4" t="n"/>
-      <c r="F719" s="4" t="n"/>
-      <c r="G719" s="4" t="n"/>
-      <c r="H719" s="4" t="n"/>
-      <c r="I719" s="4" t="n"/>
-      <c r="J719" s="3" t="n"/>
-      <c r="K719" s="3" t="n"/>
-    </row>
-    <row r="720">
-      <c r="A720" s="4" t="n"/>
-      <c r="B720" s="4" t="n"/>
-      <c r="C720" s="4" t="n"/>
-      <c r="D720" s="4" t="n"/>
-      <c r="E720" s="4" t="n"/>
-      <c r="F720" s="4" t="n"/>
-      <c r="G720" s="4" t="n"/>
-      <c r="H720" s="4" t="n"/>
-      <c r="I720" s="4" t="n"/>
-      <c r="J720" s="3" t="n"/>
-      <c r="K720" s="3" t="n"/>
-    </row>
-    <row r="721">
-      <c r="A721" s="4" t="n"/>
-      <c r="B721" s="4" t="n"/>
-      <c r="C721" s="4" t="n"/>
-      <c r="D721" s="4" t="n"/>
-      <c r="E721" s="4" t="n"/>
-      <c r="F721" s="4" t="n"/>
-      <c r="G721" s="4" t="n"/>
-      <c r="H721" s="4" t="n"/>
-      <c r="I721" s="4" t="n"/>
-      <c r="J721" s="3" t="n"/>
-      <c r="K721" s="3" t="n"/>
-    </row>
-    <row r="722">
-      <c r="A722" s="4" t="n"/>
-      <c r="B722" s="4" t="n"/>
-      <c r="C722" s="4" t="n"/>
-      <c r="D722" s="4" t="n"/>
-      <c r="E722" s="4" t="n"/>
-      <c r="F722" s="4" t="n"/>
-      <c r="G722" s="4" t="n"/>
-      <c r="H722" s="4" t="n"/>
-      <c r="I722" s="4" t="n"/>
-      <c r="J722" s="3" t="n"/>
-      <c r="K722" s="3" t="n"/>
-    </row>
-    <row r="723">
-      <c r="A723" s="4" t="n"/>
-      <c r="B723" s="4" t="n"/>
-      <c r="C723" s="4" t="n"/>
-      <c r="D723" s="4" t="n"/>
-      <c r="E723" s="4" t="n"/>
-      <c r="F723" s="4" t="n"/>
-      <c r="G723" s="4" t="n"/>
-      <c r="H723" s="4" t="n"/>
-      <c r="I723" s="4" t="n"/>
-      <c r="J723" s="3" t="n"/>
-      <c r="K723" s="3" t="n"/>
-    </row>
-    <row r="724">
-      <c r="A724" s="4" t="n"/>
-      <c r="B724" s="4" t="n"/>
-      <c r="C724" s="4" t="n"/>
-      <c r="D724" s="4" t="n"/>
-      <c r="E724" s="4" t="n"/>
-      <c r="F724" s="4" t="n"/>
-      <c r="G724" s="4" t="n"/>
-      <c r="H724" s="4" t="n"/>
-      <c r="I724" s="4" t="n"/>
-      <c r="J724" s="3" t="n"/>
-      <c r="K724" s="3" t="n"/>
-    </row>
-    <row r="725">
-      <c r="A725" s="4" t="n"/>
-      <c r="B725" s="4" t="n"/>
-      <c r="C725" s="4" t="n"/>
-      <c r="D725" s="4" t="n"/>
-      <c r="E725" s="4" t="n"/>
-      <c r="F725" s="4" t="n"/>
-      <c r="G725" s="4" t="n"/>
-      <c r="H725" s="4" t="n"/>
-      <c r="I725" s="4" t="n"/>
-      <c r="J725" s="3" t="n"/>
-      <c r="K725" s="3" t="n"/>
-    </row>
-    <row r="726">
-      <c r="A726" s="4" t="n"/>
-      <c r="B726" s="4" t="n"/>
-      <c r="C726" s="4" t="n"/>
-      <c r="D726" s="4" t="n"/>
-      <c r="E726" s="4" t="n"/>
-      <c r="F726" s="4" t="n"/>
-      <c r="G726" s="4" t="n"/>
-      <c r="H726" s="4" t="n"/>
-      <c r="I726" s="4" t="n"/>
-      <c r="J726" s="3" t="n"/>
-      <c r="K726" s="3" t="n"/>
-    </row>
-    <row r="727">
-      <c r="A727" s="4" t="n"/>
-      <c r="B727" s="4" t="n"/>
-      <c r="C727" s="4" t="n"/>
-      <c r="D727" s="4" t="n"/>
-      <c r="E727" s="4" t="n"/>
-      <c r="F727" s="4" t="n"/>
-      <c r="G727" s="4" t="n"/>
-      <c r="H727" s="4" t="n"/>
-      <c r="I727" s="4" t="n"/>
-      <c r="J727" s="3" t="n"/>
-      <c r="K727" s="3" t="n"/>
-    </row>
-    <row r="728">
-      <c r="A728" s="4" t="n"/>
-      <c r="B728" s="4" t="n"/>
-      <c r="C728" s="4" t="n"/>
-      <c r="D728" s="4" t="n"/>
-      <c r="E728" s="4" t="n"/>
-      <c r="F728" s="4" t="n"/>
-      <c r="G728" s="4" t="n"/>
-      <c r="H728" s="4" t="n"/>
-      <c r="I728" s="4" t="n"/>
-      <c r="J728" s="3" t="n"/>
-      <c r="K728" s="3" t="n"/>
-    </row>
-    <row r="729">
-      <c r="A729" s="4" t="n"/>
-      <c r="B729" s="4" t="n"/>
-      <c r="C729" s="4" t="n"/>
-      <c r="D729" s="4" t="n"/>
-      <c r="E729" s="4" t="n"/>
-      <c r="F729" s="4" t="n"/>
-      <c r="G729" s="4" t="n"/>
-      <c r="H729" s="4" t="n"/>
-      <c r="I729" s="4" t="n"/>
-      <c r="J729" s="3" t="n"/>
-      <c r="K729" s="3" t="n"/>
-    </row>
-    <row r="730">
-      <c r="A730" s="4" t="n"/>
-      <c r="B730" s="4" t="n"/>
-      <c r="C730" s="4" t="n"/>
-      <c r="D730" s="4" t="n"/>
-      <c r="E730" s="4" t="n"/>
-      <c r="F730" s="4" t="n"/>
-      <c r="G730" s="4" t="n"/>
-      <c r="H730" s="4" t="n"/>
-      <c r="I730" s="4" t="n"/>
-      <c r="J730" s="3" t="n"/>
-      <c r="K730" s="3" t="n"/>
-    </row>
-    <row r="731">
-      <c r="A731" s="4" t="n"/>
-      <c r="B731" s="4" t="n"/>
-      <c r="C731" s="4" t="n"/>
-      <c r="D731" s="4" t="n"/>
-      <c r="E731" s="4" t="n"/>
-      <c r="F731" s="4" t="n"/>
-      <c r="G731" s="4" t="n"/>
-      <c r="H731" s="4" t="n"/>
-      <c r="I731" s="4" t="n"/>
-      <c r="J731" s="3" t="n"/>
-      <c r="K731" s="3" t="n"/>
-    </row>
-    <row r="732">
-      <c r="A732" s="4" t="n"/>
-      <c r="B732" s="4" t="n"/>
-      <c r="C732" s="4" t="n"/>
-      <c r="D732" s="4" t="n"/>
-      <c r="E732" s="4" t="n"/>
-      <c r="F732" s="4" t="n"/>
-      <c r="G732" s="4" t="n"/>
-      <c r="H732" s="4" t="n"/>
-      <c r="I732" s="4" t="n"/>
-      <c r="J732" s="3" t="n"/>
-      <c r="K732" s="3" t="n"/>
-    </row>
-    <row r="733">
-      <c r="A733" s="4" t="n"/>
-      <c r="B733" s="4" t="n"/>
-      <c r="C733" s="4" t="n"/>
-      <c r="D733" s="4" t="n"/>
-      <c r="E733" s="4" t="n"/>
-      <c r="F733" s="4" t="n"/>
-      <c r="G733" s="4" t="n"/>
-      <c r="H733" s="4" t="n"/>
-      <c r="I733" s="4" t="n"/>
-      <c r="J733" s="3" t="n"/>
-      <c r="K733" s="3" t="n"/>
-    </row>
-    <row r="734">
-      <c r="A734" s="4" t="n"/>
-      <c r="B734" s="4" t="n"/>
-      <c r="C734" s="4" t="n"/>
-      <c r="D734" s="4" t="n"/>
-      <c r="E734" s="4" t="n"/>
-      <c r="F734" s="4" t="n"/>
-      <c r="G734" s="4" t="n"/>
-      <c r="H734" s="4" t="n"/>
-      <c r="I734" s="4" t="n"/>
-      <c r="J734" s="3" t="n"/>
-      <c r="K734" s="3" t="n"/>
-    </row>
-    <row r="735">
-      <c r="A735" s="4" t="n"/>
-      <c r="B735" s="4" t="n"/>
-      <c r="C735" s="4" t="n"/>
-      <c r="D735" s="4" t="n"/>
-      <c r="E735" s="4" t="n"/>
-      <c r="F735" s="4" t="n"/>
-      <c r="G735" s="4" t="n"/>
-      <c r="H735" s="4" t="n"/>
-      <c r="I735" s="4" t="n"/>
-      <c r="J735" s="3" t="n"/>
-      <c r="K735" s="3" t="n"/>
-    </row>
-    <row r="736">
-      <c r="A736" s="4" t="n"/>
-      <c r="B736" s="4" t="n"/>
-      <c r="C736" s="4" t="n"/>
-      <c r="D736" s="4" t="n"/>
-      <c r="E736" s="4" t="n"/>
-      <c r="F736" s="4" t="n"/>
-      <c r="G736" s="4" t="n"/>
-      <c r="H736" s="4" t="n"/>
-      <c r="I736" s="4" t="n"/>
-      <c r="J736" s="3" t="n"/>
-      <c r="K736" s="3" t="n"/>
-    </row>
-    <row r="737">
-      <c r="A737" s="4" t="n"/>
-      <c r="B737" s="4" t="n"/>
-      <c r="C737" s="4" t="n"/>
-      <c r="D737" s="4" t="n"/>
-      <c r="E737" s="4" t="n"/>
-      <c r="F737" s="4" t="n"/>
-      <c r="G737" s="4" t="n"/>
-      <c r="H737" s="4" t="n"/>
-      <c r="I737" s="4" t="n"/>
-      <c r="J737" s="3" t="n"/>
-      <c r="K737" s="3" t="n"/>
-    </row>
-    <row r="738">
-      <c r="A738" s="4" t="n"/>
-      <c r="B738" s="4" t="n"/>
-      <c r="C738" s="4" t="n"/>
-      <c r="D738" s="4" t="n"/>
-      <c r="E738" s="4" t="n"/>
-      <c r="F738" s="4" t="n"/>
-      <c r="G738" s="4" t="n"/>
-      <c r="H738" s="4" t="n"/>
-      <c r="I738" s="4" t="n"/>
-      <c r="J738" s="3" t="n"/>
-      <c r="K738" s="3" t="n"/>
-    </row>
-    <row r="739">
-      <c r="A739" s="4" t="n"/>
-      <c r="B739" s="4" t="n"/>
-      <c r="C739" s="4" t="n"/>
-      <c r="D739" s="4" t="n"/>
-      <c r="E739" s="4" t="n"/>
-      <c r="F739" s="4" t="n"/>
-      <c r="G739" s="4" t="n"/>
-      <c r="H739" s="4" t="n"/>
-      <c r="I739" s="4" t="n"/>
-      <c r="J739" s="3" t="n"/>
-      <c r="K739" s="3" t="n"/>
-    </row>
-    <row r="740">
-      <c r="A740" s="4" t="n"/>
-      <c r="B740" s="4" t="n"/>
-      <c r="C740" s="4" t="n"/>
-      <c r="D740" s="4" t="n"/>
-      <c r="E740" s="4" t="n"/>
-      <c r="F740" s="4" t="n"/>
-      <c r="G740" s="4" t="n"/>
-      <c r="H740" s="4" t="n"/>
-      <c r="I740" s="4" t="n"/>
-      <c r="J740" s="3" t="n"/>
-      <c r="K740" s="3" t="n"/>
-    </row>
-    <row r="741">
-      <c r="A741" s="4" t="n"/>
-      <c r="B741" s="4" t="n"/>
-      <c r="C741" s="4" t="n"/>
-      <c r="D741" s="4" t="n"/>
-      <c r="E741" s="4" t="n"/>
-      <c r="F741" s="4" t="n"/>
-      <c r="G741" s="4" t="n"/>
-      <c r="H741" s="4" t="n"/>
-      <c r="I741" s="4" t="n"/>
-      <c r="J741" s="3" t="n"/>
-      <c r="K741" s="3" t="n"/>
-    </row>
-    <row r="742">
-      <c r="A742" s="4" t="n"/>
-      <c r="B742" s="4" t="n"/>
-      <c r="C742" s="4" t="n"/>
-      <c r="D742" s="4" t="n"/>
-      <c r="E742" s="4" t="n"/>
-      <c r="F742" s="4" t="n"/>
-      <c r="G742" s="4" t="n"/>
-      <c r="H742" s="4" t="n"/>
-      <c r="I742" s="4" t="n"/>
-      <c r="J742" s="3" t="n"/>
-      <c r="K742" s="3" t="n"/>
-    </row>
-    <row r="743">
-      <c r="A743" s="4" t="n"/>
-      <c r="B743" s="4" t="n"/>
-      <c r="C743" s="4" t="n"/>
-      <c r="D743" s="4" t="n"/>
-      <c r="E743" s="4" t="n"/>
-      <c r="F743" s="4" t="n"/>
-      <c r="G743" s="4" t="n"/>
-      <c r="H743" s="4" t="n"/>
-      <c r="I743" s="4" t="n"/>
-      <c r="J743" s="3" t="n"/>
-      <c r="K743" s="3" t="n"/>
-    </row>
-    <row r="744">
-      <c r="A744" s="4" t="n"/>
-      <c r="B744" s="4" t="n"/>
-      <c r="C744" s="4" t="n"/>
-      <c r="D744" s="4" t="n"/>
-      <c r="E744" s="4" t="n"/>
-      <c r="F744" s="4" t="n"/>
-      <c r="G744" s="4" t="n"/>
-      <c r="H744" s="4" t="n"/>
-      <c r="I744" s="4" t="n"/>
-      <c r="J744" s="3" t="n"/>
-      <c r="K744" s="3" t="n"/>
-    </row>
-    <row r="745">
-      <c r="A745" s="4" t="n"/>
-      <c r="B745" s="4" t="n"/>
-      <c r="C745" s="4" t="n"/>
-      <c r="D745" s="4" t="n"/>
-      <c r="E745" s="4" t="n"/>
-      <c r="F745" s="4" t="n"/>
-      <c r="G745" s="4" t="n"/>
-      <c r="H745" s="4" t="n"/>
-      <c r="I745" s="4" t="n"/>
-      <c r="J745" s="3" t="n"/>
-      <c r="K745" s="3" t="n"/>
-    </row>
-    <row r="746">
-      <c r="A746" s="4" t="n"/>
-      <c r="B746" s="4" t="n"/>
-      <c r="C746" s="4" t="n"/>
-      <c r="D746" s="4" t="n"/>
-      <c r="E746" s="4" t="n"/>
-      <c r="F746" s="4" t="n"/>
-      <c r="G746" s="4" t="n"/>
-      <c r="H746" s="4" t="n"/>
-      <c r="I746" s="4" t="n"/>
-      <c r="J746" s="3" t="n"/>
-      <c r="K746" s="3" t="n"/>
-    </row>
-    <row r="747">
-      <c r="A747" s="4" t="n"/>
-      <c r="B747" s="4" t="n"/>
-      <c r="C747" s="4" t="n"/>
-      <c r="D747" s="4" t="n"/>
-      <c r="E747" s="4" t="n"/>
-      <c r="F747" s="4" t="n"/>
-      <c r="G747" s="4" t="n"/>
-      <c r="H747" s="4" t="n"/>
-      <c r="I747" s="4" t="n"/>
-      <c r="J747" s="3" t="n"/>
-      <c r="K747" s="3" t="n"/>
-    </row>
-    <row r="748">
-      <c r="A748" s="4" t="n"/>
-      <c r="B748" s="4" t="n"/>
-      <c r="C748" s="4" t="n"/>
-      <c r="D748" s="4" t="n"/>
-      <c r="E748" s="4" t="n"/>
-      <c r="F748" s="4" t="n"/>
-      <c r="G748" s="4" t="n"/>
-      <c r="H748" s="4" t="n"/>
-      <c r="I748" s="4" t="n"/>
-      <c r="J748" s="3" t="n"/>
-      <c r="K748" s="3" t="n"/>
-    </row>
-    <row r="749">
-      <c r="A749" s="4" t="n"/>
-      <c r="B749" s="4" t="n"/>
-      <c r="C749" s="4" t="n"/>
-      <c r="D749" s="4" t="n"/>
-      <c r="E749" s="4" t="n"/>
-      <c r="F749" s="4" t="n"/>
-      <c r="G749" s="4" t="n"/>
-      <c r="H749" s="4" t="n"/>
-      <c r="I749" s="4" t="n"/>
-      <c r="J749" s="3" t="n"/>
-      <c r="K749" s="3" t="n"/>
-    </row>
-    <row r="750">
-      <c r="A750" s="4" t="n"/>
-      <c r="B750" s="4" t="n"/>
-      <c r="C750" s="4" t="n"/>
-      <c r="D750" s="4" t="n"/>
-      <c r="E750" s="4" t="n"/>
-      <c r="F750" s="4" t="n"/>
-      <c r="G750" s="4" t="n"/>
-      <c r="H750" s="4" t="n"/>
-      <c r="I750" s="4" t="n"/>
-      <c r="J750" s="3" t="n"/>
-      <c r="K750" s="3" t="n"/>
-    </row>
-    <row r="751">
-      <c r="A751" s="4" t="n"/>
-      <c r="B751" s="4" t="n"/>
-      <c r="C751" s="4" t="n"/>
-      <c r="D751" s="4" t="n"/>
-      <c r="E751" s="4" t="n"/>
-      <c r="F751" s="4" t="n"/>
-      <c r="G751" s="4" t="n"/>
-      <c r="H751" s="4" t="n"/>
-      <c r="I751" s="4" t="n"/>
-      <c r="J751" s="3" t="n"/>
-      <c r="K751" s="3" t="n"/>
-    </row>
-    <row r="752">
-      <c r="A752" s="4" t="n"/>
-      <c r="B752" s="4" t="n"/>
-      <c r="C752" s="4" t="n"/>
-      <c r="D752" s="4" t="n"/>
-      <c r="E752" s="4" t="n"/>
-      <c r="F752" s="4" t="n"/>
-      <c r="G752" s="4" t="n"/>
-      <c r="H752" s="4" t="n"/>
-      <c r="I752" s="4" t="n"/>
-      <c r="J752" s="3" t="n"/>
-      <c r="K752" s="3" t="n"/>
-    </row>
-    <row r="753">
-      <c r="A753" s="4" t="n"/>
-      <c r="B753" s="4" t="n"/>
-      <c r="C753" s="4" t="n"/>
-      <c r="D753" s="4" t="n"/>
-      <c r="E753" s="4" t="n"/>
-      <c r="F753" s="4" t="n"/>
-      <c r="G753" s="4" t="n"/>
-      <c r="H753" s="4" t="n"/>
-      <c r="I753" s="4" t="n"/>
-      <c r="J753" s="3" t="n"/>
-      <c r="K753" s="3" t="n"/>
-    </row>
-    <row r="754">
-      <c r="A754" s="4" t="n"/>
-      <c r="B754" s="4" t="n"/>
-      <c r="C754" s="4" t="n"/>
-      <c r="D754" s="4" t="n"/>
-      <c r="E754" s="4" t="n"/>
-      <c r="F754" s="4" t="n"/>
-      <c r="G754" s="4" t="n"/>
-      <c r="H754" s="4" t="n"/>
-      <c r="I754" s="4" t="n"/>
-      <c r="J754" s="3" t="n"/>
-      <c r="K754" s="3" t="n"/>
-    </row>
-    <row r="755">
-      <c r="A755" s="4" t="n"/>
-      <c r="B755" s="4" t="n"/>
-      <c r="C755" s="4" t="n"/>
-      <c r="D755" s="4" t="n"/>
-      <c r="E755" s="4" t="n"/>
-      <c r="F755" s="4" t="n"/>
-      <c r="G755" s="4" t="n"/>
-      <c r="H755" s="4" t="n"/>
-      <c r="I755" s="4" t="n"/>
-      <c r="J755" s="3" t="n"/>
-      <c r="K755" s="3" t="n"/>
-    </row>
-    <row r="756">
-      <c r="A756" s="4" t="n"/>
-      <c r="B756" s="4" t="n"/>
-      <c r="C756" s="4" t="n"/>
-      <c r="D756" s="4" t="n"/>
-      <c r="E756" s="4" t="n"/>
-      <c r="F756" s="4" t="n"/>
-      <c r="G756" s="4" t="n"/>
-      <c r="H756" s="4" t="n"/>
-      <c r="I756" s="4" t="n"/>
-      <c r="J756" s="3" t="n"/>
-      <c r="K756" s="3" t="n"/>
-    </row>
-    <row r="757">
-      <c r="A757" s="4" t="n"/>
-      <c r="B757" s="4" t="n"/>
-      <c r="C757" s="4" t="n"/>
-      <c r="D757" s="4" t="n"/>
-      <c r="E757" s="4" t="n"/>
-      <c r="F757" s="4" t="n"/>
-      <c r="G757" s="4" t="n"/>
-      <c r="H757" s="4" t="n"/>
-      <c r="I757" s="4" t="n"/>
-      <c r="J757" s="3" t="n"/>
-      <c r="K757" s="3" t="n"/>
-    </row>
-    <row r="758">
-      <c r="A758" s="4" t="n"/>
-      <c r="B758" s="4" t="n"/>
-      <c r="C758" s="4" t="n"/>
-      <c r="D758" s="4" t="n"/>
-      <c r="E758" s="4" t="n"/>
-      <c r="F758" s="4" t="n"/>
-      <c r="G758" s="4" t="n"/>
-      <c r="H758" s="4" t="n"/>
-      <c r="I758" s="4" t="n"/>
-      <c r="J758" s="3" t="n"/>
-      <c r="K758" s="3" t="n"/>
-    </row>
-    <row r="759">
-      <c r="A759" s="4" t="n"/>
-      <c r="B759" s="4" t="n"/>
-      <c r="C759" s="4" t="n"/>
-      <c r="D759" s="4" t="n"/>
-      <c r="E759" s="4" t="n"/>
-      <c r="F759" s="4" t="n"/>
-      <c r="G759" s="4" t="n"/>
-      <c r="H759" s="4" t="n"/>
-      <c r="I759" s="4" t="n"/>
-      <c r="J759" s="3" t="n"/>
-      <c r="K759" s="3" t="n"/>
-    </row>
-    <row r="760">
-      <c r="A760" s="4" t="n"/>
-      <c r="B760" s="4" t="n"/>
-      <c r="C760" s="4" t="n"/>
-      <c r="D760" s="4" t="n"/>
-      <c r="E760" s="4" t="n"/>
-      <c r="F760" s="4" t="n"/>
-      <c r="G760" s="4" t="n"/>
-      <c r="H760" s="4" t="n"/>
-      <c r="I760" s="4" t="n"/>
-      <c r="J760" s="3" t="n"/>
-      <c r="K760" s="3" t="n"/>
-    </row>
-    <row r="761">
-      <c r="A761" s="4" t="n"/>
-      <c r="B761" s="4" t="n"/>
-      <c r="C761" s="4" t="n"/>
-      <c r="D761" s="4" t="n"/>
-      <c r="E761" s="4" t="n"/>
-      <c r="F761" s="4" t="n"/>
-      <c r="G761" s="4" t="n"/>
-      <c r="H761" s="4" t="n"/>
-      <c r="I761" s="4" t="n"/>
-      <c r="J761" s="3" t="n"/>
-      <c r="K761" s="3" t="n"/>
-    </row>
-    <row r="762">
-      <c r="A762" s="4" t="n"/>
-      <c r="B762" s="4" t="n"/>
-      <c r="C762" s="4" t="n"/>
-      <c r="D762" s="4" t="n"/>
-      <c r="E762" s="4" t="n"/>
-      <c r="F762" s="4" t="n"/>
-      <c r="G762" s="4" t="n"/>
-      <c r="H762" s="4" t="n"/>
-      <c r="I762" s="4" t="n"/>
-      <c r="J762" s="3" t="n"/>
-      <c r="K762" s="3" t="n"/>
-    </row>
-    <row r="763">
-      <c r="A763" s="4" t="n"/>
-      <c r="B763" s="4" t="n"/>
-      <c r="C763" s="4" t="n"/>
-      <c r="D763" s="4" t="n"/>
-      <c r="E763" s="4" t="n"/>
-      <c r="F763" s="4" t="n"/>
-      <c r="G763" s="4" t="n"/>
-      <c r="H763" s="4" t="n"/>
-      <c r="I763" s="4" t="n"/>
-      <c r="J763" s="3" t="n"/>
-      <c r="K763" s="3" t="n"/>
-    </row>
-    <row r="764">
-      <c r="A764" s="4" t="n"/>
-      <c r="B764" s="4" t="n"/>
-      <c r="C764" s="4" t="n"/>
-      <c r="D764" s="4" t="n"/>
-      <c r="E764" s="4" t="n"/>
-      <c r="F764" s="4" t="n"/>
-      <c r="G764" s="4" t="n"/>
-      <c r="H764" s="4" t="n"/>
-      <c r="I764" s="4" t="n"/>
-      <c r="J764" s="3" t="n"/>
-      <c r="K764" s="3" t="n"/>
-    </row>
-    <row r="765">
-      <c r="A765" s="4" t="n"/>
-      <c r="B765" s="4" t="n"/>
-      <c r="C765" s="4" t="n"/>
-      <c r="D765" s="4" t="n"/>
-      <c r="E765" s="4" t="n"/>
-      <c r="F765" s="4" t="n"/>
-      <c r="G765" s="4" t="n"/>
-      <c r="H765" s="4" t="n"/>
-      <c r="I765" s="4" t="n"/>
-      <c r="J765" s="3" t="n"/>
-      <c r="K765" s="3" t="n"/>
-    </row>
-    <row r="766">
-      <c r="A766" s="4" t="n"/>
-      <c r="B766" s="4" t="n"/>
-      <c r="C766" s="4" t="n"/>
-      <c r="D766" s="4" t="n"/>
-      <c r="E766" s="4" t="n"/>
-      <c r="F766" s="4" t="n"/>
-      <c r="G766" s="4" t="n"/>
-      <c r="H766" s="4" t="n"/>
-      <c r="I766" s="4" t="n"/>
-      <c r="J766" s="3" t="n"/>
-      <c r="K766" s="3" t="n"/>
-    </row>
-    <row r="767">
-      <c r="A767" s="4" t="n"/>
-      <c r="B767" s="4" t="n"/>
-      <c r="C767" s="4" t="n"/>
-      <c r="D767" s="4" t="n"/>
-      <c r="E767" s="4" t="n"/>
-      <c r="F767" s="4" t="n"/>
-      <c r="G767" s="4" t="n"/>
-      <c r="H767" s="4" t="n"/>
-      <c r="I767" s="4" t="n"/>
-      <c r="J767" s="3" t="n"/>
-      <c r="K767" s="3" t="n"/>
-    </row>
-    <row r="768">
-      <c r="A768" s="4" t="n"/>
-      <c r="B768" s="4" t="n"/>
-      <c r="C768" s="4" t="n"/>
-      <c r="D768" s="4" t="n"/>
-      <c r="E768" s="4" t="n"/>
-      <c r="F768" s="4" t="n"/>
-      <c r="G768" s="4" t="n"/>
-      <c r="H768" s="4" t="n"/>
-      <c r="I768" s="4" t="n"/>
-      <c r="J768" s="3" t="n"/>
-      <c r="K768" s="3" t="n"/>
-    </row>
-    <row r="769">
-      <c r="A769" s="4" t="n"/>
-      <c r="B769" s="4" t="n"/>
-      <c r="C769" s="4" t="n"/>
-      <c r="D769" s="4" t="n"/>
-      <c r="E769" s="4" t="n"/>
-      <c r="F769" s="4" t="n"/>
-      <c r="G769" s="4" t="n"/>
-      <c r="H769" s="4" t="n"/>
-      <c r="I769" s="4" t="n"/>
-      <c r="J769" s="3" t="n"/>
-      <c r="K769" s="3" t="n"/>
-    </row>
-    <row r="770">
-      <c r="A770" s="4" t="n"/>
-      <c r="B770" s="4" t="n"/>
-      <c r="C770" s="4" t="n"/>
-      <c r="D770" s="4" t="n"/>
-      <c r="E770" s="4" t="n"/>
-      <c r="F770" s="4" t="n"/>
-      <c r="G770" s="4" t="n"/>
-      <c r="H770" s="4" t="n"/>
-      <c r="I770" s="4" t="n"/>
-      <c r="J770" s="3" t="n"/>
-      <c r="K770" s="3" t="n"/>
-    </row>
-    <row r="771">
-      <c r="A771" s="4" t="n"/>
-      <c r="B771" s="4" t="n"/>
-      <c r="C771" s="4" t="n"/>
-      <c r="D771" s="4" t="n"/>
-      <c r="E771" s="4" t="n"/>
-      <c r="F771" s="4" t="n"/>
-      <c r="G771" s="4" t="n"/>
-      <c r="H771" s="4" t="n"/>
-      <c r="I771" s="4" t="n"/>
-      <c r="J771" s="3" t="n"/>
-      <c r="K771" s="3" t="n"/>
-    </row>
-    <row r="772">
-      <c r="A772" s="4" t="n"/>
-      <c r="B772" s="4" t="n"/>
-      <c r="C772" s="4" t="n"/>
-      <c r="D772" s="4" t="n"/>
-      <c r="E772" s="4" t="n"/>
-      <c r="F772" s="4" t="n"/>
-      <c r="G772" s="4" t="n"/>
-      <c r="H772" s="4" t="n"/>
-      <c r="I772" s="4" t="n"/>
-      <c r="J772" s="3" t="n"/>
-      <c r="K772" s="3" t="n"/>
-    </row>
-    <row r="773">
-      <c r="A773" s="4" t="n"/>
-      <c r="B773" s="4" t="n"/>
-      <c r="C773" s="4" t="n"/>
-      <c r="D773" s="4" t="n"/>
-      <c r="E773" s="4" t="n"/>
-      <c r="F773" s="4" t="n"/>
-      <c r="G773" s="4" t="n"/>
-      <c r="H773" s="4" t="n"/>
-      <c r="I773" s="4" t="n"/>
-      <c r="J773" s="3" t="n"/>
-      <c r="K773" s="3" t="n"/>
-    </row>
-    <row r="774">
-      <c r="A774" s="4" t="n"/>
-      <c r="B774" s="4" t="n"/>
-      <c r="C774" s="4" t="n"/>
-      <c r="D774" s="4" t="n"/>
-      <c r="E774" s="4" t="n"/>
-      <c r="F774" s="4" t="n"/>
-      <c r="G774" s="4" t="n"/>
-      <c r="H774" s="4" t="n"/>
-      <c r="I774" s="4" t="n"/>
-      <c r="J774" s="3" t="n"/>
-      <c r="K774" s="3" t="n"/>
-    </row>
-    <row r="775">
-      <c r="A775" s="4" t="n"/>
-      <c r="B775" s="4" t="n"/>
-      <c r="C775" s="4" t="n"/>
-      <c r="D775" s="4" t="n"/>
-      <c r="E775" s="4" t="n"/>
-      <c r="F775" s="4" t="n"/>
-      <c r="G775" s="4" t="n"/>
-      <c r="H775" s="4" t="n"/>
-      <c r="I775" s="4" t="n"/>
-      <c r="J775" s="3" t="n"/>
-      <c r="K775" s="3" t="n"/>
-    </row>
-    <row r="776">
-      <c r="A776" s="4" t="n"/>
-      <c r="B776" s="4" t="n"/>
-      <c r="C776" s="4" t="n"/>
-      <c r="D776" s="4" t="n"/>
-      <c r="E776" s="4" t="n"/>
-      <c r="F776" s="4" t="n"/>
-      <c r="G776" s="4" t="n"/>
-      <c r="H776" s="4" t="n"/>
-      <c r="I776" s="4" t="n"/>
-      <c r="J776" s="3" t="n"/>
-      <c r="K776" s="3" t="n"/>
-    </row>
-    <row r="777">
-      <c r="A777" s="4" t="n"/>
-      <c r="B777" s="4" t="n"/>
-      <c r="C777" s="4" t="n"/>
-      <c r="D777" s="4" t="n"/>
-      <c r="E777" s="4" t="n"/>
-      <c r="F777" s="4" t="n"/>
-      <c r="G777" s="4" t="n"/>
-      <c r="H777" s="4" t="n"/>
-      <c r="I777" s="4" t="n"/>
-      <c r="J777" s="3" t="n"/>
-      <c r="K777" s="3" t="n"/>
-    </row>
-    <row r="778">
-      <c r="A778" s="4" t="n"/>
-      <c r="B778" s="4" t="n"/>
-      <c r="C778" s="4" t="n"/>
-      <c r="D778" s="4" t="n"/>
-      <c r="E778" s="4" t="n"/>
-      <c r="F778" s="4" t="n"/>
-      <c r="G778" s="4" t="n"/>
-      <c r="H778" s="4" t="n"/>
-      <c r="I778" s="4" t="n"/>
-      <c r="J778" s="3" t="n"/>
-      <c r="K778" s="3" t="n"/>
-    </row>
-    <row r="779">
-      <c r="A779" s="4" t="n"/>
-      <c r="B779" s="4" t="n"/>
-      <c r="C779" s="4" t="n"/>
-      <c r="D779" s="4" t="n"/>
-      <c r="E779" s="4" t="n"/>
-      <c r="F779" s="4" t="n"/>
-      <c r="G779" s="4" t="n"/>
-      <c r="H779" s="4" t="n"/>
-      <c r="I779" s="4" t="n"/>
-      <c r="J779" s="3" t="n"/>
-      <c r="K779" s="3" t="n"/>
-    </row>
-    <row r="780">
-      <c r="A780" s="4" t="n"/>
-      <c r="B780" s="4" t="n"/>
-      <c r="C780" s="4" t="n"/>
-      <c r="D780" s="4" t="n"/>
-      <c r="E780" s="4" t="n"/>
-      <c r="F780" s="4" t="n"/>
-      <c r="G780" s="4" t="n"/>
-      <c r="H780" s="4" t="n"/>
-      <c r="I780" s="4" t="n"/>
-      <c r="J780" s="3" t="n"/>
-      <c r="K780" s="3" t="n"/>
-    </row>
-    <row r="781">
-      <c r="A781" s="4" t="n"/>
-      <c r="B781" s="4" t="n"/>
-      <c r="C781" s="4" t="n"/>
-      <c r="D781" s="4" t="n"/>
-      <c r="E781" s="4" t="n"/>
-      <c r="F781" s="4" t="n"/>
-      <c r="G781" s="4" t="n"/>
-      <c r="H781" s="4" t="n"/>
-      <c r="I781" s="4" t="n"/>
-      <c r="J781" s="3" t="n"/>
-      <c r="K781" s="3" t="n"/>
-    </row>
-    <row r="782">
-      <c r="A782" s="4" t="n"/>
-      <c r="B782" s="4" t="n"/>
-      <c r="C782" s="4" t="n"/>
-      <c r="D782" s="4" t="n"/>
-      <c r="E782" s="4" t="n"/>
-      <c r="F782" s="4" t="n"/>
-      <c r="G782" s="4" t="n"/>
-      <c r="H782" s="4" t="n"/>
-      <c r="I782" s="4" t="n"/>
-      <c r="J782" s="3" t="n"/>
-      <c r="K782" s="3" t="n"/>
-    </row>
-    <row r="783">
-      <c r="A783" s="4" t="n"/>
-      <c r="B783" s="4" t="n"/>
-      <c r="C783" s="4" t="n"/>
-      <c r="D783" s="4" t="n"/>
-      <c r="E783" s="4" t="n"/>
-      <c r="F783" s="4" t="n"/>
-      <c r="G783" s="4" t="n"/>
-      <c r="H783" s="4" t="n"/>
-      <c r="I783" s="4" t="n"/>
-      <c r="J783" s="3" t="n"/>
-      <c r="K783" s="3" t="n"/>
-    </row>
-    <row r="784">
-      <c r="A784" s="4" t="n"/>
-      <c r="B784" s="4" t="n"/>
-      <c r="C784" s="4" t="n"/>
-      <c r="D784" s="4" t="n"/>
-      <c r="E784" s="4" t="n"/>
-      <c r="F784" s="4" t="n"/>
-      <c r="G784" s="4" t="n"/>
-      <c r="H784" s="4" t="n"/>
-      <c r="I784" s="4" t="n"/>
-      <c r="J784" s="3" t="n"/>
-      <c r="K784" s="3" t="n"/>
-    </row>
-    <row r="785">
-      <c r="A785" s="4" t="n"/>
-      <c r="B785" s="4" t="n"/>
-      <c r="C785" s="4" t="n"/>
-      <c r="D785" s="4" t="n"/>
-      <c r="E785" s="4" t="n"/>
-      <c r="F785" s="4" t="n"/>
-      <c r="G785" s="4" t="n"/>
-      <c r="H785" s="4" t="n"/>
-      <c r="I785" s="4" t="n"/>
-      <c r="J785" s="3" t="n"/>
-      <c r="K785" s="3" t="n"/>
-    </row>
-    <row r="786">
-      <c r="A786" s="4" t="n"/>
-      <c r="B786" s="4" t="n"/>
-      <c r="C786" s="4" t="n"/>
-      <c r="D786" s="4" t="n"/>
-      <c r="E786" s="4" t="n"/>
-      <c r="F786" s="4" t="n"/>
-      <c r="G786" s="4" t="n"/>
-      <c r="H786" s="4" t="n"/>
-      <c r="I786" s="4" t="n"/>
-      <c r="J786" s="3" t="n"/>
-      <c r="K786" s="3" t="n"/>
-    </row>
-    <row r="787">
-      <c r="A787" s="4" t="n"/>
-      <c r="B787" s="4" t="n"/>
-      <c r="C787" s="4" t="n"/>
-      <c r="D787" s="4" t="n"/>
-      <c r="E787" s="4" t="n"/>
-      <c r="F787" s="4" t="n"/>
-      <c r="G787" s="4" t="n"/>
-      <c r="H787" s="4" t="n"/>
-      <c r="I787" s="4" t="n"/>
-      <c r="J787" s="3" t="n"/>
-      <c r="K787" s="3" t="n"/>
-    </row>
-    <row r="788">
-      <c r="A788" s="4" t="n"/>
-      <c r="B788" s="4" t="n"/>
-      <c r="C788" s="4" t="n"/>
-      <c r="D788" s="4" t="n"/>
-      <c r="E788" s="4" t="n"/>
-      <c r="F788" s="4" t="n"/>
-      <c r="G788" s="4" t="n"/>
-      <c r="H788" s="4" t="n"/>
-      <c r="I788" s="4" t="n"/>
-      <c r="J788" s="3" t="n"/>
-      <c r="K788" s="3" t="n"/>
-    </row>
-    <row r="789">
-      <c r="A789" s="4" t="n"/>
-      <c r="B789" s="4" t="n"/>
-      <c r="C789" s="4" t="n"/>
-      <c r="D789" s="4" t="n"/>
-      <c r="E789" s="4" t="n"/>
-      <c r="F789" s="4" t="n"/>
-      <c r="G789" s="4" t="n"/>
-      <c r="H789" s="4" t="n"/>
-      <c r="I789" s="4" t="n"/>
-      <c r="J789" s="3" t="n"/>
-      <c r="K789" s="3" t="n"/>
-    </row>
-    <row r="790">
-      <c r="A790" s="4" t="n"/>
-      <c r="B790" s="4" t="n"/>
-      <c r="C790" s="4" t="n"/>
-      <c r="D790" s="4" t="n"/>
-      <c r="E790" s="4" t="n"/>
-      <c r="F790" s="4" t="n"/>
-      <c r="G790" s="4" t="n"/>
-      <c r="H790" s="4" t="n"/>
-      <c r="I790" s="4" t="n"/>
-      <c r="J790" s="3" t="n"/>
-      <c r="K790" s="3" t="n"/>
-    </row>
-    <row r="791">
-      <c r="A791" s="4" t="n"/>
-      <c r="B791" s="4" t="n"/>
-      <c r="C791" s="4" t="n"/>
-      <c r="D791" s="4" t="n"/>
-      <c r="E791" s="4" t="n"/>
-      <c r="F791" s="4" t="n"/>
-      <c r="G791" s="4" t="n"/>
-      <c r="H791" s="4" t="n"/>
-      <c r="I791" s="4" t="n"/>
-      <c r="J791" s="3" t="n"/>
-      <c r="K791" s="3" t="n"/>
-    </row>
-    <row r="792">
-      <c r="A792" s="4" t="n"/>
-      <c r="B792" s="4" t="n"/>
-      <c r="C792" s="4" t="n"/>
-      <c r="D792" s="4" t="n"/>
-      <c r="E792" s="4" t="n"/>
-      <c r="F792" s="4" t="n"/>
-      <c r="G792" s="4" t="n"/>
-      <c r="H792" s="4" t="n"/>
-      <c r="I792" s="4" t="n"/>
-      <c r="J792" s="3" t="n"/>
-      <c r="K792" s="3" t="n"/>
-    </row>
-    <row r="793">
-      <c r="A793" s="4" t="n"/>
-      <c r="B793" s="4" t="n"/>
-      <c r="C793" s="4" t="n"/>
-      <c r="D793" s="4" t="n"/>
-      <c r="E793" s="4" t="n"/>
-      <c r="F793" s="4" t="n"/>
-      <c r="G793" s="4" t="n"/>
-      <c r="H793" s="4" t="n"/>
-      <c r="I793" s="4" t="n"/>
-      <c r="J793" s="3" t="n"/>
-      <c r="K793" s="3" t="n"/>
-    </row>
-    <row r="794">
-      <c r="A794" s="4" t="n"/>
-      <c r="B794" s="4" t="n"/>
-      <c r="C794" s="4" t="n"/>
-      <c r="D794" s="4" t="n"/>
-      <c r="E794" s="4" t="n"/>
-      <c r="F794" s="4" t="n"/>
-      <c r="G794" s="4" t="n"/>
-      <c r="H794" s="4" t="n"/>
-      <c r="I794" s="4" t="n"/>
-      <c r="J794" s="3" t="n"/>
-      <c r="K794" s="3" t="n"/>
-    </row>
-    <row r="795">
-      <c r="A795" s="4" t="n"/>
-      <c r="B795" s="4" t="n"/>
-      <c r="C795" s="4" t="n"/>
-      <c r="D795" s="4" t="n"/>
-      <c r="E795" s="4" t="n"/>
-      <c r="F795" s="4" t="n"/>
-      <c r="G795" s="4" t="n"/>
-      <c r="H795" s="4" t="n"/>
-      <c r="I795" s="4" t="n"/>
-      <c r="J795" s="3" t="n"/>
-      <c r="K795" s="3" t="n"/>
-    </row>
-    <row r="796">
-      <c r="A796" s="4" t="n"/>
-      <c r="B796" s="4" t="n"/>
-      <c r="C796" s="4" t="n"/>
-      <c r="D796" s="4" t="n"/>
-      <c r="E796" s="4" t="n"/>
-      <c r="F796" s="4" t="n"/>
-      <c r="G796" s="4" t="n"/>
-      <c r="H796" s="4" t="n"/>
-      <c r="I796" s="4" t="n"/>
-      <c r="J796" s="3" t="n"/>
-      <c r="K796" s="3" t="n"/>
-    </row>
-    <row r="797">
-      <c r="A797" s="4" t="n"/>
-      <c r="B797" s="4" t="n"/>
-      <c r="C797" s="4" t="n"/>
-      <c r="D797" s="4" t="n"/>
-      <c r="E797" s="4" t="n"/>
-      <c r="F797" s="4" t="n"/>
-      <c r="G797" s="4" t="n"/>
-      <c r="H797" s="4" t="n"/>
-      <c r="I797" s="4" t="n"/>
-      <c r="J797" s="3" t="n"/>
-      <c r="K797" s="3" t="n"/>
-    </row>
-    <row r="798">
-      <c r="A798" s="4" t="n"/>
-      <c r="B798" s="4" t="n"/>
-      <c r="C798" s="4" t="n"/>
-      <c r="D798" s="4" t="n"/>
-      <c r="E798" s="4" t="n"/>
-      <c r="F798" s="4" t="n"/>
-      <c r="G798" s="4" t="n"/>
-      <c r="H798" s="4" t="n"/>
-      <c r="I798" s="4" t="n"/>
-      <c r="J798" s="3" t="n"/>
-      <c r="K798" s="3" t="n"/>
-    </row>
-    <row r="799">
-      <c r="A799" s="4" t="n"/>
-      <c r="B799" s="4" t="n"/>
-      <c r="C799" s="4" t="n"/>
-      <c r="D799" s="4" t="n"/>
-      <c r="E799" s="4" t="n"/>
-      <c r="F799" s="4" t="n"/>
-      <c r="G799" s="4" t="n"/>
-      <c r="H799" s="4" t="n"/>
-      <c r="I799" s="4" t="n"/>
-      <c r="J799" s="3" t="n"/>
-      <c r="K799" s="3" t="n"/>
-    </row>
-    <row r="800">
-      <c r="A800" s="4" t="n"/>
-      <c r="B800" s="4" t="n"/>
-      <c r="C800" s="4" t="n"/>
-      <c r="D800" s="4" t="n"/>
-      <c r="E800" s="4" t="n"/>
-      <c r="F800" s="4" t="n"/>
-      <c r="G800" s="4" t="n"/>
-      <c r="H800" s="4" t="n"/>
-      <c r="I800" s="4" t="n"/>
-      <c r="J800" s="3" t="n"/>
-      <c r="K800" s="3" t="n"/>
-    </row>
-    <row r="801">
-      <c r="A801" s="4" t="n"/>
-      <c r="B801" s="4" t="n"/>
-      <c r="C801" s="4" t="n"/>
-      <c r="D801" s="4" t="n"/>
-      <c r="E801" s="4" t="n"/>
-      <c r="F801" s="4" t="n"/>
-      <c r="G801" s="4" t="n"/>
-      <c r="H801" s="4" t="n"/>
-      <c r="I801" s="4" t="n"/>
-      <c r="J801" s="3" t="n"/>
-      <c r="K801" s="3" t="n"/>
-    </row>
-    <row r="802">
-      <c r="A802" s="4" t="n"/>
-      <c r="B802" s="4" t="n"/>
-      <c r="C802" s="4" t="n"/>
-      <c r="D802" s="4" t="n"/>
-      <c r="E802" s="4" t="n"/>
-      <c r="F802" s="4" t="n"/>
-      <c r="G802" s="4" t="n"/>
-      <c r="H802" s="4" t="n"/>
-      <c r="I802" s="4" t="n"/>
-      <c r="J802" s="3" t="n"/>
-      <c r="K802" s="3" t="n"/>
-    </row>
-    <row r="803">
-      <c r="A803" s="4" t="n"/>
-      <c r="B803" s="4" t="n"/>
-      <c r="C803" s="4" t="n"/>
-      <c r="D803" s="4" t="n"/>
-      <c r="E803" s="4" t="n"/>
-      <c r="F803" s="4" t="n"/>
-      <c r="G803" s="4" t="n"/>
-      <c r="H803" s="4" t="n"/>
-      <c r="I803" s="4" t="n"/>
-      <c r="J803" s="3" t="n"/>
-      <c r="K803" s="3" t="n"/>
-    </row>
-    <row r="804">
-      <c r="A804" s="4" t="n"/>
-      <c r="B804" s="4" t="n"/>
-      <c r="C804" s="4" t="n"/>
-      <c r="D804" s="4" t="n"/>
-      <c r="E804" s="4" t="n"/>
-      <c r="F804" s="4" t="n"/>
-      <c r="G804" s="4" t="n"/>
-      <c r="H804" s="4" t="n"/>
-      <c r="I804" s="4" t="n"/>
-      <c r="J804" s="3" t="n"/>
-      <c r="K804" s="3" t="n"/>
-    </row>
-    <row r="805">
-      <c r="A805" s="4" t="n"/>
-      <c r="B805" s="4" t="n"/>
-      <c r="C805" s="4" t="n"/>
-      <c r="D805" s="4" t="n"/>
-      <c r="E805" s="4" t="n"/>
-      <c r="F805" s="4" t="n"/>
-      <c r="G805" s="4" t="n"/>
-      <c r="H805" s="4" t="n"/>
-      <c r="I805" s="4" t="n"/>
-      <c r="J805" s="3" t="n"/>
-      <c r="K805" s="3" t="n"/>
-    </row>
-    <row r="806">
-      <c r="A806" s="4" t="n"/>
-      <c r="B806" s="4" t="n"/>
-      <c r="C806" s="4" t="n"/>
-      <c r="D806" s="4" t="n"/>
-      <c r="E806" s="4" t="n"/>
-      <c r="F806" s="4" t="n"/>
-      <c r="G806" s="4" t="n"/>
-      <c r="H806" s="4" t="n"/>
-      <c r="I806" s="4" t="n"/>
-      <c r="J806" s="3" t="n"/>
-      <c r="K806" s="3" t="n"/>
-    </row>
-    <row r="807">
-      <c r="A807" s="4" t="n"/>
-      <c r="B807" s="4" t="n"/>
-      <c r="C807" s="4" t="n"/>
-      <c r="D807" s="4" t="n"/>
-      <c r="E807" s="4" t="n"/>
-      <c r="F807" s="4" t="n"/>
-      <c r="G807" s="4" t="n"/>
-      <c r="H807" s="4" t="n"/>
-      <c r="I807" s="4" t="n"/>
-      <c r="J807" s="3" t="n"/>
-      <c r="K807" s="3" t="n"/>
-    </row>
-    <row r="808">
-      <c r="A808" s="4" t="n"/>
-      <c r="B808" s="4" t="n"/>
-      <c r="C808" s="4" t="n"/>
-      <c r="D808" s="4" t="n"/>
-      <c r="E808" s="4" t="n"/>
-      <c r="F808" s="4" t="n"/>
-      <c r="G808" s="4" t="n"/>
-      <c r="H808" s="4" t="n"/>
-      <c r="I808" s="4" t="n"/>
-      <c r="J808" s="3" t="n"/>
-      <c r="K808" s="3" t="n"/>
-    </row>
-    <row r="809">
-      <c r="A809" s="4" t="n"/>
-      <c r="B809" s="4" t="n"/>
-      <c r="C809" s="4" t="n"/>
-      <c r="D809" s="4" t="n"/>
-      <c r="E809" s="4" t="n"/>
-      <c r="F809" s="4" t="n"/>
-      <c r="G809" s="4" t="n"/>
-      <c r="H809" s="4" t="n"/>
-      <c r="I809" s="4" t="n"/>
-      <c r="J809" s="3" t="n"/>
-      <c r="K809" s="3" t="n"/>
-    </row>
-    <row r="810">
-      <c r="A810" s="4" t="n"/>
-      <c r="B810" s="4" t="n"/>
-      <c r="C810" s="4" t="n"/>
-      <c r="D810" s="4" t="n"/>
-      <c r="E810" s="4" t="n"/>
-      <c r="F810" s="4" t="n"/>
-      <c r="G810" s="4" t="n"/>
-      <c r="H810" s="4" t="n"/>
-      <c r="I810" s="4" t="n"/>
-      <c r="J810" s="3" t="n"/>
-      <c r="K810" s="3" t="n"/>
-    </row>
-    <row r="811">
-      <c r="A811" s="4" t="n"/>
-      <c r="B811" s="4" t="n"/>
-      <c r="C811" s="4" t="n"/>
-      <c r="D811" s="4" t="n"/>
-      <c r="E811" s="4" t="n"/>
-      <c r="F811" s="4" t="n"/>
-      <c r="G811" s="4" t="n"/>
-      <c r="H811" s="4" t="n"/>
-      <c r="I811" s="4" t="n"/>
-      <c r="J811" s="3" t="n"/>
-      <c r="K811" s="3" t="n"/>
-    </row>
-    <row r="812">
-      <c r="A812" s="4" t="n"/>
-      <c r="B812" s="4" t="n"/>
-      <c r="C812" s="4" t="n"/>
-      <c r="D812" s="4" t="n"/>
-      <c r="E812" s="4" t="n"/>
-      <c r="F812" s="4" t="n"/>
-      <c r="G812" s="4" t="n"/>
-      <c r="H812" s="4" t="n"/>
-      <c r="I812" s="4" t="n"/>
-      <c r="J812" s="3" t="n"/>
-      <c r="K812" s="3" t="n"/>
-    </row>
-    <row r="813">
-      <c r="A813" s="4" t="n"/>
-      <c r="B813" s="4" t="n"/>
-      <c r="C813" s="4" t="n"/>
-      <c r="D813" s="4" t="n"/>
-      <c r="E813" s="4" t="n"/>
-      <c r="F813" s="4" t="n"/>
-      <c r="G813" s="4" t="n"/>
-      <c r="H813" s="4" t="n"/>
-      <c r="I813" s="4" t="n"/>
-      <c r="J813" s="3" t="n"/>
-      <c r="K813" s="3" t="n"/>
-    </row>
-    <row r="814">
-      <c r="A814" s="4" t="n"/>
-      <c r="B814" s="4" t="n"/>
-      <c r="C814" s="4" t="n"/>
-      <c r="D814" s="4" t="n"/>
-      <c r="E814" s="4" t="n"/>
-      <c r="F814" s="4" t="n"/>
-      <c r="G814" s="4" t="n"/>
-      <c r="H814" s="4" t="n"/>
-      <c r="I814" s="4" t="n"/>
-      <c r="J814" s="3" t="n"/>
-      <c r="K814" s="3" t="n"/>
-    </row>
-    <row r="815">
-      <c r="A815" s="4" t="n"/>
-      <c r="B815" s="4" t="n"/>
-      <c r="C815" s="4" t="n"/>
-      <c r="D815" s="4" t="n"/>
-      <c r="E815" s="4" t="n"/>
-      <c r="F815" s="4" t="n"/>
-      <c r="G815" s="4" t="n"/>
-      <c r="H815" s="4" t="n"/>
-      <c r="I815" s="4" t="n"/>
-      <c r="J815" s="3" t="n"/>
-      <c r="K815" s="3" t="n"/>
-    </row>
-    <row r="816">
-      <c r="A816" s="4" t="n"/>
-      <c r="B816" s="4" t="n"/>
-      <c r="C816" s="4" t="n"/>
-      <c r="D816" s="4" t="n"/>
-      <c r="E816" s="4" t="n"/>
-      <c r="F816" s="4" t="n"/>
-      <c r="G816" s="4" t="n"/>
-      <c r="H816" s="4" t="n"/>
-      <c r="I816" s="4" t="n"/>
-      <c r="J816" s="3" t="n"/>
-      <c r="K816" s="3" t="n"/>
-    </row>
-    <row r="817">
-      <c r="A817" s="4" t="n"/>
-      <c r="B817" s="4" t="n"/>
-      <c r="C817" s="4" t="n"/>
-      <c r="D817" s="4" t="n"/>
-      <c r="E817" s="4" t="n"/>
-      <c r="F817" s="4" t="n"/>
-      <c r="G817" s="4" t="n"/>
-      <c r="H817" s="4" t="n"/>
-      <c r="I817" s="4" t="n"/>
-      <c r="J817" s="3" t="n"/>
-      <c r="K817" s="3" t="n"/>
-    </row>
-    <row r="818">
-      <c r="A818" s="4" t="n"/>
-      <c r="B818" s="4" t="n"/>
-      <c r="C818" s="4" t="n"/>
-      <c r="D818" s="4" t="n"/>
-      <c r="E818" s="4" t="n"/>
-      <c r="F818" s="4" t="n"/>
-      <c r="G818" s="4" t="n"/>
-      <c r="H818" s="4" t="n"/>
-      <c r="I818" s="4" t="n"/>
-      <c r="J818" s="3" t="n"/>
-      <c r="K818" s="3" t="n"/>
-    </row>
-    <row r="819">
-      <c r="A819" s="4" t="n"/>
-      <c r="B819" s="4" t="n"/>
-      <c r="C819" s="4" t="n"/>
-      <c r="D819" s="4" t="n"/>
-      <c r="E819" s="4" t="n"/>
-      <c r="F819" s="4" t="n"/>
-      <c r="G819" s="4" t="n"/>
-      <c r="H819" s="4" t="n"/>
-      <c r="I819" s="4" t="n"/>
-      <c r="J819" s="3" t="n"/>
-      <c r="K819" s="3" t="n"/>
-    </row>
-    <row r="820">
-      <c r="A820" s="4" t="n"/>
-      <c r="B820" s="4" t="n"/>
-      <c r="C820" s="4" t="n"/>
-      <c r="D820" s="4" t="n"/>
-      <c r="E820" s="4" t="n"/>
-      <c r="F820" s="4" t="n"/>
-      <c r="G820" s="4" t="n"/>
-      <c r="H820" s="4" t="n"/>
-      <c r="I820" s="4" t="n"/>
-      <c r="J820" s="3" t="n"/>
-      <c r="K820" s="3" t="n"/>
-    </row>
-    <row r="821">
-      <c r="A821" s="4" t="n"/>
-      <c r="B821" s="4" t="n"/>
-      <c r="C821" s="4" t="n"/>
-      <c r="D821" s="4" t="n"/>
-      <c r="E821" s="4" t="n"/>
-      <c r="F821" s="4" t="n"/>
-      <c r="G821" s="4" t="n"/>
-      <c r="H821" s="4" t="n"/>
-      <c r="I821" s="4" t="n"/>
-      <c r="J821" s="3" t="n"/>
-      <c r="K821" s="3" t="n"/>
-    </row>
-    <row r="822">
-      <c r="A822" s="4" t="n"/>
-      <c r="B822" s="4" t="n"/>
-      <c r="C822" s="4" t="n"/>
-      <c r="D822" s="4" t="n"/>
-      <c r="E822" s="4" t="n"/>
-      <c r="F822" s="4" t="n"/>
-      <c r="G822" s="4" t="n"/>
-      <c r="H822" s="4" t="n"/>
-      <c r="I822" s="4" t="n"/>
-      <c r="J822" s="3" t="n"/>
-      <c r="K822" s="3" t="n"/>
-    </row>
-    <row r="823">
-      <c r="A823" s="4" t="n"/>
-      <c r="B823" s="4" t="n"/>
-      <c r="C823" s="4" t="n"/>
-      <c r="D823" s="4" t="n"/>
-      <c r="E823" s="4" t="n"/>
-      <c r="F823" s="4" t="n"/>
-      <c r="G823" s="4" t="n"/>
-      <c r="H823" s="4" t="n"/>
-      <c r="I823" s="4" t="n"/>
-      <c r="J823" s="3" t="n"/>
-      <c r="K823" s="3" t="n"/>
-    </row>
-    <row r="824">
-      <c r="A824" s="4" t="n"/>
-      <c r="B824" s="4" t="n"/>
-      <c r="C824" s="4" t="n"/>
-      <c r="D824" s="4" t="n"/>
-      <c r="E824" s="4" t="n"/>
-      <c r="F824" s="4" t="n"/>
-      <c r="G824" s="4" t="n"/>
-      <c r="H824" s="4" t="n"/>
-      <c r="I824" s="4" t="n"/>
-      <c r="J824" s="3" t="n"/>
-      <c r="K824" s="3" t="n"/>
-    </row>
-    <row r="825">
-      <c r="A825" s="4" t="n"/>
-      <c r="B825" s="4" t="n"/>
-      <c r="C825" s="4" t="n"/>
-      <c r="D825" s="4" t="n"/>
-      <c r="E825" s="4" t="n"/>
-      <c r="F825" s="4" t="n"/>
-      <c r="G825" s="4" t="n"/>
-      <c r="H825" s="4" t="n"/>
-      <c r="I825" s="4" t="n"/>
-      <c r="J825" s="3" t="n"/>
-      <c r="K825" s="3" t="n"/>
-    </row>
-    <row r="826">
-      <c r="A826" s="4" t="n"/>
-      <c r="B826" s="4" t="n"/>
-      <c r="C826" s="4" t="n"/>
-      <c r="D826" s="4" t="n"/>
-      <c r="E826" s="4" t="n"/>
-      <c r="F826" s="4" t="n"/>
-      <c r="G826" s="4" t="n"/>
-      <c r="H826" s="4" t="n"/>
-      <c r="I826" s="4" t="n"/>
-      <c r="J826" s="3" t="n"/>
-      <c r="K826" s="3" t="n"/>
-    </row>
-    <row r="827">
-      <c r="A827" s="4" t="n"/>
-      <c r="B827" s="4" t="n"/>
-      <c r="C827" s="4" t="n"/>
-      <c r="D827" s="4" t="n"/>
-      <c r="E827" s="4" t="n"/>
-      <c r="F827" s="4" t="n"/>
-      <c r="G827" s="4" t="n"/>
-      <c r="H827" s="4" t="n"/>
-      <c r="I827" s="4" t="n"/>
-      <c r="J827" s="3" t="n"/>
-      <c r="K827" s="3" t="n"/>
-    </row>
-    <row r="828">
-      <c r="A828" s="4" t="n"/>
-      <c r="B828" s="4" t="n"/>
-      <c r="C828" s="4" t="n"/>
-      <c r="D828" s="4" t="n"/>
-      <c r="E828" s="4" t="n"/>
-      <c r="F828" s="4" t="n"/>
-      <c r="G828" s="4" t="n"/>
-      <c r="H828" s="4" t="n"/>
-      <c r="I828" s="4" t="n"/>
-      <c r="J828" s="3" t="n"/>
-      <c r="K828" s="3" t="n"/>
-    </row>
-    <row r="829">
-      <c r="A829" s="4" t="n"/>
-      <c r="B829" s="4" t="n"/>
-      <c r="C829" s="4" t="n"/>
-      <c r="D829" s="4" t="n"/>
-      <c r="E829" s="4" t="n"/>
-      <c r="F829" s="4" t="n"/>
-      <c r="G829" s="4" t="n"/>
-      <c r="H829" s="4" t="n"/>
-      <c r="I829" s="4" t="n"/>
-      <c r="J829" s="3" t="n"/>
-      <c r="K829" s="3" t="n"/>
-    </row>
-    <row r="830">
-      <c r="A830" s="4" t="n"/>
-      <c r="B830" s="4" t="n"/>
-      <c r="C830" s="4" t="n"/>
-      <c r="D830" s="4" t="n"/>
-      <c r="E830" s="4" t="n"/>
-      <c r="F830" s="4" t="n"/>
-      <c r="G830" s="4" t="n"/>
-      <c r="H830" s="4" t="n"/>
-      <c r="I830" s="4" t="n"/>
-      <c r="J830" s="3" t="n"/>
-      <c r="K830" s="3" t="n"/>
-    </row>
-    <row r="831">
-      <c r="A831" s="4" t="n"/>
-      <c r="B831" s="4" t="n"/>
-      <c r="C831" s="4" t="n"/>
-      <c r="D831" s="4" t="n"/>
-      <c r="E831" s="4" t="n"/>
-      <c r="F831" s="4" t="n"/>
-      <c r="G831" s="4" t="n"/>
-      <c r="H831" s="4" t="n"/>
-      <c r="I831" s="4" t="n"/>
-      <c r="J831" s="3" t="n"/>
-      <c r="K831" s="3" t="n"/>
-    </row>
-    <row r="832">
-      <c r="A832" s="4" t="n"/>
-      <c r="B832" s="4" t="n"/>
-      <c r="C832" s="4" t="n"/>
-      <c r="D832" s="4" t="n"/>
-      <c r="E832" s="4" t="n"/>
-      <c r="F832" s="4" t="n"/>
-      <c r="G832" s="4" t="n"/>
-      <c r="H832" s="4" t="n"/>
-      <c r="I832" s="4" t="n"/>
-      <c r="J832" s="3" t="n"/>
-      <c r="K832" s="3" t="n"/>
-    </row>
-    <row r="833">
-      <c r="A833" s="4" t="n"/>
-      <c r="B833" s="4" t="n"/>
-      <c r="C833" s="4" t="n"/>
-      <c r="D833" s="4" t="n"/>
-      <c r="E833" s="4" t="n"/>
-      <c r="F833" s="4" t="n"/>
-      <c r="G833" s="4" t="n"/>
-      <c r="H833" s="4" t="n"/>
-      <c r="I833" s="4" t="n"/>
-      <c r="J833" s="3" t="n"/>
-      <c r="K833" s="3" t="n"/>
-    </row>
-    <row r="834">
-      <c r="A834" s="4" t="n"/>
-      <c r="B834" s="4" t="n"/>
-      <c r="C834" s="4" t="n"/>
-      <c r="D834" s="4" t="n"/>
-      <c r="E834" s="4" t="n"/>
-      <c r="F834" s="4" t="n"/>
-      <c r="G834" s="4" t="n"/>
-      <c r="H834" s="4" t="n"/>
-      <c r="I834" s="4" t="n"/>
-      <c r="J834" s="3" t="n"/>
-      <c r="K834" s="3" t="n"/>
-    </row>
-    <row r="835">
-      <c r="A835" s="4" t="n"/>
-      <c r="B835" s="4" t="n"/>
-      <c r="C835" s="4" t="n"/>
-      <c r="D835" s="4" t="n"/>
-      <c r="E835" s="4" t="n"/>
-      <c r="F835" s="4" t="n"/>
-      <c r="G835" s="4" t="n"/>
-      <c r="H835" s="4" t="n"/>
-      <c r="I835" s="4" t="n"/>
-      <c r="J835" s="3" t="n"/>
-      <c r="K835" s="3" t="n"/>
-    </row>
-    <row r="836">
-      <c r="A836" s="4" t="n"/>
-      <c r="B836" s="4" t="n"/>
-      <c r="C836" s="4" t="n"/>
-      <c r="D836" s="4" t="n"/>
-      <c r="E836" s="4" t="n"/>
-      <c r="F836" s="4" t="n"/>
-      <c r="G836" s="4" t="n"/>
-      <c r="H836" s="4" t="n"/>
-      <c r="I836" s="4" t="n"/>
-      <c r="J836" s="3" t="n"/>
-      <c r="K836" s="3" t="n"/>
-    </row>
-    <row r="837">
-      <c r="A837" s="4" t="n"/>
-      <c r="B837" s="4" t="n"/>
-      <c r="C837" s="4" t="n"/>
-      <c r="D837" s="4" t="n"/>
-      <c r="E837" s="4" t="n"/>
-      <c r="F837" s="4" t="n"/>
-      <c r="G837" s="4" t="n"/>
-      <c r="H837" s="4" t="n"/>
-      <c r="I837" s="4" t="n"/>
-      <c r="J837" s="3" t="n"/>
-      <c r="K837" s="3" t="n"/>
-    </row>
-    <row r="838">
-      <c r="A838" s="4" t="n"/>
-      <c r="B838" s="4" t="n"/>
-      <c r="C838" s="4" t="n"/>
-      <c r="D838" s="4" t="n"/>
-      <c r="E838" s="4" t="n"/>
-      <c r="F838" s="4" t="n"/>
-      <c r="G838" s="4" t="n"/>
-      <c r="H838" s="4" t="n"/>
-      <c r="I838" s="4" t="n"/>
-      <c r="J838" s="3" t="n"/>
-      <c r="K838" s="3" t="n"/>
-    </row>
-    <row r="839">
-      <c r="A839" s="4" t="n"/>
-      <c r="B839" s="4" t="n"/>
-      <c r="C839" s="4" t="n"/>
-      <c r="D839" s="4" t="n"/>
-      <c r="E839" s="4" t="n"/>
-      <c r="F839" s="4" t="n"/>
-      <c r="G839" s="4" t="n"/>
-      <c r="H839" s="4" t="n"/>
-      <c r="I839" s="4" t="n"/>
-      <c r="J839" s="3" t="n"/>
-      <c r="K839" s="3" t="n"/>
-    </row>
-    <row r="840">
-      <c r="A840" s="4" t="n"/>
-      <c r="B840" s="4" t="n"/>
-      <c r="C840" s="4" t="n"/>
-      <c r="D840" s="4" t="n"/>
-      <c r="E840" s="4" t="n"/>
-      <c r="F840" s="4" t="n"/>
-      <c r="G840" s="4" t="n"/>
-      <c r="H840" s="4" t="n"/>
-      <c r="I840" s="4" t="n"/>
-      <c r="J840" s="3" t="n"/>
-      <c r="K840" s="3" t="n"/>
-    </row>
-    <row r="841">
-      <c r="A841" s="4" t="n"/>
-      <c r="B841" s="4" t="n"/>
-      <c r="C841" s="4" t="n"/>
-      <c r="D841" s="4" t="n"/>
-      <c r="E841" s="4" t="n"/>
-      <c r="F841" s="4" t="n"/>
-      <c r="G841" s="4" t="n"/>
-      <c r="H841" s="4" t="n"/>
-      <c r="I841" s="4" t="n"/>
-      <c r="J841" s="3" t="n"/>
-      <c r="K841" s="3" t="n"/>
-    </row>
-    <row r="842">
-      <c r="A842" s="4" t="n"/>
-      <c r="B842" s="4" t="n"/>
-      <c r="C842" s="4" t="n"/>
-      <c r="D842" s="4" t="n"/>
-      <c r="E842" s="4" t="n"/>
-      <c r="F842" s="4" t="n"/>
-      <c r="G842" s="4" t="n"/>
-      <c r="H842" s="4" t="n"/>
-      <c r="I842" s="4" t="n"/>
-      <c r="J842" s="3" t="n"/>
-      <c r="K842" s="3" t="n"/>
-    </row>
-    <row r="843">
-      <c r="A843" s="4" t="n"/>
-      <c r="B843" s="4" t="n"/>
-      <c r="C843" s="4" t="n"/>
-      <c r="D843" s="4" t="n"/>
-      <c r="E843" s="4" t="n"/>
-      <c r="F843" s="4" t="n"/>
-      <c r="G843" s="4" t="n"/>
-      <c r="H843" s="4" t="n"/>
-      <c r="I843" s="4" t="n"/>
-      <c r="J843" s="3" t="n"/>
-      <c r="K843" s="3" t="n"/>
-    </row>
-    <row r="844">
-      <c r="A844" s="4" t="n"/>
-      <c r="B844" s="4" t="n"/>
-      <c r="C844" s="4" t="n"/>
-      <c r="D844" s="4" t="n"/>
-      <c r="E844" s="4" t="n"/>
-      <c r="F844" s="4" t="n"/>
-      <c r="G844" s="4" t="n"/>
-      <c r="H844" s="4" t="n"/>
-      <c r="I844" s="4" t="n"/>
-      <c r="J844" s="3" t="n"/>
-      <c r="K844" s="3" t="n"/>
-    </row>
-    <row r="845">
-      <c r="A845" s="4" t="n"/>
-      <c r="B845" s="4" t="n"/>
-      <c r="C845" s="4" t="n"/>
-      <c r="D845" s="4" t="n"/>
-      <c r="E845" s="4" t="n"/>
-      <c r="F845" s="4" t="n"/>
-      <c r="G845" s="4" t="n"/>
-      <c r="H845" s="4" t="n"/>
-      <c r="I845" s="4" t="n"/>
-      <c r="J845" s="3" t="n"/>
-      <c r="K845" s="3" t="n"/>
-    </row>
-    <row r="846">
-      <c r="A846" s="4" t="n"/>
-      <c r="B846" s="4" t="n"/>
-      <c r="C846" s="4" t="n"/>
-      <c r="D846" s="4" t="n"/>
-      <c r="E846" s="4" t="n"/>
-      <c r="F846" s="4" t="n"/>
-      <c r="G846" s="4" t="n"/>
-      <c r="H846" s="4" t="n"/>
-      <c r="I846" s="4" t="n"/>
-      <c r="J846" s="3" t="n"/>
-      <c r="K846" s="3" t="n"/>
-    </row>
-    <row r="847">
-      <c r="A847" s="4" t="n"/>
-      <c r="B847" s="4" t="n"/>
-      <c r="C847" s="4" t="n"/>
-      <c r="D847" s="4" t="n"/>
-      <c r="E847" s="4" t="n"/>
-      <c r="F847" s="4" t="n"/>
-      <c r="G847" s="4" t="n"/>
-      <c r="H847" s="4" t="n"/>
-      <c r="I847" s="4" t="n"/>
-      <c r="J847" s="3" t="n"/>
-      <c r="K847" s="3" t="n"/>
-    </row>
-    <row r="848">
-      <c r="A848" s="4" t="n"/>
-      <c r="B848" s="4" t="n"/>
-      <c r="C848" s="4" t="n"/>
-      <c r="D848" s="4" t="n"/>
-      <c r="E848" s="4" t="n"/>
-      <c r="F848" s="4" t="n"/>
-      <c r="G848" s="4" t="n"/>
-      <c r="H848" s="4" t="n"/>
-      <c r="I848" s="4" t="n"/>
-      <c r="J848" s="3" t="n"/>
-      <c r="K848" s="3" t="n"/>
-    </row>
-    <row r="849">
-      <c r="A849" s="4" t="n"/>
-      <c r="B849" s="4" t="n"/>
-      <c r="C849" s="4" t="n"/>
-      <c r="D849" s="4" t="n"/>
-      <c r="E849" s="4" t="n"/>
-      <c r="F849" s="4" t="n"/>
-      <c r="G849" s="4" t="n"/>
-      <c r="H849" s="4" t="n"/>
-      <c r="I849" s="4" t="n"/>
-      <c r="J849" s="3" t="n"/>
-      <c r="K849" s="3" t="n"/>
-    </row>
-    <row r="850">
-      <c r="A850" s="4" t="n"/>
-      <c r="B850" s="4" t="n"/>
-      <c r="C850" s="4" t="n"/>
-      <c r="D850" s="4" t="n"/>
-      <c r="E850" s="4" t="n"/>
-      <c r="F850" s="4" t="n"/>
-      <c r="G850" s="4" t="n"/>
-      <c r="H850" s="4" t="n"/>
-      <c r="I850" s="4" t="n"/>
-      <c r="J850" s="3" t="n"/>
-      <c r="K850" s="3" t="n"/>
-    </row>
-    <row r="851">
-      <c r="A851" s="4" t="n"/>
-      <c r="B851" s="4" t="n"/>
-      <c r="C851" s="4" t="n"/>
-      <c r="D851" s="4" t="n"/>
-      <c r="E851" s="4" t="n"/>
-      <c r="F851" s="4" t="n"/>
-      <c r="G851" s="4" t="n"/>
-      <c r="H851" s="4" t="n"/>
-      <c r="I851" s="4" t="n"/>
-      <c r="J851" s="3" t="n"/>
-      <c r="K851" s="3" t="n"/>
-    </row>
-    <row r="852">
-      <c r="A852" s="4" t="n"/>
-      <c r="B852" s="4" t="n"/>
-      <c r="C852" s="4" t="n"/>
-      <c r="D852" s="4" t="n"/>
-      <c r="E852" s="4" t="n"/>
-      <c r="F852" s="4" t="n"/>
-      <c r="G852" s="4" t="n"/>
-      <c r="H852" s="4" t="n"/>
-      <c r="I852" s="4" t="n"/>
-      <c r="J852" s="3" t="n"/>
-      <c r="K852" s="3" t="n"/>
-    </row>
-    <row r="853">
-      <c r="A853" s="4" t="n"/>
-      <c r="B853" s="4" t="n"/>
-      <c r="C853" s="4" t="n"/>
-      <c r="D853" s="4" t="n"/>
-      <c r="E853" s="4" t="n"/>
-      <c r="F853" s="4" t="n"/>
-      <c r="G853" s="4" t="n"/>
-      <c r="H853" s="4" t="n"/>
-      <c r="I853" s="4" t="n"/>
-      <c r="J853" s="3" t="n"/>
-      <c r="K853" s="3" t="n"/>
-    </row>
-    <row r="854">
-      <c r="A854" s="4" t="n"/>
-      <c r="B854" s="4" t="n"/>
-      <c r="C854" s="4" t="n"/>
-      <c r="D854" s="4" t="n"/>
-      <c r="E854" s="4" t="n"/>
-      <c r="F854" s="4" t="n"/>
-      <c r="G854" s="4" t="n"/>
-      <c r="H854" s="4" t="n"/>
-      <c r="I854" s="4" t="n"/>
-      <c r="J854" s="3" t="n"/>
-      <c r="K854" s="3" t="n"/>
-    </row>
-    <row r="855">
-      <c r="A855" s="4" t="n"/>
-      <c r="B855" s="4" t="n"/>
-      <c r="C855" s="4" t="n"/>
-      <c r="D855" s="4" t="n"/>
-      <c r="E855" s="4" t="n"/>
-      <c r="F855" s="4" t="n"/>
-      <c r="G855" s="4" t="n"/>
-      <c r="H855" s="4" t="n"/>
-      <c r="I855" s="4" t="n"/>
-      <c r="J855" s="3" t="n"/>
-      <c r="K855" s="3" t="n"/>
-    </row>
-    <row r="856">
-      <c r="A856" s="4" t="n"/>
-      <c r="B856" s="4" t="n"/>
-      <c r="C856" s="4" t="n"/>
-      <c r="D856" s="4" t="n"/>
-      <c r="E856" s="4" t="n"/>
-      <c r="F856" s="4" t="n"/>
-      <c r="G856" s="4" t="n"/>
-      <c r="H856" s="4" t="n"/>
-      <c r="I856" s="4" t="n"/>
-      <c r="J856" s="3" t="n"/>
-      <c r="K856" s="3" t="n"/>
-    </row>
-    <row r="857">
-      <c r="A857" s="4" t="n"/>
-      <c r="B857" s="4" t="n"/>
-      <c r="C857" s="4" t="n"/>
-      <c r="D857" s="4" t="n"/>
-      <c r="E857" s="4" t="n"/>
-      <c r="F857" s="4" t="n"/>
-      <c r="G857" s="4" t="n"/>
-      <c r="H857" s="4" t="n"/>
-      <c r="I857" s="4" t="n"/>
-      <c r="J857" s="3" t="n"/>
-      <c r="K857" s="3" t="n"/>
-    </row>
-    <row r="858">
-      <c r="A858" s="4" t="n"/>
-      <c r="B858" s="4" t="n"/>
-      <c r="C858" s="4" t="n"/>
-      <c r="D858" s="4" t="n"/>
-      <c r="E858" s="4" t="n"/>
-      <c r="F858" s="4" t="n"/>
-      <c r="G858" s="4" t="n"/>
-      <c r="H858" s="4" t="n"/>
-      <c r="I858" s="4" t="n"/>
-      <c r="J858" s="3" t="n"/>
-      <c r="K858" s="3" t="n"/>
-    </row>
-    <row r="859">
-      <c r="A859" s="4" t="n"/>
-      <c r="B859" s="4" t="n"/>
-      <c r="C859" s="4" t="n"/>
-      <c r="D859" s="4" t="n"/>
-      <c r="E859" s="4" t="n"/>
-      <c r="F859" s="4" t="n"/>
-      <c r="G859" s="4" t="n"/>
-      <c r="H859" s="4" t="n"/>
-      <c r="I859" s="4" t="n"/>
-      <c r="J859" s="3" t="n"/>
-      <c r="K859" s="3" t="n"/>
-    </row>
-    <row r="860">
-      <c r="A860" s="4" t="n"/>
-      <c r="B860" s="4" t="n"/>
-      <c r="C860" s="4" t="n"/>
-      <c r="D860" s="4" t="n"/>
-      <c r="E860" s="4" t="n"/>
-      <c r="F860" s="4" t="n"/>
-      <c r="G860" s="4" t="n"/>
-      <c r="H860" s="4" t="n"/>
-      <c r="I860" s="4" t="n"/>
-      <c r="J860" s="3" t="n"/>
-      <c r="K860" s="3" t="n"/>
-    </row>
-    <row r="861">
-      <c r="A861" s="4" t="n"/>
-      <c r="B861" s="4" t="n"/>
-      <c r="C861" s="4" t="n"/>
-      <c r="D861" s="4" t="n"/>
-      <c r="E861" s="4" t="n"/>
-      <c r="F861" s="4" t="n"/>
-      <c r="G861" s="4" t="n"/>
-      <c r="H861" s="4" t="n"/>
-      <c r="I861" s="4" t="n"/>
-      <c r="J861" s="3" t="n"/>
-      <c r="K861" s="3" t="n"/>
-    </row>
-    <row r="862">
-      <c r="A862" s="4" t="n"/>
-      <c r="B862" s="4" t="n"/>
-      <c r="C862" s="4" t="n"/>
-      <c r="D862" s="4" t="n"/>
-      <c r="E862" s="4" t="n"/>
-      <c r="F862" s="4" t="n"/>
-      <c r="G862" s="4" t="n"/>
-      <c r="H862" s="4" t="n"/>
-      <c r="I862" s="4" t="n"/>
-      <c r="J862" s="3" t="n"/>
-      <c r="K862" s="3" t="n"/>
-    </row>
-    <row r="863">
-      <c r="A863" s="4" t="n"/>
-      <c r="B863" s="4" t="n"/>
-      <c r="C863" s="4" t="n"/>
-      <c r="D863" s="4" t="n"/>
-      <c r="E863" s="4" t="n"/>
-      <c r="F863" s="4" t="n"/>
-      <c r="G863" s="4" t="n"/>
-      <c r="H863" s="4" t="n"/>
-      <c r="I863" s="4" t="n"/>
-      <c r="J863" s="3" t="n"/>
-      <c r="K863" s="3" t="n"/>
-    </row>
-    <row r="864">
-      <c r="A864" s="4" t="n"/>
-      <c r="B864" s="4" t="n"/>
-      <c r="C864" s="4" t="n"/>
-      <c r="D864" s="4" t="n"/>
-      <c r="E864" s="4" t="n"/>
-      <c r="F864" s="4" t="n"/>
-      <c r="G864" s="4" t="n"/>
-      <c r="H864" s="4" t="n"/>
-      <c r="I864" s="4" t="n"/>
-      <c r="J864" s="3" t="n"/>
-      <c r="K864" s="3" t="n"/>
-    </row>
-    <row r="865">
-      <c r="A865" s="4" t="n"/>
-      <c r="B865" s="4" t="n"/>
-      <c r="C865" s="4" t="n"/>
-      <c r="D865" s="4" t="n"/>
-      <c r="E865" s="4" t="n"/>
-      <c r="F865" s="4" t="n"/>
-      <c r="G865" s="4" t="n"/>
-      <c r="H865" s="4" t="n"/>
-      <c r="I865" s="4" t="n"/>
-      <c r="J865" s="3" t="n"/>
-      <c r="K865" s="3" t="n"/>
-    </row>
-    <row r="866">
-      <c r="A866" s="4" t="n"/>
-      <c r="B866" s="4" t="n"/>
-      <c r="C866" s="4" t="n"/>
-      <c r="D866" s="4" t="n"/>
-      <c r="E866" s="4" t="n"/>
-      <c r="F866" s="4" t="n"/>
-      <c r="G866" s="4" t="n"/>
-      <c r="H866" s="4" t="n"/>
-      <c r="I866" s="4" t="n"/>
-      <c r="J866" s="3" t="n"/>
-      <c r="K866" s="3" t="n"/>
-    </row>
-    <row r="867">
-      <c r="A867" s="4" t="n"/>
-      <c r="B867" s="4" t="n"/>
-      <c r="C867" s="4" t="n"/>
-      <c r="D867" s="4" t="n"/>
-      <c r="E867" s="4" t="n"/>
-      <c r="F867" s="4" t="n"/>
-      <c r="G867" s="4" t="n"/>
-      <c r="H867" s="4" t="n"/>
-      <c r="I867" s="4" t="n"/>
-      <c r="J867" s="3" t="n"/>
-      <c r="K867" s="3" t="n"/>
-    </row>
-    <row r="868">
-      <c r="A868" s="4" t="n"/>
-      <c r="B868" s="4" t="n"/>
-      <c r="C868" s="4" t="n"/>
-      <c r="D868" s="4" t="n"/>
-      <c r="E868" s="4" t="n"/>
-      <c r="F868" s="4" t="n"/>
-      <c r="G868" s="4" t="n"/>
-      <c r="H868" s="4" t="n"/>
-      <c r="I868" s="4" t="n"/>
-      <c r="J868" s="3" t="n"/>
-      <c r="K868" s="3" t="n"/>
-    </row>
-    <row r="869">
-      <c r="A869" s="4" t="n"/>
-      <c r="B869" s="4" t="n"/>
-      <c r="C869" s="4" t="n"/>
-      <c r="D869" s="4" t="n"/>
-      <c r="E869" s="4" t="n"/>
-      <c r="F869" s="4" t="n"/>
-      <c r="G869" s="4" t="n"/>
-      <c r="H869" s="4" t="n"/>
-      <c r="I869" s="4" t="n"/>
-      <c r="J869" s="3" t="n"/>
-      <c r="K869" s="3" t="n"/>
-    </row>
-    <row r="870">
-      <c r="A870" s="4" t="n"/>
-      <c r="B870" s="4" t="n"/>
-      <c r="C870" s="4" t="n"/>
-      <c r="D870" s="4" t="n"/>
-      <c r="E870" s="4" t="n"/>
-      <c r="F870" s="4" t="n"/>
-      <c r="G870" s="4" t="n"/>
-      <c r="H870" s="4" t="n"/>
-      <c r="I870" s="4" t="n"/>
-      <c r="J870" s="3" t="n"/>
-      <c r="K870" s="3" t="n"/>
-    </row>
-    <row r="871">
-      <c r="A871" s="4" t="n"/>
-      <c r="B871" s="4" t="n"/>
-      <c r="C871" s="4" t="n"/>
-      <c r="D871" s="4" t="n"/>
-      <c r="E871" s="4" t="n"/>
-      <c r="F871" s="4" t="n"/>
-      <c r="G871" s="4" t="n"/>
-      <c r="H871" s="4" t="n"/>
-      <c r="I871" s="4" t="n"/>
-      <c r="J871" s="3" t="n"/>
-      <c r="K871" s="3" t="n"/>
-    </row>
-    <row r="872">
-      <c r="A872" s="4" t="n"/>
-      <c r="B872" s="4" t="n"/>
-      <c r="C872" s="4" t="n"/>
-      <c r="D872" s="4" t="n"/>
-      <c r="E872" s="4" t="n"/>
-      <c r="F872" s="4" t="n"/>
-      <c r="G872" s="4" t="n"/>
-      <c r="H872" s="4" t="n"/>
-      <c r="I872" s="4" t="n"/>
-      <c r="J872" s="3" t="n"/>
-      <c r="K872" s="3" t="n"/>
-    </row>
-    <row r="873">
-      <c r="A873" s="4" t="n"/>
-      <c r="B873" s="4" t="n"/>
-      <c r="C873" s="4" t="n"/>
-      <c r="D873" s="4" t="n"/>
-      <c r="E873" s="4" t="n"/>
-      <c r="F873" s="4" t="n"/>
-      <c r="G873" s="4" t="n"/>
-      <c r="H873" s="4" t="n"/>
-      <c r="I873" s="4" t="n"/>
-      <c r="J873" s="3" t="n"/>
-      <c r="K873" s="3" t="n"/>
-    </row>
-    <row r="874">
-      <c r="A874" s="4" t="n"/>
-      <c r="B874" s="4" t="n"/>
-      <c r="C874" s="4" t="n"/>
-      <c r="D874" s="4" t="n"/>
-      <c r="E874" s="4" t="n"/>
-      <c r="F874" s="4" t="n"/>
-      <c r="G874" s="4" t="n"/>
-      <c r="H874" s="4" t="n"/>
-      <c r="I874" s="4" t="n"/>
-      <c r="J874" s="3" t="n"/>
-      <c r="K874" s="3" t="n"/>
-    </row>
-    <row r="875">
-      <c r="A875" s="4" t="n"/>
-      <c r="B875" s="4" t="n"/>
-      <c r="C875" s="4" t="n"/>
-      <c r="D875" s="4" t="n"/>
-      <c r="E875" s="4" t="n"/>
-      <c r="F875" s="4" t="n"/>
-      <c r="G875" s="4" t="n"/>
-      <c r="H875" s="4" t="n"/>
-      <c r="I875" s="4" t="n"/>
-      <c r="J875" s="3" t="n"/>
-      <c r="K875" s="3" t="n"/>
-    </row>
-    <row r="876">
-      <c r="A876" s="4" t="n"/>
-      <c r="B876" s="4" t="n"/>
-      <c r="C876" s="4" t="n"/>
-      <c r="D876" s="4" t="n"/>
-      <c r="E876" s="4" t="n"/>
-      <c r="F876" s="4" t="n"/>
-      <c r="G876" s="4" t="n"/>
-      <c r="H876" s="4" t="n"/>
-      <c r="I876" s="4" t="n"/>
-      <c r="J876" s="3" t="n"/>
-      <c r="K876" s="3" t="n"/>
-    </row>
-    <row r="877">
-      <c r="A877" s="4" t="n"/>
-      <c r="B877" s="4" t="n"/>
-      <c r="C877" s="4" t="n"/>
-      <c r="D877" s="4" t="n"/>
-      <c r="E877" s="4" t="n"/>
-      <c r="F877" s="4" t="n"/>
-      <c r="G877" s="4" t="n"/>
-      <c r="H877" s="4" t="n"/>
-      <c r="I877" s="4" t="n"/>
-      <c r="J877" s="3" t="n"/>
-      <c r="K877" s="3" t="n"/>
-    </row>
-    <row r="878">
-      <c r="A878" s="4" t="n"/>
-      <c r="B878" s="4" t="n"/>
-      <c r="C878" s="4" t="n"/>
-      <c r="D878" s="4" t="n"/>
-      <c r="E878" s="4" t="n"/>
-      <c r="F878" s="4" t="n"/>
-      <c r="G878" s="4" t="n"/>
-      <c r="H878" s="4" t="n"/>
-      <c r="I878" s="4" t="n"/>
-      <c r="J878" s="3" t="n"/>
-      <c r="K878" s="3" t="n"/>
-    </row>
-    <row r="879">
-      <c r="A879" s="4" t="n"/>
-      <c r="B879" s="4" t="n"/>
-      <c r="C879" s="4" t="n"/>
-      <c r="D879" s="4" t="n"/>
-      <c r="E879" s="4" t="n"/>
-      <c r="F879" s="4" t="n"/>
-      <c r="G879" s="4" t="n"/>
-      <c r="H879" s="4" t="n"/>
-      <c r="I879" s="4" t="n"/>
-      <c r="J879" s="3" t="n"/>
-      <c r="K879" s="3" t="n"/>
-    </row>
-    <row r="880">
-      <c r="A880" s="4" t="n"/>
-      <c r="B880" s="4" t="n"/>
-      <c r="C880" s="4" t="n"/>
-      <c r="D880" s="4" t="n"/>
-      <c r="E880" s="4" t="n"/>
-      <c r="F880" s="4" t="n"/>
-      <c r="G880" s="4" t="n"/>
-      <c r="H880" s="4" t="n"/>
-      <c r="I880" s="4" t="n"/>
-      <c r="J880" s="3" t="n"/>
-      <c r="K880" s="3" t="n"/>
-    </row>
-    <row r="881">
-      <c r="A881" s="4" t="n"/>
-      <c r="B881" s="4" t="n"/>
-      <c r="C881" s="4" t="n"/>
-      <c r="D881" s="4" t="n"/>
-      <c r="E881" s="4" t="n"/>
-      <c r="F881" s="4" t="n"/>
-      <c r="G881" s="4" t="n"/>
-      <c r="H881" s="4" t="n"/>
-      <c r="I881" s="4" t="n"/>
-      <c r="J881" s="3" t="n"/>
-      <c r="K881" s="3" t="n"/>
-    </row>
-    <row r="882">
-      <c r="A882" s="4" t="n"/>
-      <c r="B882" s="4" t="n"/>
-      <c r="C882" s="4" t="n"/>
-      <c r="D882" s="4" t="n"/>
-      <c r="E882" s="4" t="n"/>
-      <c r="F882" s="4" t="n"/>
-      <c r="G882" s="4" t="n"/>
-      <c r="H882" s="4" t="n"/>
-      <c r="I882" s="4" t="n"/>
-      <c r="J882" s="3" t="n"/>
-      <c r="K882" s="3" t="n"/>
-    </row>
-    <row r="883">
-      <c r="A883" s="4" t="n"/>
-      <c r="B883" s="4" t="n"/>
-      <c r="C883" s="4" t="n"/>
-      <c r="D883" s="4" t="n"/>
-      <c r="E883" s="4" t="n"/>
-      <c r="F883" s="4" t="n"/>
-      <c r="G883" s="4" t="n"/>
-      <c r="H883" s="4" t="n"/>
-      <c r="I883" s="4" t="n"/>
-      <c r="J883" s="3" t="n"/>
-      <c r="K883" s="3" t="n"/>
-    </row>
-    <row r="884">
-      <c r="A884" s="4" t="n"/>
-      <c r="B884" s="4" t="n"/>
-      <c r="C884" s="4" t="n"/>
-      <c r="D884" s="4" t="n"/>
-      <c r="E884" s="4" t="n"/>
-      <c r="F884" s="4" t="n"/>
-      <c r="G884" s="4" t="n"/>
-      <c r="H884" s="4" t="n"/>
-      <c r="I884" s="4" t="n"/>
-      <c r="J884" s="3" t="n"/>
-      <c r="K884" s="3" t="n"/>
-    </row>
-    <row r="885">
-      <c r="A885" s="4" t="n"/>
-      <c r="B885" s="4" t="n"/>
-      <c r="C885" s="4" t="n"/>
-      <c r="D885" s="4" t="n"/>
-      <c r="E885" s="4" t="n"/>
-      <c r="F885" s="4" t="n"/>
-      <c r="G885" s="4" t="n"/>
-      <c r="H885" s="4" t="n"/>
-      <c r="I885" s="4" t="n"/>
-      <c r="J885" s="3" t="n"/>
-      <c r="K885" s="3" t="n"/>
-    </row>
-    <row r="886">
-      <c r="A886" s="4" t="n"/>
-      <c r="B886" s="4" t="n"/>
-      <c r="C886" s="4" t="n"/>
-      <c r="D886" s="4" t="n"/>
-      <c r="E886" s="4" t="n"/>
-      <c r="F886" s="4" t="n"/>
-      <c r="G886" s="4" t="n"/>
-      <c r="H886" s="4" t="n"/>
-      <c r="I886" s="4" t="n"/>
-      <c r="J886" s="3" t="n"/>
-      <c r="K886" s="3" t="n"/>
-    </row>
-    <row r="887">
-      <c r="A887" s="4" t="n"/>
-      <c r="B887" s="4" t="n"/>
-      <c r="C887" s="4" t="n"/>
-      <c r="D887" s="4" t="n"/>
-      <c r="E887" s="4" t="n"/>
-      <c r="F887" s="4" t="n"/>
-      <c r="G887" s="4" t="n"/>
-      <c r="H887" s="4" t="n"/>
-      <c r="I887" s="4" t="n"/>
-      <c r="J887" s="3" t="n"/>
-      <c r="K887" s="3" t="n"/>
-    </row>
-    <row r="888">
-      <c r="A888" s="4" t="n"/>
-      <c r="B888" s="4" t="n"/>
-      <c r="C888" s="4" t="n"/>
-      <c r="D888" s="4" t="n"/>
-      <c r="E888" s="4" t="n"/>
-      <c r="F888" s="4" t="n"/>
-      <c r="G888" s="4" t="n"/>
-      <c r="H888" s="4" t="n"/>
-      <c r="I888" s="4" t="n"/>
-      <c r="J888" s="3" t="n"/>
-      <c r="K888" s="3" t="n"/>
-    </row>
-    <row r="889">
-      <c r="A889" s="4" t="n"/>
-      <c r="B889" s="4" t="n"/>
-      <c r="C889" s="4" t="n"/>
-      <c r="D889" s="4" t="n"/>
-      <c r="E889" s="4" t="n"/>
-      <c r="F889" s="4" t="n"/>
-      <c r="G889" s="4" t="n"/>
-      <c r="H889" s="4" t="n"/>
-      <c r="I889" s="4" t="n"/>
-      <c r="J889" s="3" t="n"/>
-      <c r="K889" s="3" t="n"/>
-    </row>
-    <row r="890">
-      <c r="A890" s="4" t="n"/>
-      <c r="B890" s="4" t="n"/>
-      <c r="C890" s="4" t="n"/>
-      <c r="D890" s="4" t="n"/>
-      <c r="E890" s="4" t="n"/>
-      <c r="F890" s="4" t="n"/>
-      <c r="G890" s="4" t="n"/>
-      <c r="H890" s="4" t="n"/>
-      <c r="I890" s="4" t="n"/>
-      <c r="J890" s="3" t="n"/>
-      <c r="K890" s="3" t="n"/>
-    </row>
-    <row r="891">
-      <c r="A891" s="4" t="n"/>
-      <c r="B891" s="4" t="n"/>
-      <c r="C891" s="4" t="n"/>
-      <c r="D891" s="4" t="n"/>
-      <c r="E891" s="4" t="n"/>
-      <c r="F891" s="4" t="n"/>
-      <c r="G891" s="4" t="n"/>
-      <c r="H891" s="4" t="n"/>
-      <c r="I891" s="4" t="n"/>
-      <c r="J891" s="3" t="n"/>
-      <c r="K891" s="3" t="n"/>
-    </row>
-    <row r="892">
-      <c r="A892" s="4" t="n"/>
-      <c r="B892" s="4" t="n"/>
-      <c r="C892" s="4" t="n"/>
-      <c r="D892" s="4" t="n"/>
-      <c r="E892" s="4" t="n"/>
-      <c r="F892" s="4" t="n"/>
-      <c r="G892" s="4" t="n"/>
-      <c r="H892" s="4" t="n"/>
-      <c r="I892" s="4" t="n"/>
-      <c r="J892" s="3" t="n"/>
-      <c r="K892" s="3" t="n"/>
-    </row>
-    <row r="893">
-      <c r="A893" s="4" t="n"/>
-      <c r="B893" s="4" t="n"/>
-      <c r="C893" s="4" t="n"/>
-      <c r="D893" s="4" t="n"/>
-      <c r="E893" s="4" t="n"/>
-      <c r="F893" s="4" t="n"/>
-      <c r="G893" s="4" t="n"/>
-      <c r="H893" s="4" t="n"/>
-      <c r="I893" s="4" t="n"/>
-      <c r="J893" s="3" t="n"/>
-      <c r="K893" s="3" t="n"/>
-    </row>
-    <row r="894">
-      <c r="A894" s="4" t="n"/>
-      <c r="B894" s="4" t="n"/>
-      <c r="C894" s="4" t="n"/>
-      <c r="D894" s="4" t="n"/>
-      <c r="E894" s="4" t="n"/>
-      <c r="F894" s="4" t="n"/>
-      <c r="G894" s="4" t="n"/>
-      <c r="H894" s="4" t="n"/>
-      <c r="I894" s="4" t="n"/>
-      <c r="J894" s="3" t="n"/>
-      <c r="K894" s="3" t="n"/>
-    </row>
-    <row r="895">
-      <c r="A895" s="4" t="n"/>
-      <c r="B895" s="4" t="n"/>
-      <c r="C895" s="4" t="n"/>
-      <c r="D895" s="4" t="n"/>
-      <c r="E895" s="4" t="n"/>
-      <c r="F895" s="4" t="n"/>
-      <c r="G895" s="4" t="n"/>
-      <c r="H895" s="4" t="n"/>
-      <c r="I895" s="4" t="n"/>
-      <c r="J895" s="3" t="n"/>
-      <c r="K895" s="3" t="n"/>
-    </row>
-    <row r="896">
-      <c r="A896" s="4" t="n"/>
-      <c r="B896" s="4" t="n"/>
-      <c r="C896" s="4" t="n"/>
-      <c r="D896" s="4" t="n"/>
-      <c r="E896" s="4" t="n"/>
-      <c r="F896" s="4" t="n"/>
-      <c r="G896" s="4" t="n"/>
-      <c r="H896" s="4" t="n"/>
-      <c r="I896" s="4" t="n"/>
-      <c r="J896" s="3" t="n"/>
-      <c r="K896" s="3" t="n"/>
-    </row>
-    <row r="897">
-      <c r="A897" s="4" t="n"/>
-      <c r="B897" s="4" t="n"/>
-      <c r="C897" s="4" t="n"/>
-      <c r="D897" s="4" t="n"/>
-      <c r="E897" s="4" t="n"/>
-      <c r="F897" s="4" t="n"/>
-      <c r="G897" s="4" t="n"/>
-      <c r="H897" s="4" t="n"/>
-      <c r="I897" s="4" t="n"/>
-      <c r="J897" s="3" t="n"/>
-      <c r="K897" s="3" t="n"/>
-    </row>
-    <row r="898">
-      <c r="A898" s="4" t="n"/>
-      <c r="B898" s="4" t="n"/>
-      <c r="C898" s="4" t="n"/>
-      <c r="D898" s="4" t="n"/>
-      <c r="E898" s="4" t="n"/>
-      <c r="F898" s="4" t="n"/>
-      <c r="G898" s="4" t="n"/>
-      <c r="H898" s="4" t="n"/>
-      <c r="I898" s="4" t="n"/>
-      <c r="J898" s="3" t="n"/>
-      <c r="K898" s="3" t="n"/>
-    </row>
-    <row r="899">
-      <c r="A899" s="4" t="n"/>
-      <c r="B899" s="4" t="n"/>
-      <c r="C899" s="4" t="n"/>
-      <c r="D899" s="4" t="n"/>
-      <c r="E899" s="4" t="n"/>
-      <c r="F899" s="4" t="n"/>
-      <c r="G899" s="4" t="n"/>
-      <c r="H899" s="4" t="n"/>
-      <c r="I899" s="4" t="n"/>
-      <c r="J899" s="3" t="n"/>
-      <c r="K899" s="3" t="n"/>
-    </row>
-    <row r="900">
-      <c r="A900" s="4" t="n"/>
-      <c r="B900" s="4" t="n"/>
-      <c r="C900" s="4" t="n"/>
-      <c r="D900" s="4" t="n"/>
-      <c r="E900" s="4" t="n"/>
-      <c r="F900" s="4" t="n"/>
-      <c r="G900" s="4" t="n"/>
-      <c r="H900" s="4" t="n"/>
-      <c r="I900" s="4" t="n"/>
-      <c r="J900" s="3" t="n"/>
-      <c r="K900" s="3" t="n"/>
-    </row>
-    <row r="901">
-      <c r="A901" s="4" t="n"/>
-      <c r="B901" s="4" t="n"/>
-      <c r="C901" s="4" t="n"/>
-      <c r="D901" s="4" t="n"/>
-      <c r="E901" s="4" t="n"/>
-      <c r="F901" s="4" t="n"/>
-      <c r="G901" s="4" t="n"/>
-      <c r="H901" s="4" t="n"/>
-      <c r="I901" s="4" t="n"/>
-      <c r="J901" s="3" t="n"/>
-      <c r="K901" s="3" t="n"/>
-    </row>
-    <row r="902">
-      <c r="A902" s="4" t="n"/>
-      <c r="B902" s="4" t="n"/>
-      <c r="C902" s="4" t="n"/>
-      <c r="D902" s="4" t="n"/>
-      <c r="E902" s="4" t="n"/>
-      <c r="F902" s="4" t="n"/>
-      <c r="G902" s="4" t="n"/>
-      <c r="H902" s="4" t="n"/>
-      <c r="I902" s="4" t="n"/>
-      <c r="J902" s="3" t="n"/>
-      <c r="K902" s="3" t="n"/>
-    </row>
-    <row r="903">
-      <c r="A903" s="4" t="n"/>
-      <c r="B903" s="4" t="n"/>
-      <c r="C903" s="4" t="n"/>
-      <c r="D903" s="4" t="n"/>
-      <c r="E903" s="4" t="n"/>
-      <c r="F903" s="4" t="n"/>
-      <c r="G903" s="4" t="n"/>
-      <c r="H903" s="4" t="n"/>
-      <c r="I903" s="4" t="n"/>
-      <c r="J903" s="3" t="n"/>
-      <c r="K903" s="3" t="n"/>
-    </row>
-    <row r="904">
-      <c r="A904" s="4" t="n"/>
-      <c r="B904" s="4" t="n"/>
-      <c r="C904" s="4" t="n"/>
-      <c r="D904" s="4" t="n"/>
-      <c r="E904" s="4" t="n"/>
-      <c r="F904" s="4" t="n"/>
-      <c r="G904" s="4" t="n"/>
-      <c r="H904" s="4" t="n"/>
-      <c r="I904" s="4" t="n"/>
-      <c r="J904" s="3" t="n"/>
-      <c r="K904" s="3" t="n"/>
-    </row>
-    <row r="905">
-      <c r="A905" s="4" t="n"/>
-      <c r="B905" s="4" t="n"/>
-      <c r="C905" s="4" t="n"/>
-      <c r="D905" s="4" t="n"/>
-      <c r="E905" s="4" t="n"/>
-      <c r="F905" s="4" t="n"/>
-      <c r="G905" s="4" t="n"/>
-      <c r="H905" s="4" t="n"/>
-      <c r="I905" s="4" t="n"/>
-      <c r="J905" s="3" t="n"/>
-      <c r="K905" s="3" t="n"/>
-    </row>
-    <row r="906">
-      <c r="A906" s="4" t="n"/>
-      <c r="B906" s="4" t="n"/>
-      <c r="C906" s="4" t="n"/>
-      <c r="D906" s="4" t="n"/>
-      <c r="E906" s="4" t="n"/>
-      <c r="F906" s="4" t="n"/>
-      <c r="G906" s="4" t="n"/>
-      <c r="H906" s="4" t="n"/>
-      <c r="I906" s="4" t="n"/>
-      <c r="J906" s="3" t="n"/>
-      <c r="K906" s="3" t="n"/>
-    </row>
-    <row r="907">
-      <c r="A907" s="4" t="n"/>
-      <c r="B907" s="4" t="n"/>
-      <c r="C907" s="4" t="n"/>
-      <c r="D907" s="4" t="n"/>
-      <c r="E907" s="4" t="n"/>
-      <c r="F907" s="4" t="n"/>
-      <c r="G907" s="4" t="n"/>
-      <c r="H907" s="4" t="n"/>
-      <c r="I907" s="4" t="n"/>
-      <c r="J907" s="3" t="n"/>
-      <c r="K907" s="3" t="n"/>
-    </row>
-    <row r="908">
-      <c r="A908" s="4" t="n"/>
-      <c r="B908" s="4" t="n"/>
-      <c r="C908" s="4" t="n"/>
-      <c r="D908" s="4" t="n"/>
-      <c r="E908" s="4" t="n"/>
-      <c r="F908" s="4" t="n"/>
-      <c r="G908" s="4" t="n"/>
-      <c r="H908" s="4" t="n"/>
-      <c r="I908" s="4" t="n"/>
-      <c r="J908" s="3" t="n"/>
-      <c r="K908" s="3" t="n"/>
-    </row>
-    <row r="909">
-      <c r="A909" s="4" t="n"/>
-      <c r="B909" s="4" t="n"/>
-      <c r="C909" s="4" t="n"/>
-      <c r="D909" s="4" t="n"/>
-      <c r="E909" s="4" t="n"/>
-      <c r="F909" s="4" t="n"/>
-      <c r="G909" s="4" t="n"/>
-      <c r="H909" s="4" t="n"/>
-      <c r="I909" s="4" t="n"/>
-      <c r="J909" s="3" t="n"/>
-      <c r="K909" s="3" t="n"/>
-    </row>
-    <row r="910">
-      <c r="A910" s="4" t="n"/>
-      <c r="B910" s="4" t="n"/>
-      <c r="C910" s="4" t="n"/>
-      <c r="D910" s="4" t="n"/>
-      <c r="E910" s="4" t="n"/>
-      <c r="F910" s="4" t="n"/>
-      <c r="G910" s="4" t="n"/>
-      <c r="H910" s="4" t="n"/>
-      <c r="I910" s="4" t="n"/>
-      <c r="J910" s="3" t="n"/>
-      <c r="K910" s="3" t="n"/>
-    </row>
-    <row r="911">
-      <c r="A911" s="4" t="n"/>
-      <c r="B911" s="4" t="n"/>
-      <c r="C911" s="4" t="n"/>
-      <c r="D911" s="4" t="n"/>
-      <c r="E911" s="4" t="n"/>
-      <c r="F911" s="4" t="n"/>
-      <c r="G911" s="4" t="n"/>
-      <c r="H911" s="4" t="n"/>
-      <c r="I911" s="4" t="n"/>
-      <c r="J911" s="3" t="n"/>
-      <c r="K911" s="3" t="n"/>
-    </row>
-    <row r="912">
-      <c r="A912" s="4" t="n"/>
-      <c r="B912" s="4" t="n"/>
-      <c r="C912" s="4" t="n"/>
-      <c r="D912" s="4" t="n"/>
-      <c r="E912" s="4" t="n"/>
-      <c r="F912" s="4" t="n"/>
-      <c r="G912" s="4" t="n"/>
-      <c r="H912" s="4" t="n"/>
-      <c r="I912" s="4" t="n"/>
-      <c r="J912" s="3" t="n"/>
-      <c r="K912" s="3" t="n"/>
-    </row>
-    <row r="913">
-      <c r="A913" s="4" t="n"/>
-      <c r="B913" s="4" t="n"/>
-      <c r="C913" s="4" t="n"/>
-      <c r="D913" s="4" t="n"/>
-      <c r="E913" s="4" t="n"/>
-      <c r="F913" s="4" t="n"/>
-      <c r="G913" s="4" t="n"/>
-      <c r="H913" s="4" t="n"/>
-      <c r="I913" s="4" t="n"/>
-      <c r="J913" s="3" t="n"/>
-      <c r="K913" s="3" t="n"/>
-    </row>
-    <row r="914">
-      <c r="A914" s="4" t="n"/>
-      <c r="B914" s="4" t="n"/>
-      <c r="C914" s="4" t="n"/>
-      <c r="D914" s="4" t="n"/>
-      <c r="E914" s="4" t="n"/>
-      <c r="F914" s="4" t="n"/>
-      <c r="G914" s="4" t="n"/>
-      <c r="H914" s="4" t="n"/>
-      <c r="I914" s="4" t="n"/>
-      <c r="J914" s="3" t="n"/>
-      <c r="K914" s="3" t="n"/>
-    </row>
-    <row r="915">
-      <c r="A915" s="4" t="n"/>
-      <c r="B915" s="4" t="n"/>
-      <c r="C915" s="4" t="n"/>
-      <c r="D915" s="4" t="n"/>
-      <c r="E915" s="4" t="n"/>
-      <c r="F915" s="4" t="n"/>
-      <c r="G915" s="4" t="n"/>
-      <c r="H915" s="4" t="n"/>
-      <c r="I915" s="4" t="n"/>
-      <c r="J915" s="3" t="n"/>
-      <c r="K915" s="3" t="n"/>
-    </row>
-    <row r="916">
-      <c r="A916" s="4" t="n"/>
-      <c r="B916" s="4" t="n"/>
-      <c r="C916" s="4" t="n"/>
-      <c r="D916" s="4" t="n"/>
-      <c r="E916" s="4" t="n"/>
-      <c r="F916" s="4" t="n"/>
-      <c r="G916" s="4" t="n"/>
-      <c r="H916" s="4" t="n"/>
-      <c r="I916" s="4" t="n"/>
-      <c r="J916" s="3" t="n"/>
-      <c r="K916" s="3" t="n"/>
-    </row>
-    <row r="917">
-      <c r="A917" s="4" t="n"/>
-      <c r="B917" s="4" t="n"/>
-      <c r="C917" s="4" t="n"/>
-      <c r="D917" s="4" t="n"/>
-      <c r="E917" s="4" t="n"/>
-      <c r="F917" s="4" t="n"/>
-      <c r="G917" s="4" t="n"/>
-      <c r="H917" s="4" t="n"/>
-      <c r="I917" s="4" t="n"/>
-      <c r="J917" s="3" t="n"/>
-      <c r="K917" s="3" t="n"/>
-    </row>
-    <row r="918">
-      <c r="A918" s="4" t="n"/>
-      <c r="B918" s="4" t="n"/>
-      <c r="C918" s="4" t="n"/>
-      <c r="D918" s="4" t="n"/>
-      <c r="E918" s="4" t="n"/>
-      <c r="F918" s="4" t="n"/>
-      <c r="G918" s="4" t="n"/>
-      <c r="H918" s="4" t="n"/>
-      <c r="I918" s="4" t="n"/>
-      <c r="J918" s="3" t="n"/>
-      <c r="K918" s="3" t="n"/>
-    </row>
-    <row r="919">
-      <c r="A919" s="4" t="n"/>
-      <c r="B919" s="4" t="n"/>
-      <c r="C919" s="4" t="n"/>
-      <c r="D919" s="4" t="n"/>
-      <c r="E919" s="4" t="n"/>
-      <c r="F919" s="4" t="n"/>
-      <c r="G919" s="4" t="n"/>
-      <c r="H919" s="4" t="n"/>
-      <c r="I919" s="4" t="n"/>
-      <c r="J919" s="3" t="n"/>
-      <c r="K919" s="3" t="n"/>
-    </row>
-    <row r="920">
-      <c r="A920" s="4" t="n"/>
-      <c r="B920" s="4" t="n"/>
-      <c r="C920" s="4" t="n"/>
-      <c r="D920" s="4" t="n"/>
-      <c r="E920" s="4" t="n"/>
-      <c r="F920" s="4" t="n"/>
-      <c r="G920" s="4" t="n"/>
-      <c r="H920" s="4" t="n"/>
-      <c r="I920" s="4" t="n"/>
-      <c r="J920" s="3" t="n"/>
-      <c r="K920" s="3" t="n"/>
-    </row>
-    <row r="921">
-      <c r="A921" s="4" t="n"/>
-      <c r="B921" s="4" t="n"/>
-      <c r="C921" s="4" t="n"/>
-      <c r="D921" s="4" t="n"/>
-      <c r="E921" s="4" t="n"/>
-      <c r="F921" s="4" t="n"/>
-      <c r="G921" s="4" t="n"/>
-      <c r="H921" s="4" t="n"/>
-      <c r="I921" s="4" t="n"/>
-      <c r="J921" s="3" t="n"/>
-      <c r="K921" s="3" t="n"/>
-    </row>
-    <row r="922">
-      <c r="A922" s="4" t="n"/>
-      <c r="B922" s="4" t="n"/>
-      <c r="C922" s="4" t="n"/>
-      <c r="D922" s="4" t="n"/>
-      <c r="E922" s="4" t="n"/>
-      <c r="F922" s="4" t="n"/>
-      <c r="G922" s="4" t="n"/>
-      <c r="H922" s="4" t="n"/>
-      <c r="I922" s="4" t="n"/>
-      <c r="J922" s="3" t="n"/>
-      <c r="K922" s="3" t="n"/>
-    </row>
-    <row r="923">
-      <c r="A923" s="4" t="n"/>
-      <c r="B923" s="4" t="n"/>
-      <c r="C923" s="4" t="n"/>
-      <c r="D923" s="4" t="n"/>
-      <c r="E923" s="4" t="n"/>
-      <c r="F923" s="4" t="n"/>
-      <c r="G923" s="4" t="n"/>
-      <c r="H923" s="4" t="n"/>
-      <c r="I923" s="4" t="n"/>
-      <c r="J923" s="3" t="n"/>
-      <c r="K923" s="3" t="n"/>
-    </row>
-    <row r="924">
-      <c r="A924" s="4" t="n"/>
-      <c r="B924" s="4" t="n"/>
-      <c r="C924" s="4" t="n"/>
-      <c r="D924" s="4" t="n"/>
-      <c r="E924" s="4" t="n"/>
-      <c r="F924" s="4" t="n"/>
-      <c r="G924" s="4" t="n"/>
-      <c r="H924" s="4" t="n"/>
-      <c r="I924" s="4" t="n"/>
-      <c r="J924" s="3" t="n"/>
-      <c r="K924" s="3" t="n"/>
-    </row>
-    <row r="925">
-      <c r="A925" s="4" t="n"/>
-      <c r="B925" s="4" t="n"/>
-      <c r="C925" s="4" t="n"/>
-      <c r="D925" s="4" t="n"/>
-      <c r="E925" s="4" t="n"/>
-      <c r="F925" s="4" t="n"/>
-      <c r="G925" s="4" t="n"/>
-      <c r="H925" s="4" t="n"/>
-      <c r="I925" s="4" t="n"/>
-      <c r="J925" s="3" t="n"/>
-      <c r="K925" s="3" t="n"/>
-    </row>
-    <row r="926">
-      <c r="A926" s="4" t="n"/>
-      <c r="B926" s="4" t="n"/>
-      <c r="C926" s="4" t="n"/>
-      <c r="D926" s="4" t="n"/>
-      <c r="E926" s="4" t="n"/>
-      <c r="F926" s="4" t="n"/>
-      <c r="G926" s="4" t="n"/>
-      <c r="H926" s="4" t="n"/>
-      <c r="I926" s="4" t="n"/>
-      <c r="J926" s="3" t="n"/>
-      <c r="K926" s="3" t="n"/>
-    </row>
-    <row r="927">
-      <c r="A927" s="4" t="n"/>
-      <c r="B927" s="4" t="n"/>
-      <c r="C927" s="4" t="n"/>
-      <c r="D927" s="4" t="n"/>
-      <c r="E927" s="4" t="n"/>
-      <c r="F927" s="4" t="n"/>
-      <c r="G927" s="4" t="n"/>
-      <c r="H927" s="4" t="n"/>
-      <c r="I927" s="4" t="n"/>
-      <c r="J927" s="3" t="n"/>
-      <c r="K927" s="3" t="n"/>
-    </row>
-    <row r="928">
-      <c r="A928" s="4" t="n"/>
-      <c r="B928" s="4" t="n"/>
-      <c r="C928" s="4" t="n"/>
-      <c r="D928" s="4" t="n"/>
-      <c r="E928" s="4" t="n"/>
-      <c r="F928" s="4" t="n"/>
-      <c r="G928" s="4" t="n"/>
-      <c r="H928" s="4" t="n"/>
-      <c r="I928" s="4" t="n"/>
-      <c r="J928" s="3" t="n"/>
-      <c r="K928" s="3" t="n"/>
-    </row>
-    <row r="929">
-      <c r="A929" s="4" t="n"/>
-      <c r="B929" s="4" t="n"/>
-      <c r="C929" s="4" t="n"/>
-      <c r="D929" s="4" t="n"/>
-      <c r="E929" s="4" t="n"/>
-      <c r="F929" s="4" t="n"/>
-      <c r="G929" s="4" t="n"/>
-      <c r="H929" s="4" t="n"/>
-      <c r="I929" s="4" t="n"/>
-      <c r="J929" s="3" t="n"/>
-      <c r="K929" s="3" t="n"/>
-    </row>
-    <row r="930">
-      <c r="A930" s="4" t="n"/>
-      <c r="B930" s="4" t="n"/>
-      <c r="C930" s="4" t="n"/>
-      <c r="D930" s="4" t="n"/>
-      <c r="E930" s="4" t="n"/>
-      <c r="F930" s="4" t="n"/>
-      <c r="G930" s="4" t="n"/>
-      <c r="H930" s="4" t="n"/>
-      <c r="I930" s="4" t="n"/>
-      <c r="J930" s="3" t="n"/>
-      <c r="K930" s="3" t="n"/>
-    </row>
-    <row r="931">
-      <c r="A931" s="4" t="n"/>
-      <c r="B931" s="4" t="n"/>
-      <c r="C931" s="4" t="n"/>
-      <c r="D931" s="4" t="n"/>
-      <c r="E931" s="4" t="n"/>
-      <c r="F931" s="4" t="n"/>
-      <c r="G931" s="4" t="n"/>
-      <c r="H931" s="4" t="n"/>
-      <c r="I931" s="4" t="n"/>
-      <c r="J931" s="3" t="n"/>
-      <c r="K931" s="3" t="n"/>
-    </row>
-    <row r="932">
-      <c r="A932" s="4" t="n"/>
-      <c r="B932" s="4" t="n"/>
-      <c r="C932" s="4" t="n"/>
-      <c r="D932" s="4" t="n"/>
-      <c r="E932" s="4" t="n"/>
-      <c r="F932" s="4" t="n"/>
-      <c r="G932" s="4" t="n"/>
-      <c r="H932" s="4" t="n"/>
-      <c r="I932" s="4" t="n"/>
-      <c r="J932" s="3" t="n"/>
-      <c r="K932" s="3" t="n"/>
-    </row>
-    <row r="933">
-      <c r="A933" s="4" t="n"/>
-      <c r="B933" s="4" t="n"/>
-      <c r="C933" s="4" t="n"/>
-      <c r="D933" s="4" t="n"/>
-      <c r="E933" s="4" t="n"/>
-      <c r="F933" s="4" t="n"/>
-      <c r="G933" s="4" t="n"/>
-      <c r="H933" s="4" t="n"/>
-      <c r="I933" s="4" t="n"/>
-      <c r="J933" s="3" t="n"/>
-      <c r="K933" s="3" t="n"/>
-    </row>
-    <row r="934">
-      <c r="A934" s="4" t="n"/>
-      <c r="B934" s="4" t="n"/>
-      <c r="C934" s="4" t="n"/>
-      <c r="D934" s="4" t="n"/>
-      <c r="E934" s="4" t="n"/>
-      <c r="F934" s="4" t="n"/>
-      <c r="G934" s="4" t="n"/>
-      <c r="H934" s="4" t="n"/>
-      <c r="I934" s="4" t="n"/>
-      <c r="J934" s="3" t="n"/>
-      <c r="K934" s="3" t="n"/>
-    </row>
-    <row r="935">
-      <c r="A935" s="4" t="n"/>
-      <c r="B935" s="4" t="n"/>
-      <c r="C935" s="4" t="n"/>
-      <c r="D935" s="4" t="n"/>
-      <c r="E935" s="4" t="n"/>
-      <c r="F935" s="4" t="n"/>
-      <c r="G935" s="4" t="n"/>
-      <c r="H935" s="4" t="n"/>
-      <c r="I935" s="4" t="n"/>
-      <c r="J935" s="3" t="n"/>
-      <c r="K935" s="3" t="n"/>
-    </row>
-    <row r="936">
-      <c r="A936" s="4" t="n"/>
-      <c r="B936" s="4" t="n"/>
-      <c r="C936" s="4" t="n"/>
-      <c r="D936" s="4" t="n"/>
-      <c r="E936" s="4" t="n"/>
-      <c r="F936" s="4" t="n"/>
-      <c r="G936" s="4" t="n"/>
-      <c r="H936" s="4" t="n"/>
-      <c r="I936" s="4" t="n"/>
-      <c r="J936" s="3" t="n"/>
-      <c r="K936" s="3" t="n"/>
-    </row>
-    <row r="937">
-      <c r="A937" s="4" t="n"/>
-      <c r="B937" s="4" t="n"/>
-      <c r="C937" s="4" t="n"/>
-      <c r="D937" s="4" t="n"/>
-      <c r="E937" s="4" t="n"/>
-      <c r="F937" s="4" t="n"/>
-      <c r="G937" s="4" t="n"/>
-      <c r="H937" s="4" t="n"/>
-      <c r="I937" s="4" t="n"/>
-      <c r="J937" s="3" t="n"/>
-      <c r="K937" s="3" t="n"/>
-    </row>
-    <row r="938">
-      <c r="A938" s="4" t="n"/>
-      <c r="B938" s="4" t="n"/>
-      <c r="C938" s="4" t="n"/>
-      <c r="D938" s="4" t="n"/>
-      <c r="E938" s="4" t="n"/>
-      <c r="F938" s="4" t="n"/>
-      <c r="G938" s="4" t="n"/>
-      <c r="H938" s="4" t="n"/>
-      <c r="I938" s="4" t="n"/>
-      <c r="J938" s="3" t="n"/>
-      <c r="K938" s="3" t="n"/>
-    </row>
-    <row r="939">
-      <c r="A939" s="4" t="n"/>
-      <c r="B939" s="4" t="n"/>
-      <c r="C939" s="4" t="n"/>
-      <c r="D939" s="4" t="n"/>
-      <c r="E939" s="4" t="n"/>
-      <c r="F939" s="4" t="n"/>
-      <c r="G939" s="4" t="n"/>
-      <c r="H939" s="4" t="n"/>
-      <c r="I939" s="4" t="n"/>
-      <c r="J939" s="3" t="n"/>
-      <c r="K939" s="3" t="n"/>
-    </row>
-    <row r="940">
-      <c r="A940" s="4" t="n"/>
-      <c r="B940" s="4" t="n"/>
-      <c r="C940" s="4" t="n"/>
-      <c r="D940" s="4" t="n"/>
-      <c r="E940" s="4" t="n"/>
-      <c r="F940" s="4" t="n"/>
-      <c r="G940" s="4" t="n"/>
-      <c r="H940" s="4" t="n"/>
-      <c r="I940" s="4" t="n"/>
-      <c r="J940" s="3" t="n"/>
-      <c r="K940" s="3" t="n"/>
-    </row>
-    <row r="941">
-      <c r="A941" s="4" t="n"/>
-      <c r="B941" s="4" t="n"/>
-      <c r="C941" s="4" t="n"/>
-      <c r="D941" s="4" t="n"/>
-      <c r="E941" s="4" t="n"/>
-      <c r="F941" s="4" t="n"/>
-      <c r="G941" s="4" t="n"/>
-      <c r="H941" s="4" t="n"/>
-      <c r="I941" s="4" t="n"/>
-      <c r="J941" s="3" t="n"/>
-      <c r="K941" s="3" t="n"/>
-    </row>
-    <row r="942">
-      <c r="A942" s="4" t="n"/>
-      <c r="B942" s="4" t="n"/>
-      <c r="C942" s="4" t="n"/>
-      <c r="D942" s="4" t="n"/>
-      <c r="E942" s="4" t="n"/>
-      <c r="F942" s="4" t="n"/>
-      <c r="G942" s="4" t="n"/>
-      <c r="H942" s="4" t="n"/>
-      <c r="I942" s="4" t="n"/>
-      <c r="J942" s="3" t="n"/>
-      <c r="K942" s="3" t="n"/>
-    </row>
-    <row r="943">
-      <c r="A943" s="4" t="n"/>
-      <c r="B943" s="4" t="n"/>
-      <c r="C943" s="4" t="n"/>
-      <c r="D943" s="4" t="n"/>
-      <c r="E943" s="4" t="n"/>
-      <c r="F943" s="4" t="n"/>
-      <c r="G943" s="4" t="n"/>
-      <c r="H943" s="4" t="n"/>
-      <c r="I943" s="4" t="n"/>
-      <c r="J943" s="3" t="n"/>
-      <c r="K943" s="3" t="n"/>
-    </row>
-    <row r="944">
-      <c r="A944" s="4" t="n"/>
-      <c r="B944" s="4" t="n"/>
-      <c r="C944" s="4" t="n"/>
-      <c r="D944" s="4" t="n"/>
-      <c r="E944" s="4" t="n"/>
-      <c r="F944" s="4" t="n"/>
-      <c r="G944" s="4" t="n"/>
-      <c r="H944" s="4" t="n"/>
-      <c r="I944" s="4" t="n"/>
-      <c r="J944" s="3" t="n"/>
-      <c r="K944" s="3" t="n"/>
-    </row>
-    <row r="945">
-      <c r="A945" s="4" t="n"/>
-      <c r="B945" s="4" t="n"/>
-      <c r="C945" s="4" t="n"/>
-      <c r="D945" s="4" t="n"/>
-      <c r="E945" s="4" t="n"/>
-      <c r="F945" s="4" t="n"/>
-      <c r="G945" s="4" t="n"/>
-      <c r="H945" s="4" t="n"/>
-      <c r="I945" s="4" t="n"/>
-      <c r="J945" s="3" t="n"/>
-      <c r="K945" s="3" t="n"/>
-    </row>
-    <row r="946">
-      <c r="A946" s="4" t="n"/>
-      <c r="B946" s="4" t="n"/>
-      <c r="C946" s="4" t="n"/>
-      <c r="D946" s="4" t="n"/>
-      <c r="E946" s="4" t="n"/>
-      <c r="F946" s="4" t="n"/>
-      <c r="G946" s="4" t="n"/>
-      <c r="H946" s="4" t="n"/>
-      <c r="I946" s="4" t="n"/>
-      <c r="J946" s="3" t="n"/>
-      <c r="K946" s="3" t="n"/>
-    </row>
-    <row r="947">
-      <c r="A947" s="4" t="n"/>
-      <c r="B947" s="4" t="n"/>
-      <c r="C947" s="4" t="n"/>
-      <c r="D947" s="4" t="n"/>
-      <c r="E947" s="4" t="n"/>
-      <c r="F947" s="4" t="n"/>
-      <c r="G947" s="4" t="n"/>
-      <c r="H947" s="4" t="n"/>
-      <c r="I947" s="4" t="n"/>
-      <c r="J947" s="3" t="n"/>
-      <c r="K947" s="3" t="n"/>
-    </row>
-    <row r="948">
-      <c r="A948" s="4" t="n"/>
-      <c r="B948" s="4" t="n"/>
-      <c r="C948" s="4" t="n"/>
-      <c r="D948" s="4" t="n"/>
-      <c r="E948" s="4" t="n"/>
-      <c r="F948" s="4" t="n"/>
-      <c r="G948" s="4" t="n"/>
-      <c r="H948" s="4" t="n"/>
-      <c r="I948" s="4" t="n"/>
-      <c r="J948" s="3" t="n"/>
-      <c r="K948" s="3" t="n"/>
-    </row>
-    <row r="949">
-      <c r="A949" s="4" t="n"/>
-      <c r="B949" s="4" t="n"/>
-      <c r="C949" s="4" t="n"/>
-      <c r="D949" s="4" t="n"/>
-      <c r="E949" s="4" t="n"/>
-      <c r="F949" s="4" t="n"/>
-      <c r="G949" s="4" t="n"/>
-      <c r="H949" s="4" t="n"/>
-      <c r="I949" s="4" t="n"/>
-      <c r="J949" s="3" t="n"/>
-      <c r="K949" s="3" t="n"/>
-    </row>
-    <row r="950">
-      <c r="A950" s="4" t="n"/>
-      <c r="B950" s="4" t="n"/>
-      <c r="C950" s="4" t="n"/>
-      <c r="D950" s="4" t="n"/>
-      <c r="E950" s="4" t="n"/>
-      <c r="F950" s="4" t="n"/>
-      <c r="G950" s="4" t="n"/>
-      <c r="H950" s="4" t="n"/>
-      <c r="I950" s="4" t="n"/>
-      <c r="J950" s="3" t="n"/>
-      <c r="K950" s="3" t="n"/>
-    </row>
-    <row r="951">
-      <c r="A951" s="4" t="n"/>
-      <c r="B951" s="4" t="n"/>
-      <c r="C951" s="4" t="n"/>
-      <c r="D951" s="4" t="n"/>
-      <c r="E951" s="4" t="n"/>
-      <c r="F951" s="4" t="n"/>
-      <c r="G951" s="4" t="n"/>
-      <c r="H951" s="4" t="n"/>
-      <c r="I951" s="4" t="n"/>
-      <c r="J951" s="3" t="n"/>
-      <c r="K951" s="3" t="n"/>
-    </row>
-    <row r="952">
-      <c r="A952" s="4" t="n"/>
-      <c r="B952" s="4" t="n"/>
-      <c r="C952" s="4" t="n"/>
-      <c r="D952" s="4" t="n"/>
-      <c r="E952" s="4" t="n"/>
-      <c r="F952" s="4" t="n"/>
-      <c r="G952" s="4" t="n"/>
-      <c r="H952" s="4" t="n"/>
-      <c r="I952" s="4" t="n"/>
-      <c r="J952" s="3" t="n"/>
-      <c r="K952" s="3" t="n"/>
-    </row>
-    <row r="953">
-      <c r="A953" s="4" t="n"/>
-      <c r="B953" s="4" t="n"/>
-      <c r="C953" s="4" t="n"/>
-      <c r="D953" s="4" t="n"/>
-      <c r="E953" s="4" t="n"/>
-      <c r="F953" s="4" t="n"/>
-      <c r="G953" s="4" t="n"/>
-      <c r="H953" s="4" t="n"/>
-      <c r="I953" s="4" t="n"/>
-      <c r="J953" s="3" t="n"/>
-      <c r="K953" s="3" t="n"/>
-    </row>
-    <row r="954">
-      <c r="A954" s="4" t="n"/>
-      <c r="B954" s="4" t="n"/>
-      <c r="C954" s="4" t="n"/>
-      <c r="D954" s="4" t="n"/>
-      <c r="E954" s="4" t="n"/>
-      <c r="F954" s="4" t="n"/>
-      <c r="G954" s="4" t="n"/>
-      <c r="H954" s="4" t="n"/>
-      <c r="I954" s="4" t="n"/>
-      <c r="J954" s="3" t="n"/>
-      <c r="K954" s="3" t="n"/>
-    </row>
-    <row r="955">
-      <c r="A955" s="4" t="n"/>
-      <c r="B955" s="4" t="n"/>
-      <c r="C955" s="4" t="n"/>
-      <c r="D955" s="4" t="n"/>
-      <c r="E955" s="4" t="n"/>
-      <c r="F955" s="4" t="n"/>
-      <c r="G955" s="4" t="n"/>
-      <c r="H955" s="4" t="n"/>
-      <c r="I955" s="4" t="n"/>
-      <c r="J955" s="3" t="n"/>
-      <c r="K955" s="3" t="n"/>
-    </row>
-    <row r="956">
-      <c r="A956" s="4" t="n"/>
-      <c r="B956" s="4" t="n"/>
-      <c r="C956" s="4" t="n"/>
-      <c r="D956" s="4" t="n"/>
-      <c r="E956" s="4" t="n"/>
-      <c r="F956" s="4" t="n"/>
-      <c r="G956" s="4" t="n"/>
-      <c r="H956" s="4" t="n"/>
-      <c r="I956" s="4" t="n"/>
-      <c r="J956" s="3" t="n"/>
-      <c r="K956" s="3" t="n"/>
-    </row>
-    <row r="957">
-      <c r="A957" s="4" t="n"/>
-      <c r="B957" s="4" t="n"/>
-      <c r="C957" s="4" t="n"/>
-      <c r="D957" s="4" t="n"/>
-      <c r="E957" s="4" t="n"/>
-      <c r="F957" s="4" t="n"/>
-      <c r="G957" s="4" t="n"/>
-      <c r="H957" s="4" t="n"/>
-      <c r="I957" s="4" t="n"/>
-      <c r="J957" s="3" t="n"/>
-      <c r="K957" s="3" t="n"/>
-    </row>
-    <row r="958">
-      <c r="A958" s="4" t="n"/>
-      <c r="B958" s="4" t="n"/>
-      <c r="C958" s="4" t="n"/>
-      <c r="D958" s="4" t="n"/>
-      <c r="E958" s="4" t="n"/>
-      <c r="F958" s="4" t="n"/>
-      <c r="G958" s="4" t="n"/>
-      <c r="H958" s="4" t="n"/>
-      <c r="I958" s="4" t="n"/>
-      <c r="J958" s="3" t="n"/>
-      <c r="K958" s="3" t="n"/>
-    </row>
-    <row r="959">
-      <c r="A959" s="4" t="n"/>
-      <c r="B959" s="4" t="n"/>
-      <c r="C959" s="4" t="n"/>
-      <c r="D959" s="4" t="n"/>
-      <c r="E959" s="4" t="n"/>
-      <c r="F959" s="4" t="n"/>
-      <c r="G959" s="4" t="n"/>
-      <c r="H959" s="4" t="n"/>
-      <c r="I959" s="4" t="n"/>
-      <c r="J959" s="3" t="n"/>
-      <c r="K959" s="3" t="n"/>
-    </row>
-    <row r="960">
-      <c r="A960" s="4" t="n"/>
-      <c r="B960" s="4" t="n"/>
-      <c r="C960" s="4" t="n"/>
-      <c r="D960" s="4" t="n"/>
-      <c r="E960" s="4" t="n"/>
-      <c r="F960" s="4" t="n"/>
-      <c r="G960" s="4" t="n"/>
-      <c r="H960" s="4" t="n"/>
-      <c r="I960" s="4" t="n"/>
-      <c r="J960" s="3" t="n"/>
-      <c r="K960" s="3" t="n"/>
-    </row>
-    <row r="961">
-      <c r="A961" s="4" t="n"/>
-      <c r="B961" s="4" t="n"/>
-      <c r="C961" s="4" t="n"/>
-      <c r="D961" s="4" t="n"/>
-      <c r="E961" s="4" t="n"/>
-      <c r="F961" s="4" t="n"/>
-      <c r="G961" s="4" t="n"/>
-      <c r="H961" s="4" t="n"/>
-      <c r="I961" s="4" t="n"/>
-      <c r="J961" s="3" t="n"/>
-      <c r="K961" s="3" t="n"/>
-    </row>
-    <row r="962">
-      <c r="A962" s="4" t="n"/>
-      <c r="B962" s="4" t="n"/>
-      <c r="C962" s="4" t="n"/>
-      <c r="D962" s="4" t="n"/>
-      <c r="E962" s="4" t="n"/>
-      <c r="F962" s="4" t="n"/>
-      <c r="G962" s="4" t="n"/>
-      <c r="H962" s="4" t="n"/>
-      <c r="I962" s="4" t="n"/>
-      <c r="J962" s="3" t="n"/>
-      <c r="K962" s="3" t="n"/>
-    </row>
-    <row r="963">
-      <c r="A963" s="4" t="n"/>
-      <c r="B963" s="4" t="n"/>
-      <c r="C963" s="4" t="n"/>
-      <c r="D963" s="4" t="n"/>
-      <c r="E963" s="4" t="n"/>
-      <c r="F963" s="4" t="n"/>
-      <c r="G963" s="4" t="n"/>
-      <c r="H963" s="4" t="n"/>
-      <c r="I963" s="4" t="n"/>
-      <c r="J963" s="3" t="n"/>
-      <c r="K963" s="3" t="n"/>
-    </row>
-    <row r="964">
-      <c r="A964" s="4" t="n"/>
-      <c r="B964" s="4" t="n"/>
-      <c r="C964" s="4" t="n"/>
-      <c r="D964" s="4" t="n"/>
-      <c r="E964" s="4" t="n"/>
-      <c r="F964" s="4" t="n"/>
-      <c r="G964" s="4" t="n"/>
-      <c r="H964" s="4" t="n"/>
-      <c r="I964" s="4" t="n"/>
-      <c r="J964" s="3" t="n"/>
-      <c r="K964" s="3" t="n"/>
-    </row>
-    <row r="965">
-      <c r="A965" s="4" t="n"/>
-      <c r="B965" s="4" t="n"/>
-      <c r="C965" s="4" t="n"/>
-      <c r="D965" s="4" t="n"/>
-      <c r="E965" s="4" t="n"/>
-      <c r="F965" s="4" t="n"/>
-      <c r="G965" s="4" t="n"/>
-      <c r="H965" s="4" t="n"/>
-      <c r="I965" s="4" t="n"/>
-      <c r="J965" s="3" t="n"/>
-      <c r="K965" s="3" t="n"/>
-    </row>
-    <row r="966">
-      <c r="A966" s="4" t="n"/>
-      <c r="B966" s="4" t="n"/>
-      <c r="C966" s="4" t="n"/>
-      <c r="D966" s="4" t="n"/>
-      <c r="E966" s="4" t="n"/>
-      <c r="F966" s="4" t="n"/>
-      <c r="G966" s="4" t="n"/>
-      <c r="H966" s="4" t="n"/>
-      <c r="I966" s="4" t="n"/>
-      <c r="J966" s="3" t="n"/>
-      <c r="K966" s="3" t="n"/>
-    </row>
-    <row r="967">
-      <c r="A967" s="4" t="n"/>
-      <c r="B967" s="4" t="n"/>
-      <c r="C967" s="4" t="n"/>
-      <c r="D967" s="4" t="n"/>
-      <c r="E967" s="4" t="n"/>
-      <c r="F967" s="4" t="n"/>
-      <c r="G967" s="4" t="n"/>
-      <c r="H967" s="4" t="n"/>
-      <c r="I967" s="4" t="n"/>
-      <c r="J967" s="3" t="n"/>
-      <c r="K967" s="3" t="n"/>
-    </row>
-    <row r="968">
-      <c r="A968" s="4" t="n"/>
-      <c r="B968" s="4" t="n"/>
-      <c r="C968" s="4" t="n"/>
-      <c r="D968" s="4" t="n"/>
-      <c r="E968" s="4" t="n"/>
-      <c r="F968" s="4" t="n"/>
-      <c r="G968" s="4" t="n"/>
-      <c r="H968" s="4" t="n"/>
-      <c r="I968" s="4" t="n"/>
-      <c r="J968" s="3" t="n"/>
-      <c r="K968" s="3" t="n"/>
-    </row>
-    <row r="969">
-      <c r="A969" s="4" t="n"/>
-      <c r="B969" s="4" t="n"/>
-      <c r="C969" s="4" t="n"/>
-      <c r="D969" s="4" t="n"/>
-      <c r="E969" s="4" t="n"/>
-      <c r="F969" s="4" t="n"/>
-      <c r="G969" s="4" t="n"/>
-      <c r="H969" s="4" t="n"/>
-      <c r="I969" s="4" t="n"/>
-      <c r="J969" s="3" t="n"/>
-      <c r="K969" s="3" t="n"/>
-    </row>
-    <row r="970">
-      <c r="A970" s="4" t="n"/>
-      <c r="B970" s="4" t="n"/>
-      <c r="C970" s="4" t="n"/>
-      <c r="D970" s="4" t="n"/>
-      <c r="E970" s="4" t="n"/>
-      <c r="F970" s="4" t="n"/>
-      <c r="G970" s="4" t="n"/>
-      <c r="H970" s="4" t="n"/>
-      <c r="I970" s="4" t="n"/>
-      <c r="J970" s="3" t="n"/>
-      <c r="K970" s="3" t="n"/>
-    </row>
-    <row r="971">
-      <c r="A971" s="4" t="n"/>
-      <c r="B971" s="4" t="n"/>
-      <c r="C971" s="4" t="n"/>
-      <c r="D971" s="4" t="n"/>
-      <c r="E971" s="4" t="n"/>
-      <c r="F971" s="4" t="n"/>
-      <c r="G971" s="4" t="n"/>
-      <c r="H971" s="4" t="n"/>
-      <c r="I971" s="4" t="n"/>
-      <c r="J971" s="3" t="n"/>
-      <c r="K971" s="3" t="n"/>
-    </row>
-    <row r="972">
-      <c r="A972" s="4" t="n"/>
-      <c r="B972" s="4" t="n"/>
-      <c r="C972" s="4" t="n"/>
-      <c r="D972" s="4" t="n"/>
-      <c r="E972" s="4" t="n"/>
-      <c r="F972" s="4" t="n"/>
-      <c r="G972" s="4" t="n"/>
-      <c r="H972" s="4" t="n"/>
-      <c r="I972" s="4" t="n"/>
-      <c r="J972" s="3" t="n"/>
-      <c r="K972" s="3" t="n"/>
-    </row>
-    <row r="973">
-      <c r="A973" s="4" t="n"/>
-      <c r="B973" s="4" t="n"/>
-      <c r="C973" s="4" t="n"/>
-      <c r="D973" s="4" t="n"/>
-      <c r="E973" s="4" t="n"/>
-      <c r="F973" s="4" t="n"/>
-      <c r="G973" s="4" t="n"/>
-      <c r="H973" s="4" t="n"/>
-      <c r="I973" s="4" t="n"/>
-      <c r="J973" s="3" t="n"/>
-      <c r="K973" s="3" t="n"/>
-    </row>
-    <row r="974">
-      <c r="A974" s="4" t="n"/>
-      <c r="B974" s="4" t="n"/>
-      <c r="C974" s="4" t="n"/>
-      <c r="D974" s="4" t="n"/>
-      <c r="E974" s="4" t="n"/>
-      <c r="F974" s="4" t="n"/>
-      <c r="G974" s="4" t="n"/>
-      <c r="H974" s="4" t="n"/>
-      <c r="I974" s="4" t="n"/>
-      <c r="J974" s="3" t="n"/>
-      <c r="K974" s="3" t="n"/>
-    </row>
-    <row r="975">
-      <c r="A975" s="4" t="n"/>
-      <c r="B975" s="4" t="n"/>
-      <c r="C975" s="4" t="n"/>
-      <c r="D975" s="4" t="n"/>
-      <c r="E975" s="4" t="n"/>
-      <c r="F975" s="4" t="n"/>
-      <c r="G975" s="4" t="n"/>
-      <c r="H975" s="4" t="n"/>
-      <c r="I975" s="4" t="n"/>
-      <c r="J975" s="3" t="n"/>
-      <c r="K975" s="3" t="n"/>
-    </row>
-    <row r="976">
-      <c r="A976" s="4" t="n"/>
-      <c r="B976" s="4" t="n"/>
-      <c r="C976" s="4" t="n"/>
-      <c r="D976" s="4" t="n"/>
-      <c r="E976" s="4" t="n"/>
-      <c r="F976" s="4" t="n"/>
-      <c r="G976" s="4" t="n"/>
-      <c r="H976" s="4" t="n"/>
-      <c r="I976" s="4" t="n"/>
-      <c r="J976" s="3" t="n"/>
-      <c r="K976" s="3" t="n"/>
-    </row>
-    <row r="977">
-      <c r="A977" s="4" t="n"/>
-      <c r="B977" s="4" t="n"/>
-      <c r="C977" s="4" t="n"/>
-      <c r="D977" s="4" t="n"/>
-      <c r="E977" s="4" t="n"/>
-      <c r="F977" s="4" t="n"/>
-      <c r="G977" s="4" t="n"/>
-      <c r="H977" s="4" t="n"/>
-      <c r="I977" s="4" t="n"/>
-      <c r="J977" s="3" t="n"/>
-      <c r="K977" s="3" t="n"/>
-    </row>
-    <row r="978">
-      <c r="A978" s="4" t="n"/>
-      <c r="B978" s="4" t="n"/>
-      <c r="C978" s="4" t="n"/>
-      <c r="D978" s="4" t="n"/>
-      <c r="E978" s="4" t="n"/>
-      <c r="F978" s="4" t="n"/>
-      <c r="G978" s="4" t="n"/>
-      <c r="H978" s="4" t="n"/>
-      <c r="I978" s="4" t="n"/>
-      <c r="J978" s="3" t="n"/>
-      <c r="K978" s="3" t="n"/>
-    </row>
-    <row r="979">
-      <c r="A979" s="4" t="n"/>
-      <c r="B979" s="4" t="n"/>
-      <c r="C979" s="4" t="n"/>
-      <c r="D979" s="4" t="n"/>
-      <c r="E979" s="4" t="n"/>
-      <c r="F979" s="4" t="n"/>
-      <c r="G979" s="4" t="n"/>
-      <c r="H979" s="4" t="n"/>
-      <c r="I979" s="4" t="n"/>
-      <c r="J979" s="3" t="n"/>
-      <c r="K979" s="3" t="n"/>
-    </row>
-    <row r="980">
-      <c r="A980" s="4" t="n"/>
-      <c r="B980" s="4" t="n"/>
-      <c r="C980" s="4" t="n"/>
-      <c r="D980" s="4" t="n"/>
-      <c r="E980" s="4" t="n"/>
-      <c r="F980" s="4" t="n"/>
-      <c r="G980" s="4" t="n"/>
-      <c r="H980" s="4" t="n"/>
-      <c r="I980" s="4" t="n"/>
-      <c r="J980" s="3" t="n"/>
-      <c r="K980" s="3" t="n"/>
-    </row>
-    <row r="981">
-      <c r="A981" s="4" t="n"/>
-      <c r="B981" s="4" t="n"/>
-      <c r="C981" s="4" t="n"/>
-      <c r="D981" s="4" t="n"/>
-      <c r="E981" s="4" t="n"/>
-      <c r="F981" s="4" t="n"/>
-      <c r="G981" s="4" t="n"/>
-      <c r="H981" s="4" t="n"/>
-      <c r="I981" s="4" t="n"/>
-      <c r="J981" s="3" t="n"/>
-      <c r="K981" s="3" t="n"/>
-    </row>
-    <row r="982">
-      <c r="A982" s="4" t="n"/>
-      <c r="B982" s="4" t="n"/>
-      <c r="C982" s="4" t="n"/>
-      <c r="D982" s="4" t="n"/>
-      <c r="E982" s="4" t="n"/>
-      <c r="F982" s="4" t="n"/>
-      <c r="G982" s="4" t="n"/>
-      <c r="H982" s="4" t="n"/>
-      <c r="I982" s="4" t="n"/>
-      <c r="J982" s="3" t="n"/>
-      <c r="K982" s="3" t="n"/>
-    </row>
-    <row r="983">
-      <c r="A983" s="4" t="n"/>
-      <c r="B983" s="4" t="n"/>
-      <c r="C983" s="4" t="n"/>
-      <c r="D983" s="4" t="n"/>
-      <c r="E983" s="4" t="n"/>
-      <c r="F983" s="4" t="n"/>
-      <c r="G983" s="4" t="n"/>
-      <c r="H983" s="4" t="n"/>
-      <c r="I983" s="4" t="n"/>
-      <c r="J983" s="3" t="n"/>
-      <c r="K983" s="3" t="n"/>
-    </row>
-    <row r="984">
-      <c r="A984" s="4" t="n"/>
-      <c r="B984" s="4" t="n"/>
-      <c r="C984" s="4" t="n"/>
-      <c r="D984" s="4" t="n"/>
-      <c r="E984" s="4" t="n"/>
-      <c r="F984" s="4" t="n"/>
-      <c r="G984" s="4" t="n"/>
-      <c r="H984" s="4" t="n"/>
-      <c r="I984" s="4" t="n"/>
-      <c r="J984" s="3" t="n"/>
-      <c r="K984" s="3" t="n"/>
-    </row>
-    <row r="985">
-      <c r="A985" s="4" t="n"/>
-      <c r="B985" s="4" t="n"/>
-      <c r="C985" s="4" t="n"/>
-      <c r="D985" s="4" t="n"/>
-      <c r="E985" s="4" t="n"/>
-      <c r="F985" s="4" t="n"/>
-      <c r="G985" s="4" t="n"/>
-      <c r="H985" s="4" t="n"/>
-      <c r="I985" s="4" t="n"/>
-      <c r="J985" s="3" t="n"/>
-      <c r="K985" s="3" t="n"/>
-    </row>
-    <row r="986">
-      <c r="A986" s="4" t="n"/>
-      <c r="B986" s="4" t="n"/>
-      <c r="C986" s="4" t="n"/>
-      <c r="D986" s="4" t="n"/>
-      <c r="E986" s="4" t="n"/>
-      <c r="F986" s="4" t="n"/>
-      <c r="G986" s="4" t="n"/>
-      <c r="H986" s="4" t="n"/>
-      <c r="I986" s="4" t="n"/>
-      <c r="J986" s="3" t="n"/>
-      <c r="K986" s="3" t="n"/>
-    </row>
-    <row r="987">
-      <c r="A987" s="4" t="n"/>
-      <c r="B987" s="4" t="n"/>
-      <c r="C987" s="4" t="n"/>
-      <c r="D987" s="4" t="n"/>
-      <c r="E987" s="4" t="n"/>
-      <c r="F987" s="4" t="n"/>
-      <c r="G987" s="4" t="n"/>
-      <c r="H987" s="4" t="n"/>
-      <c r="I987" s="4" t="n"/>
-      <c r="J987" s="3" t="n"/>
-      <c r="K987" s="3" t="n"/>
-    </row>
-    <row r="988">
-      <c r="A988" s="4" t="n"/>
-      <c r="B988" s="4" t="n"/>
-      <c r="C988" s="4" t="n"/>
-      <c r="D988" s="4" t="n"/>
-      <c r="E988" s="4" t="n"/>
-      <c r="F988" s="4" t="n"/>
-      <c r="G988" s="4" t="n"/>
-      <c r="H988" s="4" t="n"/>
-      <c r="I988" s="4" t="n"/>
-      <c r="J988" s="3" t="n"/>
-      <c r="K988" s="3" t="n"/>
-    </row>
-    <row r="989">
-      <c r="A989" s="4" t="n"/>
-      <c r="B989" s="4" t="n"/>
-      <c r="C989" s="4" t="n"/>
-      <c r="D989" s="4" t="n"/>
-      <c r="E989" s="4" t="n"/>
-      <c r="F989" s="4" t="n"/>
-      <c r="G989" s="4" t="n"/>
-      <c r="H989" s="4" t="n"/>
-      <c r="I989" s="4" t="n"/>
-      <c r="J989" s="3" t="n"/>
-      <c r="K989" s="3" t="n"/>
-    </row>
-    <row r="990">
-      <c r="A990" s="4" t="n"/>
-      <c r="B990" s="4" t="n"/>
-      <c r="C990" s="4" t="n"/>
-      <c r="D990" s="4" t="n"/>
-      <c r="E990" s="4" t="n"/>
-      <c r="F990" s="4" t="n"/>
-      <c r="G990" s="4" t="n"/>
-      <c r="H990" s="4" t="n"/>
-      <c r="I990" s="4" t="n"/>
-      <c r="J990" s="3" t="n"/>
-      <c r="K990" s="3" t="n"/>
-    </row>
-    <row r="991">
-      <c r="A991" s="4" t="n"/>
-      <c r="B991" s="4" t="n"/>
-      <c r="C991" s="4" t="n"/>
-      <c r="D991" s="4" t="n"/>
-      <c r="E991" s="4" t="n"/>
-      <c r="F991" s="4" t="n"/>
-      <c r="G991" s="4" t="n"/>
-      <c r="H991" s="4" t="n"/>
-      <c r="I991" s="4" t="n"/>
-      <c r="J991" s="3" t="n"/>
-      <c r="K991" s="3" t="n"/>
-    </row>
-    <row r="992">
-      <c r="A992" s="4" t="n"/>
-      <c r="B992" s="4" t="n"/>
-      <c r="C992" s="4" t="n"/>
-      <c r="D992" s="4" t="n"/>
-      <c r="E992" s="4" t="n"/>
-      <c r="F992" s="4" t="n"/>
-      <c r="G992" s="4" t="n"/>
-      <c r="H992" s="4" t="n"/>
-      <c r="I992" s="4" t="n"/>
-      <c r="J992" s="3" t="n"/>
-      <c r="K992" s="3" t="n"/>
-    </row>
-    <row r="993">
-      <c r="A993" s="4" t="n"/>
-      <c r="B993" s="4" t="n"/>
-      <c r="C993" s="4" t="n"/>
-      <c r="D993" s="4" t="n"/>
-      <c r="E993" s="4" t="n"/>
-      <c r="F993" s="4" t="n"/>
-      <c r="G993" s="4" t="n"/>
-      <c r="H993" s="4" t="n"/>
-      <c r="I993" s="4" t="n"/>
-      <c r="J993" s="3" t="n"/>
-      <c r="K993" s="3" t="n"/>
-    </row>
-    <row r="994">
-      <c r="A994" s="4" t="n"/>
-      <c r="B994" s="4" t="n"/>
-      <c r="C994" s="4" t="n"/>
-      <c r="D994" s="4" t="n"/>
-      <c r="E994" s="4" t="n"/>
-      <c r="F994" s="4" t="n"/>
-      <c r="G994" s="4" t="n"/>
-      <c r="H994" s="4" t="n"/>
-      <c r="I994" s="4" t="n"/>
-      <c r="J994" s="3" t="n"/>
-      <c r="K994" s="3" t="n"/>
-    </row>
-    <row r="995">
-      <c r="A995" s="4" t="n"/>
-      <c r="B995" s="4" t="n"/>
-      <c r="C995" s="4" t="n"/>
-      <c r="D995" s="4" t="n"/>
-      <c r="E995" s="4" t="n"/>
-      <c r="F995" s="4" t="n"/>
-      <c r="G995" s="4" t="n"/>
-      <c r="H995" s="4" t="n"/>
-      <c r="I995" s="4" t="n"/>
-      <c r="J995" s="3" t="n"/>
-      <c r="K995" s="3" t="n"/>
-    </row>
-    <row r="996">
-      <c r="A996" s="4" t="n"/>
-      <c r="B996" s="4" t="n"/>
-      <c r="C996" s="4" t="n"/>
-      <c r="D996" s="4" t="n"/>
-      <c r="E996" s="4" t="n"/>
-      <c r="F996" s="4" t="n"/>
-      <c r="G996" s="4" t="n"/>
-      <c r="H996" s="4" t="n"/>
-      <c r="I996" s="4" t="n"/>
-      <c r="J996" s="3" t="n"/>
-      <c r="K996" s="3" t="n"/>
-    </row>
-    <row r="997">
-      <c r="A997" s="4" t="n"/>
-      <c r="B997" s="4" t="n"/>
-      <c r="C997" s="4" t="n"/>
-      <c r="D997" s="4" t="n"/>
-      <c r="E997" s="4" t="n"/>
-      <c r="F997" s="4" t="n"/>
-      <c r="G997" s="4" t="n"/>
-      <c r="H997" s="4" t="n"/>
-      <c r="I997" s="4" t="n"/>
-      <c r="J997" s="3" t="n"/>
-      <c r="K997" s="3" t="n"/>
-    </row>
-    <row r="998">
-      <c r="A998" s="4" t="n"/>
-      <c r="B998" s="4" t="n"/>
-      <c r="C998" s="4" t="n"/>
-      <c r="D998" s="4" t="n"/>
-      <c r="E998" s="4" t="n"/>
-      <c r="F998" s="4" t="n"/>
-      <c r="G998" s="4" t="n"/>
-      <c r="H998" s="4" t="n"/>
-      <c r="I998" s="4" t="n"/>
-      <c r="J998" s="3" t="n"/>
-      <c r="K998" s="3" t="n"/>
-    </row>
-    <row r="999">
-      <c r="A999" s="4" t="n"/>
-      <c r="B999" s="4" t="n"/>
-      <c r="C999" s="4" t="n"/>
-      <c r="D999" s="4" t="n"/>
-      <c r="E999" s="4" t="n"/>
-      <c r="F999" s="4" t="n"/>
-      <c r="G999" s="4" t="n"/>
-      <c r="H999" s="4" t="n"/>
-      <c r="I999" s="4" t="n"/>
-      <c r="J999" s="3" t="n"/>
-      <c r="K999" s="3" t="n"/>
-    </row>
-    <row r="1000">
-      <c r="A1000" s="4" t="n"/>
-      <c r="B1000" s="4" t="n"/>
-      <c r="C1000" s="4" t="n"/>
-      <c r="D1000" s="4" t="n"/>
-      <c r="E1000" s="4" t="n"/>
-      <c r="F1000" s="4" t="n"/>
-      <c r="G1000" s="4" t="n"/>
-      <c r="H1000" s="4" t="n"/>
-      <c r="I1000" s="4" t="n"/>
-      <c r="J1000" s="3" t="n"/>
-      <c r="K1000" s="3" t="n"/>
-    </row>
-    <row r="1001">
-      <c r="A1001" s="4" t="n"/>
-      <c r="B1001" s="4" t="n"/>
-      <c r="C1001" s="4" t="n"/>
-      <c r="D1001" s="4" t="n"/>
-      <c r="E1001" s="4" t="n"/>
-      <c r="F1001" s="4" t="n"/>
-      <c r="G1001" s="4" t="n"/>
-      <c r="H1001" s="4" t="n"/>
-      <c r="I1001" s="4" t="n"/>
-      <c r="J1001" s="3" t="n"/>
-      <c r="K1001" s="3" t="n"/>
-    </row>
-    <row r="1002">
-      <c r="A1002" s="4" t="n"/>
-      <c r="B1002" s="4" t="n"/>
-      <c r="C1002" s="4" t="n"/>
-      <c r="D1002" s="4" t="n"/>
-      <c r="E1002" s="4" t="n"/>
-      <c r="F1002" s="4" t="n"/>
-      <c r="G1002" s="4" t="n"/>
-      <c r="H1002" s="4" t="n"/>
-      <c r="I1002" s="4" t="n"/>
-      <c r="J1002" s="3" t="n"/>
-      <c r="K1002" s="3" t="n"/>
-    </row>
-    <row r="1003">
-      <c r="A1003" s="4" t="n"/>
-      <c r="B1003" s="4" t="n"/>
-      <c r="C1003" s="4" t="n"/>
-      <c r="D1003" s="4" t="n"/>
-      <c r="E1003" s="4" t="n"/>
-      <c r="F1003" s="4" t="n"/>
-      <c r="G1003" s="4" t="n"/>
-      <c r="H1003" s="4" t="n"/>
-      <c r="I1003" s="4" t="n"/>
-      <c r="J1003" s="3" t="n"/>
-      <c r="K1003" s="3" t="n"/>
-    </row>
-    <row r="1004">
-      <c r="A1004" s="4" t="n"/>
-      <c r="B1004" s="4" t="n"/>
-      <c r="C1004" s="4" t="n"/>
-      <c r="D1004" s="4" t="n"/>
-      <c r="E1004" s="4" t="n"/>
-      <c r="F1004" s="4" t="n"/>
-      <c r="G1004" s="4" t="n"/>
-      <c r="H1004" s="4" t="n"/>
-      <c r="I1004" s="4" t="n"/>
-      <c r="J1004" s="3" t="n"/>
-      <c r="K1004" s="3" t="n"/>
-    </row>
-    <row r="1005">
-      <c r="A1005" s="4" t="n"/>
-      <c r="B1005" s="4" t="n"/>
-      <c r="C1005" s="4" t="n"/>
-      <c r="D1005" s="4" t="n"/>
-      <c r="E1005" s="4" t="n"/>
-      <c r="F1005" s="4" t="n"/>
-      <c r="G1005" s="4" t="n"/>
-      <c r="H1005" s="4" t="n"/>
-      <c r="I1005" s="4" t="n"/>
-      <c r="J1005" s="3" t="n"/>
-      <c r="K1005" s="3" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/terrestrial/Level4_20-Aug-26.xlsx
+++ b/terrestrial/Level4_20-Aug-26.xlsx
@@ -586,7 +586,11 @@
       <c r="K2" s="5" t="n"/>
       <c r="L2" s="5" t="n"/>
       <c r="M2" s="4" t="n"/>
-      <c r="N2" s="4" t="n"/>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>The Canadian province of Alberta</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -630,7 +634,11 @@
       <c r="K3" s="5" t="n"/>
       <c r="L3" s="5" t="n"/>
       <c r="M3" s="4" t="n"/>
-      <c r="N3" s="4" t="n"/>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>Afghanistan</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -674,7 +682,11 @@
       <c r="K4" s="5" t="n"/>
       <c r="L4" s="5" t="n"/>
       <c r="M4" s="4" t="n"/>
-      <c r="N4" s="4" t="n"/>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>Buenos Aires Province, Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -718,7 +730,11 @@
       <c r="K5" s="5" t="n"/>
       <c r="L5" s="5" t="n"/>
       <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4" t="n"/>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>Chaco Province, Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -762,7 +778,11 @@
       <c r="K6" s="5" t="n"/>
       <c r="L6" s="5" t="n"/>
       <c r="M6" s="4" t="n"/>
-      <c r="N6" s="4" t="n"/>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>Corrientes Province, Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -806,7 +826,11 @@
       <c r="K7" s="5" t="n"/>
       <c r="L7" s="5" t="n"/>
       <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4" t="n"/>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>Córdoba Province, Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -860,7 +884,11 @@
 -AGE-DF It is not digitized on map 16 (pg 135)</t>
         </is>
       </c>
-      <c r="N8" s="4" t="n"/>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>Autonomous City of Buenos Aires, Argentina's federal capital</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -904,7 +932,11 @@
       <c r="K9" s="5" t="n"/>
       <c r="L9" s="5" t="n"/>
       <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="n"/>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>Entre Ríos Province, Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -948,7 +980,11 @@
       <c r="K10" s="5" t="n"/>
       <c r="L10" s="5" t="n"/>
       <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="n"/>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>Formosa Province, Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -992,7 +1028,11 @@
       <c r="K11" s="5" t="n"/>
       <c r="L11" s="5" t="n"/>
       <c r="M11" s="4" t="n"/>
-      <c r="N11" s="4" t="n"/>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>La Pampa Province, Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1036,7 +1076,11 @@
       <c r="K12" s="5" t="n"/>
       <c r="L12" s="5" t="n"/>
       <c r="M12" s="4" t="n"/>
-      <c r="N12" s="4" t="n"/>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>Misiones Province, Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1084,7 +1128,11 @@
           <t>Typographical error, instead of AGE-SF there was AGS-SF. Only in the database. It is correct in the book/PDF</t>
         </is>
       </c>
-      <c r="N13" s="4" t="n"/>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>Santa Fe Province, Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1128,7 +1176,11 @@
       <c r="K14" s="5" t="n"/>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="4" t="n"/>
-      <c r="N14" s="4" t="n"/>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>Chubut Province, Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1172,7 +1224,11 @@
       <c r="K15" s="5" t="n"/>
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n"/>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>Neuquén Province, Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1216,7 +1272,11 @@
       <c r="K16" s="5" t="n"/>
       <c r="L16" s="5" t="n"/>
       <c r="M16" s="4" t="n"/>
-      <c r="N16" s="4" t="n"/>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>Río Negro Province, Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1260,7 +1320,11 @@
       <c r="K17" s="5" t="n"/>
       <c r="L17" s="5" t="n"/>
       <c r="M17" s="4" t="n"/>
-      <c r="N17" s="4" t="n"/>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>Santa Cruz Province, Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1304,7 +1368,11 @@
       <c r="K18" s="5" t="n"/>
       <c r="L18" s="5" t="n"/>
       <c r="M18" s="4" t="n"/>
-      <c r="N18" s="4" t="n"/>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>Tierra del Fuego Province, Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1348,7 +1416,11 @@
       <c r="K19" s="5" t="n"/>
       <c r="L19" s="5" t="n"/>
       <c r="M19" s="4" t="n"/>
-      <c r="N19" s="4" t="n"/>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>Catamarca Province, Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1392,7 +1464,11 @@
       <c r="K20" s="5" t="n"/>
       <c r="L20" s="5" t="n"/>
       <c r="M20" s="4" t="n"/>
-      <c r="N20" s="4" t="n"/>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>Jujuy Province, Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -1436,7 +1512,11 @@
       <c r="K21" s="5" t="n"/>
       <c r="L21" s="5" t="n"/>
       <c r="M21" s="4" t="n"/>
-      <c r="N21" s="4" t="n"/>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>La Rioja Province, Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -1480,7 +1560,11 @@
       <c r="K22" s="5" t="n"/>
       <c r="L22" s="5" t="n"/>
       <c r="M22" s="4" t="n"/>
-      <c r="N22" s="4" t="n"/>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>Mendoza Province, Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -1524,7 +1608,11 @@
       <c r="K23" s="5" t="n"/>
       <c r="L23" s="5" t="n"/>
       <c r="M23" s="4" t="n"/>
-      <c r="N23" s="4" t="n"/>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>Salta Province, Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -1568,7 +1656,11 @@
       <c r="K24" s="5" t="n"/>
       <c r="L24" s="5" t="n"/>
       <c r="M24" s="4" t="n"/>
-      <c r="N24" s="4" t="n"/>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>Santiago del Estero Province, Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -1612,7 +1704,11 @@
       <c r="K25" s="5" t="n"/>
       <c r="L25" s="5" t="n"/>
       <c r="M25" s="4" t="n"/>
-      <c r="N25" s="4" t="n"/>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>San Juan Province, Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -1656,7 +1752,11 @@
       <c r="K26" s="5" t="n"/>
       <c r="L26" s="5" t="n"/>
       <c r="M26" s="4" t="n"/>
-      <c r="N26" s="4" t="n"/>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>San Luis Province, Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -1700,7 +1800,11 @@
       <c r="K27" s="5" t="n"/>
       <c r="L27" s="5" t="n"/>
       <c r="M27" s="4" t="n"/>
-      <c r="N27" s="4" t="n"/>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>Tucumán Province, Argentina</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -1744,7 +1848,11 @@
       <c r="K28" s="5" t="n"/>
       <c r="L28" s="5" t="n"/>
       <c r="M28" s="4" t="n"/>
-      <c r="N28" s="4" t="n"/>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Alabama</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -1788,7 +1896,11 @@
       <c r="K29" s="5" t="n"/>
       <c r="L29" s="5" t="n"/>
       <c r="M29" s="4" t="n"/>
-      <c r="N29" s="4" t="n"/>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>Albania</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -1832,7 +1944,11 @@
       <c r="K30" s="5" t="n"/>
       <c r="L30" s="5" t="n"/>
       <c r="M30" s="4" t="n"/>
-      <c r="N30" s="4" t="n"/>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>Aldabra Atoll, Seychelles</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -1876,7 +1992,11 @@
       <c r="K31" s="5" t="n"/>
       <c r="L31" s="5" t="n"/>
       <c r="M31" s="4" t="n"/>
-      <c r="N31" s="4" t="n"/>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -1920,7 +2040,11 @@
       <c r="K32" s="5" t="n"/>
       <c r="L32" s="5" t="n"/>
       <c r="M32" s="4" t="n"/>
-      <c r="N32" s="4" t="n"/>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>Altai region of southern Siberia, Russia</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -1964,7 +2088,11 @@
           <t>Removed the L4 ISOcode (US). The Aleutian Is. belong to two distints countries.</t>
         </is>
       </c>
-      <c r="N33" s="4" t="n"/>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>Aleutian Islands, Alaska</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -2008,7 +2136,11 @@
       <c r="K34" s="5" t="n"/>
       <c r="L34" s="5" t="n"/>
       <c r="M34" s="4" t="n"/>
-      <c r="N34" s="4" t="n"/>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>Amur Oblast, Russia</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -2052,7 +2184,11 @@
       <c r="K35" s="5" t="n"/>
       <c r="L35" s="5" t="n"/>
       <c r="M35" s="4" t="n"/>
-      <c r="N35" s="4" t="n"/>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>Andaman Islands, India</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -2096,7 +2232,11 @@
       <c r="K36" s="5" t="n"/>
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="4" t="n"/>
-      <c r="N36" s="4" t="n"/>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>Coco Islands, Myanmar</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -2140,7 +2280,11 @@
       <c r="K37" s="5" t="n"/>
       <c r="L37" s="5" t="n"/>
       <c r="M37" s="4" t="n"/>
-      <c r="N37" s="4" t="n"/>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -2184,7 +2328,11 @@
       <c r="K38" s="5" t="n"/>
       <c r="L38" s="5" t="n"/>
       <c r="M38" s="4" t="n"/>
-      <c r="N38" s="4" t="n"/>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>Antarctica</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -2228,7 +2376,11 @@
       <c r="K39" s="5" t="n"/>
       <c r="L39" s="5" t="n"/>
       <c r="M39" s="4" t="n"/>
-      <c r="N39" s="4" t="n"/>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Arizona</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -2272,7 +2424,11 @@
       <c r="K40" s="5" t="n"/>
       <c r="L40" s="5" t="n"/>
       <c r="M40" s="4" t="n"/>
-      <c r="N40" s="4" t="n"/>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Arkansas</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -2316,7 +2472,11 @@
       <c r="K41" s="5" t="n"/>
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="4" t="n"/>
-      <c r="N41" s="4" t="n"/>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -2360,7 +2520,11 @@
       <c r="K42" s="5" t="n"/>
       <c r="L42" s="5" t="n"/>
       <c r="M42" s="4" t="n"/>
-      <c r="N42" s="4" t="n"/>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>Ascension Island</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -2404,7 +2568,11 @@
       <c r="K43" s="5" t="n"/>
       <c r="L43" s="5" t="n"/>
       <c r="M43" s="4" t="n"/>
-      <c r="N43" s="4" t="n"/>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Alaska</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -2448,7 +2616,11 @@
       <c r="K44" s="5" t="n"/>
       <c r="L44" s="5" t="n"/>
       <c r="M44" s="4" t="n"/>
-      <c r="N44" s="4" t="n"/>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>Amsterdam and Saint-Paul Islands, French Southern Territories</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -2492,7 +2664,11 @@
       <c r="K45" s="5" t="n"/>
       <c r="L45" s="5" t="n"/>
       <c r="M45" s="4" t="n"/>
-      <c r="N45" s="4" t="n"/>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>Assam state, India</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -2536,7 +2712,11 @@
       <c r="K46" s="5" t="n"/>
       <c r="L46" s="5" t="n"/>
       <c r="M46" s="4" t="n"/>
-      <c r="N46" s="4" t="n"/>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>Manipur state, India</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -2580,7 +2760,11 @@
       <c r="K47" s="5" t="n"/>
       <c r="L47" s="5" t="n"/>
       <c r="M47" s="4" t="n"/>
-      <c r="N47" s="4" t="n"/>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>Meghalaya state, India</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -2624,7 +2808,11 @@
       <c r="K48" s="5" t="n"/>
       <c r="L48" s="5" t="n"/>
       <c r="M48" s="4" t="n"/>
-      <c r="N48" s="4" t="n"/>
+      <c r="N48" s="4" t="inlineStr">
+        <is>
+          <t>Mizoram state, India</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -2668,7 +2856,11 @@
       <c r="K49" s="5" t="n"/>
       <c r="L49" s="5" t="n"/>
       <c r="M49" s="4" t="n"/>
-      <c r="N49" s="4" t="n"/>
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>Nagaland state, India</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -2712,7 +2904,11 @@
       <c r="K50" s="5" t="n"/>
       <c r="L50" s="5" t="n"/>
       <c r="M50" s="4" t="n"/>
-      <c r="N50" s="4" t="n"/>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>Tripura state, India</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -2756,7 +2952,11 @@
       <c r="K51" s="5" t="n"/>
       <c r="L51" s="5" t="n"/>
       <c r="M51" s="4" t="n"/>
-      <c r="N51" s="4" t="n"/>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>Antipodes Islands, New Zealand</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -2800,7 +3000,11 @@
       <c r="K52" s="5" t="n"/>
       <c r="L52" s="5" t="n"/>
       <c r="M52" s="4" t="n"/>
-      <c r="N52" s="4" t="n"/>
+      <c r="N52" s="4" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -2844,7 +3048,11 @@
       <c r="K53" s="5" t="n"/>
       <c r="L53" s="5" t="n"/>
       <c r="M53" s="4" t="n"/>
-      <c r="N53" s="4" t="n"/>
+      <c r="N53" s="4" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -2888,7 +3096,11 @@
       <c r="K54" s="5" t="n"/>
       <c r="L54" s="5" t="n"/>
       <c r="M54" s="4" t="n"/>
-      <c r="N54" s="4" t="n"/>
+      <c r="N54" s="4" t="inlineStr">
+        <is>
+          <t>Azores, Portugal</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -2932,7 +3144,11 @@
       <c r="K55" s="5" t="n"/>
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="4" t="n"/>
-      <c r="N55" s="4" t="n"/>
+      <c r="N55" s="4" t="inlineStr">
+        <is>
+          <t>The Bahamas</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -2976,7 +3192,11 @@
       <c r="K56" s="5" t="n"/>
       <c r="L56" s="5" t="n"/>
       <c r="M56" s="4" t="n"/>
-      <c r="N56" s="4" t="n"/>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
+          <t>Balearic Islands, Spain</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -3020,7 +3240,11 @@
       <c r="K57" s="5" t="n"/>
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="4" t="n"/>
-      <c r="N57" s="4" t="n"/>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -3064,7 +3288,11 @@
       <c r="K58" s="5" t="n"/>
       <c r="L58" s="5" t="n"/>
       <c r="M58" s="4" t="n"/>
-      <c r="N58" s="4" t="n"/>
+      <c r="N58" s="4" t="inlineStr">
+        <is>
+          <t>Benin</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -3108,7 +3336,11 @@
       <c r="K59" s="5" t="n"/>
       <c r="L59" s="5" t="n"/>
       <c r="M59" s="4" t="n"/>
-      <c r="N59" s="4" t="n"/>
+      <c r="N59" s="4" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -3152,7 +3384,11 @@
       <c r="K60" s="5" t="n"/>
       <c r="L60" s="5" t="n"/>
       <c r="M60" s="4" t="n"/>
-      <c r="N60" s="4" t="n"/>
+      <c r="N60" s="4" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -3196,7 +3432,11 @@
       <c r="K61" s="5" t="n"/>
       <c r="L61" s="5" t="n"/>
       <c r="M61" s="4" t="n"/>
-      <c r="N61" s="4" t="n"/>
+      <c r="N61" s="4" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -3240,7 +3480,11 @@
       <c r="K62" s="5" t="n"/>
       <c r="L62" s="5" t="n"/>
       <c r="M62" s="4" t="n"/>
-      <c r="N62" s="4" t="n"/>
+      <c r="N62" s="4" t="inlineStr">
+        <is>
+          <t>Bismarck Archipelago, Papua New Guinea</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -3284,7 +3528,11 @@
       <c r="K63" s="5" t="n"/>
       <c r="L63" s="5" t="n"/>
       <c r="M63" s="4" t="n"/>
-      <c r="N63" s="4" t="n"/>
+      <c r="N63" s="4" t="inlineStr">
+        <is>
+          <t>Burkina Faso</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -3328,7 +3576,11 @@
       <c r="K64" s="5" t="n"/>
       <c r="L64" s="5" t="n"/>
       <c r="M64" s="4" t="n"/>
-      <c r="N64" s="4" t="n"/>
+      <c r="N64" s="4" t="inlineStr">
+        <is>
+          <t>Belarus</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -3372,7 +3624,11 @@
       <c r="K65" s="5" t="n"/>
       <c r="L65" s="5" t="n"/>
       <c r="M65" s="4" t="n"/>
-      <c r="N65" s="4" t="n"/>
+      <c r="N65" s="4" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -3416,7 +3672,11 @@
       <c r="K66" s="5" t="n"/>
       <c r="L66" s="5" t="n"/>
       <c r="M66" s="4" t="n"/>
-      <c r="N66" s="4" t="n"/>
+      <c r="N66" s="4" t="inlineStr">
+        <is>
+          <t>Kaliningrad Oblast, Russia</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -3460,7 +3720,11 @@
       <c r="K67" s="5" t="n"/>
       <c r="L67" s="5" t="n"/>
       <c r="M67" s="4" t="n"/>
-      <c r="N67" s="4" t="n"/>
+      <c r="N67" s="4" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -3504,7 +3768,11 @@
       <c r="K68" s="5" t="n"/>
       <c r="L68" s="5" t="n"/>
       <c r="M68" s="4" t="n"/>
-      <c r="N68" s="4" t="n"/>
+      <c r="N68" s="4" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -3548,7 +3816,11 @@
       <c r="K69" s="5" t="n"/>
       <c r="L69" s="5" t="n"/>
       <c r="M69" s="4" t="n"/>
-      <c r="N69" s="4" t="n"/>
+      <c r="N69" s="4" t="inlineStr">
+        <is>
+          <t>Belize</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -3592,7 +3864,11 @@
       <c r="K70" s="5" t="n"/>
       <c r="L70" s="5" t="n"/>
       <c r="M70" s="4" t="n"/>
-      <c r="N70" s="4" t="n"/>
+      <c r="N70" s="4" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -3636,7 +3912,11 @@
       <c r="K71" s="5" t="n"/>
       <c r="L71" s="5" t="n"/>
       <c r="M71" s="4" t="n"/>
-      <c r="N71" s="4" t="n"/>
+      <c r="N71" s="4" t="inlineStr">
+        <is>
+          <t>Brunei, on the island of Borneo</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -3680,7 +3960,11 @@
       <c r="K72" s="5" t="n"/>
       <c r="L72" s="5" t="n"/>
       <c r="M72" s="4" t="n"/>
-      <c r="N72" s="4" t="n"/>
+      <c r="N72" s="4" t="inlineStr">
+        <is>
+          <t>Kalimantan, Indonesian Borneo</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -3724,7 +4008,11 @@
       <c r="K73" s="5" t="n"/>
       <c r="L73" s="5" t="n"/>
       <c r="M73" s="4" t="n"/>
-      <c r="N73" s="4" t="n"/>
+      <c r="N73" s="4" t="inlineStr">
+        <is>
+          <t>Sabah state, Malaysian Borneo</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -3768,7 +4056,11 @@
       <c r="K74" s="5" t="n"/>
       <c r="L74" s="5" t="n"/>
       <c r="M74" s="4" t="n"/>
-      <c r="N74" s="4" t="n"/>
+      <c r="N74" s="4" t="inlineStr">
+        <is>
+          <t>Sarawak state, Malaysian Borneo</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -3812,7 +4104,11 @@
       <c r="K75" s="5" t="n"/>
       <c r="L75" s="5" t="n"/>
       <c r="M75" s="4" t="n"/>
-      <c r="N75" s="4" t="n"/>
+      <c r="N75" s="4" t="inlineStr">
+        <is>
+          <t>Botswana</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -3856,7 +4152,11 @@
       <c r="K76" s="5" t="n"/>
       <c r="L76" s="5" t="n"/>
       <c r="M76" s="4" t="n"/>
-      <c r="N76" s="4" t="n"/>
+      <c r="N76" s="4" t="inlineStr">
+        <is>
+          <t>Bouvet Island, Norwegian sub-Antarctic territory</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -3900,7 +4200,11 @@
       <c r="K77" s="5" t="n"/>
       <c r="L77" s="5" t="n"/>
       <c r="M77" s="4" t="n"/>
-      <c r="N77" s="4" t="n"/>
+      <c r="N77" s="4" t="inlineStr">
+        <is>
+          <t>The Canadian province of British Columbia</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -3944,7 +4248,11 @@
       <c r="K78" s="5" t="n"/>
       <c r="L78" s="5" t="n"/>
       <c r="M78" s="4" t="n"/>
-      <c r="N78" s="4" t="n"/>
+      <c r="N78" s="4" t="inlineStr">
+        <is>
+          <t>Republic of Buryatia, Russia</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
@@ -3988,7 +4296,11 @@
       <c r="K79" s="5" t="n"/>
       <c r="L79" s="5" t="n"/>
       <c r="M79" s="4" t="n"/>
-      <c r="N79" s="4" t="n"/>
+      <c r="N79" s="4" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -4032,7 +4344,11 @@
       <c r="K80" s="5" t="n"/>
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="4" t="n"/>
-      <c r="N80" s="4" t="n"/>
+      <c r="N80" s="4" t="inlineStr">
+        <is>
+          <t>Burundi</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
@@ -4076,7 +4392,11 @@
       <c r="K81" s="5" t="n"/>
       <c r="L81" s="5" t="n"/>
       <c r="M81" s="4" t="n"/>
-      <c r="N81" s="4" t="n"/>
+      <c r="N81" s="4" t="inlineStr">
+        <is>
+          <t>Federal District of Brazil (Brasília)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -4120,7 +4440,11 @@
       <c r="K82" s="5" t="n"/>
       <c r="L82" s="5" t="n"/>
       <c r="M82" s="4" t="n"/>
-      <c r="N82" s="4" t="n"/>
+      <c r="N82" s="4" t="inlineStr">
+        <is>
+          <t>The Brazilian state of Goiás</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -4164,7 +4488,11 @@
       <c r="K83" s="5" t="n"/>
       <c r="L83" s="5" t="n"/>
       <c r="M83" s="4" t="n"/>
-      <c r="N83" s="4" t="n"/>
+      <c r="N83" s="4" t="inlineStr">
+        <is>
+          <t>The Brazilian state of Mato Grosso do Sul</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -4208,7 +4536,11 @@
       <c r="K84" s="5" t="n"/>
       <c r="L84" s="5" t="n"/>
       <c r="M84" s="4" t="n"/>
-      <c r="N84" s="4" t="n"/>
+      <c r="N84" s="4" t="inlineStr">
+        <is>
+          <t>The Brazilian state of Mato Grosso</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -4252,7 +4584,11 @@
       <c r="K85" s="5" t="n"/>
       <c r="L85" s="5" t="n"/>
       <c r="M85" s="4" t="n"/>
-      <c r="N85" s="4" t="n"/>
+      <c r="N85" s="4" t="inlineStr">
+        <is>
+          <t>The Brazilian state of Alagoas</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -4296,7 +4632,11 @@
       <c r="K86" s="5" t="n"/>
       <c r="L86" s="5" t="n"/>
       <c r="M86" s="4" t="n"/>
-      <c r="N86" s="4" t="n"/>
+      <c r="N86" s="4" t="inlineStr">
+        <is>
+          <t>The Brazilian state of Bahia</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -4340,7 +4680,11 @@
       <c r="K87" s="5" t="n"/>
       <c r="L87" s="5" t="n"/>
       <c r="M87" s="4" t="n"/>
-      <c r="N87" s="4" t="n"/>
+      <c r="N87" s="4" t="inlineStr">
+        <is>
+          <t>The Brazilian state of Ceará</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -4384,7 +4728,11 @@
       <c r="K88" s="5" t="n"/>
       <c r="L88" s="5" t="n"/>
       <c r="M88" s="4" t="n"/>
-      <c r="N88" s="4" t="n"/>
+      <c r="N88" s="4" t="inlineStr">
+        <is>
+          <t>Fernando de Noronha archipelago, Brazil</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -4428,7 +4776,11 @@
       <c r="K89" s="5" t="n"/>
       <c r="L89" s="5" t="n"/>
       <c r="M89" s="4" t="n"/>
-      <c r="N89" s="4" t="n"/>
+      <c r="N89" s="4" t="inlineStr">
+        <is>
+          <t>The Brazilian state of Maranhão</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -4472,7 +4824,11 @@
       <c r="K90" s="5" t="n"/>
       <c r="L90" s="5" t="n"/>
       <c r="M90" s="4" t="n"/>
-      <c r="N90" s="4" t="n"/>
+      <c r="N90" s="4" t="inlineStr">
+        <is>
+          <t>The Brazilian state of Paraíba</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
@@ -4516,7 +4872,11 @@
       <c r="K91" s="5" t="n"/>
       <c r="L91" s="5" t="n"/>
       <c r="M91" s="4" t="n"/>
-      <c r="N91" s="4" t="n"/>
+      <c r="N91" s="4" t="inlineStr">
+        <is>
+          <t>The Brazilian state of Pernambuco</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -4560,7 +4920,11 @@
       <c r="K92" s="5" t="n"/>
       <c r="L92" s="5" t="n"/>
       <c r="M92" s="4" t="n"/>
-      <c r="N92" s="4" t="n"/>
+      <c r="N92" s="4" t="inlineStr">
+        <is>
+          <t>The Brazilian state of Piauí</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
@@ -4604,7 +4968,11 @@
       <c r="K93" s="5" t="n"/>
       <c r="L93" s="5" t="n"/>
       <c r="M93" s="4" t="n"/>
-      <c r="N93" s="4" t="n"/>
+      <c r="N93" s="4" t="inlineStr">
+        <is>
+          <t>The Brazilian state of Rio Grande do Norte</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
@@ -4648,7 +5016,11 @@
       <c r="K94" s="5" t="n"/>
       <c r="L94" s="5" t="n"/>
       <c r="M94" s="4" t="n"/>
-      <c r="N94" s="4" t="n"/>
+      <c r="N94" s="4" t="inlineStr">
+        <is>
+          <t>The Brazilian state of Sergipe</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
@@ -4692,7 +5064,11 @@
       <c r="K95" s="5" t="n"/>
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="4" t="n"/>
-      <c r="N95" s="4" t="n"/>
+      <c r="N95" s="4" t="inlineStr">
+        <is>
+          <t>The Brazilian state of Espírito Santo</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
@@ -4736,7 +5112,11 @@
       <c r="K96" s="5" t="n"/>
       <c r="L96" s="5" t="n"/>
       <c r="M96" s="4" t="n"/>
-      <c r="N96" s="4" t="n"/>
+      <c r="N96" s="4" t="inlineStr">
+        <is>
+          <t>The Brazilian state of Minas Gerais</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
@@ -4780,7 +5160,11 @@
       <c r="K97" s="5" t="n"/>
       <c r="L97" s="5" t="n"/>
       <c r="M97" s="4" t="n"/>
-      <c r="N97" s="4" t="n"/>
+      <c r="N97" s="4" t="inlineStr">
+        <is>
+          <t>The Brazilian state of Rio de Janeiro</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
@@ -4824,7 +5208,11 @@
       <c r="K98" s="5" t="n"/>
       <c r="L98" s="5" t="n"/>
       <c r="M98" s="4" t="n"/>
-      <c r="N98" s="4" t="n"/>
+      <c r="N98" s="4" t="inlineStr">
+        <is>
+          <t>The Brazilian state of São Paulo</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
@@ -4868,7 +5256,11 @@
       <c r="K99" s="5" t="n"/>
       <c r="L99" s="5" t="n"/>
       <c r="M99" s="4" t="n"/>
-      <c r="N99" s="4" t="n"/>
+      <c r="N99" s="4" t="inlineStr">
+        <is>
+          <t>Trindade Island, off Espírito Santo, Brazil</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
@@ -4912,7 +5304,11 @@
       <c r="K100" s="5" t="n"/>
       <c r="L100" s="5" t="n"/>
       <c r="M100" s="4" t="n"/>
-      <c r="N100" s="4" t="n"/>
+      <c r="N100" s="4" t="inlineStr">
+        <is>
+          <t>The Brazilian state of Acre</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
@@ -4956,7 +5352,11 @@
       <c r="K101" s="5" t="n"/>
       <c r="L101" s="5" t="n"/>
       <c r="M101" s="4" t="n"/>
-      <c r="N101" s="4" t="n"/>
+      <c r="N101" s="4" t="inlineStr">
+        <is>
+          <t>The Brazilian state of Amazonas</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
@@ -5000,7 +5400,11 @@
       <c r="K102" s="5" t="n"/>
       <c r="L102" s="5" t="n"/>
       <c r="M102" s="4" t="n"/>
-      <c r="N102" s="4" t="n"/>
+      <c r="N102" s="4" t="inlineStr">
+        <is>
+          <t>The Brazilian state of Amapá</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
@@ -5044,7 +5448,11 @@
       <c r="K103" s="5" t="n"/>
       <c r="L103" s="5" t="n"/>
       <c r="M103" s="4" t="n"/>
-      <c r="N103" s="4" t="n"/>
+      <c r="N103" s="4" t="inlineStr">
+        <is>
+          <t>The Brazilian state of Pará</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -5088,7 +5496,11 @@
       <c r="K104" s="5" t="n"/>
       <c r="L104" s="5" t="n"/>
       <c r="M104" s="4" t="n"/>
-      <c r="N104" s="4" t="n"/>
+      <c r="N104" s="4" t="inlineStr">
+        <is>
+          <t>The Brazilian state of Roraima</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
@@ -5132,7 +5544,11 @@
       <c r="K105" s="5" t="n"/>
       <c r="L105" s="5" t="n"/>
       <c r="M105" s="4" t="n"/>
-      <c r="N105" s="4" t="n"/>
+      <c r="N105" s="4" t="inlineStr">
+        <is>
+          <t>The Brazilian state of Rondônia</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
@@ -5176,7 +5592,11 @@
       <c r="K106" s="5" t="n"/>
       <c r="L106" s="5" t="n"/>
       <c r="M106" s="4" t="n"/>
-      <c r="N106" s="4" t="n"/>
+      <c r="N106" s="4" t="inlineStr">
+        <is>
+          <t>The Brazilian state of Tocantins</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
@@ -5220,7 +5640,11 @@
       <c r="K107" s="5" t="n"/>
       <c r="L107" s="5" t="n"/>
       <c r="M107" s="4" t="n"/>
-      <c r="N107" s="4" t="n"/>
+      <c r="N107" s="4" t="inlineStr">
+        <is>
+          <t>The Brazilian state of Paraná</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
@@ -5264,7 +5688,11 @@
       <c r="K108" s="5" t="n"/>
       <c r="L108" s="5" t="n"/>
       <c r="M108" s="4" t="n"/>
-      <c r="N108" s="4" t="n"/>
+      <c r="N108" s="4" t="inlineStr">
+        <is>
+          <t>The Brazilian state of Rio Grande do Sul</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
@@ -5308,7 +5736,11 @@
       <c r="K109" s="5" t="n"/>
       <c r="L109" s="5" t="n"/>
       <c r="M109" s="4" t="n"/>
-      <c r="N109" s="4" t="n"/>
+      <c r="N109" s="4" t="inlineStr">
+        <is>
+          <t>The Brazilian state of Santa Catarina</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
@@ -5352,7 +5784,11 @@
       <c r="K110" s="5" t="n"/>
       <c r="L110" s="5" t="n"/>
       <c r="M110" s="4" t="n"/>
-      <c r="N110" s="4" t="n"/>
+      <c r="N110" s="4" t="inlineStr">
+        <is>
+          <t>Cabinda, an Angolan exclave province</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
@@ -5396,7 +5832,11 @@
       <c r="K111" s="5" t="n"/>
       <c r="L111" s="5" t="n"/>
       <c r="M111" s="4" t="n"/>
-      <c r="N111" s="4" t="n"/>
+      <c r="N111" s="4" t="inlineStr">
+        <is>
+          <t>Central African Republic</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
@@ -5440,7 +5880,11 @@
       <c r="K112" s="5" t="n"/>
       <c r="L112" s="5" t="n"/>
       <c r="M112" s="4" t="n"/>
-      <c r="N112" s="4" t="n"/>
+      <c r="N112" s="4" t="inlineStr">
+        <is>
+          <t>California, USA</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
@@ -5484,7 +5928,11 @@
       <c r="K113" s="5" t="n"/>
       <c r="L113" s="5" t="n"/>
       <c r="M113" s="4" t="n"/>
-      <c r="N113" s="4" t="n"/>
+      <c r="N113" s="4" t="inlineStr">
+        <is>
+          <t>The Cayman Islands</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
@@ -5528,7 +5976,11 @@
       <c r="K114" s="5" t="n"/>
       <c r="L114" s="5" t="n"/>
       <c r="M114" s="4" t="n"/>
-      <c r="N114" s="4" t="n"/>
+      <c r="N114" s="4" t="inlineStr">
+        <is>
+          <t>Cambodia</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
@@ -5572,7 +6024,11 @@
       <c r="K115" s="5" t="n"/>
       <c r="L115" s="5" t="n"/>
       <c r="M115" s="4" t="n"/>
-      <c r="N115" s="4" t="n"/>
+      <c r="N115" s="4" t="inlineStr">
+        <is>
+          <t>Chagos Archipelago, British Indian Ocean Territory</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
@@ -5616,7 +6072,11 @@
       <c r="K116" s="5" t="n"/>
       <c r="L116" s="5" t="n"/>
       <c r="M116" s="4" t="n"/>
-      <c r="N116" s="4" t="n"/>
+      <c r="N116" s="4" t="inlineStr">
+        <is>
+          <t>Chad</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
@@ -5664,7 +6124,11 @@
         </is>
       </c>
       <c r="M117" s="4" t="n"/>
-      <c r="N117" s="4" t="n"/>
+      <c r="N117" s="4" t="inlineStr">
+        <is>
+          <t>Chongqing municipality, China</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
@@ -5708,7 +6172,11 @@
       <c r="K118" s="5" t="n"/>
       <c r="L118" s="5" t="n"/>
       <c r="M118" s="4" t="n"/>
-      <c r="N118" s="4" t="n"/>
+      <c r="N118" s="4" t="inlineStr">
+        <is>
+          <t>Guizhou province, China</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
@@ -5752,7 +6220,11 @@
       <c r="K119" s="5" t="n"/>
       <c r="L119" s="5" t="n"/>
       <c r="M119" s="4" t="n"/>
-      <c r="N119" s="4" t="n"/>
+      <c r="N119" s="4" t="inlineStr">
+        <is>
+          <t>Hubei province, China</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
@@ -5796,7 +6268,11 @@
       <c r="K120" s="5" t="n"/>
       <c r="L120" s="5" t="n"/>
       <c r="M120" s="4" t="n"/>
-      <c r="N120" s="4" t="n"/>
+      <c r="N120" s="4" t="inlineStr">
+        <is>
+          <t>Sichuan province, China</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
@@ -5840,7 +6316,11 @@
       <c r="K121" s="5" t="n"/>
       <c r="L121" s="5" t="n"/>
       <c r="M121" s="4" t="n"/>
-      <c r="N121" s="4" t="n"/>
+      <c r="N121" s="4" t="inlineStr">
+        <is>
+          <t>Yunnan province, China</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
@@ -5884,7 +6364,11 @@
       <c r="K122" s="5" t="n"/>
       <c r="L122" s="5" t="n"/>
       <c r="M122" s="4" t="n"/>
-      <c r="N122" s="4" t="n"/>
+      <c r="N122" s="4" t="inlineStr">
+        <is>
+          <t>Hainan province, China</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
@@ -5941,7 +6425,11 @@
 https://en.wikipedia.org/wiki/Jilin</t>
         </is>
       </c>
-      <c r="N123" s="4" t="n"/>
+      <c r="N123" s="4" t="inlineStr">
+        <is>
+          <t>Inner Mongolia autonomous region, China</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
@@ -5985,7 +6473,11 @@
       <c r="K124" s="5" t="n"/>
       <c r="L124" s="5" t="n"/>
       <c r="M124" s="4" t="n"/>
-      <c r="N124" s="4" t="n"/>
+      <c r="N124" s="4" t="inlineStr">
+        <is>
+          <t>Ningxia Hui autonomous region, China</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
@@ -6041,7 +6533,11 @@
           <t>Incorrect digitalization between Inner Mongolia and Heilongjiang Map 6/7, pg 115/116</t>
         </is>
       </c>
-      <c r="N125" s="4" t="n"/>
+      <c r="N125" s="4" t="inlineStr">
+        <is>
+          <t>Heilongjiang province, China</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
@@ -6098,7 +6594,11 @@
 https://en.wikipedia.org/wiki/Jilin</t>
         </is>
       </c>
-      <c r="N126" s="4" t="n"/>
+      <c r="N126" s="4" t="inlineStr">
+        <is>
+          <t>Jilin province, China</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
@@ -6154,7 +6654,11 @@
           <t>Incorrect digitalization between Inner Mongolia and Liaoning. https://en.wikipedia.org/wiki/Liaoning</t>
         </is>
       </c>
-      <c r="N127" s="4" t="n"/>
+      <c r="N127" s="4" t="inlineStr">
+        <is>
+          <t>Liaoning province, China</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
@@ -6198,7 +6702,11 @@
       <c r="K128" s="5" t="n"/>
       <c r="L128" s="5" t="n"/>
       <c r="M128" s="4" t="n"/>
-      <c r="N128" s="4" t="n"/>
+      <c r="N128" s="4" t="inlineStr">
+        <is>
+          <t>Beijing municipality, China</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
@@ -6242,7 +6750,11 @@
       <c r="K129" s="5" t="n"/>
       <c r="L129" s="5" t="n"/>
       <c r="M129" s="4" t="n"/>
-      <c r="N129" s="4" t="n"/>
+      <c r="N129" s="4" t="inlineStr">
+        <is>
+          <t>Gansu province, China</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
@@ -6299,7 +6811,11 @@
 https://en.wikipedia.org/wiki/Henan</t>
         </is>
       </c>
-      <c r="N130" s="4" t="n"/>
+      <c r="N130" s="4" t="inlineStr">
+        <is>
+          <t>Hebei province, China</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
@@ -6343,7 +6859,11 @@
       <c r="K131" s="5" t="n"/>
       <c r="L131" s="5" t="n"/>
       <c r="M131" s="4" t="n"/>
-      <c r="N131" s="4" t="n"/>
+      <c r="N131" s="4" t="inlineStr">
+        <is>
+          <t>Shaanxi province, China</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
@@ -6387,7 +6907,11 @@
       <c r="K132" s="5" t="n"/>
       <c r="L132" s="5" t="n"/>
       <c r="M132" s="4" t="n"/>
-      <c r="N132" s="4" t="n"/>
+      <c r="N132" s="4" t="inlineStr">
+        <is>
+          <t>Shandong province, China</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
@@ -6431,7 +6955,11 @@
       <c r="K133" s="5" t="n"/>
       <c r="L133" s="5" t="n"/>
       <c r="M133" s="4" t="n"/>
-      <c r="N133" s="4" t="n"/>
+      <c r="N133" s="4" t="inlineStr">
+        <is>
+          <t>Shanxi province, China</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
@@ -6475,7 +7003,11 @@
       <c r="K134" s="5" t="n"/>
       <c r="L134" s="5" t="n"/>
       <c r="M134" s="4" t="n"/>
-      <c r="N134" s="4" t="n"/>
+      <c r="N134" s="4" t="inlineStr">
+        <is>
+          <t>Tianjin municipality, China</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
@@ -6519,7 +7051,11 @@
       <c r="K135" s="5" t="n"/>
       <c r="L135" s="5" t="n"/>
       <c r="M135" s="4" t="n"/>
-      <c r="N135" s="4" t="n"/>
+      <c r="N135" s="4" t="inlineStr">
+        <is>
+          <t>Qinghai province, China</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
@@ -6563,7 +7099,11 @@
       <c r="K136" s="5" t="n"/>
       <c r="L136" s="5" t="n"/>
       <c r="M136" s="4" t="n"/>
-      <c r="N136" s="4" t="n"/>
+      <c r="N136" s="4" t="inlineStr">
+        <is>
+          <t>Anhui province, China</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
@@ -6607,7 +7147,11 @@
       <c r="K137" s="5" t="n"/>
       <c r="L137" s="5" t="n"/>
       <c r="M137" s="4" t="n"/>
-      <c r="N137" s="4" t="n"/>
+      <c r="N137" s="4" t="inlineStr">
+        <is>
+          <t>Fujian province, China</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
@@ -6651,7 +7195,11 @@
       <c r="K138" s="5" t="n"/>
       <c r="L138" s="5" t="n"/>
       <c r="M138" s="4" t="n"/>
-      <c r="N138" s="4" t="n"/>
+      <c r="N138" s="4" t="inlineStr">
+        <is>
+          <t>Guangdong province, China</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
@@ -6695,7 +7243,11 @@
       <c r="K139" s="5" t="n"/>
       <c r="L139" s="5" t="n"/>
       <c r="M139" s="4" t="n"/>
-      <c r="N139" s="4" t="n"/>
+      <c r="N139" s="4" t="inlineStr">
+        <is>
+          <t>Guangxi Zhuang autonomous region, China</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
@@ -6752,7 +7304,11 @@
 https://en.wikipedia.org/wiki/Henan</t>
         </is>
       </c>
-      <c r="N140" s="4" t="n"/>
+      <c r="N140" s="4" t="inlineStr">
+        <is>
+          <t>Henan province, China</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
@@ -6796,7 +7352,11 @@
       <c r="K141" s="5" t="n"/>
       <c r="L141" s="5" t="n"/>
       <c r="M141" s="4" t="n"/>
-      <c r="N141" s="4" t="n"/>
+      <c r="N141" s="4" t="inlineStr">
+        <is>
+          <t>Hong Kong Special Administrative Region</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
@@ -6840,7 +7400,11 @@
       <c r="K142" s="5" t="n"/>
       <c r="L142" s="5" t="n"/>
       <c r="M142" s="4" t="n"/>
-      <c r="N142" s="4" t="n"/>
+      <c r="N142" s="4" t="inlineStr">
+        <is>
+          <t>Hunan province, China</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
@@ -6884,7 +7448,11 @@
       <c r="K143" s="5" t="n"/>
       <c r="L143" s="5" t="n"/>
       <c r="M143" s="4" t="n"/>
-      <c r="N143" s="4" t="n"/>
+      <c r="N143" s="4" t="inlineStr">
+        <is>
+          <t>Jiangsu province, China</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
@@ -6928,7 +7496,11 @@
       <c r="K144" s="5" t="n"/>
       <c r="L144" s="5" t="n"/>
       <c r="M144" s="4" t="n"/>
-      <c r="N144" s="4" t="n"/>
+      <c r="N144" s="4" t="inlineStr">
+        <is>
+          <t>Jiangxi province, China</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
@@ -6972,7 +7544,11 @@
       <c r="K145" s="5" t="n"/>
       <c r="L145" s="5" t="n"/>
       <c r="M145" s="4" t="n"/>
-      <c r="N145" s="4" t="n"/>
+      <c r="N145" s="4" t="inlineStr">
+        <is>
+          <t>Kinmen (Quemoy) Islands, Taiwan</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
@@ -7016,7 +7592,11 @@
       <c r="K146" s="5" t="n"/>
       <c r="L146" s="5" t="n"/>
       <c r="M146" s="4" t="n"/>
-      <c r="N146" s="4" t="n"/>
+      <c r="N146" s="4" t="inlineStr">
+        <is>
+          <t>Macau Special Administrative Region</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
@@ -7060,7 +7640,11 @@
       <c r="K147" s="5" t="n"/>
       <c r="L147" s="5" t="n"/>
       <c r="M147" s="4" t="n"/>
-      <c r="N147" s="4" t="n"/>
+      <c r="N147" s="4" t="inlineStr">
+        <is>
+          <t>Matsu (Mazu) Islands, Taiwan</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
@@ -7104,7 +7688,11 @@
       <c r="K148" s="5" t="n"/>
       <c r="L148" s="5" t="n"/>
       <c r="M148" s="4" t="n"/>
-      <c r="N148" s="4" t="n"/>
+      <c r="N148" s="4" t="inlineStr">
+        <is>
+          <t>Shanghai municipality, China</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
@@ -7148,7 +7736,11 @@
       <c r="K149" s="5" t="n"/>
       <c r="L149" s="5" t="n"/>
       <c r="M149" s="4" t="n"/>
-      <c r="N149" s="4" t="n"/>
+      <c r="N149" s="4" t="inlineStr">
+        <is>
+          <t>Zhejiang province, China</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
@@ -7192,7 +7784,11 @@
       <c r="K150" s="5" t="n"/>
       <c r="L150" s="5" t="n"/>
       <c r="M150" s="4" t="n"/>
-      <c r="N150" s="4" t="n"/>
+      <c r="N150" s="4" t="inlineStr">
+        <is>
+          <t>Tibet Autonomous Region, China</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
@@ -7236,7 +7832,11 @@
       <c r="K151" s="5" t="n"/>
       <c r="L151" s="5" t="n"/>
       <c r="M151" s="4" t="n"/>
-      <c r="N151" s="4" t="n"/>
+      <c r="N151" s="4" t="inlineStr">
+        <is>
+          <t>Xinjiang Uyghur Autonomous Region, China</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
@@ -7280,7 +7880,11 @@
       <c r="K152" s="5" t="n"/>
       <c r="L152" s="5" t="n"/>
       <c r="M152" s="4" t="n"/>
-      <c r="N152" s="4" t="n"/>
+      <c r="N152" s="4" t="inlineStr">
+        <is>
+          <t>The Cocos (Keeling) Islands</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
@@ -7332,7 +7936,11 @@
         </is>
       </c>
       <c r="M153" s="4" t="n"/>
-      <c r="N153" s="4" t="n"/>
+      <c r="N153" s="4" t="inlineStr">
+        <is>
+          <t>Biobío region, Chile</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
@@ -7376,7 +7984,11 @@
       <c r="K154" s="5" t="n"/>
       <c r="L154" s="5" t="n"/>
       <c r="M154" s="4" t="n"/>
-      <c r="N154" s="4" t="n"/>
+      <c r="N154" s="4" t="inlineStr">
+        <is>
+          <t>Coquimbo region, Chile</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
@@ -7420,7 +8032,11 @@
       <c r="K155" s="5" t="n"/>
       <c r="L155" s="5" t="n"/>
       <c r="M155" s="4" t="n"/>
-      <c r="N155" s="4" t="n"/>
+      <c r="N155" s="4" t="inlineStr">
+        <is>
+          <t>La Araucanía region, Chile</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
@@ -7464,7 +8080,11 @@
       <c r="K156" s="5" t="n"/>
       <c r="L156" s="5" t="n"/>
       <c r="M156" s="4" t="n"/>
-      <c r="N156" s="4" t="n"/>
+      <c r="N156" s="4" t="inlineStr">
+        <is>
+          <t>Maule region, Chile</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
@@ -7516,7 +8136,11 @@
         </is>
       </c>
       <c r="M157" s="4" t="n"/>
-      <c r="N157" s="4" t="n"/>
+      <c r="N157" s="4" t="inlineStr">
+        <is>
+          <t>Ñuble region, Chile</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
@@ -7560,7 +8184,11 @@
       <c r="K158" s="5" t="n"/>
       <c r="L158" s="5" t="n"/>
       <c r="M158" s="4" t="n"/>
-      <c r="N158" s="4" t="n"/>
+      <c r="N158" s="4" t="inlineStr">
+        <is>
+          <t>O'Higgins Region, central Chile</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
@@ -7604,7 +8232,11 @@
       <c r="K159" s="5" t="n"/>
       <c r="L159" s="5" t="n"/>
       <c r="M159" s="4" t="n"/>
-      <c r="N159" s="4" t="n"/>
+      <c r="N159" s="4" t="inlineStr">
+        <is>
+          <t>Santiago Metropolitan Region, Chile</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
@@ -7648,7 +8280,11 @@
       <c r="K160" s="5" t="n"/>
       <c r="L160" s="5" t="n"/>
       <c r="M160" s="4" t="n"/>
-      <c r="N160" s="4" t="n"/>
+      <c r="N160" s="4" t="inlineStr">
+        <is>
+          <t>Valparaíso Region, Chile</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
@@ -7692,7 +8328,11 @@
       <c r="K161" s="5" t="n"/>
       <c r="L161" s="5" t="n"/>
       <c r="M161" s="4" t="n"/>
-      <c r="N161" s="4" t="n"/>
+      <c r="N161" s="4" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
@@ -7736,7 +8376,11 @@
       <c r="K162" s="5" t="n"/>
       <c r="L162" s="5" t="n"/>
       <c r="M162" s="4" t="n"/>
-      <c r="N162" s="4" t="n"/>
+      <c r="N162" s="4" t="inlineStr">
+        <is>
+          <t>Antofagasta Region, northern Chile</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
@@ -7780,7 +8424,11 @@
       <c r="K163" s="5" t="n"/>
       <c r="L163" s="5" t="n"/>
       <c r="M163" s="4" t="n"/>
-      <c r="N163" s="4" t="n"/>
+      <c r="N163" s="4" t="inlineStr">
+        <is>
+          <t>Atacama Region, northern Chile</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
@@ -7836,7 +8484,11 @@
           <t>Added level 4 Arica and Parinacota Region to Chile (is region 15 in the very north)</t>
         </is>
       </c>
-      <c r="N164" s="4" t="n"/>
+      <c r="N164" s="4" t="inlineStr">
+        <is>
+          <t>Tarapacá Region, northern Chile</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
@@ -7880,7 +8532,11 @@
       <c r="K165" s="5" t="n"/>
       <c r="L165" s="5" t="n"/>
       <c r="M165" s="4" t="n"/>
-      <c r="N165" s="4" t="n"/>
+      <c r="N165" s="4" t="inlineStr">
+        <is>
+          <t>Aysén Region, southern Chile</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
@@ -7924,7 +8580,11 @@
       <c r="K166" s="5" t="n"/>
       <c r="L166" s="5" t="n"/>
       <c r="M166" s="4" t="n"/>
-      <c r="N166" s="4" t="n"/>
+      <c r="N166" s="4" t="inlineStr">
+        <is>
+          <t>Los Lagos Region, southern Chile</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
@@ -7968,7 +8628,11 @@
       <c r="K167" s="5" t="n"/>
       <c r="L167" s="5" t="n"/>
       <c r="M167" s="4" t="n"/>
-      <c r="N167" s="4" t="n"/>
+      <c r="N167" s="4" t="inlineStr">
+        <is>
+          <t>Magallanes Region, southern Chile</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
@@ -8012,7 +8676,11 @@
       <c r="K168" s="5" t="n"/>
       <c r="L168" s="5" t="n"/>
       <c r="M168" s="4" t="n"/>
-      <c r="N168" s="4" t="n"/>
+      <c r="N168" s="4" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
@@ -8056,7 +8724,11 @@
       <c r="K169" s="5" t="n"/>
       <c r="L169" s="5" t="n"/>
       <c r="M169" s="4" t="n"/>
-      <c r="N169" s="4" t="n"/>
+      <c r="N169" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Connecticut</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
@@ -8100,7 +8772,11 @@
       <c r="K170" s="5" t="n"/>
       <c r="L170" s="5" t="n"/>
       <c r="M170" s="4" t="n"/>
-      <c r="N170" s="4" t="n"/>
+      <c r="N170" s="4" t="inlineStr">
+        <is>
+          <t>Canary Islands, Spain</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
@@ -8144,7 +8820,11 @@
       <c r="K171" s="5" t="n"/>
       <c r="L171" s="5" t="n"/>
       <c r="M171" s="4" t="n"/>
-      <c r="N171" s="4" t="n"/>
+      <c r="N171" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Colorado</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
@@ -8188,7 +8868,11 @@
       <c r="K172" s="5" t="n"/>
       <c r="L172" s="5" t="n"/>
       <c r="M172" s="4" t="n"/>
-      <c r="N172" s="4" t="n"/>
+      <c r="N172" s="4" t="inlineStr">
+        <is>
+          <t>Comoros</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
@@ -8232,7 +8916,11 @@
       <c r="K173" s="5" t="n"/>
       <c r="L173" s="5" t="n"/>
       <c r="M173" s="4" t="n"/>
-      <c r="N173" s="4" t="n"/>
+      <c r="N173" s="4" t="inlineStr">
+        <is>
+          <t>Mayotte, French territory near the Comoros</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
@@ -8276,7 +8964,11 @@
       <c r="K174" s="5" t="n"/>
       <c r="L174" s="5" t="n"/>
       <c r="M174" s="4" t="n"/>
-      <c r="N174" s="4" t="n"/>
+      <c r="N174" s="4" t="inlineStr">
+        <is>
+          <t>Republic of the Congo</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
@@ -8320,7 +9012,11 @@
       <c r="K175" s="5" t="n"/>
       <c r="L175" s="5" t="n"/>
       <c r="M175" s="4" t="n"/>
-      <c r="N175" s="4" t="n"/>
+      <c r="N175" s="4" t="inlineStr">
+        <is>
+          <t>Cook Islands</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
@@ -8364,7 +9060,11 @@
       <c r="K176" s="5" t="n"/>
       <c r="L176" s="5" t="n"/>
       <c r="M176" s="4" t="n"/>
-      <c r="N176" s="4" t="n"/>
+      <c r="N176" s="4" t="inlineStr">
+        <is>
+          <t>Corsica, France</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
@@ -8408,7 +9108,11 @@
       <c r="K177" s="5" t="n"/>
       <c r="L177" s="5" t="n"/>
       <c r="M177" s="4" t="n"/>
-      <c r="N177" s="4" t="n"/>
+      <c r="N177" s="4" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
@@ -8452,7 +9156,11 @@
       <c r="K178" s="5" t="n"/>
       <c r="L178" s="5" t="n"/>
       <c r="M178" s="4" t="n"/>
-      <c r="N178" s="4" t="n"/>
+      <c r="N178" s="4" t="inlineStr">
+        <is>
+          <t>Clipperton Island, French Pacific territory</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
@@ -8496,7 +9204,11 @@
       <c r="K179" s="5" t="n"/>
       <c r="L179" s="5" t="n"/>
       <c r="M179" s="4" t="n"/>
-      <c r="N179" s="4" t="n"/>
+      <c r="N179" s="4" t="inlineStr">
+        <is>
+          <t>Cocos Island, Costa Rica</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
@@ -8540,7 +9252,11 @@
       <c r="K180" s="5" t="n"/>
       <c r="L180" s="5" t="n"/>
       <c r="M180" s="4" t="n"/>
-      <c r="N180" s="4" t="n"/>
+      <c r="N180" s="4" t="inlineStr">
+        <is>
+          <t>Malpelo Island, Colombia</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
@@ -8584,7 +9300,11 @@
       <c r="K181" s="5" t="n"/>
       <c r="L181" s="5" t="n"/>
       <c r="M181" s="4" t="n"/>
-      <c r="N181" s="4" t="n"/>
+      <c r="N181" s="4" t="inlineStr">
+        <is>
+          <t>Eastern Cape Province, South Africa</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
@@ -8628,7 +9348,11 @@
       <c r="K182" s="5" t="n"/>
       <c r="L182" s="5" t="n"/>
       <c r="M182" s="4" t="n"/>
-      <c r="N182" s="4" t="n"/>
+      <c r="N182" s="4" t="inlineStr">
+        <is>
+          <t>Northern Cape Province, South Africa</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
@@ -8672,7 +9396,11 @@
       <c r="K183" s="5" t="n"/>
       <c r="L183" s="5" t="n"/>
       <c r="M183" s="4" t="n"/>
-      <c r="N183" s="4" t="n"/>
+      <c r="N183" s="4" t="inlineStr">
+        <is>
+          <t>Western Cape Province, South Africa</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
@@ -8716,7 +9444,11 @@
       <c r="K184" s="5" t="n"/>
       <c r="L184" s="5" t="n"/>
       <c r="M184" s="4" t="n"/>
-      <c r="N184" s="4" t="n"/>
+      <c r="N184" s="4" t="inlineStr">
+        <is>
+          <t>Caprivi Strip, Namibia</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
@@ -8760,7 +9492,11 @@
       <c r="K185" s="5" t="n"/>
       <c r="L185" s="5" t="n"/>
       <c r="M185" s="4" t="n"/>
-      <c r="N185" s="4" t="n"/>
+      <c r="N185" s="4" t="inlineStr">
+        <is>
+          <t>Federated States of Micronesia</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
@@ -8804,7 +9540,11 @@
       <c r="K186" s="5" t="n"/>
       <c r="L186" s="5" t="n"/>
       <c r="M186" s="4" t="n"/>
-      <c r="N186" s="4" t="n"/>
+      <c r="N186" s="4" t="inlineStr">
+        <is>
+          <t>Palau</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
@@ -8848,7 +9588,11 @@
       <c r="K187" s="5" t="n"/>
       <c r="L187" s="5" t="n"/>
       <c r="M187" s="4" t="n"/>
-      <c r="N187" s="4" t="n"/>
+      <c r="N187" s="4" t="inlineStr">
+        <is>
+          <t>Crozet Islands, French Southern Territories</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
@@ -8900,7 +9644,11 @@
           <t>Named Chita in previous edition</t>
         </is>
       </c>
-      <c r="N188" s="4" t="n"/>
+      <c r="N188" s="4" t="inlineStr">
+        <is>
+          <t>Zabaykalsky Krai, Russia (Transbaikal region)</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
@@ -8944,7 +9692,11 @@
       <c r="K189" s="5" t="n"/>
       <c r="L189" s="5" t="n"/>
       <c r="M189" s="4" t="n"/>
-      <c r="N189" s="4" t="n"/>
+      <c r="N189" s="4" t="inlineStr">
+        <is>
+          <t>Chatham Islands, New Zealand</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
@@ -8988,7 +9740,11 @@
       <c r="K190" s="5" t="n"/>
       <c r="L190" s="5" t="n"/>
       <c r="M190" s="4" t="n"/>
-      <c r="N190" s="4" t="n"/>
+      <c r="N190" s="4" t="inlineStr">
+        <is>
+          <t>Cuba</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
@@ -9032,7 +9788,11 @@
       <c r="K191" s="5" t="n"/>
       <c r="L191" s="5" t="n"/>
       <c r="M191" s="4" t="n"/>
-      <c r="N191" s="4" t="n"/>
+      <c r="N191" s="4" t="inlineStr">
+        <is>
+          <t>Cabo Verde (Cape Verde)</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
@@ -9076,7 +9836,11 @@
       <c r="K192" s="5" t="n"/>
       <c r="L192" s="5" t="n"/>
       <c r="M192" s="4" t="n"/>
-      <c r="N192" s="4" t="n"/>
+      <c r="N192" s="4" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
@@ -9108,7 +9872,7 @@
       </c>
       <c r="H193" s="5" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="I193" s="5" t="n"/>
@@ -9120,7 +9884,11 @@
       <c r="K193" s="5" t="n"/>
       <c r="L193" s="5" t="n"/>
       <c r="M193" s="4" t="n"/>
-      <c r="N193" s="4" t="n"/>
+      <c r="N193" s="4" t="inlineStr">
+        <is>
+          <t>Czechia (Czech Republic)</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
@@ -9152,7 +9920,7 @@
       </c>
       <c r="H194" s="5" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="I194" s="5" t="n"/>
@@ -9164,7 +9932,11 @@
       <c r="K194" s="5" t="n"/>
       <c r="L194" s="5" t="n"/>
       <c r="M194" s="4" t="n"/>
-      <c r="N194" s="4" t="n"/>
+      <c r="N194" s="4" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
@@ -9208,7 +9980,11 @@
       <c r="K195" s="5" t="n"/>
       <c r="L195" s="5" t="n"/>
       <c r="M195" s="4" t="n"/>
-      <c r="N195" s="4" t="n"/>
+      <c r="N195" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Delaware</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="5" t="inlineStr">
@@ -9252,7 +10028,11 @@
       <c r="K196" s="5" t="n"/>
       <c r="L196" s="5" t="n"/>
       <c r="M196" s="4" t="n"/>
-      <c r="N196" s="4" t="n"/>
+      <c r="N196" s="4" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
@@ -9296,7 +10076,11 @@
       <c r="K197" s="5" t="n"/>
       <c r="L197" s="5" t="n"/>
       <c r="M197" s="4" t="n"/>
-      <c r="N197" s="4" t="n"/>
+      <c r="N197" s="4" t="inlineStr">
+        <is>
+          <t>Djibouti</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
@@ -9340,7 +10124,11 @@
       <c r="K198" s="5" t="n"/>
       <c r="L198" s="5" t="n"/>
       <c r="M198" s="4" t="n"/>
-      <c r="N198" s="4" t="n"/>
+      <c r="N198" s="4" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
@@ -9388,7 +10176,11 @@
       <c r="K199" s="5" t="n"/>
       <c r="L199" s="5" t="n"/>
       <c r="M199" s="4" t="n"/>
-      <c r="N199" s="4" t="n"/>
+      <c r="N199" s="4" t="inlineStr">
+        <is>
+          <t>Desventuradas Islands, Chile</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
@@ -9432,7 +10224,11 @@
       <c r="K200" s="5" t="n"/>
       <c r="L200" s="5" t="n"/>
       <c r="M200" s="4" t="n"/>
-      <c r="N200" s="4" t="n"/>
+      <c r="N200" s="4" t="inlineStr">
+        <is>
+          <t>East Aegean Islands, Greece</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
@@ -9476,7 +10272,11 @@
       <c r="K201" s="5" t="n"/>
       <c r="L201" s="5" t="n"/>
       <c r="M201" s="4" t="n"/>
-      <c r="N201" s="4" t="n"/>
+      <c r="N201" s="4" t="inlineStr">
+        <is>
+          <t>Easter Island, Chile</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="5" t="inlineStr">
@@ -9520,7 +10320,11 @@
       <c r="K202" s="5" t="n"/>
       <c r="L202" s="5" t="n"/>
       <c r="M202" s="4" t="n"/>
-      <c r="N202" s="4" t="n"/>
+      <c r="N202" s="4" t="inlineStr">
+        <is>
+          <t>Ecuador (mainland)</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
@@ -9564,7 +10368,11 @@
       <c r="K203" s="5" t="n"/>
       <c r="L203" s="5" t="n"/>
       <c r="M203" s="4" t="n"/>
-      <c r="N203" s="4" t="n"/>
+      <c r="N203" s="4" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="5" t="inlineStr">
@@ -9608,7 +10416,11 @@
       <c r="K204" s="5" t="n"/>
       <c r="L204" s="5" t="n"/>
       <c r="M204" s="4" t="n"/>
-      <c r="N204" s="4" t="n"/>
+      <c r="N204" s="4" t="inlineStr">
+        <is>
+          <t>Arunachal Pradesh, India</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="5" t="inlineStr">
@@ -9652,7 +10464,11 @@
       <c r="K205" s="5" t="n"/>
       <c r="L205" s="5" t="n"/>
       <c r="M205" s="4" t="n"/>
-      <c r="N205" s="4" t="n"/>
+      <c r="N205" s="4" t="inlineStr">
+        <is>
+          <t>Bhutan</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="5" t="inlineStr">
@@ -9696,7 +10512,11 @@
       <c r="K206" s="5" t="n"/>
       <c r="L206" s="5" t="n"/>
       <c r="M206" s="4" t="n"/>
-      <c r="N206" s="4" t="n"/>
+      <c r="N206" s="4" t="inlineStr">
+        <is>
+          <t>Darjeeling district, India</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="5" t="inlineStr">
@@ -9740,7 +10560,11 @@
       <c r="K207" s="5" t="n"/>
       <c r="L207" s="5" t="n"/>
       <c r="M207" s="4" t="n"/>
-      <c r="N207" s="4" t="n"/>
+      <c r="N207" s="4" t="inlineStr">
+        <is>
+          <t>Sikkim, India</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="5" t="inlineStr">
@@ -9784,7 +10608,11 @@
       <c r="K208" s="5" t="n"/>
       <c r="L208" s="5" t="n"/>
       <c r="M208" s="4" t="n"/>
-      <c r="N208" s="4" t="n"/>
+      <c r="N208" s="4" t="inlineStr">
+        <is>
+          <t>El Salvador</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="5" t="inlineStr">
@@ -9828,7 +10656,11 @@
       <c r="K209" s="5" t="n"/>
       <c r="L209" s="5" t="n"/>
       <c r="M209" s="4" t="n"/>
-      <c r="N209" s="4" t="n"/>
+      <c r="N209" s="4" t="inlineStr">
+        <is>
+          <t>Equatorial Guinea (mainland Río Muni)</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
@@ -9872,7 +10704,11 @@
       <c r="K210" s="5" t="n"/>
       <c r="L210" s="5" t="n"/>
       <c r="M210" s="4" t="n"/>
-      <c r="N210" s="4" t="n"/>
+      <c r="N210" s="4" t="inlineStr">
+        <is>
+          <t>Eritrea</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="5" t="inlineStr">
@@ -9925,7 +10761,11 @@
 https://en.wikipedia.org/wiki/Eswatini</t>
         </is>
       </c>
-      <c r="N211" s="4" t="n"/>
+      <c r="N211" s="4" t="inlineStr">
+        <is>
+          <t>Eswatini (Swaziland)</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="5" t="inlineStr">
@@ -9969,7 +10809,11 @@
       <c r="K212" s="5" t="n"/>
       <c r="L212" s="5" t="n"/>
       <c r="M212" s="4" t="n"/>
-      <c r="N212" s="4" t="n"/>
+      <c r="N212" s="4" t="inlineStr">
+        <is>
+          <t>Ethiopia</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
@@ -10013,7 +10857,11 @@
       <c r="K213" s="5" t="n"/>
       <c r="L213" s="5" t="n"/>
       <c r="M213" s="4" t="n"/>
-      <c r="N213" s="4" t="n"/>
+      <c r="N213" s="4" t="inlineStr">
+        <is>
+          <t>Falkland Islands (Malvinas)</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="5" t="inlineStr">
@@ -10057,7 +10905,11 @@
       <c r="K214" s="5" t="n"/>
       <c r="L214" s="5" t="n"/>
       <c r="M214" s="4" t="n"/>
-      <c r="N214" s="4" t="n"/>
+      <c r="N214" s="4" t="inlineStr">
+        <is>
+          <t>Fiji</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="5" t="inlineStr">
@@ -10101,7 +10953,11 @@
       <c r="K215" s="5" t="n"/>
       <c r="L215" s="5" t="n"/>
       <c r="M215" s="4" t="n"/>
-      <c r="N215" s="4" t="n"/>
+      <c r="N215" s="4" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="5" t="inlineStr">
@@ -10145,7 +11001,11 @@
       <c r="K216" s="5" t="n"/>
       <c r="L216" s="5" t="n"/>
       <c r="M216" s="4" t="n"/>
-      <c r="N216" s="4" t="n"/>
+      <c r="N216" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Florida</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="5" t="inlineStr">
@@ -10189,7 +11049,11 @@
       <c r="K217" s="5" t="n"/>
       <c r="L217" s="5" t="n"/>
       <c r="M217" s="4" t="n"/>
-      <c r="N217" s="4" t="n"/>
+      <c r="N217" s="4" t="inlineStr">
+        <is>
+          <t>Faroe Islands</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="5" t="inlineStr">
@@ -10233,7 +11097,11 @@
       <c r="K218" s="5" t="n"/>
       <c r="L218" s="5" t="n"/>
       <c r="M218" s="4" t="n"/>
-      <c r="N218" s="4" t="n"/>
+      <c r="N218" s="4" t="inlineStr">
+        <is>
+          <t>Channel Islands (Jersey and Guernsey)</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="5" t="inlineStr">
@@ -10277,7 +11145,11 @@
       <c r="K219" s="5" t="n"/>
       <c r="L219" s="5" t="n"/>
       <c r="M219" s="4" t="n"/>
-      <c r="N219" s="4" t="n"/>
+      <c r="N219" s="4" t="inlineStr">
+        <is>
+          <t>Metropolitan France</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="5" t="inlineStr">
@@ -10321,7 +11193,11 @@
       <c r="K220" s="5" t="n"/>
       <c r="L220" s="5" t="n"/>
       <c r="M220" s="4" t="n"/>
-      <c r="N220" s="4" t="n"/>
+      <c r="N220" s="4" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="5" t="inlineStr">
@@ -10365,7 +11241,11 @@
       <c r="K221" s="5" t="n"/>
       <c r="L221" s="5" t="n"/>
       <c r="M221" s="4" t="n"/>
-      <c r="N221" s="4" t="n"/>
+      <c r="N221" s="4" t="inlineStr">
+        <is>
+          <t>French Guiana</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="5" t="inlineStr">
@@ -10409,7 +11289,11 @@
       <c r="K222" s="5" t="n"/>
       <c r="L222" s="5" t="n"/>
       <c r="M222" s="4" t="n"/>
-      <c r="N222" s="4" t="n"/>
+      <c r="N222" s="4" t="inlineStr">
+        <is>
+          <t>Gabon</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
@@ -10453,7 +11337,11 @@
       <c r="K223" s="5" t="n"/>
       <c r="L223" s="5" t="n"/>
       <c r="M223" s="4" t="n"/>
-      <c r="N223" s="4" t="n"/>
+      <c r="N223" s="4" t="inlineStr">
+        <is>
+          <t>Galápagos Islands, Ecuador</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="5" t="inlineStr">
@@ -10497,7 +11385,11 @@
       <c r="K224" s="5" t="n"/>
       <c r="L224" s="5" t="n"/>
       <c r="M224" s="4" t="n"/>
-      <c r="N224" s="4" t="n"/>
+      <c r="N224" s="4" t="inlineStr">
+        <is>
+          <t>The Gambia</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="5" t="inlineStr">
@@ -10541,7 +11433,11 @@
       <c r="K225" s="5" t="n"/>
       <c r="L225" s="5" t="n"/>
       <c r="M225" s="4" t="n"/>
-      <c r="N225" s="4" t="n"/>
+      <c r="N225" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Georgia</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="5" t="inlineStr">
@@ -10585,7 +11481,11 @@
       <c r="K226" s="5" t="n"/>
       <c r="L226" s="5" t="n"/>
       <c r="M226" s="4" t="n"/>
-      <c r="N226" s="4" t="n"/>
+      <c r="N226" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="5" t="inlineStr">
@@ -10629,7 +11529,11 @@
       <c r="K227" s="5" t="n"/>
       <c r="L227" s="5" t="n"/>
       <c r="M227" s="4" t="n"/>
-      <c r="N227" s="4" t="n"/>
+      <c r="N227" s="4" t="inlineStr">
+        <is>
+          <t>Annobón Island, Equatorial Guinea</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="5" t="inlineStr">
@@ -10673,7 +11577,11 @@
       <c r="K228" s="5" t="n"/>
       <c r="L228" s="5" t="n"/>
       <c r="M228" s="4" t="n"/>
-      <c r="N228" s="4" t="n"/>
+      <c r="N228" s="4" t="inlineStr">
+        <is>
+          <t>Bioko Island, Equatorial Guinea</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="5" t="inlineStr">
@@ -10717,7 +11625,11 @@
       <c r="K229" s="5" t="n"/>
       <c r="L229" s="5" t="n"/>
       <c r="M229" s="4" t="n"/>
-      <c r="N229" s="4" t="n"/>
+      <c r="N229" s="4" t="inlineStr">
+        <is>
+          <t>Príncipe Island, São Tomé and Príncipe</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="5" t="inlineStr">
@@ -10761,7 +11673,11 @@
       <c r="K230" s="5" t="n"/>
       <c r="L230" s="5" t="n"/>
       <c r="M230" s="4" t="n"/>
-      <c r="N230" s="4" t="n"/>
+      <c r="N230" s="4" t="inlineStr">
+        <is>
+          <t>São Tomé Island, São Tomé and Príncipe</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="5" t="inlineStr">
@@ -10805,7 +11721,11 @@
       <c r="K231" s="5" t="n"/>
       <c r="L231" s="5" t="n"/>
       <c r="M231" s="4" t="n"/>
-      <c r="N231" s="4" t="n"/>
+      <c r="N231" s="4" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="5" t="inlineStr">
@@ -10849,7 +11769,11 @@
       <c r="K232" s="5" t="n"/>
       <c r="L232" s="5" t="n"/>
       <c r="M232" s="4" t="n"/>
-      <c r="N232" s="4" t="n"/>
+      <c r="N232" s="4" t="inlineStr">
+        <is>
+          <t>Gilbert Islands, Kiribati</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="5" t="inlineStr">
@@ -10893,7 +11817,11 @@
       <c r="K233" s="5" t="n"/>
       <c r="L233" s="5" t="n"/>
       <c r="M233" s="4" t="n"/>
-      <c r="N233" s="4" t="n"/>
+      <c r="N233" s="4" t="inlineStr">
+        <is>
+          <t>Guinea-Bissau</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="5" t="inlineStr">
@@ -10937,7 +11865,11 @@
       <c r="K234" s="5" t="n"/>
       <c r="L234" s="5" t="n"/>
       <c r="M234" s="4" t="n"/>
-      <c r="N234" s="4" t="n"/>
+      <c r="N234" s="4" t="inlineStr">
+        <is>
+          <t>Greenland</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="5" t="inlineStr">
@@ -10981,7 +11913,11 @@
       <c r="K235" s="5" t="n"/>
       <c r="L235" s="5" t="n"/>
       <c r="M235" s="4" t="n"/>
-      <c r="N235" s="4" t="n"/>
+      <c r="N235" s="4" t="inlineStr">
+        <is>
+          <t>Great Britain (England, Scotland, Wales)</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
@@ -11025,7 +11961,11 @@
       <c r="K236" s="5" t="n"/>
       <c r="L236" s="5" t="n"/>
       <c r="M236" s="4" t="n"/>
-      <c r="N236" s="4" t="n"/>
+      <c r="N236" s="4" t="inlineStr">
+        <is>
+          <t>Greece, excluding Crete</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="5" t="inlineStr">
@@ -11069,7 +12009,11 @@
       <c r="K237" s="5" t="n"/>
       <c r="L237" s="5" t="n"/>
       <c r="M237" s="4" t="n"/>
-      <c r="N237" s="4" t="n"/>
+      <c r="N237" s="4" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="5" t="inlineStr">
@@ -11113,7 +12057,11 @@
       <c r="K238" s="5" t="n"/>
       <c r="L238" s="5" t="n"/>
       <c r="M238" s="4" t="n"/>
-      <c r="N238" s="4" t="n"/>
+      <c r="N238" s="4" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="5" t="inlineStr">
@@ -11157,7 +12105,11 @@
       <c r="K239" s="5" t="n"/>
       <c r="L239" s="5" t="n"/>
       <c r="M239" s="4" t="n"/>
-      <c r="N239" s="4" t="n"/>
+      <c r="N239" s="4" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="5" t="inlineStr">
@@ -11201,7 +12153,11 @@
       <c r="K240" s="5" t="n"/>
       <c r="L240" s="5" t="n"/>
       <c r="M240" s="4" t="n"/>
-      <c r="N240" s="4" t="n"/>
+      <c r="N240" s="4" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="5" t="inlineStr">
@@ -11245,7 +12201,11 @@
       <c r="K241" s="5" t="n"/>
       <c r="L241" s="5" t="n"/>
       <c r="M241" s="4" t="n"/>
-      <c r="N241" s="4" t="n"/>
+      <c r="N241" s="4" t="inlineStr">
+        <is>
+          <t>Guinea, West Africa</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="5" t="inlineStr">
@@ -11289,7 +12249,11 @@
       <c r="K242" s="5" t="n"/>
       <c r="L242" s="5" t="n"/>
       <c r="M242" s="4" t="n"/>
-      <c r="N242" s="4" t="n"/>
+      <c r="N242" s="4" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="5" t="inlineStr">
@@ -11333,7 +12297,11 @@
       <c r="K243" s="5" t="n"/>
       <c r="L243" s="5" t="n"/>
       <c r="M243" s="4" t="n"/>
-      <c r="N243" s="4" t="n"/>
+      <c r="N243" s="4" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="5" t="inlineStr">
@@ -11385,7 +12353,11 @@
           <t>Since no significative developments have occurred in this dispute since the publication of the WGSRPD ed. 2, we opt for maintaining codes and name as they were</t>
         </is>
       </c>
-      <c r="N244" s="4" t="n"/>
+      <c r="N244" s="4" t="inlineStr">
+        <is>
+          <t>Navassa Island</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="5" t="inlineStr">
@@ -11429,7 +12401,11 @@
       <c r="K245" s="5" t="n"/>
       <c r="L245" s="5" t="n"/>
       <c r="M245" s="4" t="n"/>
-      <c r="N245" s="4" t="n"/>
+      <c r="N245" s="4" t="inlineStr">
+        <is>
+          <t>The Hawaiian Islands, USA</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="5" t="inlineStr">
@@ -11473,7 +12449,11 @@
       <c r="K246" s="5" t="n"/>
       <c r="L246" s="5" t="n"/>
       <c r="M246" s="4" t="n"/>
-      <c r="N246" s="4" t="n"/>
+      <c r="N246" s="4" t="inlineStr">
+        <is>
+          <t>Johnston Atoll, US Pacific territory</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="5" t="inlineStr">
@@ -11517,7 +12497,11 @@
       <c r="K247" s="5" t="n"/>
       <c r="L247" s="5" t="n"/>
       <c r="M247" s="4" t="n"/>
-      <c r="N247" s="4" t="n"/>
+      <c r="N247" s="4" t="inlineStr">
+        <is>
+          <t>Midway Atoll, US Pacific territory</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="5" t="inlineStr">
@@ -11561,7 +12545,11 @@
       <c r="K248" s="5" t="n"/>
       <c r="L248" s="5" t="n"/>
       <c r="M248" s="4" t="n"/>
-      <c r="N248" s="4" t="n"/>
+      <c r="N248" s="4" t="inlineStr">
+        <is>
+          <t>Howland and Baker Islands, US Pacific territories</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
@@ -11605,7 +12593,11 @@
       <c r="K249" s="5" t="n"/>
       <c r="L249" s="5" t="n"/>
       <c r="M249" s="4" t="n"/>
-      <c r="N249" s="4" t="n"/>
+      <c r="N249" s="4" t="inlineStr">
+        <is>
+          <t>Heard Island and McDonald Islands, Australian external territory</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="5" t="inlineStr">
@@ -11649,7 +12641,11 @@
       <c r="K250" s="5" t="n"/>
       <c r="L250" s="5" t="n"/>
       <c r="M250" s="4" t="n"/>
-      <c r="N250" s="4" t="n"/>
+      <c r="N250" s="4" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="5" t="inlineStr">
@@ -11693,7 +12689,11 @@
       <c r="K251" s="5" t="n"/>
       <c r="L251" s="5" t="n"/>
       <c r="M251" s="4" t="n"/>
-      <c r="N251" s="4" t="n"/>
+      <c r="N251" s="4" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="5" t="inlineStr">
@@ -11737,7 +12737,11 @@
       <c r="K252" s="5" t="n"/>
       <c r="L252" s="5" t="n"/>
       <c r="M252" s="4" t="n"/>
-      <c r="N252" s="4" t="n"/>
+      <c r="N252" s="4" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="5" t="inlineStr">
@@ -11781,7 +12785,11 @@
       <c r="K253" s="5" t="n"/>
       <c r="L253" s="5" t="n"/>
       <c r="M253" s="4" t="n"/>
-      <c r="N253" s="4" t="n"/>
+      <c r="N253" s="4" t="inlineStr">
+        <is>
+          <t>Idaho, USA</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="5" t="inlineStr">
@@ -11825,7 +12833,11 @@
       <c r="K254" s="5" t="n"/>
       <c r="L254" s="5" t="n"/>
       <c r="M254" s="4" t="n"/>
-      <c r="N254" s="4" t="n"/>
+      <c r="N254" s="4" t="inlineStr">
+        <is>
+          <t>Illinois, USA</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="5" t="inlineStr">
@@ -11877,7 +12889,11 @@
         </is>
       </c>
       <c r="M255" s="4" t="n"/>
-      <c r="N255" s="4" t="n"/>
+      <c r="N255" s="4" t="inlineStr">
+        <is>
+          <t>Indian state of Andhra Pradesh</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="5" t="inlineStr">
@@ -11921,7 +12937,11 @@
       <c r="K256" s="5" t="n"/>
       <c r="L256" s="5" t="n"/>
       <c r="M256" s="4" t="n"/>
-      <c r="N256" s="4" t="n"/>
+      <c r="N256" s="4" t="inlineStr">
+        <is>
+          <t>Indian state of Bihar</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="5" t="inlineStr">
@@ -11965,7 +12985,11 @@
       <c r="K257" s="5" t="n"/>
       <c r="L257" s="5" t="n"/>
       <c r="M257" s="4" t="n"/>
-      <c r="N257" s="4" t="n"/>
+      <c r="N257" s="4" t="inlineStr">
+        <is>
+          <t>Union territory of Chandigarh, India</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
@@ -12009,7 +13033,11 @@
       <c r="K258" s="5" t="n"/>
       <c r="L258" s="5" t="n"/>
       <c r="M258" s="4" t="n"/>
-      <c r="N258" s="4" t="n"/>
+      <c r="N258" s="4" t="inlineStr">
+        <is>
+          <t>Indian state of Chhattisgarh</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="5" t="inlineStr">
@@ -12053,7 +13081,11 @@
       <c r="K259" s="5" t="n"/>
       <c r="L259" s="5" t="n"/>
       <c r="M259" s="4" t="n"/>
-      <c r="N259" s="4" t="n"/>
+      <c r="N259" s="4" t="inlineStr">
+        <is>
+          <t>Union territory of Dadra and Nagar Haveli, India</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="5" t="inlineStr">
@@ -12097,7 +13129,11 @@
       <c r="K260" s="5" t="n"/>
       <c r="L260" s="5" t="n"/>
       <c r="M260" s="4" t="n"/>
-      <c r="N260" s="4" t="n"/>
+      <c r="N260" s="4" t="inlineStr">
+        <is>
+          <t>National Capital Territory of Delhi, India</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="5" t="inlineStr">
@@ -12141,7 +13177,11 @@
       <c r="K261" s="5" t="n"/>
       <c r="L261" s="5" t="n"/>
       <c r="M261" s="4" t="n"/>
-      <c r="N261" s="4" t="n"/>
+      <c r="N261" s="4" t="inlineStr">
+        <is>
+          <t>Diu, part of the Indian union territory of Daman and Diu</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="5" t="inlineStr">
@@ -12185,7 +13225,11 @@
       <c r="K262" s="5" t="n"/>
       <c r="L262" s="5" t="n"/>
       <c r="M262" s="4" t="n"/>
-      <c r="N262" s="4" t="n"/>
+      <c r="N262" s="4" t="inlineStr">
+        <is>
+          <t>Daman, part of the Indian union territory of Daman and Diu</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="5" t="inlineStr">
@@ -12229,7 +13273,11 @@
       <c r="K263" s="5" t="n"/>
       <c r="L263" s="5" t="n"/>
       <c r="M263" s="4" t="n"/>
-      <c r="N263" s="4" t="n"/>
+      <c r="N263" s="4" t="inlineStr">
+        <is>
+          <t>Indian state of Goa</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="5" t="inlineStr">
@@ -12273,7 +13321,11 @@
       <c r="K264" s="5" t="n"/>
       <c r="L264" s="5" t="n"/>
       <c r="M264" s="4" t="n"/>
-      <c r="N264" s="4" t="n"/>
+      <c r="N264" s="4" t="inlineStr">
+        <is>
+          <t>Indian state of Gujarat</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="5" t="inlineStr">
@@ -12317,7 +13369,11 @@
       <c r="K265" s="5" t="n"/>
       <c r="L265" s="5" t="n"/>
       <c r="M265" s="4" t="n"/>
-      <c r="N265" s="4" t="n"/>
+      <c r="N265" s="4" t="inlineStr">
+        <is>
+          <t>Indian state of Haryana</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="5" t="inlineStr">
@@ -12361,7 +13417,11 @@
       <c r="K266" s="5" t="n"/>
       <c r="L266" s="5" t="n"/>
       <c r="M266" s="4" t="n"/>
-      <c r="N266" s="4" t="n"/>
+      <c r="N266" s="4" t="inlineStr">
+        <is>
+          <t>Indian state of Jharkhand</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="5" t="inlineStr">
@@ -12405,7 +13465,11 @@
       <c r="K267" s="5" t="n"/>
       <c r="L267" s="5" t="n"/>
       <c r="M267" s="4" t="n"/>
-      <c r="N267" s="4" t="n"/>
+      <c r="N267" s="4" t="inlineStr">
+        <is>
+          <t>Indian state of Kerala</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="5" t="inlineStr">
@@ -12449,7 +13513,11 @@
       <c r="K268" s="5" t="n"/>
       <c r="L268" s="5" t="n"/>
       <c r="M268" s="4" t="n"/>
-      <c r="N268" s="4" t="n"/>
+      <c r="N268" s="4" t="inlineStr">
+        <is>
+          <t>Karaikal district, Indian union territory of Puducherry</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="5" t="inlineStr">
@@ -12493,7 +13561,11 @@
       <c r="K269" s="5" t="n"/>
       <c r="L269" s="5" t="n"/>
       <c r="M269" s="4" t="n"/>
-      <c r="N269" s="4" t="n"/>
+      <c r="N269" s="4" t="inlineStr">
+        <is>
+          <t>Indian state of Karnataka</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="5" t="inlineStr">
@@ -12537,7 +13609,11 @@
       <c r="K270" s="5" t="n"/>
       <c r="L270" s="5" t="n"/>
       <c r="M270" s="4" t="n"/>
-      <c r="N270" s="4" t="n"/>
+      <c r="N270" s="4" t="inlineStr">
+        <is>
+          <t>Mahé district, Indian union territory of Puducherry</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="5" t="inlineStr">
@@ -12581,7 +13657,11 @@
       <c r="K271" s="5" t="n"/>
       <c r="L271" s="5" t="n"/>
       <c r="M271" s="4" t="n"/>
-      <c r="N271" s="4" t="n"/>
+      <c r="N271" s="4" t="inlineStr">
+        <is>
+          <t>Indian state of Madhya Pradesh</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="5" t="inlineStr">
@@ -12625,7 +13705,11 @@
       <c r="K272" s="5" t="n"/>
       <c r="L272" s="5" t="n"/>
       <c r="M272" s="4" t="n"/>
-      <c r="N272" s="4" t="n"/>
+      <c r="N272" s="4" t="inlineStr">
+        <is>
+          <t>Indian state of Maharashtra</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="5" t="inlineStr">
@@ -12669,7 +13753,11 @@
       <c r="K273" s="5" t="n"/>
       <c r="L273" s="5" t="n"/>
       <c r="M273" s="4" t="n"/>
-      <c r="N273" s="4" t="n"/>
+      <c r="N273" s="4" t="inlineStr">
+        <is>
+          <t>Indian state of Odisha (Orissa)</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="5" t="inlineStr">
@@ -12713,7 +13801,11 @@
       <c r="K274" s="5" t="n"/>
       <c r="L274" s="5" t="n"/>
       <c r="M274" s="4" t="n"/>
-      <c r="N274" s="4" t="n"/>
+      <c r="N274" s="4" t="inlineStr">
+        <is>
+          <t>Puducherry (Pondicherry), Indian union territory</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="5" t="inlineStr">
@@ -12757,7 +13849,11 @@
       <c r="K275" s="5" t="n"/>
       <c r="L275" s="5" t="n"/>
       <c r="M275" s="4" t="n"/>
-      <c r="N275" s="4" t="n"/>
+      <c r="N275" s="4" t="inlineStr">
+        <is>
+          <t>Indian state of Punjab</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="5" t="inlineStr">
@@ -12801,7 +13897,11 @@
       <c r="K276" s="5" t="n"/>
       <c r="L276" s="5" t="n"/>
       <c r="M276" s="4" t="n"/>
-      <c r="N276" s="4" t="n"/>
+      <c r="N276" s="4" t="inlineStr">
+        <is>
+          <t>Indian state of Rajasthan</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="5" t="inlineStr">
@@ -12845,7 +13945,11 @@
       <c r="K277" s="5" t="n"/>
       <c r="L277" s="5" t="n"/>
       <c r="M277" s="4" t="n"/>
-      <c r="N277" s="4" t="n"/>
+      <c r="N277" s="4" t="inlineStr">
+        <is>
+          <t>Indian state of Tamil Nadu</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="5" t="inlineStr">
@@ -12889,7 +13993,11 @@
       <c r="K278" s="5" t="n"/>
       <c r="L278" s="5" t="n"/>
       <c r="M278" s="4" t="n"/>
-      <c r="N278" s="4" t="n"/>
+      <c r="N278" s="4" t="inlineStr">
+        <is>
+          <t>Indian state of Uttar Pradesh</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="5" t="inlineStr">
@@ -12933,7 +14041,11 @@
       <c r="K279" s="5" t="n"/>
       <c r="L279" s="5" t="n"/>
       <c r="M279" s="4" t="n"/>
-      <c r="N279" s="4" t="n"/>
+      <c r="N279" s="4" t="inlineStr">
+        <is>
+          <t>Indian state of West Bengal</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="5" t="inlineStr">
@@ -12977,7 +14089,11 @@
       <c r="K280" s="5" t="n"/>
       <c r="L280" s="5" t="n"/>
       <c r="M280" s="4" t="n"/>
-      <c r="N280" s="4" t="n"/>
+      <c r="N280" s="4" t="inlineStr">
+        <is>
+          <t>Yanam district, Indian union territory of Puducherry</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="5" t="inlineStr">
@@ -13021,7 +14137,11 @@
       <c r="K281" s="5" t="n"/>
       <c r="L281" s="5" t="n"/>
       <c r="M281" s="4" t="n"/>
-      <c r="N281" s="4" t="n"/>
+      <c r="N281" s="4" t="inlineStr">
+        <is>
+          <t>Indiana, USA</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="5" t="inlineStr">
@@ -13065,7 +14185,11 @@
       <c r="K282" s="5" t="n"/>
       <c r="L282" s="5" t="n"/>
       <c r="M282" s="4" t="n"/>
-      <c r="N282" s="4" t="n"/>
+      <c r="N282" s="4" t="inlineStr">
+        <is>
+          <t>Iowa, USA</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
@@ -13109,7 +14233,11 @@
       <c r="K283" s="5" t="n"/>
       <c r="L283" s="5" t="n"/>
       <c r="M283" s="4" t="n"/>
-      <c r="N283" s="4" t="n"/>
+      <c r="N283" s="4" t="inlineStr">
+        <is>
+          <t>Republic of Ireland</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="5" t="inlineStr">
@@ -13153,7 +14281,11 @@
       <c r="K284" s="5" t="n"/>
       <c r="L284" s="5" t="n"/>
       <c r="M284" s="4" t="n"/>
-      <c r="N284" s="4" t="n"/>
+      <c r="N284" s="4" t="inlineStr">
+        <is>
+          <t>Northern Ireland, UK</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
@@ -13197,7 +14329,11 @@
       <c r="K285" s="5" t="n"/>
       <c r="L285" s="5" t="n"/>
       <c r="M285" s="4" t="n"/>
-      <c r="N285" s="4" t="n"/>
+      <c r="N285" s="4" t="inlineStr">
+        <is>
+          <t>Irkutsk Oblast, Russia</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="5" t="inlineStr">
@@ -13241,7 +14377,11 @@
       <c r="K286" s="5" t="n"/>
       <c r="L286" s="5" t="n"/>
       <c r="M286" s="4" t="n"/>
-      <c r="N286" s="4" t="n"/>
+      <c r="N286" s="4" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
@@ -13285,7 +14425,11 @@
       <c r="K287" s="5" t="n"/>
       <c r="L287" s="5" t="n"/>
       <c r="M287" s="4" t="n"/>
-      <c r="N287" s="4" t="n"/>
+      <c r="N287" s="4" t="inlineStr">
+        <is>
+          <t>Iraq</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
@@ -13329,7 +14473,11 @@
       <c r="K288" s="5" t="n"/>
       <c r="L288" s="5" t="n"/>
       <c r="M288" s="4" t="n"/>
-      <c r="N288" s="4" t="n"/>
+      <c r="N288" s="4" t="inlineStr">
+        <is>
+          <t>Italy, excluding San Marino and the Holy See</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="5" t="inlineStr">
@@ -13373,7 +14521,11 @@
       <c r="K289" s="5" t="n"/>
       <c r="L289" s="5" t="n"/>
       <c r="M289" s="4" t="n"/>
-      <c r="N289" s="4" t="n"/>
+      <c r="N289" s="4" t="inlineStr">
+        <is>
+          <t>San Marino</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="5" t="inlineStr">
@@ -13417,7 +14569,11 @@
       <c r="K290" s="5" t="n"/>
       <c r="L290" s="5" t="n"/>
       <c r="M290" s="4" t="n"/>
-      <c r="N290" s="4" t="n"/>
+      <c r="N290" s="4" t="inlineStr">
+        <is>
+          <t>Vatican City (the Holy See)</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="5" t="inlineStr">
@@ -13461,7 +14617,11 @@
       <c r="K291" s="5" t="n"/>
       <c r="L291" s="5" t="n"/>
       <c r="M291" s="4" t="n"/>
-      <c r="N291" s="4" t="n"/>
+      <c r="N291" s="4" t="inlineStr">
+        <is>
+          <t>Côte d'Ivoire (Ivory Coast)</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="5" t="inlineStr">
@@ -13505,7 +14665,11 @@
       <c r="K292" s="5" t="n"/>
       <c r="L292" s="5" t="n"/>
       <c r="M292" s="4" t="n"/>
-      <c r="N292" s="4" t="n"/>
+      <c r="N292" s="4" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
@@ -13549,7 +14713,11 @@
       <c r="K293" s="5" t="n"/>
       <c r="L293" s="5" t="n"/>
       <c r="M293" s="4" t="n"/>
-      <c r="N293" s="4" t="n"/>
+      <c r="N293" s="4" t="inlineStr">
+        <is>
+          <t>Hokkaido, Japan</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="5" t="inlineStr">
@@ -13593,7 +14761,11 @@
       <c r="K294" s="5" t="n"/>
       <c r="L294" s="5" t="n"/>
       <c r="M294" s="4" t="n"/>
-      <c r="N294" s="4" t="n"/>
+      <c r="N294" s="4" t="inlineStr">
+        <is>
+          <t>Honshu, Japan</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="5" t="inlineStr">
@@ -13637,7 +14809,11 @@
       <c r="K295" s="5" t="n"/>
       <c r="L295" s="5" t="n"/>
       <c r="M295" s="4" t="n"/>
-      <c r="N295" s="4" t="n"/>
+      <c r="N295" s="4" t="inlineStr">
+        <is>
+          <t>Kyushu, Japan</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="5" t="inlineStr">
@@ -13681,7 +14857,11 @@
       <c r="K296" s="5" t="n"/>
       <c r="L296" s="5" t="n"/>
       <c r="M296" s="4" t="n"/>
-      <c r="N296" s="4" t="n"/>
+      <c r="N296" s="4" t="inlineStr">
+        <is>
+          <t>Shikoku, Japan</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="5" t="inlineStr">
@@ -13725,7 +14905,11 @@
       <c r="K297" s="5" t="n"/>
       <c r="L297" s="5" t="n"/>
       <c r="M297" s="4" t="n"/>
-      <c r="N297" s="4" t="n"/>
+      <c r="N297" s="4" t="inlineStr">
+        <is>
+          <t>Java, Indonesia</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="5" t="inlineStr">
@@ -13769,7 +14953,11 @@
       <c r="K298" s="5" t="n"/>
       <c r="L298" s="5" t="n"/>
       <c r="M298" s="4" t="n"/>
-      <c r="N298" s="4" t="n"/>
+      <c r="N298" s="4" t="inlineStr">
+        <is>
+          <t>Juan Fernández Islands, Chile</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="5" t="inlineStr">
@@ -13813,7 +15001,11 @@
       <c r="K299" s="5" t="n"/>
       <c r="L299" s="5" t="n"/>
       <c r="M299" s="4" t="n"/>
-      <c r="N299" s="4" t="n"/>
+      <c r="N299" s="4" t="inlineStr">
+        <is>
+          <t>Kamchatka Krai, Russia</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="5" t="inlineStr">
@@ -13857,7 +15049,11 @@
       <c r="K300" s="5" t="n"/>
       <c r="L300" s="5" t="n"/>
       <c r="M300" s="4" t="n"/>
-      <c r="N300" s="4" t="n"/>
+      <c r="N300" s="4" t="inlineStr">
+        <is>
+          <t>Kansas, USA</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="5" t="inlineStr">
@@ -13901,7 +15097,11 @@
       <c r="K301" s="5" t="n"/>
       <c r="L301" s="5" t="n"/>
       <c r="M301" s="4" t="n"/>
-      <c r="N301" s="4" t="n"/>
+      <c r="N301" s="4" t="inlineStr">
+        <is>
+          <t>Kazakhstan</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="5" t="inlineStr">
@@ -13945,7 +15145,11 @@
       <c r="K302" s="5" t="n"/>
       <c r="L302" s="5" t="n"/>
       <c r="M302" s="4" t="n"/>
-      <c r="N302" s="4" t="n"/>
+      <c r="N302" s="4" t="inlineStr">
+        <is>
+          <t>Kerguelen Islands, French Southern Territories</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="5" t="inlineStr">
@@ -13989,7 +15193,11 @@
       <c r="K303" s="5" t="n"/>
       <c r="L303" s="5" t="n"/>
       <c r="M303" s="4" t="n"/>
-      <c r="N303" s="4" t="n"/>
+      <c r="N303" s="4" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="5" t="inlineStr">
@@ -14033,7 +15241,11 @@
       <c r="K304" s="5" t="n"/>
       <c r="L304" s="5" t="n"/>
       <c r="M304" s="4" t="n"/>
-      <c r="N304" s="4" t="n"/>
+      <c r="N304" s="4" t="inlineStr">
+        <is>
+          <t>Kermadec Islands, New Zealand</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="5" t="inlineStr">
@@ -14077,7 +15289,11 @@
       <c r="K305" s="5" t="n"/>
       <c r="L305" s="5" t="n"/>
       <c r="M305" s="4" t="n"/>
-      <c r="N305" s="4" t="n"/>
+      <c r="N305" s="4" t="inlineStr">
+        <is>
+          <t>Kyrgyzstan</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="5" t="inlineStr">
@@ -14121,7 +15337,11 @@
       <c r="K306" s="5" t="n"/>
       <c r="L306" s="5" t="n"/>
       <c r="M306" s="4" t="n"/>
-      <c r="N306" s="4" t="n"/>
+      <c r="N306" s="4" t="inlineStr">
+        <is>
+          <t>Khabarovsk Krai, Russia</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="5" t="inlineStr">
@@ -14165,7 +15385,11 @@
       <c r="K307" s="5" t="n"/>
       <c r="L307" s="5" t="n"/>
       <c r="M307" s="4" t="n"/>
-      <c r="N307" s="4" t="n"/>
+      <c r="N307" s="4" t="inlineStr">
+        <is>
+          <t>North Korea</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="5" t="inlineStr">
@@ -14209,7 +15433,11 @@
       <c r="K308" s="5" t="n"/>
       <c r="L308" s="5" t="n"/>
       <c r="M308" s="4" t="n"/>
-      <c r="N308" s="4" t="n"/>
+      <c r="N308" s="4" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="5" t="inlineStr">
@@ -14253,7 +15481,11 @@
       <c r="K309" s="5" t="n"/>
       <c r="L309" s="5" t="n"/>
       <c r="M309" s="4" t="n"/>
-      <c r="N309" s="4" t="n"/>
+      <c r="N309" s="4" t="inlineStr">
+        <is>
+          <t>Krasnoyarsk Krai, Russia</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="5" t="inlineStr">
@@ -14297,7 +15529,11 @@
       <c r="K310" s="5" t="n"/>
       <c r="L310" s="5" t="n"/>
       <c r="M310" s="4" t="n"/>
-      <c r="N310" s="4" t="n"/>
+      <c r="N310" s="4" t="inlineStr">
+        <is>
+          <t>Crete, Greece</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="5" t="inlineStr">
@@ -14345,7 +15581,11 @@
           <t>We conclude that no changes are needed in this regard</t>
         </is>
       </c>
-      <c r="N311" s="4" t="n"/>
+      <c r="N311" s="4" t="inlineStr">
+        <is>
+          <t>Crimea</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="5" t="inlineStr">
@@ -14389,7 +15629,11 @@
       <c r="K312" s="5" t="n"/>
       <c r="L312" s="5" t="n"/>
       <c r="M312" s="4" t="n"/>
-      <c r="N312" s="4" t="n"/>
+      <c r="N312" s="4" t="inlineStr">
+        <is>
+          <t>Kentucky, USA</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="5" t="inlineStr">
@@ -14433,7 +15677,11 @@
       <c r="K313" s="5" t="n"/>
       <c r="L313" s="5" t="n"/>
       <c r="M313" s="4" t="n"/>
-      <c r="N313" s="4" t="n"/>
+      <c r="N313" s="4" t="inlineStr">
+        <is>
+          <t>Kuril Islands, Russia</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="5" t="inlineStr">
@@ -14477,7 +15725,11 @@
       <c r="K314" s="5" t="n"/>
       <c r="L314" s="5" t="n"/>
       <c r="M314" s="4" t="n"/>
-      <c r="N314" s="4" t="n"/>
+      <c r="N314" s="4" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="5" t="inlineStr">
@@ -14521,7 +15773,11 @@
       <c r="K315" s="5" t="n"/>
       <c r="L315" s="5" t="n"/>
       <c r="M315" s="4" t="n"/>
-      <c r="N315" s="4" t="n"/>
+      <c r="N315" s="4" t="inlineStr">
+        <is>
+          <t>Kazan Islands (Volcano Islands), Japan</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="5" t="inlineStr">
@@ -14565,7 +15821,11 @@
       <c r="K316" s="5" t="n"/>
       <c r="L316" s="5" t="n"/>
       <c r="M316" s="4" t="n"/>
-      <c r="N316" s="4" t="n"/>
+      <c r="N316" s="4" t="inlineStr">
+        <is>
+          <t>Labrador, Canada</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="5" t="inlineStr">
@@ -14609,7 +15869,11 @@
       <c r="K317" s="5" t="n"/>
       <c r="L317" s="5" t="n"/>
       <c r="M317" s="4" t="n"/>
-      <c r="N317" s="4" t="n"/>
+      <c r="N317" s="4" t="inlineStr">
+        <is>
+          <t>Laos</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="5" t="inlineStr">
@@ -14653,7 +15917,11 @@
       <c r="K318" s="5" t="n"/>
       <c r="L318" s="5" t="n"/>
       <c r="M318" s="4" t="n"/>
-      <c r="N318" s="4" t="n"/>
+      <c r="N318" s="4" t="inlineStr">
+        <is>
+          <t>Liberia</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="5" t="inlineStr">
@@ -14697,7 +15965,11 @@
       <c r="K319" s="5" t="n"/>
       <c r="L319" s="5" t="n"/>
       <c r="M319" s="4" t="n"/>
-      <c r="N319" s="4" t="n"/>
+      <c r="N319" s="4" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="5" t="inlineStr">
@@ -14741,7 +16013,11 @@
       <c r="K320" s="5" t="n"/>
       <c r="L320" s="5" t="n"/>
       <c r="M320" s="4" t="n"/>
-      <c r="N320" s="4" t="n"/>
+      <c r="N320" s="4" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="5" t="inlineStr">
@@ -14785,7 +16061,11 @@
       <c r="K321" s="5" t="n"/>
       <c r="L321" s="5" t="n"/>
       <c r="M321" s="4" t="n"/>
-      <c r="N321" s="4" t="n"/>
+      <c r="N321" s="4" t="inlineStr">
+        <is>
+          <t>Libya</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="5" t="inlineStr">
@@ -14829,7 +16109,11 @@
       <c r="K322" s="5" t="n"/>
       <c r="L322" s="5" t="n"/>
       <c r="M322" s="4" t="n"/>
-      <c r="N322" s="4" t="n"/>
+      <c r="N322" s="4" t="inlineStr">
+        <is>
+          <t>Laccadive Islands (Lakshadweep), India</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="5" t="inlineStr">
@@ -14873,7 +16157,11 @@
       <c r="K323" s="5" t="n"/>
       <c r="L323" s="5" t="n"/>
       <c r="M323" s="4" t="n"/>
-      <c r="N323" s="4" t="n"/>
+      <c r="N323" s="4" t="inlineStr">
+        <is>
+          <t>Antigua and Barbuda</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="5" t="inlineStr">
@@ -14917,7 +16205,11 @@
       <c r="K324" s="5" t="n"/>
       <c r="L324" s="5" t="n"/>
       <c r="M324" s="4" t="n"/>
-      <c r="N324" s="4" t="n"/>
+      <c r="N324" s="4" t="inlineStr">
+        <is>
+          <t>Anguilla, British Caribbean territory</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="5" t="inlineStr">
@@ -14961,7 +16253,11 @@
       <c r="K325" s="5" t="n"/>
       <c r="L325" s="5" t="n"/>
       <c r="M325" s="4" t="n"/>
-      <c r="N325" s="4" t="n"/>
+      <c r="N325" s="4" t="inlineStr">
+        <is>
+          <t>Aves Island, Venezuela</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="5" t="inlineStr">
@@ -15005,7 +16301,11 @@
       <c r="K326" s="5" t="n"/>
       <c r="L326" s="5" t="n"/>
       <c r="M326" s="4" t="n"/>
-      <c r="N326" s="4" t="n"/>
+      <c r="N326" s="4" t="inlineStr">
+        <is>
+          <t>British Virgin Islands</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="5" t="inlineStr">
@@ -15049,7 +16349,11 @@
       <c r="K327" s="5" t="n"/>
       <c r="L327" s="5" t="n"/>
       <c r="M327" s="4" t="n"/>
-      <c r="N327" s="4" t="n"/>
+      <c r="N327" s="4" t="inlineStr">
+        <is>
+          <t>Guadeloupe, French Caribbean territory</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="5" t="inlineStr">
@@ -15093,7 +16397,11 @@
       <c r="K328" s="5" t="n"/>
       <c r="L328" s="5" t="n"/>
       <c r="M328" s="4" t="n"/>
-      <c r="N328" s="4" t="n"/>
+      <c r="N328" s="4" t="inlineStr">
+        <is>
+          <t>Montserrat, British Caribbean territory</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="5" t="inlineStr">
@@ -15137,7 +16445,11 @@
           <t>No ISO code as BQ Also includes Bonaire, not part of this unit</t>
         </is>
       </c>
-      <c r="N329" s="4" t="n"/>
+      <c r="N329" s="4" t="inlineStr">
+        <is>
+          <t>Saba and Sint Eustatius, Dutch Caribbean</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="5" t="inlineStr">
@@ -15181,7 +16493,11 @@
       <c r="K330" s="5" t="n"/>
       <c r="L330" s="5" t="n"/>
       <c r="M330" s="4" t="n"/>
-      <c r="N330" s="4" t="n"/>
+      <c r="N330" s="4" t="inlineStr">
+        <is>
+          <t>Saint Kitts and Nevis</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="5" t="inlineStr">
@@ -15226,7 +16542,11 @@
 https://en.wikipedia.org/wiki/Saint_Martin_(island)</t>
         </is>
       </c>
-      <c r="N331" s="4" t="n"/>
+      <c r="N331" s="4" t="inlineStr">
+        <is>
+          <t>Saint-Martin and Saint-Barthélemy, French Caribbean islands</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="5" t="inlineStr">
@@ -15270,7 +16590,11 @@
       <c r="K332" s="5" t="n"/>
       <c r="L332" s="5" t="n"/>
       <c r="M332" s="4" t="n"/>
-      <c r="N332" s="4" t="n"/>
+      <c r="N332" s="4" t="inlineStr">
+        <is>
+          <t>U.S. Virgin Islands</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="5" t="inlineStr">
@@ -15314,7 +16638,11 @@
       <c r="K333" s="5" t="n"/>
       <c r="L333" s="5" t="n"/>
       <c r="M333" s="4" t="n"/>
-      <c r="N333" s="4" t="n"/>
+      <c r="N333" s="4" t="inlineStr">
+        <is>
+          <t>Lesotho</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="5" t="inlineStr">
@@ -15358,7 +16686,11 @@
       <c r="K334" s="5" t="n"/>
       <c r="L334" s="5" t="n"/>
       <c r="M334" s="4" t="n"/>
-      <c r="N334" s="4" t="n"/>
+      <c r="N334" s="4" t="inlineStr">
+        <is>
+          <t>Line Islands, Kiribati</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="5" t="inlineStr">
@@ -15402,7 +16734,11 @@
       <c r="K335" s="5" t="n"/>
       <c r="L335" s="5" t="n"/>
       <c r="M335" s="4" t="n"/>
-      <c r="N335" s="4" t="n"/>
+      <c r="N335" s="4" t="inlineStr">
+        <is>
+          <t>U.S. Line Islands (Palmyra Atoll, Kingman Reef, Jarvis Island)</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="5" t="inlineStr">
@@ -15446,7 +16782,11 @@
       <c r="K336" s="5" t="n"/>
       <c r="L336" s="5" t="n"/>
       <c r="M336" s="4" t="n"/>
-      <c r="N336" s="4" t="n"/>
+      <c r="N336" s="4" t="inlineStr">
+        <is>
+          <t>Louisiana, USA</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="5" t="inlineStr">
@@ -15490,7 +16830,11 @@
       <c r="K337" s="5" t="n"/>
       <c r="L337" s="5" t="n"/>
       <c r="M337" s="4" t="n"/>
-      <c r="N337" s="4" t="n"/>
+      <c r="N337" s="4" t="inlineStr">
+        <is>
+          <t>Bali, Indonesia</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="5" t="inlineStr">
@@ -15550,7 +16894,11 @@
           <t>ISO Code for LSI-ET changes to TL</t>
         </is>
       </c>
-      <c r="N338" s="4" t="n"/>
+      <c r="N338" s="4" t="inlineStr">
+        <is>
+          <t>Timor-Leste (East Timor)</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="5" t="inlineStr">
@@ -15606,7 +16954,11 @@
           <t>Limits of LSI-LS, changes to exclude the Indonesian part of Timor from this unit.</t>
         </is>
       </c>
-      <c r="N339" s="4" t="n"/>
+      <c r="N339" s="4" t="inlineStr">
+        <is>
+          <t>Lesser Sunda Islands, Indonesia</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="5" t="inlineStr">
@@ -15650,7 +17002,11 @@
       <c r="K340" s="5" t="n"/>
       <c r="L340" s="5" t="n"/>
       <c r="M340" s="4" t="n"/>
-      <c r="N340" s="4" t="n"/>
+      <c r="N340" s="4" t="inlineStr">
+        <is>
+          <t>Magadan Oblast, Russia</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="5" t="inlineStr">
@@ -15694,7 +17050,11 @@
       <c r="K341" s="5" t="n"/>
       <c r="L341" s="5" t="n"/>
       <c r="M341" s="4" t="n"/>
-      <c r="N341" s="4" t="n"/>
+      <c r="N341" s="4" t="inlineStr">
+        <is>
+          <t>Maine, USA</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="5" t="inlineStr">
@@ -15738,7 +17098,11 @@
       <c r="K342" s="5" t="n"/>
       <c r="L342" s="5" t="n"/>
       <c r="M342" s="4" t="n"/>
-      <c r="N342" s="4" t="n"/>
+      <c r="N342" s="4" t="inlineStr">
+        <is>
+          <t>Manitoba, Canada</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="5" t="inlineStr">
@@ -15782,7 +17146,11 @@
       <c r="K343" s="5" t="n"/>
       <c r="L343" s="5" t="n"/>
       <c r="M343" s="4" t="n"/>
-      <c r="N343" s="4" t="n"/>
+      <c r="N343" s="4" t="inlineStr">
+        <is>
+          <t>Macquarie Island, Australia</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="5" t="inlineStr">
@@ -15826,7 +17194,11 @@
       <c r="K344" s="5" t="n"/>
       <c r="L344" s="5" t="n"/>
       <c r="M344" s="4" t="n"/>
-      <c r="N344" s="4" t="n"/>
+      <c r="N344" s="4" t="inlineStr">
+        <is>
+          <t>Massachusetts, USA</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="5" t="inlineStr">
@@ -15870,7 +17242,11 @@
       <c r="K345" s="5" t="n"/>
       <c r="L345" s="5" t="n"/>
       <c r="M345" s="4" t="n"/>
-      <c r="N345" s="4" t="n"/>
+      <c r="N345" s="4" t="inlineStr">
+        <is>
+          <t>Mauritius</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="5" t="inlineStr">
@@ -15915,7 +17291,11 @@
 https://en.wikipedia.org/wiki/Mozambique_Channel</t>
         </is>
       </c>
-      <c r="N346" s="4" t="n"/>
+      <c r="N346" s="4" t="inlineStr">
+        <is>
+          <t>Scattered Islands in the Mozambique Channel</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="5" t="inlineStr">
@@ -15959,7 +17339,11 @@
       <c r="K347" s="5" t="n"/>
       <c r="L347" s="5" t="n"/>
       <c r="M347" s="4" t="n"/>
-      <c r="N347" s="4" t="n"/>
+      <c r="N347" s="4" t="inlineStr">
+        <is>
+          <t>Marcus Island (Minami-Tori-shima), Japan</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="5" t="inlineStr">
@@ -16003,7 +17387,11 @@
       <c r="K348" s="5" t="n"/>
       <c r="L348" s="5" t="n"/>
       <c r="M348" s="4" t="n"/>
-      <c r="N348" s="4" t="n"/>
+      <c r="N348" s="4" t="inlineStr">
+        <is>
+          <t>Madagascar</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="5" t="inlineStr">
@@ -16047,7 +17435,11 @@
       <c r="K349" s="5" t="n"/>
       <c r="L349" s="5" t="n"/>
       <c r="M349" s="4" t="n"/>
-      <c r="N349" s="4" t="n"/>
+      <c r="N349" s="4" t="inlineStr">
+        <is>
+          <t>Madeira, Portugal</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="5" t="inlineStr">
@@ -16091,7 +17483,11 @@
       <c r="K350" s="5" t="n"/>
       <c r="L350" s="5" t="n"/>
       <c r="M350" s="4" t="n"/>
-      <c r="N350" s="4" t="n"/>
+      <c r="N350" s="4" t="inlineStr">
+        <is>
+          <t>Maldives</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="5" t="inlineStr">
@@ -16135,7 +17531,11 @@
       <c r="K351" s="5" t="n"/>
       <c r="L351" s="5" t="n"/>
       <c r="M351" s="4" t="n"/>
-      <c r="N351" s="4" t="n"/>
+      <c r="N351" s="4" t="inlineStr">
+        <is>
+          <t>Michigan, USA</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="5" t="inlineStr">
@@ -16179,7 +17579,11 @@
       <c r="K352" s="5" t="n"/>
       <c r="L352" s="5" t="n"/>
       <c r="M352" s="4" t="n"/>
-      <c r="N352" s="4" t="n"/>
+      <c r="N352" s="4" t="inlineStr">
+        <is>
+          <t>Minnesota, USA</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="5" t="inlineStr">
@@ -16223,7 +17627,11 @@
       <c r="K353" s="5" t="n"/>
       <c r="L353" s="5" t="n"/>
       <c r="M353" s="4" t="n"/>
-      <c r="N353" s="4" t="n"/>
+      <c r="N353" s="4" t="inlineStr">
+        <is>
+          <t>Mali</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="5" t="inlineStr">
@@ -16267,7 +17675,11 @@
       <c r="K354" s="5" t="n"/>
       <c r="L354" s="5" t="n"/>
       <c r="M354" s="4" t="n"/>
-      <c r="N354" s="4" t="n"/>
+      <c r="N354" s="4" t="inlineStr">
+        <is>
+          <t>Malawi</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="5" t="inlineStr">
@@ -16311,7 +17723,11 @@
       <c r="K355" s="5" t="n"/>
       <c r="L355" s="5" t="n"/>
       <c r="M355" s="4" t="n"/>
-      <c r="N355" s="4" t="n"/>
+      <c r="N355" s="4" t="inlineStr">
+        <is>
+          <t>Peninsular Malaysia</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="5" t="inlineStr">
@@ -16355,7 +17771,11 @@
       <c r="K356" s="5" t="n"/>
       <c r="L356" s="5" t="n"/>
       <c r="M356" s="4" t="n"/>
-      <c r="N356" s="4" t="n"/>
+      <c r="N356" s="4" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="5" t="inlineStr">
@@ -16399,7 +17819,11 @@
       <c r="K357" s="5" t="n"/>
       <c r="L357" s="5" t="n"/>
       <c r="M357" s="4" t="n"/>
-      <c r="N357" s="4" t="n"/>
+      <c r="N357" s="4" t="inlineStr">
+        <is>
+          <t>Montana, USA</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="5" t="inlineStr">
@@ -16443,7 +17867,11 @@
       <c r="K358" s="5" t="n"/>
       <c r="L358" s="5" t="n"/>
       <c r="M358" s="4" t="n"/>
-      <c r="N358" s="4" t="n"/>
+      <c r="N358" s="4" t="inlineStr">
+        <is>
+          <t>Maluku Islands (Moluccas), Indonesia</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="5" t="inlineStr">
@@ -16487,7 +17915,11 @@
       <c r="K359" s="5" t="n"/>
       <c r="L359" s="5" t="n"/>
       <c r="M359" s="4" t="n"/>
-      <c r="N359" s="4" t="n"/>
+      <c r="N359" s="4" t="inlineStr">
+        <is>
+          <t>Mongolia</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="5" t="inlineStr">
@@ -16531,7 +17963,11 @@
       <c r="K360" s="5" t="n"/>
       <c r="L360" s="5" t="n"/>
       <c r="M360" s="4" t="n"/>
-      <c r="N360" s="4" t="n"/>
+      <c r="N360" s="4" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="5" t="inlineStr">
@@ -16575,7 +18011,11 @@
       <c r="K361" s="5" t="n"/>
       <c r="L361" s="5" t="n"/>
       <c r="M361" s="4" t="n"/>
-      <c r="N361" s="4" t="n"/>
+      <c r="N361" s="4" t="inlineStr">
+        <is>
+          <t>Spanish territories in North Africa (Ceuta, Melilla)</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="5" t="inlineStr">
@@ -16619,7 +18059,11 @@
       <c r="K362" s="5" t="n"/>
       <c r="L362" s="5" t="n"/>
       <c r="M362" s="4" t="n"/>
-      <c r="N362" s="4" t="n"/>
+      <c r="N362" s="4" t="inlineStr">
+        <is>
+          <t>Mozambique</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="5" t="inlineStr">
@@ -16663,7 +18107,11 @@
       <c r="K363" s="5" t="n"/>
       <c r="L363" s="5" t="n"/>
       <c r="M363" s="4" t="n"/>
-      <c r="N363" s="4" t="n"/>
+      <c r="N363" s="4" t="inlineStr">
+        <is>
+          <t>Marion and Prince Edward Islands, South Africa</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="5" t="inlineStr">
@@ -16707,7 +18155,11 @@
       <c r="K364" s="5" t="n"/>
       <c r="L364" s="5" t="n"/>
       <c r="M364" s="4" t="n"/>
-      <c r="N364" s="4" t="n"/>
+      <c r="N364" s="4" t="inlineStr">
+        <is>
+          <t>Guam</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="5" t="inlineStr">
@@ -16751,7 +18203,11 @@
       <c r="K365" s="5" t="n"/>
       <c r="L365" s="5" t="n"/>
       <c r="M365" s="4" t="n"/>
-      <c r="N365" s="4" t="n"/>
+      <c r="N365" s="4" t="inlineStr">
+        <is>
+          <t>Northern Mariana Islands</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="5" t="inlineStr">
@@ -16795,7 +18251,11 @@
       <c r="K366" s="5" t="n"/>
       <c r="L366" s="5" t="n"/>
       <c r="M366" s="4" t="n"/>
-      <c r="N366" s="4" t="n"/>
+      <c r="N366" s="4" t="inlineStr">
+        <is>
+          <t>Marquesas Islands, French Polynesia</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="5" t="inlineStr">
@@ -16839,7 +18299,11 @@
       <c r="K367" s="5" t="n"/>
       <c r="L367" s="5" t="n"/>
       <c r="M367" s="4" t="n"/>
-      <c r="N367" s="4" t="n"/>
+      <c r="N367" s="4" t="inlineStr">
+        <is>
+          <t>Marshall Islands</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="5" t="inlineStr">
@@ -16883,7 +18347,11 @@
       <c r="K368" s="5" t="n"/>
       <c r="L368" s="5" t="n"/>
       <c r="M368" s="4" t="n"/>
-      <c r="N368" s="4" t="n"/>
+      <c r="N368" s="4" t="inlineStr">
+        <is>
+          <t>Maryland, USA</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="5" t="inlineStr">
@@ -16927,7 +18395,11 @@
       <c r="K369" s="5" t="n"/>
       <c r="L369" s="5" t="n"/>
       <c r="M369" s="4" t="n"/>
-      <c r="N369" s="4" t="n"/>
+      <c r="N369" s="4" t="inlineStr">
+        <is>
+          <t>Mississippi, USA</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="5" t="inlineStr">
@@ -16971,7 +18443,11 @@
       <c r="K370" s="5" t="n"/>
       <c r="L370" s="5" t="n"/>
       <c r="M370" s="4" t="n"/>
-      <c r="N370" s="4" t="n"/>
+      <c r="N370" s="4" t="inlineStr">
+        <is>
+          <t>Missouri, USA</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="5" t="inlineStr">
@@ -17015,7 +18491,11 @@
       <c r="K371" s="5" t="n"/>
       <c r="L371" s="5" t="n"/>
       <c r="M371" s="4" t="n"/>
-      <c r="N371" s="4" t="n"/>
+      <c r="N371" s="4" t="inlineStr">
+        <is>
+          <t>Mauritania</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="5" t="inlineStr">
@@ -17059,7 +18539,11 @@
       <c r="K372" s="5" t="n"/>
       <c r="L372" s="5" t="n"/>
       <c r="M372" s="4" t="n"/>
-      <c r="N372" s="4" t="n"/>
+      <c r="N372" s="4" t="inlineStr">
+        <is>
+          <t>Mexico City (Federal District), Mexico</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="5" t="inlineStr">
@@ -17103,7 +18587,11 @@
       <c r="K373" s="5" t="n"/>
       <c r="L373" s="5" t="n"/>
       <c r="M373" s="4" t="n"/>
-      <c r="N373" s="4" t="n"/>
+      <c r="N373" s="4" t="inlineStr">
+        <is>
+          <t>State of México, Mexico</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="5" t="inlineStr">
@@ -17147,7 +18635,11 @@
       <c r="K374" s="5" t="n"/>
       <c r="L374" s="5" t="n"/>
       <c r="M374" s="4" t="n"/>
-      <c r="N374" s="4" t="n"/>
+      <c r="N374" s="4" t="inlineStr">
+        <is>
+          <t>Morelos, Mexico</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="5" t="inlineStr">
@@ -17191,7 +18683,11 @@
       <c r="K375" s="5" t="n"/>
       <c r="L375" s="5" t="n"/>
       <c r="M375" s="4" t="n"/>
-      <c r="N375" s="4" t="n"/>
+      <c r="N375" s="4" t="inlineStr">
+        <is>
+          <t>Puebla, Mexico</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="5" t="inlineStr">
@@ -17235,7 +18731,11 @@
       <c r="K376" s="5" t="n"/>
       <c r="L376" s="5" t="n"/>
       <c r="M376" s="4" t="n"/>
-      <c r="N376" s="4" t="n"/>
+      <c r="N376" s="4" t="inlineStr">
+        <is>
+          <t>Tlaxcala, Mexico</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="5" t="inlineStr">
@@ -17279,7 +18779,11 @@
       <c r="K377" s="5" t="n"/>
       <c r="L377" s="5" t="n"/>
       <c r="M377" s="4" t="n"/>
-      <c r="N377" s="4" t="n"/>
+      <c r="N377" s="4" t="inlineStr">
+        <is>
+          <t>Aguascalientes, Mexico</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="5" t="inlineStr">
@@ -17323,7 +18827,11 @@
       <c r="K378" s="5" t="n"/>
       <c r="L378" s="5" t="n"/>
       <c r="M378" s="4" t="n"/>
-      <c r="N378" s="4" t="n"/>
+      <c r="N378" s="4" t="inlineStr">
+        <is>
+          <t>Coahuila, Mexico</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="5" t="inlineStr">
@@ -17367,7 +18875,11 @@
       <c r="K379" s="5" t="n"/>
       <c r="L379" s="5" t="n"/>
       <c r="M379" s="4" t="n"/>
-      <c r="N379" s="4" t="n"/>
+      <c r="N379" s="4" t="inlineStr">
+        <is>
+          <t>Chihuahua, Mexico</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="5" t="inlineStr">
@@ -17411,7 +18923,11 @@
       <c r="K380" s="5" t="n"/>
       <c r="L380" s="5" t="n"/>
       <c r="M380" s="4" t="n"/>
-      <c r="N380" s="4" t="n"/>
+      <c r="N380" s="4" t="inlineStr">
+        <is>
+          <t>Durango, Mexico</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="5" t="inlineStr">
@@ -17455,7 +18971,11 @@
       <c r="K381" s="5" t="n"/>
       <c r="L381" s="5" t="n"/>
       <c r="M381" s="4" t="n"/>
-      <c r="N381" s="4" t="n"/>
+      <c r="N381" s="4" t="inlineStr">
+        <is>
+          <t>Guanajuato, Mexico</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="5" t="inlineStr">
@@ -17499,7 +19019,11 @@
       <c r="K382" s="5" t="n"/>
       <c r="L382" s="5" t="n"/>
       <c r="M382" s="4" t="n"/>
-      <c r="N382" s="4" t="n"/>
+      <c r="N382" s="4" t="inlineStr">
+        <is>
+          <t>Hidalgo, Mexico</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="5" t="inlineStr">
@@ -17543,7 +19067,11 @@
       <c r="K383" s="5" t="n"/>
       <c r="L383" s="5" t="n"/>
       <c r="M383" s="4" t="n"/>
-      <c r="N383" s="4" t="n"/>
+      <c r="N383" s="4" t="inlineStr">
+        <is>
+          <t>Nuevo León, Mexico</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="5" t="inlineStr">
@@ -17587,7 +19115,11 @@
       <c r="K384" s="5" t="n"/>
       <c r="L384" s="5" t="n"/>
       <c r="M384" s="4" t="n"/>
-      <c r="N384" s="4" t="n"/>
+      <c r="N384" s="4" t="inlineStr">
+        <is>
+          <t>Querétaro, Mexico</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="5" t="inlineStr">
@@ -17631,7 +19163,11 @@
       <c r="K385" s="5" t="n"/>
       <c r="L385" s="5" t="n"/>
       <c r="M385" s="4" t="n"/>
-      <c r="N385" s="4" t="n"/>
+      <c r="N385" s="4" t="inlineStr">
+        <is>
+          <t>San Luis Potosí, Mexico</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="5" t="inlineStr">
@@ -17675,7 +19211,11 @@
       <c r="K386" s="5" t="n"/>
       <c r="L386" s="5" t="n"/>
       <c r="M386" s="4" t="n"/>
-      <c r="N386" s="4" t="n"/>
+      <c r="N386" s="4" t="inlineStr">
+        <is>
+          <t>Tamaulipas, Mexico</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="5" t="inlineStr">
@@ -17719,7 +19259,11 @@
       <c r="K387" s="5" t="n"/>
       <c r="L387" s="5" t="n"/>
       <c r="M387" s="4" t="n"/>
-      <c r="N387" s="4" t="n"/>
+      <c r="N387" s="4" t="inlineStr">
+        <is>
+          <t>Zacatecas, Mexico</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="5" t="inlineStr">
@@ -17763,7 +19307,11 @@
       <c r="K388" s="5" t="n"/>
       <c r="L388" s="5" t="n"/>
       <c r="M388" s="4" t="n"/>
-      <c r="N388" s="4" t="n"/>
+      <c r="N388" s="4" t="inlineStr">
+        <is>
+          <t>Veracruz, Mexico</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="5" t="inlineStr">
@@ -17807,7 +19355,11 @@
       <c r="K389" s="5" t="n"/>
       <c r="L389" s="5" t="n"/>
       <c r="M389" s="4" t="n"/>
-      <c r="N389" s="4" t="n"/>
+      <c r="N389" s="4" t="inlineStr">
+        <is>
+          <t>Guadalupe Island, Mexican Pacific</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="5" t="inlineStr">
@@ -17851,7 +19403,11 @@
       <c r="K390" s="5" t="n"/>
       <c r="L390" s="5" t="n"/>
       <c r="M390" s="4" t="n"/>
-      <c r="N390" s="4" t="n"/>
+      <c r="N390" s="4" t="inlineStr">
+        <is>
+          <t>Rocas Alijos, Mexican Pacific islets</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="5" t="inlineStr">
@@ -17895,7 +19451,11 @@
       <c r="K391" s="5" t="n"/>
       <c r="L391" s="5" t="n"/>
       <c r="M391" s="4" t="n"/>
-      <c r="N391" s="4" t="n"/>
+      <c r="N391" s="4" t="inlineStr">
+        <is>
+          <t>Revillagigedo Islands, Mexican Pacific</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="5" t="inlineStr">
@@ -17939,7 +19499,11 @@
       <c r="K392" s="5" t="n"/>
       <c r="L392" s="5" t="n"/>
       <c r="M392" s="4" t="n"/>
-      <c r="N392" s="4" t="n"/>
+      <c r="N392" s="4" t="inlineStr">
+        <is>
+          <t>The Mexican state of Baja California</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="5" t="inlineStr">
@@ -17983,7 +19547,11 @@
       <c r="K393" s="5" t="n"/>
       <c r="L393" s="5" t="n"/>
       <c r="M393" s="4" t="n"/>
-      <c r="N393" s="4" t="n"/>
+      <c r="N393" s="4" t="inlineStr">
+        <is>
+          <t>The Mexican state of Baja California Sur</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="5" t="inlineStr">
@@ -18027,7 +19595,11 @@
       <c r="K394" s="5" t="n"/>
       <c r="L394" s="5" t="n"/>
       <c r="M394" s="4" t="n"/>
-      <c r="N394" s="4" t="n"/>
+      <c r="N394" s="4" t="inlineStr">
+        <is>
+          <t>The Mexican state of Sinaloa</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="5" t="inlineStr">
@@ -18071,7 +19643,11 @@
       <c r="K395" s="5" t="n"/>
       <c r="L395" s="5" t="n"/>
       <c r="M395" s="4" t="n"/>
-      <c r="N395" s="4" t="n"/>
+      <c r="N395" s="4" t="inlineStr">
+        <is>
+          <t>The Mexican state of Sonora</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="5" t="inlineStr">
@@ -18115,7 +19691,11 @@
       <c r="K396" s="5" t="n"/>
       <c r="L396" s="5" t="n"/>
       <c r="M396" s="4" t="n"/>
-      <c r="N396" s="4" t="n"/>
+      <c r="N396" s="4" t="inlineStr">
+        <is>
+          <t>The Mexican state of Colima</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="5" t="inlineStr">
@@ -18159,7 +19739,11 @@
       <c r="K397" s="5" t="n"/>
       <c r="L397" s="5" t="n"/>
       <c r="M397" s="4" t="n"/>
-      <c r="N397" s="4" t="n"/>
+      <c r="N397" s="4" t="inlineStr">
+        <is>
+          <t>The Mexican state of Guerrero</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="5" t="inlineStr">
@@ -18203,7 +19787,11 @@
       <c r="K398" s="5" t="n"/>
       <c r="L398" s="5" t="n"/>
       <c r="M398" s="4" t="n"/>
-      <c r="N398" s="4" t="n"/>
+      <c r="N398" s="4" t="inlineStr">
+        <is>
+          <t>The Mexican state of Jalisco</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="5" t="inlineStr">
@@ -18247,7 +19835,11 @@
       <c r="K399" s="5" t="n"/>
       <c r="L399" s="5" t="n"/>
       <c r="M399" s="4" t="n"/>
-      <c r="N399" s="4" t="n"/>
+      <c r="N399" s="4" t="inlineStr">
+        <is>
+          <t>The Mexican state of Michoacán</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="5" t="inlineStr">
@@ -18291,7 +19883,11 @@
       <c r="K400" s="5" t="n"/>
       <c r="L400" s="5" t="n"/>
       <c r="M400" s="4" t="n"/>
-      <c r="N400" s="4" t="n"/>
+      <c r="N400" s="4" t="inlineStr">
+        <is>
+          <t>The Mexican state of Nayarit</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="5" t="inlineStr">
@@ -18335,7 +19931,11 @@
       <c r="K401" s="5" t="n"/>
       <c r="L401" s="5" t="n"/>
       <c r="M401" s="4" t="n"/>
-      <c r="N401" s="4" t="n"/>
+      <c r="N401" s="4" t="inlineStr">
+        <is>
+          <t>The Mexican state of Oaxaca</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="5" t="inlineStr">
@@ -18379,7 +19979,11 @@
       <c r="K402" s="5" t="n"/>
       <c r="L402" s="5" t="n"/>
       <c r="M402" s="4" t="n"/>
-      <c r="N402" s="4" t="n"/>
+      <c r="N402" s="4" t="inlineStr">
+        <is>
+          <t>The Mexican state of Campeche</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="5" t="inlineStr">
@@ -18423,7 +20027,11 @@
       <c r="K403" s="5" t="n"/>
       <c r="L403" s="5" t="n"/>
       <c r="M403" s="4" t="n"/>
-      <c r="N403" s="4" t="n"/>
+      <c r="N403" s="4" t="inlineStr">
+        <is>
+          <t>The Mexican state of Chiapas</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="5" t="inlineStr">
@@ -18467,7 +20075,11 @@
       <c r="K404" s="5" t="n"/>
       <c r="L404" s="5" t="n"/>
       <c r="M404" s="4" t="n"/>
-      <c r="N404" s="4" t="n"/>
+      <c r="N404" s="4" t="inlineStr">
+        <is>
+          <t>The Mexican state of Quintana Roo</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="5" t="inlineStr">
@@ -18511,7 +20123,11 @@
       <c r="K405" s="5" t="n"/>
       <c r="L405" s="5" t="n"/>
       <c r="M405" s="4" t="n"/>
-      <c r="N405" s="4" t="n"/>
+      <c r="N405" s="4" t="inlineStr">
+        <is>
+          <t>The Mexican state of Tabasco</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="5" t="inlineStr">
@@ -18555,7 +20171,11 @@
       <c r="K406" s="5" t="n"/>
       <c r="L406" s="5" t="n"/>
       <c r="M406" s="4" t="n"/>
-      <c r="N406" s="4" t="n"/>
+      <c r="N406" s="4" t="inlineStr">
+        <is>
+          <t>The Mexican state of Yucatán</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="5" t="inlineStr">
@@ -18599,7 +20219,11 @@
       <c r="K407" s="5" t="n"/>
       <c r="L407" s="5" t="n"/>
       <c r="M407" s="4" t="n"/>
-      <c r="N407" s="4" t="n"/>
+      <c r="N407" s="4" t="inlineStr">
+        <is>
+          <t>Myanmar (Burma)</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="5" t="inlineStr">
@@ -18643,7 +20267,11 @@
       <c r="K408" s="5" t="n"/>
       <c r="L408" s="5" t="n"/>
       <c r="M408" s="4" t="n"/>
-      <c r="N408" s="4" t="n"/>
+      <c r="N408" s="4" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="5" t="inlineStr">
@@ -18687,7 +20315,11 @@
       <c r="K409" s="5" t="n"/>
       <c r="L409" s="5" t="n"/>
       <c r="M409" s="4" t="n"/>
-      <c r="N409" s="4" t="n"/>
+      <c r="N409" s="4" t="inlineStr">
+        <is>
+          <t>The South African province of KwaZulu-Natal</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="5" t="inlineStr">
@@ -18731,7 +20363,11 @@
       <c r="K410" s="5" t="n"/>
       <c r="L410" s="5" t="n"/>
       <c r="M410" s="4" t="n"/>
-      <c r="N410" s="4" t="n"/>
+      <c r="N410" s="4" t="inlineStr">
+        <is>
+          <t>The Canadian province of New Brunswick</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="5" t="inlineStr">
@@ -18775,7 +20411,11 @@
       <c r="K411" s="5" t="n"/>
       <c r="L411" s="5" t="n"/>
       <c r="M411" s="4" t="n"/>
-      <c r="N411" s="4" t="n"/>
+      <c r="N411" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of North Carolina</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="5" t="inlineStr">
@@ -18819,7 +20459,11 @@
       <c r="K412" s="5" t="n"/>
       <c r="L412" s="5" t="n"/>
       <c r="M412" s="4" t="n"/>
-      <c r="N412" s="4" t="n"/>
+      <c r="N412" s="4" t="inlineStr">
+        <is>
+          <t>The Nicobar Islands, India</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="5" t="inlineStr">
@@ -18863,7 +20507,11 @@
       <c r="K413" s="5" t="n"/>
       <c r="L413" s="5" t="n"/>
       <c r="M413" s="4" t="n"/>
-      <c r="N413" s="4" t="n"/>
+      <c r="N413" s="4" t="inlineStr">
+        <is>
+          <t>The Russian republic of Chechnya</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="5" t="inlineStr">
@@ -18907,7 +20555,11 @@
       <c r="K414" s="5" t="n"/>
       <c r="L414" s="5" t="n"/>
       <c r="M414" s="4" t="n"/>
-      <c r="N414" s="4" t="n"/>
+      <c r="N414" s="4" t="inlineStr">
+        <is>
+          <t>The Russian republic of Dagestan</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="5" t="inlineStr">
@@ -18951,7 +20603,11 @@
       <c r="K415" s="5" t="n"/>
       <c r="L415" s="5" t="n"/>
       <c r="M415" s="4" t="n"/>
-      <c r="N415" s="4" t="n"/>
+      <c r="N415" s="4" t="inlineStr">
+        <is>
+          <t>The Russian republic of Ingushetia</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="5" t="inlineStr">
@@ -18995,7 +20651,11 @@
       <c r="K416" s="5" t="n"/>
       <c r="L416" s="5" t="n"/>
       <c r="M416" s="4" t="n"/>
-      <c r="N416" s="4" t="n"/>
+      <c r="N416" s="4" t="inlineStr">
+        <is>
+          <t>The Russian republic of Kabardino-Balkaria</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="5" t="inlineStr">
@@ -19039,7 +20699,11 @@
       <c r="K417" s="5" t="n"/>
       <c r="L417" s="5" t="n"/>
       <c r="M417" s="4" t="n"/>
-      <c r="N417" s="4" t="n"/>
+      <c r="N417" s="4" t="inlineStr">
+        <is>
+          <t>The Russian republic of Karachay-Cherkessia</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="5" t="inlineStr">
@@ -19083,7 +20747,11 @@
       <c r="K418" s="5" t="n"/>
       <c r="L418" s="5" t="n"/>
       <c r="M418" s="4" t="n"/>
-      <c r="N418" s="4" t="n"/>
+      <c r="N418" s="4" t="inlineStr">
+        <is>
+          <t>Krasnodar Krai, Russia</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="5" t="inlineStr">
@@ -19127,7 +20795,11 @@
       <c r="K419" s="5" t="n"/>
       <c r="L419" s="5" t="n"/>
       <c r="M419" s="4" t="n"/>
-      <c r="N419" s="4" t="n"/>
+      <c r="N419" s="4" t="inlineStr">
+        <is>
+          <t>The Russian republic of North Ossetia-Alania</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="5" t="inlineStr">
@@ -19171,7 +20843,11 @@
       <c r="K420" s="5" t="n"/>
       <c r="L420" s="5" t="n"/>
       <c r="M420" s="4" t="n"/>
-      <c r="N420" s="4" t="n"/>
+      <c r="N420" s="4" t="inlineStr">
+        <is>
+          <t>Stavropol Krai, Russia</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="5" t="inlineStr">
@@ -19215,7 +20891,11 @@
       <c r="K421" s="5" t="n"/>
       <c r="L421" s="5" t="n"/>
       <c r="M421" s="4" t="n"/>
-      <c r="N421" s="4" t="n"/>
+      <c r="N421" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of North Dakota</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="5" t="inlineStr">
@@ -19259,7 +20939,11 @@
       <c r="K422" s="5" t="n"/>
       <c r="L422" s="5" t="n"/>
       <c r="M422" s="4" t="n"/>
-      <c r="N422" s="4" t="n"/>
+      <c r="N422" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Nebraska</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="5" t="inlineStr">
@@ -19303,7 +20987,11 @@
       <c r="K423" s="5" t="n"/>
       <c r="L423" s="5" t="n"/>
       <c r="M423" s="4" t="n"/>
-      <c r="N423" s="4" t="n"/>
+      <c r="N423" s="4" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="5" t="inlineStr">
@@ -19347,7 +21035,11 @@
       <c r="K424" s="5" t="n"/>
       <c r="L424" s="5" t="n"/>
       <c r="M424" s="4" t="n"/>
-      <c r="N424" s="4" t="n"/>
+      <c r="N424" s="4" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="5" t="inlineStr">
@@ -19391,7 +21083,11 @@
       <c r="K425" s="5" t="n"/>
       <c r="L425" s="5" t="n"/>
       <c r="M425" s="4" t="n"/>
-      <c r="N425" s="4" t="n"/>
+      <c r="N425" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Nevada</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="5" t="inlineStr">
@@ -19435,7 +21131,11 @@
       <c r="K426" s="5" t="n"/>
       <c r="L426" s="5" t="n"/>
       <c r="M426" s="4" t="n"/>
-      <c r="N426" s="4" t="n"/>
+      <c r="N426" s="4" t="inlineStr">
+        <is>
+          <t>Lord Howe Island, Australia</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="5" t="inlineStr">
@@ -19479,7 +21179,11 @@
       <c r="K427" s="5" t="n"/>
       <c r="L427" s="5" t="n"/>
       <c r="M427" s="4" t="n"/>
-      <c r="N427" s="4" t="n"/>
+      <c r="N427" s="4" t="inlineStr">
+        <is>
+          <t>Norfolk Island, Australian external territory</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="5" t="inlineStr">
@@ -19523,7 +21227,11 @@
       <c r="K428" s="5" t="n"/>
       <c r="L428" s="5" t="n"/>
       <c r="M428" s="4" t="n"/>
-      <c r="N428" s="4" t="n"/>
+      <c r="N428" s="4" t="inlineStr">
+        <is>
+          <t>The island of Newfoundland, Canada</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="5" t="inlineStr">
@@ -19567,7 +21275,11 @@
       <c r="K429" s="5" t="n"/>
       <c r="L429" s="5" t="n"/>
       <c r="M429" s="4" t="n"/>
-      <c r="N429" s="4" t="n"/>
+      <c r="N429" s="4" t="inlineStr">
+        <is>
+          <t>Saint Pierre and Miquelon, French territory near Newfoundland</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="5" t="inlineStr">
@@ -19611,7 +21323,11 @@
       <c r="K430" s="5" t="n"/>
       <c r="L430" s="5" t="n"/>
       <c r="M430" s="4" t="n"/>
-      <c r="N430" s="4" t="n"/>
+      <c r="N430" s="4" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="5" t="inlineStr">
@@ -19655,7 +21371,11 @@
       <c r="K431" s="5" t="n"/>
       <c r="L431" s="5" t="n"/>
       <c r="M431" s="4" t="n"/>
-      <c r="N431" s="4" t="n"/>
+      <c r="N431" s="4" t="inlineStr">
+        <is>
+          <t>Niger</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="5" t="inlineStr">
@@ -19699,7 +21419,11 @@
       <c r="K432" s="5" t="n"/>
       <c r="L432" s="5" t="n"/>
       <c r="M432" s="4" t="n"/>
-      <c r="N432" s="4" t="n"/>
+      <c r="N432" s="4" t="inlineStr">
+        <is>
+          <t>Nicaragua</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="5" t="inlineStr">
@@ -19749,7 +21473,11 @@
 https://en.wikipedia.org/wiki/Caribbean_Netherlands</t>
         </is>
       </c>
-      <c r="N433" s="4" t="n"/>
+      <c r="N433" s="4" t="inlineStr">
+        <is>
+          <t>Bonaire, Caribbean Netherlands</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="5" t="inlineStr">
@@ -19799,7 +21527,11 @@
 https://www.bbc.com/news/world-latin-america-11511355</t>
         </is>
       </c>
-      <c r="N434" s="4" t="n"/>
+      <c r="N434" s="4" t="inlineStr">
+        <is>
+          <t>Curaçao, Caribbean island country</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="5" t="inlineStr">
@@ -19843,7 +21575,11 @@
       <c r="K435" s="5" t="n"/>
       <c r="L435" s="5" t="n"/>
       <c r="M435" s="4" t="n"/>
-      <c r="N435" s="4" t="n"/>
+      <c r="N435" s="4" t="inlineStr">
+        <is>
+          <t>The Nansei (Ryukyu) Islands, Japan</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="5" t="inlineStr">
@@ -19887,7 +21623,11 @@
       <c r="K436" s="5" t="n"/>
       <c r="L436" s="5" t="n"/>
       <c r="M436" s="4" t="n"/>
-      <c r="N436" s="4" t="n"/>
+      <c r="N436" s="4" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="5" t="inlineStr">
@@ -19939,7 +21679,11 @@
         </is>
       </c>
       <c r="M437" s="4" t="n"/>
-      <c r="N437" s="4" t="n"/>
+      <c r="N437" s="4" t="inlineStr">
+        <is>
+          <t>The South African province of Gauteng</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="5" t="inlineStr">
@@ -19999,7 +21743,11 @@
           <t>TVL-NP as a Level 4 unit, is it correct to change the L4 code (Table 4 in WGSRPD 2) to TVL-LI and the L4 country to Limpopo ?.</t>
         </is>
       </c>
-      <c r="N438" s="4" t="n"/>
+      <c r="N438" s="4" t="inlineStr">
+        <is>
+          <t>The South African province of Limpopo</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="5" t="inlineStr">
@@ -20047,7 +21795,11 @@
       <c r="K439" s="5" t="n"/>
       <c r="L439" s="5" t="n"/>
       <c r="M439" s="4" t="n"/>
-      <c r="N439" s="4" t="n"/>
+      <c r="N439" s="4" t="inlineStr">
+        <is>
+          <t>The South African province of Mpumalanga</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="5" t="inlineStr">
@@ -20095,7 +21847,11 @@
       <c r="K440" s="5" t="n"/>
       <c r="L440" s="5" t="n"/>
       <c r="M440" s="4" t="n"/>
-      <c r="N440" s="4" t="n"/>
+      <c r="N440" s="4" t="inlineStr">
+        <is>
+          <t>The South African North West province</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="5" t="inlineStr">
@@ -20139,7 +21895,11 @@
       <c r="K441" s="5" t="n"/>
       <c r="L441" s="5" t="n"/>
       <c r="M441" s="4" t="n"/>
-      <c r="N441" s="4" t="n"/>
+      <c r="N441" s="4" t="inlineStr">
+        <is>
+          <t>Naoero, an island country in the Pacific also long known as Nauru</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="5" t="inlineStr">
@@ -20183,7 +21943,11 @@
       <c r="K442" s="5" t="n"/>
       <c r="L442" s="5" t="n"/>
       <c r="M442" s="4" t="n"/>
-      <c r="N442" s="4" t="n"/>
+      <c r="N442" s="4" t="inlineStr">
+        <is>
+          <t>The Canadian province of Nova Scotia</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="5" t="inlineStr">
@@ -20227,7 +21991,11 @@
       <c r="K443" s="5" t="n"/>
       <c r="L443" s="5" t="n"/>
       <c r="M443" s="4" t="n"/>
-      <c r="N443" s="4" t="n"/>
+      <c r="N443" s="4" t="inlineStr">
+        <is>
+          <t>The Australian Capital Territory</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="5" t="inlineStr">
@@ -20271,7 +22039,11 @@
       <c r="K444" s="5" t="n"/>
       <c r="L444" s="5" t="n"/>
       <c r="M444" s="4" t="n"/>
-      <c r="N444" s="4" t="n"/>
+      <c r="N444" s="4" t="inlineStr">
+        <is>
+          <t>The Australian state of New South Wales</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="5" t="inlineStr">
@@ -20315,7 +22087,11 @@
       <c r="K445" s="5" t="n"/>
       <c r="L445" s="5" t="n"/>
       <c r="M445" s="4" t="n"/>
-      <c r="N445" s="4" t="n"/>
+      <c r="N445" s="4" t="inlineStr">
+        <is>
+          <t>The Northern Territory of Australia</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="5" t="inlineStr">
@@ -20359,7 +22135,11 @@
       <c r="K446" s="5" t="n"/>
       <c r="L446" s="5" t="n"/>
       <c r="M446" s="4" t="n"/>
-      <c r="N446" s="4" t="n"/>
+      <c r="N446" s="4" t="inlineStr">
+        <is>
+          <t>Niue, Pacific island nation</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="5" t="inlineStr">
@@ -20403,7 +22183,11 @@
       <c r="K447" s="5" t="n"/>
       <c r="L447" s="5" t="n"/>
       <c r="M447" s="4" t="n"/>
-      <c r="N447" s="4" t="n"/>
+      <c r="N447" s="4" t="inlineStr">
+        <is>
+          <t>The Canadian territory of Nunavut</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="5" t="inlineStr">
@@ -20463,7 +22247,11 @@
           <t>New name for former Yugoslavia: Balkans or West Balkans?New name for former Yugoslavia: Balkans or West Balkans? (LEVEL 3)</t>
         </is>
       </c>
-      <c r="N448" s="4" t="n"/>
+      <c r="N448" s="4" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="5" t="inlineStr">
@@ -20523,7 +22311,11 @@
           <t>New name for former Yugoslavia: Balkans or West Balkans?New name for former Yugoslavia: Balkans or West Balkans? (LEVEL 3)</t>
         </is>
       </c>
-      <c r="N449" s="4" t="n"/>
+      <c r="N449" s="4" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="5" t="inlineStr">
@@ -20583,7 +22375,11 @@
           <t>New name for former Yugoslavia: Balkans or West Balkans?New name for former Yugoslavia: Balkans or West Balkans? (LEVEL 3)</t>
         </is>
       </c>
-      <c r="N450" s="4" t="n"/>
+      <c r="N450" s="4" t="inlineStr">
+        <is>
+          <t>Kosovo</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="5" t="inlineStr">
@@ -20643,7 +22439,11 @@
           <t>New name for former Yugoslavia: Balkans or West Balkans?New name for former Yugoslavia: Balkans or West Balkans? (LEVEL 3)</t>
         </is>
       </c>
-      <c r="N451" s="4" t="n"/>
+      <c r="N451" s="4" t="inlineStr">
+        <is>
+          <t>North Macedonia</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="5" t="inlineStr">
@@ -20703,7 +22503,11 @@
           <t>New name for former Yugoslavia: Balkans or West Balkans?New name for former Yugoslavia: Balkans or West Balkans? (LEVEL 3)</t>
         </is>
       </c>
-      <c r="N452" s="4" t="n"/>
+      <c r="N452" s="4" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="5" t="inlineStr">
@@ -20763,7 +22567,11 @@
           <t>New name for former Yugoslavia: Balkans or West Balkans?New name for former Yugoslavia: Balkans or West Balkans? (LEVEL 3)</t>
         </is>
       </c>
-      <c r="N453" s="4" t="n"/>
+      <c r="N453" s="4" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="5" t="inlineStr">
@@ -20823,7 +22631,11 @@
           <t>New name for former Yugoslavia: Balkans or West Balkans?New name for former Yugoslavia: Balkans or West Balkans? (LEVEL 3)</t>
         </is>
       </c>
-      <c r="N454" s="4" t="n"/>
+      <c r="N454" s="4" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="5" t="inlineStr">
@@ -20867,7 +22679,11 @@
       <c r="K455" s="5" t="n"/>
       <c r="L455" s="5" t="n"/>
       <c r="M455" s="4" t="n"/>
-      <c r="N455" s="4" t="n"/>
+      <c r="N455" s="4" t="inlineStr">
+        <is>
+          <t>New Caledonia, French territory in the Pacific</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="5" t="inlineStr">
@@ -20911,7 +22727,11 @@
       <c r="K456" s="5" t="n"/>
       <c r="L456" s="5" t="n"/>
       <c r="M456" s="4" t="n"/>
-      <c r="N456" s="4" t="n"/>
+      <c r="N456" s="4" t="inlineStr">
+        <is>
+          <t>Irian Jaya, the Indonesian (western) portion of New Guinea</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="5" t="inlineStr">
@@ -20955,7 +22775,11 @@
       <c r="K457" s="5" t="n"/>
       <c r="L457" s="5" t="n"/>
       <c r="M457" s="4" t="n"/>
-      <c r="N457" s="4" t="n"/>
+      <c r="N457" s="4" t="inlineStr">
+        <is>
+          <t>Papua New Guinea</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="5" t="inlineStr">
@@ -20999,7 +22823,11 @@
       <c r="K458" s="5" t="n"/>
       <c r="L458" s="5" t="n"/>
       <c r="M458" s="4" t="n"/>
-      <c r="N458" s="4" t="n"/>
+      <c r="N458" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of New Hampshire</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="5" t="inlineStr">
@@ -21043,7 +22871,11 @@
       <c r="K459" s="5" t="n"/>
       <c r="L459" s="5" t="n"/>
       <c r="M459" s="4" t="n"/>
-      <c r="N459" s="4" t="n"/>
+      <c r="N459" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of New Jersey</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="5" t="inlineStr">
@@ -21087,7 +22919,11 @@
       <c r="K460" s="5" t="n"/>
       <c r="L460" s="5" t="n"/>
       <c r="M460" s="4" t="n"/>
-      <c r="N460" s="4" t="n"/>
+      <c r="N460" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of New Mexico</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="5" t="inlineStr">
@@ -21131,7 +22967,11 @@
       <c r="K461" s="5" t="n"/>
       <c r="L461" s="5" t="n"/>
       <c r="M461" s="4" t="n"/>
-      <c r="N461" s="4" t="n"/>
+      <c r="N461" s="4" t="inlineStr">
+        <is>
+          <t>The Canadian territory of Northwest Territories</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" s="5" t="inlineStr">
@@ -21175,7 +23015,11 @@
       <c r="K462" s="5" t="n"/>
       <c r="L462" s="5" t="n"/>
       <c r="M462" s="4" t="n"/>
-      <c r="N462" s="4" t="n"/>
+      <c r="N462" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of New York</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" s="5" t="inlineStr">
@@ -21219,7 +23063,11 @@
       <c r="K463" s="5" t="n"/>
       <c r="L463" s="5" t="n"/>
       <c r="M463" s="4" t="n"/>
-      <c r="N463" s="4" t="n"/>
+      <c r="N463" s="4" t="inlineStr">
+        <is>
+          <t>North Island, New Zealand</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" s="5" t="inlineStr">
@@ -21263,7 +23111,11 @@
       <c r="K464" s="5" t="n"/>
       <c r="L464" s="5" t="n"/>
       <c r="M464" s="4" t="n"/>
-      <c r="N464" s="4" t="n"/>
+      <c r="N464" s="4" t="inlineStr">
+        <is>
+          <t>South Island, New Zealand</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" s="5" t="inlineStr">
@@ -21307,7 +23159,11 @@
       <c r="K465" s="5" t="n"/>
       <c r="L465" s="5" t="n"/>
       <c r="M465" s="4" t="n"/>
-      <c r="N465" s="4" t="n"/>
+      <c r="N465" s="4" t="inlineStr">
+        <is>
+          <t>The South African province of Free State</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" s="5" t="inlineStr">
@@ -21351,7 +23207,11 @@
       <c r="K466" s="5" t="n"/>
       <c r="L466" s="5" t="n"/>
       <c r="M466" s="4" t="n"/>
-      <c r="N466" s="4" t="n"/>
+      <c r="N466" s="4" t="inlineStr">
+        <is>
+          <t>The Ogasawara (Bonin) Islands, Japan</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="5" t="inlineStr">
@@ -21395,7 +23255,11 @@
       <c r="K467" s="5" t="n"/>
       <c r="L467" s="5" t="n"/>
       <c r="M467" s="4" t="n"/>
-      <c r="N467" s="4" t="n"/>
+      <c r="N467" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Ohio</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="5" t="inlineStr">
@@ -21439,7 +23303,11 @@
       <c r="K468" s="5" t="n"/>
       <c r="L468" s="5" t="n"/>
       <c r="M468" s="4" t="n"/>
-      <c r="N468" s="4" t="n"/>
+      <c r="N468" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Oklahoma</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" s="5" t="inlineStr">
@@ -21483,7 +23351,11 @@
       <c r="K469" s="5" t="n"/>
       <c r="L469" s="5" t="n"/>
       <c r="M469" s="4" t="n"/>
-      <c r="N469" s="4" t="n"/>
+      <c r="N469" s="4" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="5" t="inlineStr">
@@ -21527,7 +23399,11 @@
       <c r="K470" s="5" t="n"/>
       <c r="L470" s="5" t="n"/>
       <c r="M470" s="4" t="n"/>
-      <c r="N470" s="4" t="n"/>
+      <c r="N470" s="4" t="inlineStr">
+        <is>
+          <t>The Canadian province of Ontario</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="5" t="inlineStr">
@@ -21571,7 +23447,11 @@
       <c r="K471" s="5" t="n"/>
       <c r="L471" s="5" t="n"/>
       <c r="M471" s="4" t="n"/>
-      <c r="N471" s="4" t="n"/>
+      <c r="N471" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Oregon</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="5" t="inlineStr">
@@ -21615,7 +23495,11 @@
       <c r="K472" s="5" t="n"/>
       <c r="L472" s="5" t="n"/>
       <c r="M472" s="4" t="n"/>
-      <c r="N472" s="4" t="n"/>
+      <c r="N472" s="4" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="5" t="inlineStr">
@@ -21667,7 +23551,11 @@
           <t>New unit, split from PAL-IS per issue #10.</t>
         </is>
       </c>
-      <c r="N473" s="4" t="n"/>
+      <c r="N473" s="4" t="inlineStr">
+        <is>
+          <t>The Gaza Strip</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="5" t="inlineStr">
@@ -21719,7 +23607,11 @@
           <t>Redefined per issue #10: previously included Gaza Strip and West Bank (WGSRPD ed. 2 limits); now split into PAL-GZ and PAL-WB.</t>
         </is>
       </c>
-      <c r="N474" s="4" t="n"/>
+      <c r="N474" s="4" t="inlineStr">
+        <is>
+          <t>Israel, within its internationally recognized borders</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" s="5" t="inlineStr">
@@ -21763,7 +23655,11 @@
       <c r="K475" s="5" t="n"/>
       <c r="L475" s="5" t="n"/>
       <c r="M475" s="4" t="n"/>
-      <c r="N475" s="4" t="n"/>
+      <c r="N475" s="4" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" s="5" t="inlineStr">
@@ -21815,7 +23711,11 @@
           <t>New unit, split from PAL-IS per issue #10.</t>
         </is>
       </c>
-      <c r="N476" s="4" t="n"/>
+      <c r="N476" s="4" t="inlineStr">
+        <is>
+          <t>The West Bank</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="5" t="inlineStr">
@@ -21859,7 +23759,11 @@
       <c r="K477" s="5" t="n"/>
       <c r="L477" s="5" t="n"/>
       <c r="M477" s="4" t="n"/>
-      <c r="N477" s="4" t="n"/>
+      <c r="N477" s="4" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="5" t="inlineStr">
@@ -21903,7 +23807,11 @@
       <c r="K478" s="5" t="n"/>
       <c r="L478" s="5" t="n"/>
       <c r="M478" s="4" t="n"/>
-      <c r="N478" s="4" t="n"/>
+      <c r="N478" s="4" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="5" t="inlineStr">
@@ -21947,7 +23855,11 @@
       <c r="K479" s="5" t="n"/>
       <c r="L479" s="5" t="n"/>
       <c r="M479" s="4" t="n"/>
-      <c r="N479" s="4" t="n"/>
+      <c r="N479" s="4" t="inlineStr">
+        <is>
+          <t>The Canadian province of Prince Edward Island</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="5" t="inlineStr">
@@ -21991,7 +23903,11 @@
       <c r="K480" s="5" t="n"/>
       <c r="L480" s="5" t="n"/>
       <c r="M480" s="4" t="n"/>
-      <c r="N480" s="4" t="n"/>
+      <c r="N480" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Pennsylvania</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" s="5" t="inlineStr">
@@ -22035,7 +23951,11 @@
       <c r="K481" s="5" t="n"/>
       <c r="L481" s="5" t="n"/>
       <c r="M481" s="4" t="n"/>
-      <c r="N481" s="4" t="n"/>
+      <c r="N481" s="4" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" s="5" t="inlineStr">
@@ -22079,7 +23999,11 @@
       <c r="K482" s="5" t="n"/>
       <c r="L482" s="5" t="n"/>
       <c r="M482" s="4" t="n"/>
-      <c r="N482" s="4" t="n"/>
+      <c r="N482" s="4" t="inlineStr">
+        <is>
+          <t>The Philippines</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" s="5" t="inlineStr">
@@ -22123,7 +24047,11 @@
       <c r="K483" s="5" t="n"/>
       <c r="L483" s="5" t="n"/>
       <c r="M483" s="4" t="n"/>
-      <c r="N483" s="4" t="n"/>
+      <c r="N483" s="4" t="inlineStr">
+        <is>
+          <t>The Phoenix Islands, Kiribati</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="5" t="inlineStr">
@@ -22167,7 +24095,11 @@
       <c r="K484" s="5" t="n"/>
       <c r="L484" s="5" t="n"/>
       <c r="M484" s="4" t="n"/>
-      <c r="N484" s="4" t="n"/>
+      <c r="N484" s="4" t="inlineStr">
+        <is>
+          <t>The Pitcairn Islands</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" s="5" t="inlineStr">
@@ -22211,7 +24143,11 @@
       <c r="K485" s="5" t="n"/>
       <c r="L485" s="5" t="n"/>
       <c r="M485" s="4" t="n"/>
-      <c r="N485" s="4" t="n"/>
+      <c r="N485" s="4" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="5" t="inlineStr">
@@ -22255,7 +24191,11 @@
       <c r="K486" s="5" t="n"/>
       <c r="L486" s="5" t="n"/>
       <c r="M486" s="4" t="n"/>
-      <c r="N486" s="4" t="n"/>
+      <c r="N486" s="4" t="inlineStr">
+        <is>
+          <t>Continental Portugal</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" s="5" t="inlineStr">
@@ -22299,7 +24239,11 @@
       <c r="K487" s="5" t="n"/>
       <c r="L487" s="5" t="n"/>
       <c r="M487" s="4" t="n"/>
-      <c r="N487" s="4" t="n"/>
+      <c r="N487" s="4" t="inlineStr">
+        <is>
+          <t>Primorye, Russian Far East (Primorsky Krai)</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" s="5" t="inlineStr">
@@ -22343,7 +24287,11 @@
       <c r="K488" s="5" t="n"/>
       <c r="L488" s="5" t="n"/>
       <c r="M488" s="4" t="n"/>
-      <c r="N488" s="4" t="n"/>
+      <c r="N488" s="4" t="inlineStr">
+        <is>
+          <t>Puerto Rico</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" s="5" t="inlineStr">
@@ -22387,7 +24335,11 @@
       <c r="K489" s="5" t="n"/>
       <c r="L489" s="5" t="n"/>
       <c r="M489" s="4" t="n"/>
-      <c r="N489" s="4" t="n"/>
+      <c r="N489" s="4" t="inlineStr">
+        <is>
+          <t>The Coral Sea Islands Territory, Australia</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" s="5" t="inlineStr">
@@ -22431,7 +24383,11 @@
       <c r="K490" s="5" t="n"/>
       <c r="L490" s="5" t="n"/>
       <c r="M490" s="4" t="n"/>
-      <c r="N490" s="4" t="n"/>
+      <c r="N490" s="4" t="inlineStr">
+        <is>
+          <t>The Australian state of Queensland</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="5" t="inlineStr">
@@ -22475,7 +24431,11 @@
       <c r="K491" s="5" t="n"/>
       <c r="L491" s="5" t="n"/>
       <c r="M491" s="4" t="n"/>
-      <c r="N491" s="4" t="n"/>
+      <c r="N491" s="4" t="inlineStr">
+        <is>
+          <t>The Canadian province of Quebec</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" s="5" t="inlineStr">
@@ -22523,7 +24483,11 @@
       <c r="K492" s="5" t="n"/>
       <c r="L492" s="5" t="n"/>
       <c r="M492" s="4" t="n"/>
-      <c r="N492" s="4" t="n"/>
+      <c r="N492" s="4" t="inlineStr">
+        <is>
+          <t>Réunion Island</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="5" t="inlineStr">
@@ -22571,7 +24535,11 @@
       <c r="K493" s="5" t="n"/>
       <c r="L493" s="5" t="n"/>
       <c r="M493" s="4" t="n"/>
-      <c r="N493" s="4" t="n"/>
+      <c r="N493" s="4" t="inlineStr">
+        <is>
+          <t>Tromelin Island, Indian Ocean</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="5" t="inlineStr">
@@ -22615,7 +24583,11 @@
       <c r="K494" s="5" t="n"/>
       <c r="L494" s="5" t="n"/>
       <c r="M494" s="4" t="n"/>
-      <c r="N494" s="4" t="n"/>
+      <c r="N494" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Rhode Island</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="5" t="inlineStr">
@@ -22659,7 +24631,11 @@
       <c r="K495" s="5" t="n"/>
       <c r="L495" s="5" t="n"/>
       <c r="M495" s="4" t="n"/>
-      <c r="N495" s="4" t="n"/>
+      <c r="N495" s="4" t="inlineStr">
+        <is>
+          <t>Rodrigues Island, Mauritius</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" s="5" t="inlineStr">
@@ -22703,7 +24679,11 @@
       <c r="K496" s="5" t="n"/>
       <c r="L496" s="5" t="n"/>
       <c r="M496" s="4" t="n"/>
-      <c r="N496" s="4" t="n"/>
+      <c r="N496" s="4" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" s="5" t="inlineStr">
@@ -22747,7 +24727,11 @@
       <c r="K497" s="5" t="n"/>
       <c r="L497" s="5" t="n"/>
       <c r="M497" s="4" t="n"/>
-      <c r="N497" s="4" t="n"/>
+      <c r="N497" s="4" t="inlineStr">
+        <is>
+          <t>Central European Russia</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="5" t="inlineStr">
@@ -22791,7 +24775,11 @@
       <c r="K498" s="5" t="n"/>
       <c r="L498" s="5" t="n"/>
       <c r="M498" s="4" t="n"/>
-      <c r="N498" s="4" t="n"/>
+      <c r="N498" s="4" t="inlineStr">
+        <is>
+          <t>East European Russia</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" s="5" t="inlineStr">
@@ -22835,7 +24823,11 @@
       <c r="K499" s="5" t="n"/>
       <c r="L499" s="5" t="n"/>
       <c r="M499" s="4" t="n"/>
-      <c r="N499" s="4" t="n"/>
+      <c r="N499" s="4" t="inlineStr">
+        <is>
+          <t>North European Russia</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" s="5" t="inlineStr">
@@ -22879,7 +24871,11 @@
       <c r="K500" s="5" t="n"/>
       <c r="L500" s="5" t="n"/>
       <c r="M500" s="4" t="n"/>
-      <c r="N500" s="4" t="n"/>
+      <c r="N500" s="4" t="inlineStr">
+        <is>
+          <t>South European Russia</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" s="5" t="inlineStr">
@@ -22923,7 +24919,11 @@
       <c r="K501" s="5" t="n"/>
       <c r="L501" s="5" t="n"/>
       <c r="M501" s="4" t="n"/>
-      <c r="N501" s="4" t="n"/>
+      <c r="N501" s="4" t="inlineStr">
+        <is>
+          <t>Northwest European Russia</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" s="5" t="inlineStr">
@@ -22967,7 +24967,11 @@
       <c r="K502" s="5" t="n"/>
       <c r="L502" s="5" t="n"/>
       <c r="M502" s="4" t="n"/>
-      <c r="N502" s="4" t="n"/>
+      <c r="N502" s="4" t="inlineStr">
+        <is>
+          <t>Rwanda</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" s="5" t="inlineStr">
@@ -23011,7 +25015,11 @@
       <c r="K503" s="5" t="n"/>
       <c r="L503" s="5" t="n"/>
       <c r="M503" s="4" t="n"/>
-      <c r="N503" s="4" t="n"/>
+      <c r="N503" s="4" t="inlineStr">
+        <is>
+          <t>Sakhalin Island, Russian Far East</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" s="5" t="inlineStr">
@@ -23055,7 +25063,11 @@
       <c r="K504" s="5" t="n"/>
       <c r="L504" s="5" t="n"/>
       <c r="M504" s="4" t="n"/>
-      <c r="N504" s="4" t="n"/>
+      <c r="N504" s="4" t="inlineStr">
+        <is>
+          <t>American Samoa</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" s="5" t="inlineStr">
@@ -23103,7 +25115,11 @@
         </is>
       </c>
       <c r="M505" s="4" t="n"/>
-      <c r="N505" s="4" t="n"/>
+      <c r="N505" s="4" t="inlineStr">
+        <is>
+          <t>Samoa, the independent Pacific island nation</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" s="5" t="inlineStr">
@@ -23147,7 +25163,11 @@
       <c r="K506" s="5" t="n"/>
       <c r="L506" s="5" t="n"/>
       <c r="M506" s="4" t="n"/>
-      <c r="N506" s="4" t="n"/>
+      <c r="N506" s="4" t="inlineStr">
+        <is>
+          <t>Sardinia, Italy</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" s="5" t="inlineStr">
@@ -23191,7 +25211,11 @@
       <c r="K507" s="5" t="n"/>
       <c r="L507" s="5" t="n"/>
       <c r="M507" s="4" t="n"/>
-      <c r="N507" s="4" t="n"/>
+      <c r="N507" s="4" t="inlineStr">
+        <is>
+          <t>The Canadian province of Saskatchewan</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" s="5" t="inlineStr">
@@ -23235,7 +25259,11 @@
       <c r="K508" s="5" t="n"/>
       <c r="L508" s="5" t="n"/>
       <c r="M508" s="4" t="n"/>
-      <c r="N508" s="4" t="n"/>
+      <c r="N508" s="4" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" s="5" t="inlineStr">
@@ -23279,7 +25307,11 @@
       <c r="K509" s="5" t="n"/>
       <c r="L509" s="5" t="n"/>
       <c r="M509" s="4" t="n"/>
-      <c r="N509" s="4" t="n"/>
+      <c r="N509" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of South Carolina</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" s="5" t="inlineStr">
@@ -23323,7 +25355,11 @@
       <c r="K510" s="5" t="n"/>
       <c r="L510" s="5" t="n"/>
       <c r="M510" s="4" t="n"/>
-      <c r="N510" s="4" t="n"/>
+      <c r="N510" s="4" t="inlineStr">
+        <is>
+          <t>The Society Islands, French Polynesia</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" s="5" t="inlineStr">
@@ -23367,7 +25403,11 @@
           <t>political status is disputed</t>
         </is>
       </c>
-      <c r="N511" s="4" t="n"/>
+      <c r="N511" s="4" t="inlineStr">
+        <is>
+          <t>The Paracel Islands, South China Sea</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" s="5" t="inlineStr">
@@ -23415,7 +25455,11 @@
           <t>Typographical error in L4 ISOcode, SI is replaced by PI *</t>
         </is>
       </c>
-      <c r="N512" s="4" t="n"/>
+      <c r="N512" s="4" t="inlineStr">
+        <is>
+          <t>The Spratly Islands, South China Sea</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" s="5" t="inlineStr">
@@ -23459,7 +25503,11 @@
       <c r="K513" s="5" t="n"/>
       <c r="L513" s="5" t="n"/>
       <c r="M513" s="4" t="n"/>
-      <c r="N513" s="4" t="n"/>
+      <c r="N513" s="4" t="inlineStr">
+        <is>
+          <t>The Santa Cruz Islands, Solomon Islands</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" s="5" t="inlineStr">
@@ -23503,7 +25551,11 @@
       <c r="K514" s="5" t="n"/>
       <c r="L514" s="5" t="n"/>
       <c r="M514" s="4" t="n"/>
-      <c r="N514" s="4" t="n"/>
+      <c r="N514" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of South Dakota</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" s="5" t="inlineStr">
@@ -23547,7 +25599,11 @@
       <c r="K515" s="5" t="n"/>
       <c r="L515" s="5" t="n"/>
       <c r="M515" s="4" t="n"/>
-      <c r="N515" s="4" t="n"/>
+      <c r="N515" s="4" t="inlineStr">
+        <is>
+          <t>The Selvagens Islands, Portugal</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" s="5" t="inlineStr">
@@ -23591,7 +25647,11 @@
       <c r="K516" s="5" t="n"/>
       <c r="L516" s="5" t="n"/>
       <c r="M516" s="4" t="n"/>
-      <c r="N516" s="4" t="n"/>
+      <c r="N516" s="4" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" s="5" t="inlineStr">
@@ -23635,7 +25695,11 @@
       <c r="K517" s="5" t="n"/>
       <c r="L517" s="5" t="n"/>
       <c r="M517" s="4" t="n"/>
-      <c r="N517" s="4" t="n"/>
+      <c r="N517" s="4" t="inlineStr">
+        <is>
+          <t>Seychelles</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" s="5" t="inlineStr">
@@ -23679,7 +25743,11 @@
       <c r="K518" s="5" t="n"/>
       <c r="L518" s="5" t="n"/>
       <c r="M518" s="4" t="n"/>
-      <c r="N518" s="4" t="n"/>
+      <c r="N518" s="4" t="inlineStr">
+        <is>
+          <t>South Georgia Island</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" s="5" t="inlineStr">
@@ -23723,7 +25791,11 @@
       <c r="K519" s="5" t="n"/>
       <c r="L519" s="5" t="n"/>
       <c r="M519" s="4" t="n"/>
-      <c r="N519" s="4" t="n"/>
+      <c r="N519" s="4" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" s="5" t="inlineStr">
@@ -23767,7 +25839,11 @@
       <c r="K520" s="5" t="n"/>
       <c r="L520" s="5" t="n"/>
       <c r="M520" s="4" t="n"/>
-      <c r="N520" s="4" t="n"/>
+      <c r="N520" s="4" t="inlineStr">
+        <is>
+          <t>Sicily, Italy</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" s="5" t="inlineStr">
@@ -23811,7 +25887,11 @@
       <c r="K521" s="5" t="n"/>
       <c r="L521" s="5" t="n"/>
       <c r="M521" s="4" t="n"/>
-      <c r="N521" s="4" t="n"/>
+      <c r="N521" s="4" t="inlineStr">
+        <is>
+          <t>Sierra Leone</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" s="5" t="inlineStr">
@@ -23855,7 +25935,11 @@
       <c r="K522" s="5" t="n"/>
       <c r="L522" s="5" t="n"/>
       <c r="M522" s="4" t="n"/>
-      <c r="N522" s="4" t="n"/>
+      <c r="N522" s="4" t="inlineStr">
+        <is>
+          <t>The Sinai Peninsula, Egypt</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" s="5" t="inlineStr">
@@ -23899,7 +25983,11 @@
       <c r="K523" s="5" t="n"/>
       <c r="L523" s="5" t="n"/>
       <c r="M523" s="4" t="n"/>
-      <c r="N523" s="4" t="n"/>
+      <c r="N523" s="4" t="inlineStr">
+        <is>
+          <t>The Australian state of South Australia</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" s="5" t="inlineStr">
@@ -23943,7 +26031,11 @@
       <c r="K524" s="5" t="n"/>
       <c r="L524" s="5" t="n"/>
       <c r="M524" s="4" t="n"/>
-      <c r="N524" s="4" t="n"/>
+      <c r="N524" s="4" t="inlineStr">
+        <is>
+          <t>Socotra Island, Yemen</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" s="5" t="inlineStr">
@@ -23987,7 +26079,11 @@
       <c r="K525" s="5" t="n"/>
       <c r="L525" s="5" t="n"/>
       <c r="M525" s="4" t="n"/>
-      <c r="N525" s="4" t="n"/>
+      <c r="N525" s="4" t="inlineStr">
+        <is>
+          <t>Bougainville (former North Solomons Province), Papua New Guinea</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" s="5" t="inlineStr">
@@ -24031,7 +26127,11 @@
       <c r="K526" s="5" t="n"/>
       <c r="L526" s="5" t="n"/>
       <c r="M526" s="4" t="n"/>
-      <c r="N526" s="4" t="n"/>
+      <c r="N526" s="4" t="inlineStr">
+        <is>
+          <t>The southern Solomon Islands (nation of Solomon Islands)</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" s="5" t="inlineStr">
@@ -24075,7 +26175,11 @@
       <c r="K527" s="5" t="n"/>
       <c r="L527" s="5" t="n"/>
       <c r="M527" s="4" t="n"/>
-      <c r="N527" s="4" t="n"/>
+      <c r="N527" s="4" t="inlineStr">
+        <is>
+          <t>Somalia</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" s="5" t="inlineStr">
@@ -24119,7 +26223,11 @@
       <c r="K528" s="5" t="n"/>
       <c r="L528" s="5" t="n"/>
       <c r="M528" s="4" t="n"/>
-      <c r="N528" s="4" t="n"/>
+      <c r="N528" s="4" t="inlineStr">
+        <is>
+          <t>Andorra</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" s="5" t="inlineStr">
@@ -24163,7 +26271,11 @@
       <c r="K529" s="5" t="n"/>
       <c r="L529" s="5" t="n"/>
       <c r="M529" s="4" t="n"/>
-      <c r="N529" s="4" t="n"/>
+      <c r="N529" s="4" t="inlineStr">
+        <is>
+          <t>Gibraltar</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" s="5" t="inlineStr">
@@ -24207,7 +26319,11 @@
       <c r="K530" s="5" t="n"/>
       <c r="L530" s="5" t="n"/>
       <c r="M530" s="4" t="n"/>
-      <c r="N530" s="4" t="n"/>
+      <c r="N530" s="4" t="inlineStr">
+        <is>
+          <t>Continental Spain</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" s="5" t="inlineStr">
@@ -24251,7 +26367,11 @@
       <c r="K531" s="5" t="n"/>
       <c r="L531" s="5" t="n"/>
       <c r="M531" s="4" t="n"/>
-      <c r="N531" s="4" t="n"/>
+      <c r="N531" s="4" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" s="5" t="inlineStr">
@@ -24299,7 +26419,11 @@
         </is>
       </c>
       <c r="M532" s="4" t="n"/>
-      <c r="N532" s="4" t="n"/>
+      <c r="N532" s="4" t="inlineStr">
+        <is>
+          <t>The South Sandwich Islands</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" s="5" t="inlineStr">
@@ -24343,7 +26467,11 @@
       <c r="K533" s="5" t="n"/>
       <c r="L533" s="5" t="n"/>
       <c r="M533" s="4" t="n"/>
-      <c r="N533" s="4" t="n"/>
+      <c r="N533" s="4" t="inlineStr">
+        <is>
+          <t>Saint Helena Island</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" s="5" t="inlineStr">
@@ -24403,7 +26531,11 @@
           <t>Country area reduced by the creation of a South Sudan, new Level 4 Unit created, old Level 4 unid (SUD-OO) deprecated</t>
         </is>
       </c>
-      <c r="N534" s="4" t="n"/>
+      <c r="N534" s="4" t="inlineStr">
+        <is>
+          <t>Sudan</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" s="5" t="inlineStr">
@@ -24463,7 +26595,11 @@
           <t>New country, new Level 4 Unit</t>
         </is>
       </c>
-      <c r="N535" s="4" t="n"/>
+      <c r="N535" s="4" t="inlineStr">
+        <is>
+          <t>South Sudan</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" s="5" t="inlineStr">
@@ -24507,7 +26643,11 @@
       <c r="K536" s="5" t="n"/>
       <c r="L536" s="5" t="n"/>
       <c r="M536" s="4" t="n"/>
-      <c r="N536" s="4" t="n"/>
+      <c r="N536" s="4" t="inlineStr">
+        <is>
+          <t>Sulawesi, Indonesia</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" s="5" t="inlineStr">
@@ -24551,7 +26691,11 @@
       <c r="K537" s="5" t="n"/>
       <c r="L537" s="5" t="n"/>
       <c r="M537" s="4" t="n"/>
-      <c r="N537" s="4" t="n"/>
+      <c r="N537" s="4" t="inlineStr">
+        <is>
+          <t>Sumatra, Indonesia</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" s="5" t="inlineStr">
@@ -24595,7 +26739,11 @@
       <c r="K538" s="5" t="n"/>
       <c r="L538" s="5" t="n"/>
       <c r="M538" s="4" t="n"/>
-      <c r="N538" s="4" t="n"/>
+      <c r="N538" s="4" t="inlineStr">
+        <is>
+          <t>Suriname</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" s="5" t="inlineStr">
@@ -24639,7 +26787,11 @@
       <c r="K539" s="5" t="n"/>
       <c r="L539" s="5" t="n"/>
       <c r="M539" s="4" t="n"/>
-      <c r="N539" s="4" t="n"/>
+      <c r="N539" s="4" t="inlineStr">
+        <is>
+          <t>Svalbard, Norway</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" s="5" t="inlineStr">
@@ -24683,7 +26835,11 @@
       <c r="K540" s="5" t="n"/>
       <c r="L540" s="5" t="n"/>
       <c r="M540" s="4" t="n"/>
-      <c r="N540" s="4" t="n"/>
+      <c r="N540" s="4" t="inlineStr">
+        <is>
+          <t>Colombian Caribbean islands (San Andrés and Providencia archipelago)</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" s="5" t="inlineStr">
@@ -24727,7 +26883,11 @@
       <c r="K541" s="5" t="n"/>
       <c r="L541" s="5" t="n"/>
       <c r="M541" s="4" t="n"/>
-      <c r="N541" s="4" t="n"/>
+      <c r="N541" s="4" t="inlineStr">
+        <is>
+          <t>Honduran Caribbean islands (Bay Islands)</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" s="5" t="inlineStr">
@@ -24771,7 +26931,11 @@
       <c r="K542" s="5" t="n"/>
       <c r="L542" s="5" t="n"/>
       <c r="M542" s="4" t="n"/>
-      <c r="N542" s="4" t="n"/>
+      <c r="N542" s="4" t="inlineStr">
+        <is>
+          <t>Nicaraguan Caribbean islands (Corn Islands and Miskito Cays)</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" s="5" t="inlineStr">
@@ -24823,7 +26987,11 @@
           <t>https://en.wikipedia.org/wiki/Eswatini</t>
         </is>
       </c>
-      <c r="N543" s="4" t="n"/>
+      <c r="N543" s="4" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" s="5" t="inlineStr">
@@ -24867,7 +27035,11 @@
       <c r="K544" s="5" t="n"/>
       <c r="L544" s="5" t="n"/>
       <c r="M544" s="4" t="n"/>
-      <c r="N544" s="4" t="n"/>
+      <c r="N544" s="4" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" s="5" t="inlineStr">
@@ -24911,7 +27083,11 @@
       <c r="K545" s="5" t="n"/>
       <c r="L545" s="5" t="n"/>
       <c r="M545" s="4" t="n"/>
-      <c r="N545" s="4" t="n"/>
+      <c r="N545" s="4" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" s="5" t="inlineStr">
@@ -24955,7 +27131,11 @@
       <c r="K546" s="5" t="n"/>
       <c r="L546" s="5" t="n"/>
       <c r="M546" s="4" t="n"/>
-      <c r="N546" s="4" t="n"/>
+      <c r="N546" s="4" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" s="5" t="inlineStr">
@@ -25003,7 +27183,11 @@
         </is>
       </c>
       <c r="M547" s="4" t="n"/>
-      <c r="N547" s="4" t="n"/>
+      <c r="N547" s="4" t="inlineStr">
+        <is>
+          <t>The Australian state of Tasmania</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" s="5" t="inlineStr">
@@ -25047,7 +27231,11 @@
       <c r="K548" s="5" t="n"/>
       <c r="L548" s="5" t="n"/>
       <c r="M548" s="4" t="n"/>
-      <c r="N548" s="4" t="n"/>
+      <c r="N548" s="4" t="inlineStr">
+        <is>
+          <t>The Turks and Caicos Islands</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" s="5" t="inlineStr">
@@ -25103,7 +27291,11 @@
           <t>The cartographic limits of the absajia region are discontinuous in google maps and the country to which it corresponds is not labeled. Does this region correspond to Georgia?</t>
         </is>
       </c>
-      <c r="N549" s="4" t="n"/>
+      <c r="N549" s="4" t="inlineStr">
+        <is>
+          <t>Abkhazia</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" s="5" t="inlineStr">
@@ -25147,7 +27339,11 @@
       <c r="K550" s="5" t="n"/>
       <c r="L550" s="5" t="n"/>
       <c r="M550" s="4" t="n"/>
-      <c r="N550" s="4" t="n"/>
+      <c r="N550" s="4" t="inlineStr">
+        <is>
+          <t>Adjara, an autonomous republic of Georgia</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" s="5" t="inlineStr">
@@ -25191,7 +27387,11 @@
       <c r="K551" s="5" t="n"/>
       <c r="L551" s="5" t="n"/>
       <c r="M551" s="4" t="n"/>
-      <c r="N551" s="4" t="n"/>
+      <c r="N551" s="4" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" s="5" t="inlineStr">
@@ -25235,7 +27435,11 @@
       <c r="K552" s="5" t="n"/>
       <c r="L552" s="5" t="n"/>
       <c r="M552" s="4" t="n"/>
-      <c r="N552" s="4" t="n"/>
+      <c r="N552" s="4" t="inlineStr">
+        <is>
+          <t>Azerbaijan</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" s="5" t="inlineStr">
@@ -25283,7 +27487,11 @@
         </is>
       </c>
       <c r="M553" s="4" t="n"/>
-      <c r="N553" s="4" t="n"/>
+      <c r="N553" s="4" t="inlineStr">
+        <is>
+          <t>The country of Georgia</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" s="5" t="inlineStr">
@@ -25327,7 +27535,11 @@
       <c r="K554" s="5" t="n"/>
       <c r="L554" s="5" t="n"/>
       <c r="M554" s="4" t="n"/>
-      <c r="N554" s="4" t="n"/>
+      <c r="N554" s="4" t="inlineStr">
+        <is>
+          <t>Nakhchivan, an exclave autonomous republic of Azerbaijan</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" s="5" t="inlineStr">
@@ -25381,7 +27593,11 @@
 Nagorno-Karabakh, is a region disputed between Armenia and Azerbaijan for decades. The Republic of Artsakh controls the de facto self-governed Nagorno-Karabakh even though it is legally part of Azerbaijan.</t>
         </is>
       </c>
-      <c r="N555" s="4" t="n"/>
+      <c r="N555" s="4" t="inlineStr">
+        <is>
+          <t>Nagorno-Karabakh</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" s="5" t="inlineStr">
@@ -25425,7 +27641,11 @@
       <c r="K556" s="5" t="n"/>
       <c r="L556" s="5" t="n"/>
       <c r="M556" s="4" t="n"/>
-      <c r="N556" s="4" t="n"/>
+      <c r="N556" s="4" t="inlineStr">
+        <is>
+          <t>Tristan da Cunha, a remote island group in the South Atlantic</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" s="5" t="inlineStr">
@@ -25469,7 +27689,11 @@
       <c r="K557" s="5" t="n"/>
       <c r="L557" s="5" t="n"/>
       <c r="M557" s="4" t="n"/>
-      <c r="N557" s="4" t="n"/>
+      <c r="N557" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Tennessee</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" s="5" t="inlineStr">
@@ -25513,7 +27737,11 @@
       <c r="K558" s="5" t="n"/>
       <c r="L558" s="5" t="n"/>
       <c r="M558" s="4" t="n"/>
-      <c r="N558" s="4" t="n"/>
+      <c r="N558" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Texas</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" s="5" t="inlineStr">
@@ -25557,7 +27785,11 @@
       <c r="K559" s="5" t="n"/>
       <c r="L559" s="5" t="n"/>
       <c r="M559" s="4" t="n"/>
-      <c r="N559" s="4" t="n"/>
+      <c r="N559" s="4" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" s="5" t="inlineStr">
@@ -25601,7 +27833,11 @@
       <c r="K560" s="5" t="n"/>
       <c r="L560" s="5" t="n"/>
       <c r="M560" s="4" t="n"/>
-      <c r="N560" s="4" t="n"/>
+      <c r="N560" s="4" t="inlineStr">
+        <is>
+          <t>Turkmenistan</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" s="5" t="inlineStr">
@@ -25645,7 +27881,11 @@
       <c r="K561" s="5" t="n"/>
       <c r="L561" s="5" t="n"/>
       <c r="M561" s="4" t="n"/>
-      <c r="N561" s="4" t="n"/>
+      <c r="N561" s="4" t="inlineStr">
+        <is>
+          <t>Togo</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" s="5" t="inlineStr">
@@ -25689,7 +27929,11 @@
       <c r="K562" s="5" t="n"/>
       <c r="L562" s="5" t="n"/>
       <c r="M562" s="4" t="n"/>
-      <c r="N562" s="4" t="n"/>
+      <c r="N562" s="4" t="inlineStr">
+        <is>
+          <t>Manihiki Atoll, part of the Cook Islands -- grouped with Tokelau as one WGSRPD Level 3 unit ('Tokelau-Manihiki')</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" s="5" t="inlineStr">
@@ -25733,7 +27977,11 @@
       <c r="K563" s="5" t="n"/>
       <c r="L563" s="5" t="n"/>
       <c r="M563" s="4" t="n"/>
-      <c r="N563" s="4" t="n"/>
+      <c r="N563" s="4" t="inlineStr">
+        <is>
+          <t>Swains Island, part of American Samoa</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" s="5" t="inlineStr">
@@ -25777,7 +28025,11 @@
       <c r="K564" s="5" t="n"/>
       <c r="L564" s="5" t="n"/>
       <c r="M564" s="4" t="n"/>
-      <c r="N564" s="4" t="n"/>
+      <c r="N564" s="4" t="inlineStr">
+        <is>
+          <t>Tokelau, a New Zealand territory in the Pacific</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" s="5" t="inlineStr">
@@ -25821,7 +28073,11 @@
       <c r="K565" s="5" t="n"/>
       <c r="L565" s="5" t="n"/>
       <c r="M565" s="4" t="n"/>
-      <c r="N565" s="4" t="n"/>
+      <c r="N565" s="4" t="inlineStr">
+        <is>
+          <t>Tonga</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" s="5" t="inlineStr">
@@ -25865,7 +28121,11 @@
       <c r="K566" s="5" t="n"/>
       <c r="L566" s="5" t="n"/>
       <c r="M566" s="4" t="n"/>
-      <c r="N566" s="4" t="n"/>
+      <c r="N566" s="4" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" s="5" t="inlineStr">
@@ -25909,7 +28169,11 @@
       <c r="K567" s="5" t="n"/>
       <c r="L567" s="5" t="n"/>
       <c r="M567" s="4" t="n"/>
-      <c r="N567" s="4" t="n"/>
+      <c r="N567" s="4" t="inlineStr">
+        <is>
+          <t>The Tuamotu Archipelago, French Polynesia</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" s="5" t="inlineStr">
@@ -25953,7 +28217,11 @@
       <c r="K568" s="5" t="n"/>
       <c r="L568" s="5" t="n"/>
       <c r="M568" s="4" t="n"/>
-      <c r="N568" s="4" t="n"/>
+      <c r="N568" s="4" t="inlineStr">
+        <is>
+          <t>The Tubuai (Austral) Islands, French Polynesia</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" s="5" t="inlineStr">
@@ -26001,7 +28269,11 @@
       <c r="K569" s="5" t="n"/>
       <c r="L569" s="5" t="n"/>
       <c r="M569" s="4" t="n"/>
-      <c r="N569" s="4" t="n"/>
+      <c r="N569" s="4" t="inlineStr">
+        <is>
+          <t>European Turkey (Eastern Thrace)</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" s="5" t="inlineStr">
@@ -26045,7 +28317,11 @@
       <c r="K570" s="5" t="n"/>
       <c r="L570" s="5" t="n"/>
       <c r="M570" s="4" t="n"/>
-      <c r="N570" s="4" t="n"/>
+      <c r="N570" s="4" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" s="5" t="inlineStr">
@@ -26093,7 +28369,11 @@
       <c r="K571" s="5" t="n"/>
       <c r="L571" s="5" t="n"/>
       <c r="M571" s="4" t="n"/>
-      <c r="N571" s="4" t="n"/>
+      <c r="N571" s="4" t="inlineStr">
+        <is>
+          <t>Turkey (Anatolia), the Asian part of the country</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" s="5" t="inlineStr">
@@ -26137,7 +28417,11 @@
       <c r="K572" s="5" t="n"/>
       <c r="L572" s="5" t="n"/>
       <c r="M572" s="4" t="n"/>
-      <c r="N572" s="4" t="n"/>
+      <c r="N572" s="4" t="inlineStr">
+        <is>
+          <t>Tuvalu</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" s="5" t="inlineStr">
@@ -26181,7 +28465,11 @@
       <c r="K573" s="5" t="n"/>
       <c r="L573" s="5" t="n"/>
       <c r="M573" s="4" t="n"/>
-      <c r="N573" s="4" t="n"/>
+      <c r="N573" s="4" t="inlineStr">
+        <is>
+          <t>The Tuva Republic, Russia</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" s="5" t="inlineStr">
@@ -26225,7 +28513,11 @@
       <c r="K574" s="5" t="n"/>
       <c r="L574" s="5" t="n"/>
       <c r="M574" s="4" t="n"/>
-      <c r="N574" s="4" t="n"/>
+      <c r="N574" s="4" t="inlineStr">
+        <is>
+          <t>Tajikistan</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" s="5" t="inlineStr">
@@ -26269,7 +28561,11 @@
       <c r="K575" s="5" t="n"/>
       <c r="L575" s="5" t="n"/>
       <c r="M575" s="4" t="n"/>
-      <c r="N575" s="4" t="n"/>
+      <c r="N575" s="4" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" s="5" t="inlineStr">
@@ -26313,7 +28609,11 @@
       <c r="K576" s="5" t="n"/>
       <c r="L576" s="5" t="n"/>
       <c r="M576" s="4" t="n"/>
-      <c r="N576" s="4" t="n"/>
+      <c r="N576" s="4" t="inlineStr">
+        <is>
+          <t>Moldova</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" s="5" t="inlineStr">
@@ -26357,7 +28657,11 @@
       <c r="K577" s="5" t="n"/>
       <c r="L577" s="5" t="n"/>
       <c r="M577" s="4" t="n"/>
-      <c r="N577" s="4" t="n"/>
+      <c r="N577" s="4" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" s="5" t="inlineStr">
@@ -26401,7 +28705,11 @@
       <c r="K578" s="5" t="n"/>
       <c r="L578" s="5" t="n"/>
       <c r="M578" s="4" t="n"/>
-      <c r="N578" s="4" t="n"/>
+      <c r="N578" s="4" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" s="5" t="inlineStr">
@@ -26445,7 +28753,11 @@
       <c r="K579" s="5" t="n"/>
       <c r="L579" s="5" t="n"/>
       <c r="M579" s="4" t="n"/>
-      <c r="N579" s="4" t="n"/>
+      <c r="N579" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Utah</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" s="5" t="inlineStr">
@@ -26489,7 +28801,11 @@
       <c r="K580" s="5" t="n"/>
       <c r="L580" s="5" t="n"/>
       <c r="M580" s="4" t="n"/>
-      <c r="N580" s="4" t="n"/>
+      <c r="N580" s="4" t="inlineStr">
+        <is>
+          <t>Uzbekistan</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" s="5" t="inlineStr">
@@ -26533,7 +28849,11 @@
       <c r="K581" s="5" t="n"/>
       <c r="L581" s="5" t="n"/>
       <c r="M581" s="4" t="n"/>
-      <c r="N581" s="4" t="n"/>
+      <c r="N581" s="4" t="inlineStr">
+        <is>
+          <t>Vanuatu</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" s="5" t="inlineStr">
@@ -26577,7 +28897,11 @@
       <c r="K582" s="5" t="n"/>
       <c r="L582" s="5" t="n"/>
       <c r="M582" s="4" t="n"/>
-      <c r="N582" s="4" t="n"/>
+      <c r="N582" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" s="5" t="inlineStr">
@@ -26621,7 +28945,11 @@
       <c r="K583" s="5" t="n"/>
       <c r="L583" s="5" t="n"/>
       <c r="M583" s="4" t="n"/>
-      <c r="N583" s="4" t="n"/>
+      <c r="N583" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Vermont</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" s="5" t="inlineStr">
@@ -26665,7 +28993,11 @@
       <c r="K584" s="5" t="n"/>
       <c r="L584" s="5" t="n"/>
       <c r="M584" s="4" t="n"/>
-      <c r="N584" s="4" t="n"/>
+      <c r="N584" s="4" t="inlineStr">
+        <is>
+          <t>The Australian state of Victoria</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" s="5" t="inlineStr">
@@ -26709,7 +29041,11 @@
       <c r="K585" s="5" t="n"/>
       <c r="L585" s="5" t="n"/>
       <c r="M585" s="4" t="n"/>
-      <c r="N585" s="4" t="n"/>
+      <c r="N585" s="4" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" s="5" t="inlineStr">
@@ -26753,7 +29089,11 @@
       <c r="K586" s="5" t="n"/>
       <c r="L586" s="5" t="n"/>
       <c r="M586" s="4" t="n"/>
-      <c r="N586" s="4" t="n"/>
+      <c r="N586" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela's offshore Caribbean islands (e.g. Margarita, Los Roques)</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" s="5" t="inlineStr">
@@ -26797,7 +29137,11 @@
       <c r="K587" s="5" t="n"/>
       <c r="L587" s="5" t="n"/>
       <c r="M587" s="4" t="n"/>
-      <c r="N587" s="4" t="n"/>
+      <c r="N587" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Virginia</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" s="5" t="inlineStr">
@@ -26841,7 +29185,11 @@
       <c r="K588" s="5" t="n"/>
       <c r="L588" s="5" t="n"/>
       <c r="M588" s="4" t="n"/>
-      <c r="N588" s="4" t="n"/>
+      <c r="N588" s="4" t="inlineStr">
+        <is>
+          <t>Wake Island, a U.S. territory in the Pacific</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" s="5" t="inlineStr">
@@ -26885,7 +29233,11 @@
       <c r="K589" s="5" t="n"/>
       <c r="L589" s="5" t="n"/>
       <c r="M589" s="4" t="n"/>
-      <c r="N589" s="4" t="n"/>
+      <c r="N589" s="4" t="inlineStr">
+        <is>
+          <t>Wallis and Futuna, a French territory in the Pacific</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" s="5" t="inlineStr">
@@ -26929,7 +29281,11 @@
       <c r="K590" s="5" t="n"/>
       <c r="L590" s="5" t="n"/>
       <c r="M590" s="4" t="n"/>
-      <c r="N590" s="4" t="n"/>
+      <c r="N590" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Washington</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" s="5" t="inlineStr">
@@ -26973,7 +29329,11 @@
       <c r="K591" s="5" t="n"/>
       <c r="L591" s="5" t="n"/>
       <c r="M591" s="4" t="n"/>
-      <c r="N591" s="4" t="n"/>
+      <c r="N591" s="4" t="inlineStr">
+        <is>
+          <t>Ashmore and Cartier Islands, an Australian external territory</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" s="5" t="inlineStr">
@@ -27017,7 +29377,11 @@
       <c r="K592" s="5" t="n"/>
       <c r="L592" s="5" t="n"/>
       <c r="M592" s="4" t="n"/>
-      <c r="N592" s="4" t="n"/>
+      <c r="N592" s="4" t="inlineStr">
+        <is>
+          <t>The Australian state of Western Australia</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" s="5" t="inlineStr">
@@ -27061,7 +29425,11 @@
       <c r="K593" s="5" t="n"/>
       <c r="L593" s="5" t="n"/>
       <c r="M593" s="4" t="n"/>
-      <c r="N593" s="4" t="n"/>
+      <c r="N593" s="4" t="inlineStr">
+        <is>
+          <t>Washington, D.C., USA</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" s="5" t="inlineStr">
@@ -27105,7 +29473,11 @@
       <c r="K594" s="5" t="n"/>
       <c r="L594" s="5" t="n"/>
       <c r="M594" s="4" t="n"/>
-      <c r="N594" s="4" t="n"/>
+      <c r="N594" s="4" t="inlineStr">
+        <is>
+          <t>The Indian state of Himachal Pradesh</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" s="5" t="inlineStr">
@@ -27149,7 +29521,11 @@
       <c r="K595" s="5" t="n"/>
       <c r="L595" s="5" t="n"/>
       <c r="M595" s="4" t="n"/>
-      <c r="N595" s="4" t="n"/>
+      <c r="N595" s="4" t="inlineStr">
+        <is>
+          <t>Jammu and Kashmir, a union territory of India</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" s="5" t="inlineStr">
@@ -27193,7 +29569,11 @@
       <c r="K596" s="5" t="n"/>
       <c r="L596" s="5" t="n"/>
       <c r="M596" s="4" t="n"/>
-      <c r="N596" s="4" t="n"/>
+      <c r="N596" s="4" t="inlineStr">
+        <is>
+          <t>Uttarakhand (formerly Uttaranchal), an Indian state</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" s="5" t="inlineStr">
@@ -27237,7 +29617,11 @@
       <c r="K597" s="5" t="n"/>
       <c r="L597" s="5" t="n"/>
       <c r="M597" s="4" t="n"/>
-      <c r="N597" s="4" t="n"/>
+      <c r="N597" s="4" t="inlineStr">
+        <is>
+          <t>Barbados</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" s="5" t="inlineStr">
@@ -27281,7 +29665,11 @@
       <c r="K598" s="5" t="n"/>
       <c r="L598" s="5" t="n"/>
       <c r="M598" s="4" t="n"/>
-      <c r="N598" s="4" t="n"/>
+      <c r="N598" s="4" t="inlineStr">
+        <is>
+          <t>Dominica</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" s="5" t="inlineStr">
@@ -27325,7 +29713,11 @@
       <c r="K599" s="5" t="n"/>
       <c r="L599" s="5" t="n"/>
       <c r="M599" s="4" t="n"/>
-      <c r="N599" s="4" t="n"/>
+      <c r="N599" s="4" t="inlineStr">
+        <is>
+          <t>Grenada</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" s="5" t="inlineStr">
@@ -27377,7 +29769,11 @@
           <t>https://en.wikipedia.org/wiki/Saint_Vincent_and_the_Grenadines</t>
         </is>
       </c>
-      <c r="N600" s="4" t="n"/>
+      <c r="N600" s="4" t="inlineStr">
+        <is>
+          <t>Martinique, a French territory in the Caribbean</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" s="5" t="inlineStr">
@@ -27421,7 +29817,11 @@
       <c r="K601" s="5" t="n"/>
       <c r="L601" s="5" t="n"/>
       <c r="M601" s="4" t="n"/>
-      <c r="N601" s="4" t="n"/>
+      <c r="N601" s="4" t="inlineStr">
+        <is>
+          <t>Saint Lucia</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" s="5" t="inlineStr">
@@ -27479,7 +29879,11 @@
 Name for unit "WIN-SV" Changed to "St. Vincent and the Grenadines" in the working documents. The use of "St." for "·Saint" is maintained flowing the rule stated on page 9 of the 2nd Ed. of the standard</t>
         </is>
       </c>
-      <c r="N602" s="4" t="n"/>
+      <c r="N602" s="4" t="inlineStr">
+        <is>
+          <t>Saint Vincent and the Grenadines</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" s="5" t="inlineStr">
@@ -27523,7 +29927,11 @@
       <c r="K603" s="5" t="n"/>
       <c r="L603" s="5" t="n"/>
       <c r="M603" s="4" t="n"/>
-      <c r="N603" s="4" t="n"/>
+      <c r="N603" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Wisconsin</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" s="5" t="inlineStr">
@@ -27567,7 +29975,11 @@
       <c r="K604" s="5" t="n"/>
       <c r="L604" s="5" t="n"/>
       <c r="M604" s="4" t="n"/>
-      <c r="N604" s="4" t="n"/>
+      <c r="N604" s="4" t="inlineStr">
+        <is>
+          <t>Western Sahara</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" s="5" t="inlineStr">
@@ -27611,7 +30023,11 @@
       <c r="K605" s="5" t="n"/>
       <c r="L605" s="5" t="n"/>
       <c r="M605" s="4" t="n"/>
-      <c r="N605" s="4" t="n"/>
+      <c r="N605" s="4" t="inlineStr">
+        <is>
+          <t>West Siberia, Russia</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" s="5" t="inlineStr">
@@ -27655,7 +30071,11 @@
       <c r="K606" s="5" t="n"/>
       <c r="L606" s="5" t="n"/>
       <c r="M606" s="4" t="n"/>
-      <c r="N606" s="4" t="n"/>
+      <c r="N606" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of West Virginia</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" s="5" t="inlineStr">
@@ -27699,7 +30119,11 @@
       <c r="K607" s="5" t="n"/>
       <c r="L607" s="5" t="n"/>
       <c r="M607" s="4" t="n"/>
-      <c r="N607" s="4" t="n"/>
+      <c r="N607" s="4" t="inlineStr">
+        <is>
+          <t>The U.S. state of Wyoming</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" s="5" t="inlineStr">
@@ -27743,7 +30167,11 @@
       <c r="K608" s="5" t="n"/>
       <c r="L608" s="5" t="n"/>
       <c r="M608" s="4" t="n"/>
-      <c r="N608" s="4" t="n"/>
+      <c r="N608" s="4" t="inlineStr">
+        <is>
+          <t>Christmas Island, an Australian territory in the Indian Ocean</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" s="5" t="inlineStr">
@@ -27787,7 +30215,11 @@
       <c r="K609" s="5" t="n"/>
       <c r="L609" s="5" t="n"/>
       <c r="M609" s="4" t="n"/>
-      <c r="N609" s="4" t="n"/>
+      <c r="N609" s="4" t="inlineStr">
+        <is>
+          <t>The Sakha Republic (Yakutia), Russia</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" s="5" t="inlineStr">
@@ -27835,7 +30267,11 @@
         </is>
       </c>
       <c r="M610" s="4" t="n"/>
-      <c r="N610" s="4" t="n"/>
+      <c r="N610" s="4" t="inlineStr">
+        <is>
+          <t>North Yemen, a former state now part of Yemen</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" s="5" t="inlineStr">
@@ -27883,7 +30319,11 @@
         </is>
       </c>
       <c r="M611" s="4" t="n"/>
-      <c r="N611" s="4" t="n"/>
+      <c r="N611" s="4" t="inlineStr">
+        <is>
+          <t>South Yemen, a former state now part of Yemen</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" s="5" t="inlineStr">
@@ -27927,7 +30367,11 @@
       <c r="K612" s="5" t="n"/>
       <c r="L612" s="5" t="n"/>
       <c r="M612" s="4" t="n"/>
-      <c r="N612" s="4" t="n"/>
+      <c r="N612" s="4" t="inlineStr">
+        <is>
+          <t>Yukon, a Canadian territory</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" s="5" t="inlineStr">
@@ -27979,7 +30423,11 @@
         </is>
       </c>
       <c r="M613" s="4" t="n"/>
-      <c r="N613" s="4" t="n"/>
+      <c r="N613" s="4" t="inlineStr">
+        <is>
+          <t>The Democratic Republic of the Congo</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" s="5" t="inlineStr">
@@ -28023,7 +30471,11 @@
       <c r="K614" s="5" t="n"/>
       <c r="L614" s="5" t="n"/>
       <c r="M614" s="4" t="n"/>
-      <c r="N614" s="4" t="n"/>
+      <c r="N614" s="4" t="inlineStr">
+        <is>
+          <t>Zambia</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" s="5" t="inlineStr">
@@ -28067,7 +30519,11 @@
       <c r="K615" s="5" t="n"/>
       <c r="L615" s="5" t="n"/>
       <c r="M615" s="4" t="n"/>
-      <c r="N615" s="4" t="n"/>
+      <c r="N615" s="4" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" s="5" t="inlineStr">
@@ -28119,7 +30575,11 @@
         </is>
       </c>
       <c r="M616" s="4" t="n"/>
-      <c r="N616" s="4" t="n"/>
+      <c r="N616" s="4" t="inlineStr">
+        <is>
+          <t>West Timor, part of Indonesia</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" s="5" t="inlineStr">
@@ -28171,7 +30631,11 @@
         </is>
       </c>
       <c r="M617" s="4" t="n"/>
-      <c r="N617" s="4" t="n"/>
+      <c r="N617" s="4" t="inlineStr">
+        <is>
+          <t>The Indian state of Telangana</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" s="5" t="inlineStr">
@@ -28227,7 +30691,11 @@
           <t>I agree. That implies the creation of a new level 4 unit and the modification of the limits of unit TARAPACÁ 85 CLN-TA [CL]</t>
         </is>
       </c>
-      <c r="N618" s="4" t="n"/>
+      <c r="N618" s="4" t="inlineStr">
+        <is>
+          <t>The Arica y Parinacota Region, Chile</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
